--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,43 +546,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24193889</v>
+        <v>0.24158126</v>
       </c>
       <c r="C2" t="n">
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3144417</v>
+        <v>0.31396002</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3943098</v>
+        <v>0.3940598</v>
       </c>
       <c r="K2" t="n">
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1532965</v>
+        <v>4.141844</v>
       </c>
       <c r="O2" t="n">
         <v>15</v>
@@ -594,13 +594,13 @@
         <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2827641</v>
+        <v>1.2813239</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24932022</v>
+        <v>0.24922183</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,46 +613,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24772163</v>
+        <v>0.24778943</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E3" t="n">
         <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32126948</v>
+        <v>0.32098082</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4059652</v>
+        <v>0.40653917</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.44586</v>
+        <v>5.421344</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
         <v>212</v>
@@ -661,13 +661,13 @@
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5007962</v>
+        <v>1.4972332</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26929358</v>
+        <v>0.26876268</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,64 +680,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24853188</v>
+        <v>0.24796833</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31245255</v>
+        <v>0.31182796</v>
       </c>
       <c r="I4" t="n">
         <v>23</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4123322</v>
+        <v>0.4121692</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5726838</v>
+        <v>3.5785713</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q4" t="n">
         <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2452077</v>
+        <v>1.2484127</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23198631</v>
+        <v>0.23227176</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23473483</v>
+        <v>0.23430611</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
@@ -756,34 +756,34 @@
         <v>640</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>172</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3162521</v>
+        <v>0.3160535</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39509824</v>
+        <v>0.3942893</v>
       </c>
       <c r="K5" t="n">
         <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>1305</v>
+        <v>1315</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1538463</v>
+        <v>4.159822</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
@@ -792,16 +792,16 @@
         <v>152</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3411485</v>
+        <v>1.3426628</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2535589</v>
+        <v>0.25353268</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24926625</v>
+        <v>0.24927175</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="E6" t="n">
         <v>15</v>
@@ -829,28 +829,28 @@
         <v>148</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3226891</v>
+        <v>0.32283172</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4067086</v>
+        <v>0.40574282</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6474934</v>
+        <v>3.6216924</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
@@ -862,13 +862,13 @@
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2387862</v>
+        <v>1.2378831</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24208762</v>
+        <v>0.24161632</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25122648</v>
+        <v>0.2520292</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33892858</v>
+        <v>0.33989012</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43111202</v>
+        <v>0.43161526</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1202</v>
+        <v>1211</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1609344</v>
+        <v>4.1668406</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2578105</v>
+        <v>1.2591242</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24431936</v>
+        <v>0.24399337</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23621382</v>
+        <v>0.23583718</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31830934</v>
+        <v>0.31772575</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40523982</v>
+        <v>0.40537137</v>
       </c>
       <c r="K8" t="n">
         <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1279</v>
+        <v>1291</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.120223</v>
+        <v>4.133597</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q8" t="n">
+        <v>16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3083004</v>
+      </c>
+      <c r="S8" t="n">
         <v>17</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.3097134</v>
-      </c>
-      <c r="S8" t="n">
-        <v>18</v>
-      </c>
       <c r="T8" t="n">
-        <v>0.24015248</v>
+        <v>0.24006727</v>
       </c>
       <c r="U8" t="n">
         <v>14</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22857143</v>
+        <v>0.22946656</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30761942</v>
+        <v>0.3080399</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39616203</v>
+        <v>0.39796782</v>
       </c>
       <c r="K9" t="n">
         <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>1340</v>
+        <v>1352</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.676259</v>
+        <v>4.6571426</v>
       </c>
       <c r="O9" t="n">
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4268585</v>
+        <v>1.4261905</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2524979</v>
+        <v>0.252377</v>
       </c>
       <c r="U9" t="n">
         <v>24</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23658639</v>
+        <v>0.23587482</v>
       </c>
       <c r="C10" t="n">
         <v>23</v>
@@ -1091,7 +1091,7 @@
         <v>577</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>133</v>
@@ -1100,46 +1100,46 @@
         <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31444654</v>
+        <v>0.31367794</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37220109</v>
+        <v>0.37072045</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="M10" t="n">
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7450461</v>
+        <v>3.7610178</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q10" t="n">
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2626157</v>
+        <v>1.2646905</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2371633</v>
+        <v>0.2376279</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2532332</v>
+        <v>0.2537808</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>156</v>
@@ -1167,43 +1167,43 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32351297</v>
+        <v>0.32419923</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41656238</v>
+        <v>0.41620055</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.426115</v>
+        <v>5.43745</v>
       </c>
       <c r="O11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5145084</v>
+        <v>1.5156043</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28638023</v>
+        <v>0.2868061</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,46 +1216,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23849548</v>
+        <v>0.23894912</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31448895</v>
+        <v>0.3146944</v>
       </c>
       <c r="I12" t="n">
         <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39588147</v>
+        <v>0.39678898</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>1213</v>
+        <v>1229</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7181745</v>
+        <v>3.6915739</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>146</v>
@@ -1264,16 +1264,16 @@
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2313851</v>
+        <v>1.2257552</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23356105</v>
+        <v>0.23285927</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24018475</v>
+        <v>0.2401583</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>186</v>
@@ -1301,46 +1301,46 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31515834</v>
+        <v>0.3148596</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4081461</v>
+        <v>0.4076234</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.534515</v>
+        <v>4.5200734</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q13" t="n">
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3567839</v>
+        <v>1.3547624</v>
       </c>
       <c r="S13" t="n">
         <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23766151</v>
+        <v>0.23754467</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1350,43 +1350,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24769102</v>
+        <v>0.24744631</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31578946</v>
+        <v>0.31553307</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40281275</v>
+        <v>0.40233478</v>
       </c>
       <c r="K14" t="n">
         <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.736716</v>
+        <v>4.724284</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
@@ -1398,13 +1398,13 @@
         <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3930573</v>
+        <v>1.3958112</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25776657</v>
+        <v>0.25838017</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23322006</v>
+        <v>0.23388116</v>
       </c>
       <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>577</v>
+      </c>
+      <c r="E15" t="n">
         <v>28</v>
       </c>
-      <c r="D15" t="n">
-        <v>571</v>
-      </c>
-      <c r="E15" t="n">
-        <v>29</v>
-      </c>
       <c r="F15" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G15" t="n">
         <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3077655</v>
+        <v>0.3079539</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3693713</v>
+        <v>0.37020648</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="M15" t="n">
         <v>28</v>
       </c>
       <c r="N15" t="n">
-        <v>4.254414</v>
+        <v>4.231076</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3451043</v>
+        <v>1.3450199</v>
       </c>
       <c r="S15" t="n">
         <v>21</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23584704</v>
+        <v>0.23594314</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25667998</v>
+        <v>0.25647992</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33574745</v>
+        <v>0.33573142</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42036608</v>
+        <v>0.41973245</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6903365</v>
+        <v>3.6997085</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
         <v>158</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1636412</v>
+        <v>1.1656507</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21973288</v>
+        <v>0.22017956</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24724342</v>
+        <v>0.24689278</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32481682</v>
+        <v>0.3251911</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3980068</v>
+        <v>0.39835685</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9705882</v>
+        <v>3.9851341</v>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2561498</v>
+        <v>1.2622777</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23190263</v>
+        <v>0.23288833</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2566335</v>
+        <v>0.25648415</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3391685</v>
+        <v>0.33894622</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3998756</v>
+        <v>0.39954713</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="n">
-        <v>1187</v>
+        <v>1201</v>
       </c>
       <c r="M18" t="n">
         <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4973726</v>
+        <v>3.510705</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>1.172885</v>
+        <v>1.1757181</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22077923</v>
+        <v>0.22172903</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24637681</v>
+        <v>0.24624687</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32002997</v>
+        <v>0.31981397</v>
       </c>
       <c r="I19" t="n">
         <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40810755</v>
+        <v>0.40804836</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.627745</v>
+        <v>4.6232386</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3738619</v>
+        <v>1.3703803</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25146443</v>
+        <v>0.2509869</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23618726</v>
+        <v>0.2356021</v>
       </c>
       <c r="C20" t="n">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E20" t="n">
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G20" t="n">
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30604103</v>
+        <v>0.30560273</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39097428</v>
+        <v>0.39015707</v>
       </c>
       <c r="K20" t="n">
         <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.099814</v>
+        <v>4.1346865</v>
       </c>
       <c r="O20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3052827</v>
+        <v>1.3054824</v>
       </c>
       <c r="S20" t="n">
         <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.239135</v>
+        <v>0.23947479</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23332618</v>
+        <v>0.23360306</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
         <v>193</v>
@@ -1837,43 +1837,43 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31061473</v>
+        <v>0.31136364</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40789193</v>
+        <v>0.40715504</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2331483</v>
+        <v>3.2173228</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1704996</v>
+        <v>1.1692914</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22442456</v>
+        <v>0.22363405</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24217428</v>
+        <v>0.24238606</v>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31251183</v>
+        <v>0.3129111</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39974618</v>
+        <v>0.399916</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L22" t="n">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9978695</v>
+        <v>3.9836066</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2814914</v>
+        <v>1.2778953</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24566896</v>
+        <v>0.2451265</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25250664</v>
+        <v>0.25249034</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G23" t="n">
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3306686</v>
+        <v>0.3306859</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40188256</v>
+        <v>0.40191096</v>
       </c>
       <c r="K23" t="n">
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>1349</v>
+        <v>1358</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1936927</v>
+        <v>4.2064195</v>
       </c>
       <c r="O23" t="n">
         <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3088042</v>
+        <v>1.308977</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23696287</v>
+        <v>0.23758279</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23704022</v>
+        <v>0.23616157</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G24" t="n">
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3141381</v>
+        <v>0.31369942</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38631964</v>
+        <v>0.38512504</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24" t="n">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9148197</v>
+        <v>3.9225874</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2065,16 +2065,16 @@
         <v>156</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2873163</v>
+        <v>1.2908272</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2411953</v>
+        <v>0.24141586</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24792187</v>
+        <v>0.24819475</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30923164</v>
+        <v>0.30933633</v>
       </c>
       <c r="I25" t="n">
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40586033</v>
+        <v>0.40891272</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="M25" t="n">
         <v>8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.402878</v>
+        <v>4.392857</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3645084</v>
+        <v>1.3611112</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24899767</v>
+        <v>0.248114</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22954305</v>
+        <v>0.22925903</v>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
@@ -2169,46 +2169,46 @@
         <v>163</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31078026</v>
+        <v>0.31055784</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37619555</v>
+        <v>0.37513193</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2223406</v>
+        <v>4.227885</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2574468</v>
+        <v>1.2564034</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.251621</v>
+        <v>0.25166112</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,46 +2221,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24200627</v>
+        <v>0.24279495</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G27" t="n">
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31576988</v>
+        <v>0.3161493</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.384535</v>
+        <v>0.38606676</v>
       </c>
       <c r="K27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.250066</v>
+        <v>4.29401</v>
       </c>
       <c r="O27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P27" t="n">
         <v>142</v>
@@ -2269,13 +2269,13 @@
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3503553</v>
+        <v>1.3536489</v>
       </c>
       <c r="S27" t="n">
         <v>22</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25368488</v>
+        <v>0.2542268</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25997046</v>
+        <v>0.26005024</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32834408</v>
+        <v>0.32831892</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4028276</v>
+        <v>0.4036851</v>
       </c>
       <c r="K28" t="n">
         <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8101668</v>
+        <v>3.8014185</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.152502</v>
+        <v>1.1481482</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23153439</v>
+        <v>0.23099539</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2430998</v>
+        <v>0.24246892</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31771624</v>
+        <v>0.31663212</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3985138</v>
+        <v>0.3981462</v>
       </c>
       <c r="K29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>1197</v>
+        <v>1207</v>
       </c>
       <c r="M29" t="n">
         <v>19</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2852545</v>
+        <v>4.286968</v>
       </c>
       <c r="O29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P29" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3109919</v>
+        <v>1.3109043</v>
       </c>
       <c r="S29" t="n">
         <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24947895</v>
+        <v>0.24963805</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24681562</v>
+        <v>0.2475145</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
         <v>134</v>
@@ -2440,46 +2440,46 @@
         <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30865365</v>
+        <v>0.30922413</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38191688</v>
+        <v>0.3819387</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9110818</v>
+        <v>3.904637</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2989446</v>
+        <v>1.2968299</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23710905</v>
+        <v>0.23693599</v>
       </c>
       <c r="U30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24841157</v>
+        <v>0.24862665</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -2507,43 +2507,43 @@
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32450694</v>
+        <v>0.3245105</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42898133</v>
+        <v>0.42889115</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6913385</v>
+        <v>4.7042255</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.388189</v>
+        <v>1.387324</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25492612</v>
+        <v>0.254742</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.19473684</v>
+        <v>0.18238993</v>
       </c>
       <c r="C2" t="n">
         <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>30</v>
@@ -2815,31 +2815,31 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.26794258</v>
+        <v>0.2556818</v>
       </c>
       <c r="I2" t="n">
         <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>0.27894738</v>
+        <v>0.2893082</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1153846</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -2848,16 +2848,16 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2115384</v>
+        <v>1.1111112</v>
       </c>
       <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.22891566</v>
+      </c>
+      <c r="U2" t="n">
         <v>8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.21989529</v>
-      </c>
-      <c r="U2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.29032257</v>
+        <v>0.28514057</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36879432</v>
+        <v>0.3501805</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5180723</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.49596775</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>63</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7540984</v>
+        <v>5.6065574</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4918033</v>
+        <v>1.4426229</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26271185</v>
+        <v>0.26068377</v>
       </c>
       <c r="U3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25365853</v>
+        <v>0.24637681</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.30666667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.42028984</v>
+      </c>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.9056604</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11</v>
+      </c>
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.32300884</v>
-      </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>14</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.3333333</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>1.226415</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.23383084</v>
+      </c>
+      <c r="U4" t="n">
         <v>10</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.1481482</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.22885571</v>
-      </c>
-      <c r="U4" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.20338982</v>
+        <v>0.19827586</v>
       </c>
       <c r="C5" t="n">
         <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.27586207</v>
+        <v>0.27237353</v>
       </c>
       <c r="I5" t="n">
+        <v>29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3275862</v>
+      </c>
+      <c r="K5" t="n">
         <v>28</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.33898306</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>61</v>
+      </c>
+      <c r="M5" t="n">
         <v>25</v>
       </c>
-      <c r="L5" t="n">
-        <v>60</v>
-      </c>
-      <c r="M5" t="n">
-        <v>21</v>
-      </c>
       <c r="N5" t="n">
-        <v>3.3926702</v>
+        <v>3.6753926</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
         <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3350785</v>
+        <v>1.3036649</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2489796</v>
+        <v>0.24291497</v>
       </c>
       <c r="U5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -3068,46 +3068,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24731183</v>
+        <v>0.25609756</v>
       </c>
       <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.31851852</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.44715446</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>59</v>
+      </c>
+      <c r="M6" t="n">
         <v>18</v>
       </c>
-      <c r="D6" t="n">
-        <v>34</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.30819672</v>
-      </c>
-      <c r="I6" t="n">
-        <v>19</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.44802868</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>67</v>
-      </c>
-      <c r="M6" t="n">
-        <v>26</v>
-      </c>
       <c r="N6" t="n">
-        <v>6.8450704</v>
+        <v>6.428571</v>
       </c>
       <c r="O6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P6" t="n">
         <v>13</v>
@@ -3116,16 +3116,16 @@
         <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5352113</v>
+        <v>1.6031746</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3024911</v>
+        <v>0.29795918</v>
       </c>
       <c r="U6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.28915662</v>
+        <v>0.27272728</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.36298934</v>
+        <v>0.35272726</v>
       </c>
       <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5041322</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.57831323</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3333334</v>
+        <v>1.3650794</v>
       </c>
       <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.25619835</v>
+      </c>
+      <c r="U7" t="n">
         <v>17</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.2581967</v>
-      </c>
-      <c r="U7" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.17040358</v>
+        <v>0.18222222</v>
       </c>
       <c r="C8" t="n">
         <v>30</v>
       </c>
       <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
         <v>18</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
+        <v>0.27559054</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.30222222</v>
+      </c>
+      <c r="K8" t="n">
         <v>29</v>
       </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.27734375</v>
-      </c>
-      <c r="I8" t="n">
-        <v>27</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.2735426</v>
-      </c>
-      <c r="K8" t="n">
-        <v>30</v>
-      </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3559322</v>
+        <v>3.9661016</v>
       </c>
       <c r="O8" t="n">
+        <v>13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
+        <v>1.2372881</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.22566372</v>
+      </c>
+      <c r="U8" t="n">
         <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.1864407</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.21621622</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24623115</v>
+        <v>0.27</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.4522613</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
       <c r="L9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
         <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>6.962264</v>
+        <v>4.3333335</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6603774</v>
+        <v>1.4074074</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3080357</v>
+        <v>0.26976743</v>
       </c>
       <c r="U9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -3336,49 +3336,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24568966</v>
+        <v>0.24229075</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31007752</v>
+        <v>0.3083004</v>
       </c>
       <c r="I10" t="n">
         <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.42672414</v>
+        <v>0.40528634</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.078125</v>
+        <v>3.9375</v>
       </c>
       <c r="O10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
         <v>4</v>
@@ -3387,13 +3387,13 @@
         <v>1.359375</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>0.25984251</v>
+        <v>0.2579365</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2606635</v>
+        <v>0.2748815</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31441048</v>
+        <v>0.33043477</v>
       </c>
       <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.43601894</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>53</v>
+      </c>
+      <c r="M11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.6964285</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3392857</v>
+      </c>
+      <c r="S11" t="n">
         <v>16</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.42180094</v>
-      </c>
-      <c r="K11" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" t="n">
-        <v>56</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="T11" t="n">
+        <v>0.2488263</v>
+      </c>
+      <c r="U11" t="n">
         <v>16</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.9454546</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.2727273</v>
-      </c>
-      <c r="S11" t="n">
-        <v>12</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.2254902</v>
-      </c>
-      <c r="U11" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3470,43 +3470,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.22357723</v>
+        <v>0.23715416</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2977941</v>
+        <v>0.29710144</v>
       </c>
       <c r="I12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3478261</v>
+      </c>
+      <c r="K12" t="n">
         <v>25</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.31707317</v>
-      </c>
-      <c r="K12" t="n">
-        <v>27</v>
-      </c>
       <c r="L12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2198954</v>
+        <v>6.078534</v>
       </c>
       <c r="O12" t="n">
         <v>27</v>
@@ -3515,19 +3515,19 @@
         <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4136125</v>
+        <v>1.3507853</v>
       </c>
       <c r="S12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T12" t="n">
-        <v>0.25506073</v>
+        <v>0.24793388</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2117117</v>
+        <v>0.22608696</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>0.28629032</v>
+        <v>0.2952756</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J13" t="n">
-        <v>0.37387386</v>
+        <v>0.37826088</v>
       </c>
       <c r="K13" t="n">
         <v>21</v>
       </c>
       <c r="L13" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7580645</v>
+        <v>2.25</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2419355</v>
+        <v>1.171875</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1891892</v>
+        <v>0.17410715</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3604,37 +3604,37 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24878049</v>
+        <v>0.23115578</v>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>0.30493274</v>
+        <v>0.29357797</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>0.44390243</v>
+        <v>0.41708544</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -3643,25 +3643,25 @@
         <v>6.792453</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="n">
         <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3773584</v>
+        <v>1.5471698</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2761905</v>
+        <v>0.30414745</v>
       </c>
       <c r="U14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -3671,61 +3671,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2039801</v>
+        <v>0.23786408</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.26940638</v>
+        <v>0.2927928</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>0.29353234</v>
+        <v>0.3398058</v>
       </c>
       <c r="K15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>3.3333333</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3272728</v>
+        <v>1.3148148</v>
       </c>
       <c r="S15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T15" t="n">
-        <v>0.26213592</v>
+        <v>0.2682927</v>
       </c>
       <c r="U15" t="n">
         <v>23</v>
@@ -3738,46 +3738,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.22772278</v>
+        <v>0.23383084</v>
       </c>
       <c r="C16" t="n">
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.37313432</v>
+      </c>
+      <c r="K16" t="n">
+        <v>22</v>
+      </c>
+      <c r="L16" t="n">
+        <v>53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.909091</v>
+      </c>
+      <c r="O16" t="n">
         <v>18</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>25</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.33613446</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.36138615</v>
-      </c>
-      <c r="K16" t="n">
-        <v>23</v>
-      </c>
-      <c r="L16" t="n">
-        <v>46</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.4723926</v>
-      </c>
-      <c r="O16" t="n">
-        <v>17</v>
       </c>
       <c r="P16" t="n">
         <v>7</v>
@@ -3786,16 +3786,16 @@
         <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2331289</v>
+        <v>1.2545455</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T16" t="n">
-        <v>0.25365853</v>
+        <v>0.26540285</v>
       </c>
       <c r="U16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2212766</v>
+        <v>0.22510822</v>
       </c>
       <c r="C17" t="n">
         <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.31178707</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.41125542</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16</v>
+      </c>
+      <c r="L17" t="n">
+        <v>59</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.3114753</v>
+      </c>
+      <c r="O17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P17" t="n">
         <v>9</v>
       </c>
-      <c r="G17" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.29924244</v>
-      </c>
-      <c r="I17" t="n">
-        <v>24</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.38723403</v>
-      </c>
-      <c r="K17" t="n">
-        <v>18</v>
-      </c>
-      <c r="L17" t="n">
-        <v>69</v>
-      </c>
-      <c r="M17" t="n">
-        <v>29</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.962162</v>
-      </c>
-      <c r="O17" t="n">
-        <v>19</v>
-      </c>
-      <c r="P17" t="n">
-        <v>8</v>
-      </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R17" t="n">
-        <v>1.427027</v>
+        <v>1.5573771</v>
       </c>
       <c r="S17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T17" t="n">
-        <v>0.26068377</v>
+        <v>0.27896994</v>
       </c>
       <c r="U17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.27235773</v>
+        <v>0.272</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3501805</v>
+        <v>0.35106382</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44308943</v>
+        <v>0.428</v>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N18" t="n">
-        <v>6.196721</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
         <v>30</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4426229</v>
+        <v>1.5166667</v>
       </c>
       <c r="S18" t="n">
         <v>24</v>
       </c>
       <c r="T18" t="n">
-        <v>0.25416666</v>
+        <v>0.26970956</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25238097</v>
+        <v>0.26168224</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>0.338843</v>
+        <v>0.3495935</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.44761905</v>
+        <v>0.47196263</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0535715</v>
+        <v>3.375</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0535715</v>
+        <v>1.0357143</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>0.20192307</v>
+        <v>0.21428572</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2524272</v>
+        <v>0.22439024</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" t="n">
         <v>11</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
       </c>
       <c r="G20" t="n">
         <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.31858408</v>
+        <v>0.29955947</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>0.46116504</v>
+        <v>0.4292683</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.075472</v>
+        <v>5.4339623</v>
       </c>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3207548</v>
+        <v>1.4150944</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2631579</v>
+        <v>0.28504673</v>
       </c>
       <c r="U20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.29387754</v>
+        <v>0.3018868</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>0.33082706</v>
+        <v>0.36134455</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41632652</v>
+        <v>0.44339624</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5526316</v>
+        <v>2.981595</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0421053</v>
+        <v>1.01227</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22362868</v>
+        <v>0.20707071</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22613065</v>
+        <v>0.2361809</v>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
         <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30222222</v>
+        <v>0.30493274</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>0.33668342</v>
+        <v>0.36683416</v>
       </c>
       <c r="K22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L22" t="n">
         <v>42</v>
@@ -4176,25 +4176,25 @@
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8333334</v>
+        <v>2.037736</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9814815</v>
+        <v>1.018868</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0.19387755</v>
+        <v>0.20103092</v>
       </c>
       <c r="U22" t="n">
         <v>3</v>
@@ -4207,46 +4207,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2705314</v>
+        <v>0.26237625</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H23" t="n">
-        <v>0.36666667</v>
+        <v>0.3617021</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.38647342</v>
+        <v>0.37128714</v>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L23" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7636364</v>
+        <v>4.581818</v>
       </c>
       <c r="O23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -4255,16 +4255,16 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1818181</v>
+        <v>1.3090909</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>0.20707071</v>
+        <v>0.24630542</v>
       </c>
       <c r="U23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24401914</v>
+        <v>0.21782178</v>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>0.30603448</v>
+        <v>0.2907489</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37320575</v>
+        <v>0.34653464</v>
       </c>
       <c r="K24" t="n">
+        <v>26</v>
+      </c>
+      <c r="L24" t="n">
+        <v>60</v>
+      </c>
+      <c r="M24" t="n">
         <v>22</v>
       </c>
-      <c r="L24" t="n">
-        <v>56</v>
-      </c>
-      <c r="M24" t="n">
-        <v>16</v>
-      </c>
       <c r="N24" t="n">
-        <v>3.375</v>
+        <v>3.4785275</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q24" t="n">
         <v>8</v>
       </c>
-      <c r="Q24" t="n">
-        <v>17</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.2375001</v>
+        <v>1.2515337</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23469388</v>
+        <v>0.22564103</v>
       </c>
       <c r="U24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25630254</v>
+        <v>0.2761905</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>0.35842294</v>
+        <v>0.36363637</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.38235295</v>
+        <v>0.50476193</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M25" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N25" t="n">
-        <v>5.4</v>
+        <v>5.468354</v>
       </c>
       <c r="O25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
         <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.508108</v>
+        <v>1.5189873</v>
       </c>
       <c r="S25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>0.27160493</v>
+        <v>0.2631579</v>
       </c>
       <c r="U25" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -4411,61 +4411,61 @@
         <v>0.25714287</v>
       </c>
       <c r="C26" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" t="n">
+        <v>37</v>
+      </c>
+      <c r="E26" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
-        <v>38</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7</v>
-      </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>0.34875444</v>
+        <v>0.35106382</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.40816328</v>
+        <v>0.4</v>
       </c>
       <c r="K26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
+        <v>28</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6.0641713</v>
+      </c>
+      <c r="O26" t="n">
+        <v>26</v>
+      </c>
+      <c r="P26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q26" t="n">
         <v>29</v>
       </c>
-      <c r="N26" t="n">
-        <v>6.0163045</v>
-      </c>
-      <c r="O26" t="n">
-        <v>25</v>
-      </c>
-      <c r="P26" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
+        <v>1.5721925</v>
+      </c>
+      <c r="S26" t="n">
         <v>28</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.6304349</v>
-      </c>
-      <c r="S26" t="n">
-        <v>29</v>
-      </c>
       <c r="T26" t="n">
-        <v>0.30241936</v>
+        <v>0.31102362</v>
       </c>
       <c r="U26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -4475,61 +4475,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.25700936</v>
+        <v>0.29680365</v>
       </c>
       <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>41</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="n">
-        <v>36</v>
-      </c>
-      <c r="E27" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" t="n">
-        <v>9</v>
-      </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>0.30801687</v>
+        <v>0.338843</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.42523363</v>
+        <v>0.48401827</v>
       </c>
       <c r="K27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N27" t="n">
-        <v>4.969325</v>
+        <v>5.7375</v>
       </c>
       <c r="O27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q27" t="n">
         <v>8</v>
       </c>
-      <c r="Q27" t="n">
-        <v>17</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.601227</v>
+        <v>1.63125</v>
       </c>
       <c r="S27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25821596</v>
+        <v>0.2631579</v>
       </c>
       <c r="U27" t="n">
         <v>20</v>
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25619835</v>
+        <v>0.2489796</v>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3071161</v>
+      </c>
+      <c r="I28" t="n">
+        <v>19</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.39591837</v>
+      </c>
+      <c r="K28" t="n">
+        <v>19</v>
+      </c>
+      <c r="L28" t="n">
+        <v>49</v>
+      </c>
+      <c r="M28" t="n">
         <v>8</v>
       </c>
-      <c r="G28" t="n">
-        <v>12</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.31439394</v>
-      </c>
-      <c r="I28" t="n">
-        <v>17</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.3966942</v>
-      </c>
-      <c r="K28" t="n">
-        <v>16</v>
-      </c>
-      <c r="L28" t="n">
-        <v>47</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>4.0153847</v>
+      </c>
+      <c r="O28" t="n">
+        <v>14</v>
+      </c>
+      <c r="P28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>19</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.1538461</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.23012552</v>
+      </c>
+      <c r="U28" t="n">
         <v>9</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>18</v>
-      </c>
-      <c r="P28" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>14</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.296875</v>
-      </c>
-      <c r="S28" t="n">
-        <v>14</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.24686192</v>
-      </c>
-      <c r="U28" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.27510917</v>
+        <v>0.26180258</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
         <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34732825</v>
+        <v>0.3244275</v>
       </c>
       <c r="I29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4549356</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>49</v>
+      </c>
+      <c r="M29" t="n">
         <v>8</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.46724892</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6</v>
-      </c>
       <c r="N29" t="n">
-        <v>4.209677</v>
+        <v>4.21875</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3387097</v>
+        <v>1.34375</v>
       </c>
       <c r="S29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24152543</v>
+        <v>0.24691358</v>
       </c>
       <c r="U29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -4676,52 +4676,52 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2669903</v>
+        <v>0.29166666</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3559322</v>
+        <v>0.36363637</v>
       </c>
       <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.41666666</v>
+      </c>
+      <c r="K30" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>44</v>
+      </c>
+      <c r="M30" t="n">
         <v>5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.39320388</v>
-      </c>
-      <c r="K30" t="n">
-        <v>17</v>
-      </c>
-      <c r="L30" t="n">
-        <v>46</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6</v>
       </c>
       <c r="N30" t="n">
         <v>2.3773584</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
         <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
         <v>0.9433962</v>
@@ -4730,10 +4730,10 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.18518518</v>
+        <v>0.18947369</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4743,46 +4743,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2512563</v>
+        <v>0.25757575</v>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
         <v>25</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32286996</v>
+        <v>0.32735425</v>
       </c>
       <c r="I31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" t="n">
-        <v>0.35678393</v>
+        <v>0.37878788</v>
       </c>
       <c r="K31" t="n">
+        <v>20</v>
+      </c>
+      <c r="L31" t="n">
+        <v>57</v>
+      </c>
+      <c r="M31" t="n">
+        <v>17</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.7115383</v>
+      </c>
+      <c r="O31" t="n">
         <v>24</v>
-      </c>
-      <c r="L31" t="n">
-        <v>51</v>
-      </c>
-      <c r="M31" t="n">
-        <v>12</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5.1666665</v>
-      </c>
-      <c r="O31" t="n">
-        <v>22</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
@@ -4791,16 +4791,16 @@
         <v>14</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2962962</v>
+        <v>1.3269231</v>
       </c>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T31" t="n">
-        <v>0.225</v>
+        <v>0.23469388</v>
       </c>
       <c r="U31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24158126</v>
+        <v>0.24179476</v>
       </c>
       <c r="C2" t="n">
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31396002</v>
+        <v>0.31390384</v>
       </c>
       <c r="I2" t="n">
         <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3940598</v>
+        <v>0.39426672</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.141844</v>
+        <v>4.1267605</v>
       </c>
       <c r="O2" t="n">
         <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q2" t="n">
         <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2813239</v>
+        <v>1.2793428</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24922183</v>
+        <v>0.24891819</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24778943</v>
+        <v>0.24657534</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>631</v>
@@ -628,28 +628,28 @@
         <v>174</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32098082</v>
+        <v>0.3197653</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40653917</v>
+        <v>0.40441626</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.421344</v>
+        <v>5.401414</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4972332</v>
+        <v>1.4941084</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26876268</v>
+        <v>0.26849425</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24796833</v>
+        <v>0.24824162</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31182796</v>
+        <v>0.31172723</v>
       </c>
       <c r="I4" t="n">
         <v>23</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4121692</v>
+        <v>0.41311544</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5785713</v>
+        <v>3.567376</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q4" t="n">
         <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2484127</v>
+        <v>1.2458628</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23227176</v>
+        <v>0.23208264</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23430611</v>
+        <v>0.23383395</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>172</v>
@@ -765,43 +765,43 @@
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3160535</v>
+        <v>0.3151672</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3942893</v>
+        <v>0.39340842</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1315</v>
+        <v>1332</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.159822</v>
+        <v>4.1306496</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3426628</v>
+        <v>1.3402597</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25353268</v>
+        <v>0.25269583</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24927175</v>
+        <v>0.24844977</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32283172</v>
+        <v>0.32241443</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40574282</v>
+        <v>0.40471268</v>
       </c>
       <c r="K6" t="n">
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6216924</v>
+        <v>3.603278</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
@@ -859,19 +859,19 @@
         <v>141</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2378831</v>
+        <v>1.2330905</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24161632</v>
+        <v>0.241101</v>
       </c>
       <c r="U6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2520292</v>
+        <v>0.2518653</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33989012</v>
+        <v>0.3395562</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43161526</v>
+        <v>0.43133697</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1668406</v>
+        <v>4.2108808</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2591242</v>
+        <v>1.2645078</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24399337</v>
+        <v>0.24454957</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23583718</v>
+        <v>0.23651884</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31772575</v>
+        <v>0.31915286</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40537137</v>
+        <v>0.40703726</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1291</v>
+        <v>1303</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.133597</v>
+        <v>4.1114597</v>
       </c>
       <c r="O8" t="n">
         <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3083004</v>
+        <v>1.3029827</v>
       </c>
       <c r="S8" t="n">
         <v>17</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24006727</v>
+        <v>0.23939838</v>
       </c>
       <c r="U8" t="n">
         <v>14</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22946656</v>
+        <v>0.23057538</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3080399</v>
+        <v>0.3097015</v>
       </c>
       <c r="I9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39796782</v>
+        <v>0.39899203</v>
       </c>
       <c r="K9" t="n">
         <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6571426</v>
+        <v>4.680851</v>
       </c>
       <c r="O9" t="n">
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4261905</v>
+        <v>1.429472</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.252377</v>
+        <v>0.25210428</v>
       </c>
       <c r="U9" t="n">
         <v>24</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23587482</v>
+        <v>0.23576048</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G10" t="n">
         <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31367794</v>
+        <v>0.31349647</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37072045</v>
+        <v>0.37095764</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7610178</v>
+        <v>3.7457054</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
@@ -1127,19 +1127,19 @@
         <v>159</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2646905</v>
+        <v>1.261062</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2376279</v>
+        <v>0.23688032</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2537808</v>
+        <v>0.25390625</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32419923</v>
+        <v>0.3239566</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41620055</v>
+        <v>0.4165296</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1230</v>
+        <v>1246</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
-        <v>5.43745</v>
+        <v>5.470074</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5156043</v>
+        <v>1.5190679</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2868061</v>
+        <v>0.28750998</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23894912</v>
+        <v>0.23819387</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>160</v>
@@ -1234,43 +1234,43 @@
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3146944</v>
+        <v>0.3140801</v>
       </c>
       <c r="I12" t="n">
         <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39678898</v>
+        <v>0.39540184</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6915739</v>
+        <v>3.679558</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2257552</v>
+        <v>1.2241515</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23285927</v>
+        <v>0.23276408</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
@@ -1283,64 +1283,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2401583</v>
+        <v>0.23991726</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3148596</v>
+        <v>0.31468144</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4076234</v>
+        <v>0.40703207</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5200734</v>
+        <v>4.50938</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q13" t="n">
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3547624</v>
+        <v>1.3522668</v>
       </c>
       <c r="S13" t="n">
         <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23754467</v>
+        <v>0.23778705</v>
       </c>
       <c r="U13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24744631</v>
+        <v>0.24730738</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31553307</v>
+        <v>0.31616142</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40233478</v>
+        <v>0.4026512</v>
       </c>
       <c r="K14" t="n">
         <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.724284</v>
+        <v>4.6978154</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q14" t="n">
         <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3958112</v>
+        <v>1.3929981</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25838017</v>
+        <v>0.2583247</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23388116</v>
+        <v>0.23341009</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
         <v>577</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>136</v>
@@ -1435,43 +1435,43 @@
         <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3079539</v>
+        <v>0.3076201</v>
       </c>
       <c r="I15" t="n">
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37020648</v>
+        <v>0.36906007</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="M15" t="n">
         <v>28</v>
       </c>
       <c r="N15" t="n">
-        <v>4.231076</v>
+        <v>4.2114015</v>
       </c>
       <c r="O15" t="n">
         <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q15" t="n">
         <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3450199</v>
+        <v>1.3396674</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23594314</v>
+        <v>0.2352817</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25647992</v>
+        <v>0.25674555</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33573142</v>
+        <v>0.33608058</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.41973245</v>
+        <v>0.41988376</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6997085</v>
+        <v>3.7089474</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q16" t="n">
         <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1656507</v>
+        <v>1.1692106</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22017956</v>
+        <v>0.22054766</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24689278</v>
+        <v>0.24743778</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3251911</v>
+        <v>0.32605478</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39835685</v>
+        <v>0.39907968</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9851341</v>
+        <v>3.9781234</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2622777</v>
+        <v>1.261202</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23288833</v>
+        <v>0.2328421</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25648415</v>
+        <v>0.25618482</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33894622</v>
+        <v>0.33938196</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39954713</v>
+        <v>0.3995093</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="M18" t="n">
         <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>3.510705</v>
+        <v>3.5448885</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q18" t="n">
         <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1757181</v>
+        <v>1.1870784</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22172903</v>
+        <v>0.22289789</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24624687</v>
+        <v>0.24554497</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3189049</v>
+      </c>
+      <c r="I19" t="n">
         <v>12</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.31981397</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.40804836</v>
+        <v>0.40696228</v>
       </c>
       <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1139</v>
+      </c>
+      <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="L19" t="n">
-        <v>1124</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6</v>
-      </c>
       <c r="N19" t="n">
-        <v>4.6232386</v>
+        <v>4.6652575</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3703803</v>
+        <v>1.3791282</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2509869</v>
+        <v>0.25154638</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -1752,43 +1752,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2356021</v>
+        <v>0.23568603</v>
       </c>
       <c r="C20" t="n">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E20" t="n">
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G20" t="n">
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30560273</v>
+        <v>0.3055712</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39015707</v>
+        <v>0.3907974</v>
       </c>
       <c r="K20" t="n">
         <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1346865</v>
+        <v>4.119602</v>
       </c>
       <c r="O20" t="n">
         <v>14</v>
@@ -1800,13 +1800,13 @@
         <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3054824</v>
+        <v>1.3001833</v>
       </c>
       <c r="S20" t="n">
         <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23947479</v>
+        <v>0.23887394</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23360306</v>
+        <v>0.23350254</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
         <v>193</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31136364</v>
+        <v>0.31145382</v>
       </c>
       <c r="I21" t="n">
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40715504</v>
+        <v>0.40630287</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2173228</v>
+        <v>3.225352</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.1674491</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.1692914</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
       <c r="T21" t="n">
-        <v>0.22363405</v>
+        <v>0.22353189</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24238606</v>
+        <v>0.24212721</v>
       </c>
       <c r="C22" t="n">
         <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3129111</v>
+        <v>0.31230167</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.399916</v>
+        <v>0.40020856</v>
       </c>
       <c r="K22" t="n">
         <v>16</v>
       </c>
       <c r="L22" t="n">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9836066</v>
+        <v>3.9908113</v>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2778953</v>
+        <v>1.2775007</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2451265</v>
+        <v>0.24541898</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25249034</v>
+        <v>0.25176945</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G23" t="n">
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3306859</v>
+        <v>0.3298006</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40191096</v>
+        <v>0.4010111</v>
       </c>
       <c r="K23" t="n">
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2064195</v>
+        <v>4.176989</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
         <v>139</v>
@@ -2001,13 +2001,13 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.308977</v>
+        <v>1.3060378</v>
       </c>
       <c r="S23" t="n">
         <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23758279</v>
+        <v>0.23709644</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23616157</v>
+        <v>0.23598132</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31369942</v>
+        <v>0.3132439</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38512504</v>
+        <v>0.38657603</v>
       </c>
       <c r="K24" t="n">
         <v>26</v>
       </c>
       <c r="L24" t="n">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9225874</v>
+        <v>3.9089234</v>
       </c>
       <c r="O24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P24" t="n">
         <v>156</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2908272</v>
+        <v>1.2911292</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24141586</v>
+        <v>0.24126315</v>
       </c>
       <c r="U24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24819475</v>
+        <v>0.24754098</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>164</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30933633</v>
+        <v>0.30836594</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40891272</v>
+        <v>0.40717214</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="M25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.392857</v>
+        <v>4.393533</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3611112</v>
+        <v>1.3596214</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.248114</v>
+        <v>0.248125</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22925903</v>
+        <v>0.22923657</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
@@ -2169,31 +2169,31 @@
         <v>163</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31055784</v>
+        <v>0.31019723</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37513193</v>
+        <v>0.37416106</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.227885</v>
+        <v>4.197955</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
         <v>174</v>
@@ -2202,16 +2202,16 @@
         <v>21</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2564034</v>
+        <v>1.2498689</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25166112</v>
+        <v>0.25041288</v>
       </c>
       <c r="U26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24279495</v>
+        <v>0.24388237</v>
       </c>
       <c r="C27" t="n">
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G27" t="n">
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3161493</v>
+        <v>0.3169569</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38606676</v>
+        <v>0.38720953</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.29401</v>
+        <v>4.32</v>
       </c>
       <c r="O27" t="n">
         <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3536489</v>
+        <v>1.351948</v>
       </c>
       <c r="S27" t="n">
         <v>22</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2542268</v>
+        <v>0.25434828</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26005024</v>
+        <v>0.2601829</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
         <v>149</v>
       </c>
       <c r="G28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32831892</v>
+        <v>0.3283582</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4036851</v>
+        <v>0.40295094</v>
       </c>
       <c r="K28" t="n">
         <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8014185</v>
+        <v>3.8198903</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q28" t="n">
         <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1481482</v>
+        <v>1.1542678</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23099539</v>
+        <v>0.23171493</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24246892</v>
+        <v>0.24310201</v>
       </c>
       <c r="C29" t="n">
         <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31663212</v>
+        <v>0.31732386</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3981462</v>
+        <v>0.39987457</v>
       </c>
       <c r="K29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L29" t="n">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="M29" t="n">
         <v>19</v>
       </c>
       <c r="N29" t="n">
-        <v>4.286968</v>
+        <v>4.2991815</v>
       </c>
       <c r="O29" t="n">
         <v>21</v>
@@ -2403,13 +2403,13 @@
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3109043</v>
+        <v>1.3126485</v>
       </c>
       <c r="S29" t="n">
         <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24963805</v>
+        <v>0.24984603</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2475145</v>
+        <v>0.24753086</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E30" t="n">
         <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G30" t="n">
         <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30922413</v>
+        <v>0.30912825</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3819387</v>
+        <v>0.38168725</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.904637</v>
+        <v>3.922416</v>
       </c>
       <c r="O30" t="n">
+        <v>10</v>
+      </c>
+      <c r="P30" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q30" t="n">
         <v>9</v>
       </c>
-      <c r="P30" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.2968299</v>
+        <v>1.2996615</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23693599</v>
+        <v>0.23686406</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24862665</v>
+        <v>0.24878739</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3245105</v>
+        <v>0.325054</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42889115</v>
+        <v>0.42906225</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1202</v>
+        <v>1213</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7042255</v>
+        <v>4.7239504</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P31" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.387324</v>
+        <v>1.3903577</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.254742</v>
+        <v>0.25501317</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.18238993</v>
+        <v>0.19791667</v>
       </c>
       <c r="C2" t="n">
         <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>30</v>
       </c>
       <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.26415095</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L2" t="n">
+        <v>54</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.8333333</v>
+      </c>
+      <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="G2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.2556818</v>
-      </c>
-      <c r="I2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.2893082</v>
-      </c>
-      <c r="K2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L2" t="n">
-        <v>46</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1111112</v>
+        <v>1.0925926</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.22891566</v>
+        <v>0.225</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.28514057</v>
+        <v>0.2603306</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3501805</v>
+        <v>0.32713756</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5180723</v>
+        <v>0.4752066</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M3" t="n">
         <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6065574</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4426229</v>
+        <v>1.4666667</v>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26068377</v>
+        <v>0.26406926</v>
       </c>
       <c r="U3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2937,13 +2937,13 @@
         <v>0.24637681</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
         <v>9</v>
@@ -2952,43 +2952,43 @@
         <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.30666667</v>
+        <v>0.29596412</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J4" t="n">
-        <v>0.42028984</v>
+        <v>0.43961352</v>
       </c>
       <c r="K4" t="n">
         <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9056604</v>
+        <v>3.9807692</v>
       </c>
       <c r="O4" t="n">
         <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
         <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.226415</v>
+        <v>1.2692307</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23383084</v>
+        <v>0.235</v>
       </c>
       <c r="U4" t="n">
         <v>10</v>
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.19827586</v>
+        <v>0.19213974</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
         <v>25</v>
       </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.27237353</v>
+        <v>0.26190478</v>
       </c>
       <c r="I5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3275862</v>
+        <v>0.28820962</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M5" t="n">
         <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6753926</v>
+        <v>2.9685864</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3036649</v>
+        <v>1.2565445</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>0.24291497</v>
+        <v>0.22540984</v>
       </c>
       <c r="U5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25609756</v>
+        <v>0.24291497</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>14</v>
       </c>
       <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3188406</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.44129553</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>63</v>
+      </c>
+      <c r="M6" t="n">
+        <v>23</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.21875</v>
+      </c>
+      <c r="O6" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.265625</v>
+      </c>
+      <c r="S6" t="n">
         <v>10</v>
       </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.31851852</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.44715446</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>59</v>
-      </c>
-      <c r="M6" t="n">
-        <v>18</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6.428571</v>
-      </c>
-      <c r="O6" t="n">
-        <v>28</v>
-      </c>
-      <c r="P6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.6031746</v>
-      </c>
-      <c r="S6" t="n">
-        <v>29</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.29795918</v>
+        <v>0.25104603</v>
       </c>
       <c r="U6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27272728</v>
+        <v>0.27004218</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.35272726</v>
+        <v>0.35661766</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5041322</v>
+        <v>0.4978903</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.516129</v>
       </c>
       <c r="O7" t="n">
+        <v>26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.451613</v>
+      </c>
+      <c r="S7" t="n">
+        <v>23</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.26050422</v>
+      </c>
+      <c r="U7" t="n">
         <v>19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>24</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3650794</v>
-      </c>
-      <c r="S7" t="n">
-        <v>20</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.25619835</v>
-      </c>
-      <c r="U7" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.18222222</v>
+        <v>0.20524018</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" t="n">
         <v>19</v>
       </c>
-      <c r="E8" t="n">
-        <v>28</v>
-      </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>0.27559054</v>
+        <v>0.32342008</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>0.30222222</v>
+        <v>0.36681223</v>
       </c>
       <c r="K8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" t="n">
+        <v>67</v>
+      </c>
+      <c r="M8" t="n">
         <v>29</v>
       </c>
-      <c r="L8" t="n">
-        <v>60</v>
-      </c>
-      <c r="M8" t="n">
-        <v>22</v>
-      </c>
       <c r="N8" t="n">
-        <v>3.9661016</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
         <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2372881</v>
+        <v>1.1166667</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>0.22566372</v>
+        <v>0.20444444</v>
       </c>
       <c r="U8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.27</v>
+        <v>0.285</v>
       </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
         <v>9</v>
       </c>
-      <c r="D9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E9" t="n">
-        <v>16</v>
-      </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.33333334</v>
+        <v>0.36796537</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.49</v>
+        <v>0.465</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3333335</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.4074074</v>
+        <v>1.537037</v>
       </c>
       <c r="S9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26976743</v>
+        <v>0.26415095</v>
       </c>
       <c r="U9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -3336,43 +3336,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24229075</v>
+        <v>0.21875</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3083004</v>
+        <v>0.2874494</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.40528634</v>
+        <v>0.36607143</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9375</v>
+        <v>4.0153847</v>
       </c>
       <c r="O10" t="n">
         <v>12</v>
@@ -3381,19 +3381,19 @@
         <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.359375</v>
+        <v>1.3076923</v>
       </c>
       <c r="S10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2579365</v>
+        <v>0.248</v>
       </c>
       <c r="U10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2748815</v>
+        <v>0.28638497</v>
       </c>
       <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33043477</v>
+        <v>0.34334764</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.43601894</v>
+        <v>0.46478873</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6964285</v>
+        <v>4.982143</v>
       </c>
       <c r="O11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3392857</v>
+        <v>1.4107143</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2488263</v>
+        <v>0.26605505</v>
       </c>
       <c r="U11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23715416</v>
+        <v>0.24124514</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
         <v>16</v>
@@ -3485,49 +3485,49 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>0.29710144</v>
+        <v>0.30496454</v>
       </c>
       <c r="I12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.35797665</v>
+      </c>
+      <c r="K12" t="n">
         <v>23</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.3478261</v>
-      </c>
-      <c r="K12" t="n">
-        <v>25</v>
-      </c>
       <c r="L12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M12" t="n">
         <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>6.078534</v>
+        <v>5.513089</v>
       </c>
       <c r="O12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P12" t="n">
         <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3507853</v>
+        <v>1.3036649</v>
       </c>
       <c r="S12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T12" t="n">
-        <v>0.24793388</v>
+        <v>0.24166666</v>
       </c>
       <c r="U12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -3537,61 +3537,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.22608696</v>
+        <v>0.21585903</v>
       </c>
       <c r="C13" t="n">
+        <v>27</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="n">
         <v>24</v>
       </c>
-      <c r="D13" t="n">
-        <v>27</v>
-      </c>
-      <c r="E13" t="n">
-        <v>21</v>
-      </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2952756</v>
+        <v>0.28968254</v>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>0.37826088</v>
+        <v>0.3524229</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.25</v>
+        <v>2.390625</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1.171875</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>0.17410715</v>
+        <v>0.19026549</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.23115578</v>
+        <v>0.23469388</v>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3167421</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4489796</v>
+      </c>
+      <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="n">
-        <v>14</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.29357797</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.41708544</v>
-      </c>
-      <c r="K14" t="n">
-        <v>14</v>
-      </c>
       <c r="L14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>6.792453</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5471698</v>
+        <v>1.3703704</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="T14" t="n">
-        <v>0.30414745</v>
+        <v>0.28504673</v>
       </c>
       <c r="U14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -3671,16 +3671,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23786408</v>
+        <v>0.2254902</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -3689,46 +3689,46 @@
         <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2927928</v>
+        <v>0.27853882</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3398058</v>
+        <v>0.32352942</v>
       </c>
       <c r="K15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3333333</v>
+        <v>2.7169812</v>
       </c>
       <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="n">
         <v>6</v>
       </c>
-      <c r="P15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.3148148</v>
+        <v>1.1509434</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2682927</v>
+        <v>0.24489796</v>
       </c>
       <c r="U15" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23383084</v>
+        <v>0.23880596</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35</v>
+        <v>0.35833332</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
         <v>0.37313432</v>
       </c>
       <c r="K16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
         <v>12</v>
       </c>
       <c r="N16" t="n">
-        <v>4.909091</v>
+        <v>5.5636363</v>
       </c>
       <c r="O16" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
         <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2545455</v>
+        <v>1.4545455</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T16" t="n">
-        <v>0.26540285</v>
+        <v>0.29166666</v>
       </c>
       <c r="U16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.22510822</v>
+        <v>0.25106382</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.33207548</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.44680852</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>55</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.4590163</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24</v>
+      </c>
+      <c r="P17" t="n">
         <v>10</v>
       </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.31178707</v>
-      </c>
-      <c r="I17" t="n">
-        <v>17</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.41125542</v>
-      </c>
-      <c r="K17" t="n">
-        <v>16</v>
-      </c>
-      <c r="L17" t="n">
-        <v>59</v>
-      </c>
-      <c r="M17" t="n">
-        <v>18</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.3114753</v>
-      </c>
-      <c r="O17" t="n">
-        <v>20</v>
-      </c>
-      <c r="P17" t="n">
-        <v>9</v>
-      </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5573771</v>
+        <v>1.5409836</v>
       </c>
       <c r="S17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.28085107</v>
+      </c>
+      <c r="U17" t="n">
         <v>27</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.27896994</v>
-      </c>
-      <c r="U17" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.272</v>
+        <v>0.27309236</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>0.35106382</v>
+        <v>0.35915494</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.428</v>
+        <v>0.437751</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L18" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>7.1694913</v>
       </c>
       <c r="O18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
         <v>30</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5166667</v>
+        <v>1.7118644</v>
       </c>
       <c r="S18" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="T18" t="n">
-        <v>0.26970956</v>
+        <v>0.28630707</v>
       </c>
       <c r="U18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.26168224</v>
+        <v>0.23943663</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3495935</v>
+        <v>0.32786885</v>
       </c>
       <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.44131455</v>
+      </c>
+      <c r="K19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.47196263</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6</v>
-      </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>3.375</v>
+        <v>4.909091</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0357143</v>
+        <v>1.3454546</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>0.21428572</v>
+        <v>0.23831776</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.22439024</v>
+        <v>0.23762377</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3063063</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.44059405</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45</v>
+      </c>
+      <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.29955947</v>
-      </c>
-      <c r="I20" t="n">
-        <v>22</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.4292683</v>
-      </c>
-      <c r="K20" t="n">
-        <v>11</v>
-      </c>
-      <c r="L20" t="n">
-        <v>48</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7</v>
-      </c>
       <c r="N20" t="n">
-        <v>5.4339623</v>
+        <v>4.924528</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
+        <v>20</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3018868</v>
+      </c>
+      <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.26666668</v>
+      </c>
+      <c r="U20" t="n">
         <v>24</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4150944</v>
-      </c>
-      <c r="S20" t="n">
-        <v>22</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.28504673</v>
-      </c>
-      <c r="U20" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3018868</v>
+        <v>0.25603864</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
+        <v>23</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3187773</v>
+      </c>
+      <c r="I21" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.33816424</v>
+      </c>
+      <c r="K21" t="n">
+        <v>27</v>
+      </c>
+      <c r="L21" t="n">
+        <v>64</v>
+      </c>
+      <c r="M21" t="n">
+        <v>24</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.54375</v>
+      </c>
+      <c r="O21" t="n">
         <v>9</v>
       </c>
-      <c r="F21" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.36134455</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.44339624</v>
-      </c>
-      <c r="K21" t="n">
-        <v>9</v>
-      </c>
-      <c r="L21" t="n">
-        <v>59</v>
-      </c>
-      <c r="M21" t="n">
-        <v>18</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.981595</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.01227</v>
+        <v>1.0125</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.20707071</v>
+        <v>0.20408164</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4140,13 +4140,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2361809</v>
+        <v>0.22222222</v>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
         <v>27</v>
@@ -4155,49 +4155,49 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30493274</v>
+        <v>0.28310502</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>0.36683416</v>
+        <v>0.35353535</v>
       </c>
       <c r="K22" t="n">
         <v>24</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.037736</v>
+        <v>2.54717</v>
       </c>
       <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="P22" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.20918368</v>
+      </c>
+      <c r="U22" t="n">
         <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.018868</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.20103092</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.26237625</v>
+        <v>0.25</v>
       </c>
       <c r="C23" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>29</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.34684685</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.33854166</v>
+      </c>
+      <c r="K23" t="n">
+        <v>26</v>
+      </c>
+      <c r="L23" t="n">
+        <v>45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.9272728</v>
+      </c>
+      <c r="O23" t="n">
         <v>10</v>
-      </c>
-      <c r="D23" t="n">
-        <v>29</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>27</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.3617021</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.37128714</v>
-      </c>
-      <c r="K23" t="n">
-        <v>23</v>
-      </c>
-      <c r="L23" t="n">
-        <v>56</v>
-      </c>
-      <c r="M23" t="n">
-        <v>16</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.581818</v>
-      </c>
-      <c r="O23" t="n">
-        <v>17</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3090909</v>
+        <v>1.2363636</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24630542</v>
+        <v>0.23115578</v>
       </c>
       <c r="U23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.21782178</v>
+        <v>0.2244898</v>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
         <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2907489</v>
+        <v>0.29166666</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>0.34653464</v>
+        <v>0.41836736</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4785275</v>
+        <v>3.2264152</v>
       </c>
       <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2830188</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2303665</v>
+      </c>
+      <c r="U24" t="n">
         <v>8</v>
-      </c>
-      <c r="P24" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2515337</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.22564103</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -4341,16 +4341,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2761905</v>
+        <v>0.25925925</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
@@ -4359,43 +4359,43 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>0.36363637</v>
+        <v>0.33818182</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>0.50476193</v>
+        <v>0.45679012</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M25" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N25" t="n">
-        <v>5.468354</v>
+        <v>5.340659</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5189873</v>
+        <v>1.4670329</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2631579</v>
+        <v>0.2616034</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -4408,16 +4408,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.25714287</v>
+        <v>0.2782258</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
@@ -4426,46 +4426,46 @@
         <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>0.35106382</v>
+        <v>0.36619717</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4</v>
+        <v>0.41532257</v>
       </c>
       <c r="K26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L26" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>6.0641713</v>
+        <v>4.9736843</v>
       </c>
       <c r="O26" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="n">
         <v>29</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5721925</v>
+        <v>1.3736843</v>
       </c>
       <c r="S26" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T26" t="n">
-        <v>0.31102362</v>
+        <v>0.28</v>
       </c>
       <c r="U26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.29680365</v>
+        <v>0.3169643</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>0.338843</v>
+        <v>0.35772356</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>0.48401827</v>
+        <v>0.5223214</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N27" t="n">
-        <v>5.7375</v>
+        <v>6.4125</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P27" t="n">
         <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>1.63125</v>
+        <v>1.59375</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2631579</v>
+        <v>0.27142859</v>
       </c>
       <c r="U27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2489796</v>
+        <v>0.26122448</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3108614</v>
+      </c>
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3877551</v>
+      </c>
+      <c r="K28" t="n">
+        <v>18</v>
+      </c>
+      <c r="L28" t="n">
+        <v>43</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.790323</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15</v>
+      </c>
+      <c r="P28" t="n">
         <v>11</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.3071161</v>
-      </c>
-      <c r="I28" t="n">
-        <v>19</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.39591837</v>
-      </c>
-      <c r="K28" t="n">
-        <v>19</v>
-      </c>
-      <c r="L28" t="n">
-        <v>49</v>
-      </c>
-      <c r="M28" t="n">
-        <v>8</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.0153847</v>
-      </c>
-      <c r="O28" t="n">
-        <v>14</v>
-      </c>
-      <c r="P28" t="n">
-        <v>8</v>
-      </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1538461</v>
+        <v>1.3225807</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23012552</v>
+        <v>0.25311205</v>
       </c>
       <c r="U28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.26180258</v>
+        <v>0.27155173</v>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3244275</v>
+        <v>0.33333334</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4549356</v>
+        <v>0.4698276</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
         <v>49</v>
       </c>
       <c r="M29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
-        <v>4.21875</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34375</v>
+        <v>1.359375</v>
       </c>
       <c r="S29" t="n">
+        <v>18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.25714287</v>
+      </c>
+      <c r="U29" t="n">
         <v>17</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.24691358</v>
-      </c>
-      <c r="U29" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.29166666</v>
+        <v>0.2824074</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.36363637</v>
+        <v>0.34728032</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>0.41666666</v>
+        <v>0.38425925</v>
       </c>
       <c r="K30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L30" t="n">
         <v>44</v>
       </c>
       <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.4615386</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>14</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.1730769</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.21761657</v>
+      </c>
+      <c r="U30" t="n">
         <v>5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.3773584</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.9433962</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.18947369</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25757575</v>
+        <v>0.26732674</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
+        <v>28</v>
+      </c>
+      <c r="E31" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
         <v>25</v>
       </c>
-      <c r="E31" t="n">
-        <v>23</v>
-      </c>
-      <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="n">
-        <v>29</v>
-      </c>
       <c r="H31" t="n">
-        <v>0.32735425</v>
+        <v>0.34210527</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>0.37878788</v>
+        <v>0.4059406</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L31" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7115383</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3269231</v>
+        <v>1.4313725</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T31" t="n">
-        <v>0.23469388</v>
+        <v>0.26</v>
       </c>
       <c r="U31" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24179476</v>
+        <v>0.24201195</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
@@ -564,28 +564,28 @@
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31390384</v>
+        <v>0.31392777</v>
       </c>
       <c r="I2" t="n">
         <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39426672</v>
+        <v>0.39332098</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1267605</v>
+        <v>4.115683</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
         <v>162</v>
@@ -594,13 +594,13 @@
         <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2793428</v>
+        <v>1.2787267</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24891819</v>
+        <v>0.24867076</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24657534</v>
+        <v>0.24609137</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E3" t="n">
         <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3197653</v>
+        <v>0.31937364</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40441626</v>
+        <v>0.4036548</v>
       </c>
       <c r="K3" t="n">
         <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>1235</v>
+        <v>1245</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.401414</v>
+        <v>5.398596</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4941084</v>
+        <v>1.4929798</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26849425</v>
+        <v>0.26846847</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24824162</v>
+        <v>0.24722336</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>665</v>
@@ -698,46 +698,46 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31172723</v>
+        <v>0.31073025</v>
       </c>
       <c r="I4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41311544</v>
+        <v>0.41114768</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1165</v>
+        <v>1177</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.567376</v>
+        <v>3.5520751</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q4" t="n">
         <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2458628</v>
+        <v>1.2427565</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23208264</v>
+        <v>0.23160763</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23383395</v>
+        <v>0.23409985</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3151672</v>
+        <v>0.31604034</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39340842</v>
+        <v>0.39403355</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>1332</v>
+        <v>1343</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1306496</v>
+        <v>4.1297393</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3402597</v>
+        <v>1.33789</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25269583</v>
+        <v>0.25277835</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,64 +814,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24844977</v>
+        <v>0.2486653</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32241443</v>
+        <v>0.32279292</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40471268</v>
+        <v>0.40554416</v>
       </c>
       <c r="K6" t="n">
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.603278</v>
+        <v>3.5920951</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2330905</v>
+        <v>1.2314647</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.241101</v>
+        <v>0.24069887</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -881,43 +881,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2518653</v>
+        <v>0.25145262</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3395562</v>
+        <v>0.3392826</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43133697</v>
+        <v>0.43117613</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2108808</v>
+        <v>4.2126675</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
@@ -929,16 +929,16 @@
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2645078</v>
+        <v>1.2644181</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24454957</v>
+        <v>0.24442627</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -951,7 +951,7 @@
         <v>0.23651884</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
         <v>680</v>
@@ -969,13 +969,13 @@
         <v>0.31915286</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>0.40703726</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>1303</v>
@@ -993,7 +993,7 @@
         <v>161</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
         <v>1.3029827</v>
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23057538</v>
+        <v>0.23040034</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3097015</v>
+        <v>0.30917516</v>
       </c>
       <c r="I9" t="n">
         <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39899203</v>
+        <v>0.39887407</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>1361</v>
+        <v>1375</v>
       </c>
       <c r="M9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.680851</v>
+        <v>4.6726704</v>
       </c>
       <c r="O9" t="n">
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.429472</v>
+        <v>1.4275646</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25210428</v>
+        <v>0.25132707</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23576048</v>
+        <v>0.23596437</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G10" t="n">
         <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31349647</v>
+        <v>0.31319085</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37095764</v>
+        <v>0.3710379</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7457054</v>
+        <v>3.764356</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q10" t="n">
         <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.261062</v>
+        <v>1.2656493</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23688032</v>
+        <v>0.23712403</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23819387</v>
+        <v>0.23822258</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G12" t="n">
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3140801</v>
+        <v>0.31402382</v>
       </c>
       <c r="I12" t="n">
         <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39540184</v>
+        <v>0.39600906</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>1246</v>
+        <v>1258</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.679558</v>
+        <v>3.6818182</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2241515</v>
+        <v>1.2264891</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23276408</v>
+        <v>0.23287958</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
@@ -1310,13 +1310,13 @@
         <v>0.40703207</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>1180</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
         <v>4.50938</v>
@@ -1328,13 +1328,13 @@
         <v>183</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
         <v>1.3522668</v>
       </c>
       <c r="S13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
         <v>0.23778705</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24730738</v>
+        <v>0.24707091</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
@@ -1368,25 +1368,25 @@
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31616142</v>
+        <v>0.31611</v>
       </c>
       <c r="I14" t="n">
         <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4026512</v>
+        <v>0.40184996</v>
       </c>
       <c r="K14" t="n">
         <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6978154</v>
+        <v>4.6892138</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
@@ -1398,13 +1398,13 @@
         <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3929981</v>
+        <v>1.3922695</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2583247</v>
+        <v>0.25841543</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23341009</v>
+        <v>0.23305613</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E15" t="n">
         <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3076201</v>
+        <v>0.30736253</v>
       </c>
       <c r="I15" t="n">
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.36906007</v>
+        <v>0.36860707</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1351</v>
+        <v>1366</v>
       </c>
       <c r="M15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2114015</v>
+        <v>4.220299</v>
       </c>
       <c r="O15" t="n">
         <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3396674</v>
+        <v>1.3422502</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2352817</v>
+        <v>0.23559003</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25674555</v>
+        <v>0.25593394</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33608058</v>
+        <v>0.3357598</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.41988376</v>
+        <v>0.41898865</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7089474</v>
+        <v>3.7039456</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q16" t="n">
         <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1692106</v>
+        <v>1.1672329</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22054766</v>
+        <v>0.22044258</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,46 +1551,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24743778</v>
+        <v>0.24709061</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32605478</v>
+        <v>0.32579517</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39907968</v>
+        <v>0.39879468</v>
       </c>
       <c r="K17" t="n">
         <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="M17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9781234</v>
+        <v>3.9994767</v>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
         <v>144</v>
@@ -1599,13 +1599,13 @@
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.261202</v>
+        <v>1.269563</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2328421</v>
+        <v>0.23414023</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25618482</v>
+        <v>0.25599837</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -1636,43 +1636,43 @@
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33938196</v>
+        <v>0.3392283</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3995093</v>
+        <v>0.39873934</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5448885</v>
+        <v>3.5410976</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q18" t="n">
         <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1870784</v>
+        <v>1.1865499</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22289789</v>
+        <v>0.22266194</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24554497</v>
+        <v>0.24557431</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3189049</v>
+        <v>0.31962547</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40696228</v>
+        <v>0.40675175</v>
       </c>
       <c r="K19" t="n">
         <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6652575</v>
+        <v>4.6642165</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3791282</v>
+        <v>1.377527</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25154638</v>
+        <v>0.25148475</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1752,16 +1752,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23568603</v>
+        <v>0.2369453</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>176</v>
@@ -1770,43 +1770,43 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3055712</v>
+        <v>0.3069344</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3907974</v>
+        <v>0.39153767</v>
       </c>
       <c r="K20" t="n">
         <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="M20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.119602</v>
+        <v>4.118763</v>
       </c>
       <c r="O20" t="n">
+        <v>15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q20" t="n">
         <v>14</v>
       </c>
-      <c r="P20" t="n">
-        <v>160</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>16</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3001833</v>
+        <v>1.2972974</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23887394</v>
+        <v>0.23858495</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1828,19 +1828,19 @@
         <v>646</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>193</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
         <v>0.31145382</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
         <v>0.40630287</v>
@@ -1870,7 +1870,7 @@
         <v>1.1674491</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>0.22353189</v>
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24212721</v>
+        <v>0.24160099</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31230167</v>
+        <v>0.31173414</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40020856</v>
+        <v>0.3996267</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>1183</v>
+        <v>1193</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9908113</v>
+        <v>3.9627216</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P22" t="n">
         <v>167</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2775007</v>
+        <v>1.2708551</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24541898</v>
+        <v>0.2444217</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1956,7 +1956,7 @@
         <v>0.25176945</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
         <v>694</v>
@@ -1986,7 +1986,7 @@
         <v>1362</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N23" t="n">
         <v>4.176989</v>
@@ -1998,7 +1998,7 @@
         <v>139</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>1.3060378</v>
@@ -2010,7 +2010,7 @@
         <v>0.23709644</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23598132</v>
+        <v>0.23633678</v>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E24" t="n">
         <v>24</v>
@@ -2038,46 +2038,46 @@
         <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3132439</v>
+        <v>0.31362614</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38657603</v>
+        <v>0.38636842</v>
       </c>
       <c r="K24" t="n">
         <v>26</v>
       </c>
       <c r="L24" t="n">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9089234</v>
+        <v>3.8954523</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q24" t="n">
         <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2911292</v>
+        <v>1.2859383</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24126315</v>
+        <v>0.24069427</v>
       </c>
       <c r="U24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24754098</v>
+        <v>0.24776241</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
         <v>164</v>
@@ -2105,43 +2105,43 @@
         <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30836594</v>
+        <v>0.3087447</v>
       </c>
       <c r="I25" t="n">
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40717214</v>
+        <v>0.4068348</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="M25" t="n">
         <v>9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.393533</v>
+        <v>4.36982</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3596214</v>
+        <v>1.3588741</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.248125</v>
+        <v>0.24788266</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2221,43 +2221,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24388237</v>
+        <v>0.24367863</v>
       </c>
       <c r="C27" t="n">
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G27" t="n">
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3169569</v>
+        <v>0.3167939</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38720953</v>
+        <v>0.38662317</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.32</v>
+        <v>4.2994075</v>
       </c>
       <c r="O27" t="n">
         <v>22</v>
@@ -2269,13 +2269,13 @@
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.351948</v>
+        <v>1.3527442</v>
       </c>
       <c r="S27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25434828</v>
+        <v>0.2545196</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2303,7 +2303,7 @@
         <v>149</v>
       </c>
       <c r="G28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" t="n">
         <v>0.3283582</v>
@@ -2345,7 +2345,7 @@
         <v>0.23171493</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2382,13 +2382,13 @@
         <v>0.39987457</v>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L29" t="n">
         <v>1215</v>
       </c>
       <c r="M29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N29" t="n">
         <v>4.2991815</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24753086</v>
+        <v>0.24765019</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E30" t="n">
         <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30912825</v>
+        <v>0.30917516</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38168725</v>
+        <v>0.38291785</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.922416</v>
+        <v>3.9309542</v>
       </c>
       <c r="O30" t="n">
         <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2996615</v>
+        <v>1.2986811</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23686406</v>
+        <v>0.23643893</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,43 +2489,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24878739</v>
+        <v>0.24819277</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.325054</v>
+        <v>0.32408732</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42906225</v>
+        <v>0.42811245</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7239504</v>
+        <v>4.7156105</v>
       </c>
       <c r="O31" t="n">
         <v>28</v>
@@ -2537,13 +2537,13 @@
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3903577</v>
+        <v>1.3910356</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25501317</v>
+        <v>0.2552335</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.19791667</v>
+        <v>0.20103092</v>
       </c>
       <c r="C2" t="n">
         <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>0.26415095</v>
+        <v>0.26168224</v>
       </c>
       <c r="I2" t="n">
         <v>29</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3125</v>
+        <v>0.30927834</v>
       </c>
       <c r="K2" t="n">
         <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8333333</v>
+        <v>2.9454546</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0925926</v>
+        <v>1.1272727</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>0.225</v>
+        <v>0.23039216</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2603306</v>
+        <v>0.26612905</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32713756</v>
+        <v>0.34172663</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4752066</v>
+        <v>0.48790324</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M3" t="n">
         <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>4.2786884</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4666667</v>
+        <v>1.409836</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26406926</v>
+        <v>0.26180258</v>
       </c>
       <c r="U3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24637681</v>
+        <v>0.22</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.29596412</v>
+        <v>0.2764977</v>
       </c>
       <c r="I4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>0.43961352</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9807692</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2692307</v>
+        <v>1.137255</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.235</v>
+        <v>0.21052632</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.19213974</v>
+        <v>0.21030043</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2857143</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.32618025</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>71</v>
+      </c>
+      <c r="M5" t="n">
         <v>29</v>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.26190478</v>
-      </c>
-      <c r="I5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.28820962</v>
-      </c>
-      <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>65</v>
-      </c>
-      <c r="M5" t="n">
-        <v>25</v>
-      </c>
       <c r="N5" t="n">
-        <v>2.9685864</v>
+        <v>3.3926702</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>20</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.209424</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.22857143</v>
+      </c>
+      <c r="U5" t="n">
         <v>8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>14</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.2565445</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.22540984</v>
-      </c>
-      <c r="U5" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3068,16 +3068,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24291497</v>
+        <v>0.2345679</v>
       </c>
       <c r="C6" t="n">
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
         <v>11</v>
@@ -3086,46 +3086,46 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3188406</v>
+        <v>0.31365314</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>0.44129553</v>
+        <v>0.4238683</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N6" t="n">
-        <v>4.21875</v>
+        <v>3.4285715</v>
       </c>
       <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
         <v>13</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
+        <v>1.2063493</v>
+      </c>
+      <c r="S6" t="n">
         <v>8</v>
       </c>
-      <c r="Q6" t="n">
-        <v>14</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.265625</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.25104603</v>
+        <v>0.23504274</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27004218</v>
+        <v>0.22222222</v>
       </c>
       <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.31128404</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.36888888</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.7540984</v>
+      </c>
+      <c r="O7" t="n">
+        <v>29</v>
+      </c>
+      <c r="P7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
-        <v>43</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>14</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.35661766</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4978903</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>48</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.516129</v>
-      </c>
-      <c r="O7" t="n">
-        <v>26</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9</v>
-      </c>
       <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4590164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.25541127</v>
+      </c>
+      <c r="U7" t="n">
         <v>20</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.451613</v>
-      </c>
-      <c r="S7" t="n">
-        <v>23</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.26050422</v>
-      </c>
-      <c r="U7" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20524018</v>
+        <v>0.21428572</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.31555554</v>
+      </c>
+      <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.38265306</v>
+      </c>
+      <c r="K8" t="n">
         <v>19</v>
       </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.32342008</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
+        <v>56</v>
+      </c>
+      <c r="M8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.36681223</v>
-      </c>
-      <c r="K8" t="n">
-        <v>21</v>
-      </c>
-      <c r="L8" t="n">
-        <v>67</v>
-      </c>
-      <c r="M8" t="n">
-        <v>29</v>
-      </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>2.9423077</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1166667</v>
+        <v>1.0769231</v>
       </c>
       <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.19791667</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.20444444</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.285</v>
+        <v>0.29064038</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.36796537</v>
+        <v>0.3580786</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.465</v>
+        <v>0.49261084</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M9" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.754717</v>
+      </c>
+      <c r="O9" t="n">
         <v>17</v>
       </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>21</v>
-      </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.537037</v>
+        <v>1.4528302</v>
       </c>
       <c r="S9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26415095</v>
+        <v>0.22335026</v>
       </c>
       <c r="U9" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.21875</v>
+        <v>0.2248062</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2874494</v>
+        <v>0.2846975</v>
       </c>
       <c r="I10" t="n">
         <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36607143</v>
+        <v>0.36821705</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.3150687</v>
+      </c>
+      <c r="O10" t="n">
+        <v>14</v>
+      </c>
+      <c r="P10" t="n">
         <v>7</v>
       </c>
-      <c r="N10" t="n">
-        <v>4.0153847</v>
-      </c>
-      <c r="O10" t="n">
-        <v>12</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3076923</v>
+        <v>1.3835616</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>0.248</v>
+        <v>0.2508834</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -3403,16 +3403,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.28638497</v>
+        <v>0.29444444</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
@@ -3421,46 +3421,46 @@
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34334764</v>
+        <v>0.3469388</v>
       </c>
       <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.49444443</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>49</v>
+      </c>
+      <c r="M11" t="n">
         <v>9</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.46478873</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>57</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17</v>
-      </c>
       <c r="N11" t="n">
-        <v>4.982143</v>
+        <v>5.5531917</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4107143</v>
+        <v>1.468085</v>
       </c>
       <c r="S11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T11" t="n">
-        <v>0.26605505</v>
+        <v>0.2857143</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24124514</v>
+        <v>0.25</v>
       </c>
       <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
         <v>18</v>
       </c>
-      <c r="D12" t="n">
-        <v>31</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>20</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.30496454</v>
+        <v>0.30985916</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>0.35797665</v>
+        <v>0.3846154</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M12" t="n">
         <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>5.513089</v>
+        <v>4.5927835</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3036649</v>
+        <v>1.2525774</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>0.24166666</v>
+        <v>0.2375</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.21585903</v>
+        <v>0.2113402</v>
       </c>
       <c r="C13" t="n">
+        <v>26</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" t="n">
         <v>27</v>
       </c>
-      <c r="D13" t="n">
-        <v>23</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.28703704</v>
+      </c>
+      <c r="I13" t="n">
         <v>24</v>
       </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.28968254</v>
-      </c>
-      <c r="I13" t="n">
-        <v>25</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.3524229</v>
+        <v>0.34020618</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>2.390625</v>
+        <v>2.290909</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
       </c>
       <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.0909091</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
+        <v>0.19689119</v>
+      </c>
+      <c r="U13" t="n">
         <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.171875</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.19026549</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3604,46 +3604,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.23469388</v>
+        <v>0.23175965</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3167421</v>
+        <v>0.31558937</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4489796</v>
+        <v>0.4248927</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4.78125</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P14" t="n">
         <v>9</v>
@@ -3652,13 +3652,13 @@
         <v>20</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3703704</v>
+        <v>1.359375</v>
       </c>
       <c r="S14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28504673</v>
+        <v>0.28286853</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2254902</v>
+        <v>0.2</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.24528302</v>
+      </c>
+      <c r="I15" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>30</v>
+      </c>
+      <c r="L15" t="n">
+        <v>65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.4615386</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3269231</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.26020408</v>
+      </c>
+      <c r="U15" t="n">
         <v>22</v>
-      </c>
-      <c r="E15" t="n">
-        <v>26</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>29</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.27853882</v>
-      </c>
-      <c r="I15" t="n">
-        <v>28</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.32352942</v>
-      </c>
-      <c r="K15" t="n">
-        <v>28</v>
-      </c>
-      <c r="L15" t="n">
-        <v>60</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.7169812</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.1509434</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.24489796</v>
-      </c>
-      <c r="U15" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23880596</v>
+        <v>0.2236842</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35833332</v>
+        <v>0.3490909</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.37313432</v>
+        <v>0.35964912</v>
       </c>
       <c r="K16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5636363</v>
+        <v>5.203125</v>
       </c>
       <c r="O16" t="n">
+        <v>23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>23</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="S16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U16" t="n">
         <v>27</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>14</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4545455</v>
-      </c>
-      <c r="S16" t="n">
-        <v>24</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.29166666</v>
-      </c>
-      <c r="U16" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25106382</v>
+        <v>0.23275863</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3219697</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.44827586</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>60</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.516129</v>
+      </c>
+      <c r="O17" t="n">
+        <v>26</v>
+      </c>
+      <c r="P17" t="n">
         <v>8</v>
       </c>
-      <c r="F17" t="n">
-        <v>11</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.33207548</v>
-      </c>
-      <c r="I17" t="n">
-        <v>13</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.44680852</v>
-      </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>55</v>
-      </c>
-      <c r="M17" t="n">
-        <v>14</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.4590163</v>
-      </c>
-      <c r="O17" t="n">
-        <v>24</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5409836</v>
+        <v>1.6451613</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>0.28085107</v>
+        <v>0.29098362</v>
       </c>
       <c r="U17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.27309236</v>
+        <v>0.26859504</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>0.35915494</v>
+        <v>0.3607143</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.437751</v>
+        <v>0.41735536</v>
       </c>
       <c r="K18" t="n">
+        <v>11</v>
+      </c>
+      <c r="L18" t="n">
+        <v>64</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O18" t="n">
+        <v>19</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>23</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.24017467</v>
+      </c>
+      <c r="U18" t="n">
         <v>14</v>
-      </c>
-      <c r="L18" t="n">
-        <v>66</v>
-      </c>
-      <c r="M18" t="n">
-        <v>26</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7.1694913</v>
-      </c>
-      <c r="O18" t="n">
-        <v>30</v>
-      </c>
-      <c r="P18" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>30</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.7118644</v>
-      </c>
-      <c r="S18" t="n">
-        <v>30</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.28630707</v>
-      </c>
-      <c r="U18" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -3939,34 +3939,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.23943663</v>
+        <v>0.23474178</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
         <v>0.32786885</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>0.44131455</v>
+        <v>0.38967136</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
         <v>50</v>
@@ -3975,28 +3975,28 @@
         <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>4.909091</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
+        <v>23</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3888888</v>
+      </c>
+      <c r="S19" t="n">
         <v>20</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.3454546</v>
-      </c>
-      <c r="S19" t="n">
-        <v>17</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.23831776</v>
+        <v>0.24884793</v>
       </c>
       <c r="U19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23762377</v>
+        <v>0.2596154</v>
       </c>
       <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.34188035</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.45192307</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>43</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.264151</v>
+      </c>
+      <c r="O20" t="n">
+        <v>24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.245283</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.25728154</v>
+      </c>
+      <c r="U20" t="n">
         <v>21</v>
-      </c>
-      <c r="D20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.3063063</v>
-      </c>
-      <c r="I20" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.44059405</v>
-      </c>
-      <c r="K20" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" t="n">
-        <v>45</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.924528</v>
-      </c>
-      <c r="O20" t="n">
-        <v>18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>20</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3018868</v>
-      </c>
-      <c r="S20" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.26666668</v>
-      </c>
-      <c r="U20" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.25603864</v>
+        <v>0.26857144</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="n">
         <v>24</v>
       </c>
-      <c r="E21" t="n">
-        <v>23</v>
-      </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
+        <v>28</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3401015</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.34857142</v>
+      </c>
+      <c r="K21" t="n">
         <v>25</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.3187773</v>
-      </c>
-      <c r="I21" t="n">
-        <v>18</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.33816424</v>
-      </c>
-      <c r="K21" t="n">
-        <v>27</v>
-      </c>
       <c r="L21" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N21" t="n">
-        <v>3.54375</v>
+        <v>2.3823528</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
         <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0125</v>
+        <v>0.8382353</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.20408164</v>
+        <v>0.17610063</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4140,43 +4140,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22222222</v>
+        <v>0.21875</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H22" t="n">
-        <v>0.28310502</v>
+        <v>0.2783019</v>
       </c>
       <c r="I22" t="n">
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>0.35353535</v>
+        <v>0.35416666</v>
       </c>
       <c r="K22" t="n">
         <v>24</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.54717</v>
+        <v>2.3773584</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
@@ -4185,19 +4185,19 @@
         <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0.8113208</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.20918368</v>
+        <v>0.17989418</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4210,61 +4210,61 @@
         <v>0.25</v>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
         <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" t="n">
         <v>0.34684685</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
         <v>0.33854166</v>
       </c>
       <c r="K23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L23" t="n">
         <v>45</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
         <v>3.9272728</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>1.2363636</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T23" t="n">
         <v>0.23115578</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2244898</v>
+        <v>0.2054054</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
         <v>27</v>
@@ -4289,49 +4289,49 @@
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29166666</v>
+        <v>0.28846154</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>0.41836736</v>
+        <v>0.4054054</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2264152</v>
+        <v>3.5660377</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.2830188</v>
+        <v>1.2075472</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2303665</v>
+        <v>0.22916667</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25925925</v>
+        <v>0.25619835</v>
       </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3393502</v>
+      </c>
+      <c r="I25" t="n">
         <v>12</v>
       </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.33818182</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11</v>
-      </c>
       <c r="J25" t="n">
-        <v>0.45679012</v>
+        <v>0.4214876</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>5.340659</v>
+        <v>5.0265956</v>
       </c>
       <c r="O25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
         <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4670329</v>
+        <v>1.4840425</v>
       </c>
       <c r="S25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2616034</v>
+        <v>0.25514403</v>
       </c>
       <c r="U25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2782258</v>
+        <v>0.2761905</v>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>0.36619717</v>
+        <v>0.36514524</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.41532257</v>
+        <v>0.3857143</v>
       </c>
       <c r="K26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L26" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="M26" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
-        <v>4.9736843</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q26" t="n">
         <v>29</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3736843</v>
+        <v>1.2962962</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.27102804</v>
       </c>
       <c r="U26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -4475,61 +4475,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3169643</v>
+        <v>0.3018868</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0.35772356</v>
+        <v>0.34812286</v>
       </c>
       <c r="I27" t="n">
         <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5223214</v>
+        <v>0.49056605</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="M27" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N27" t="n">
-        <v>6.4125</v>
+        <v>5.6544504</v>
       </c>
       <c r="O27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P27" t="n">
         <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.59375</v>
+        <v>1.5706806</v>
       </c>
       <c r="S27" t="n">
         <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>0.27142859</v>
+        <v>0.27235773</v>
       </c>
       <c r="U27" t="n">
         <v>25</v>
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26122448</v>
+        <v>0.26190478</v>
       </c>
       <c r="C28" t="n">
         <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
@@ -4557,49 +4557,49 @@
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3108614</v>
+        <v>0.31304348</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3877551</v>
+        <v>0.40952381</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.790323</v>
+        <v>5.09434</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3225807</v>
+        <v>1.3584906</v>
       </c>
       <c r="S28" t="n">
         <v>16</v>
       </c>
       <c r="T28" t="n">
-        <v>0.25311205</v>
+        <v>0.24878049</v>
       </c>
       <c r="U28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.27155173</v>
+        <v>0.27</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.32735425</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K29" t="n">
         <v>5</v>
       </c>
-      <c r="F29" t="n">
-        <v>11</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I29" t="n">
-        <v>12</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.4698276</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
       <c r="L29" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>5.072727</v>
       </c>
       <c r="O29" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P29" t="n">
         <v>11</v>
       </c>
       <c r="Q29" t="n">
+        <v>29</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5272727</v>
+      </c>
+      <c r="S29" t="n">
+        <v>28</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2764977</v>
+      </c>
+      <c r="U29" t="n">
         <v>26</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.359375</v>
-      </c>
-      <c r="S29" t="n">
-        <v>18</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.25714287</v>
-      </c>
-      <c r="U29" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2824074</v>
+        <v>0.28</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H30" t="n">
-        <v>0.34728032</v>
+        <v>0.3429603</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38425925</v>
+        <v>0.408</v>
       </c>
       <c r="K30" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4615386</v>
+        <v>3.7087913</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1730769</v>
+        <v>1.1703297</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>0.21761657</v>
+        <v>0.21145375</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -4743,46 +4743,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.26732674</v>
+        <v>0.23880596</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
         <v>28</v>
       </c>
-      <c r="E31" t="n">
-        <v>19</v>
-      </c>
-      <c r="F31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" t="n">
-        <v>25</v>
-      </c>
       <c r="H31" t="n">
-        <v>0.34210527</v>
+        <v>0.3080357</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4059406</v>
+        <v>0.3681592</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M31" t="n">
         <v>22</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
@@ -4791,13 +4791,13 @@
         <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4313725</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>0.26</v>
+        <v>0.2538071</v>
       </c>
       <c r="U31" t="n">
         <v>18</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24201195</v>
+        <v>0.24202128</v>
       </c>
       <c r="C2" t="n">
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31392777</v>
+        <v>0.31421265</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39332098</v>
+        <v>0.39320785</v>
       </c>
       <c r="K2" t="n">
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.115683</v>
+        <v>4.0946884</v>
       </c>
       <c r="O2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q2" t="n">
         <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2787267</v>
+        <v>1.2786759</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24867076</v>
+        <v>0.24822406</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24609137</v>
+        <v>0.24571313</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31937364</v>
+        <v>0.31873304</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4036548</v>
+        <v>0.40346983</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.398596</v>
+        <v>5.388846</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4929798</v>
+        <v>1.4918668</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26846847</v>
+        <v>0.26878726</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24722336</v>
+        <v>0.24662852</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
@@ -698,46 +698,46 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31073025</v>
+        <v>0.3099426</v>
       </c>
       <c r="I4" t="n">
         <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41114768</v>
+        <v>0.409481</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5520751</v>
+        <v>3.569207</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2427565</v>
+        <v>1.2457231</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23160763</v>
+        <v>0.23201664</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23409985</v>
+        <v>0.23374486</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31604034</v>
+        <v>0.31573197</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39403355</v>
+        <v>0.39382717</v>
       </c>
       <c r="K5" t="n">
         <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1297393</v>
+        <v>4.142674</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33789</v>
+        <v>1.3417008</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25277835</v>
+        <v>0.25330928</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2486653</v>
+        <v>0.24790859</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>151</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32279292</v>
+        <v>0.32219398</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40554416</v>
+        <v>0.40399918</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5920951</v>
+        <v>3.6087737</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2314647</v>
+        <v>1.2360184</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24069887</v>
+        <v>0.24194206</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25145262</v>
+        <v>0.2510943</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -899,43 +899,43 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3392826</v>
+        <v>0.33912438</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43117613</v>
+        <v>0.42996418</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2126675</v>
+        <v>4.203221</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2644181</v>
+        <v>1.268405</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24442627</v>
+        <v>0.2450264</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23651884</v>
+        <v>0.23619442</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31915286</v>
+        <v>0.31838155</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40703726</v>
+        <v>0.40661842</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1114597</v>
+        <v>4.145752</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3029827</v>
+        <v>1.3102105</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23939838</v>
+        <v>0.2410437</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23040034</v>
+        <v>0.2299565</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30917516</v>
+        <v>0.30871248</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39887407</v>
+        <v>0.3981769</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6726704</v>
+        <v>4.6645913</v>
       </c>
       <c r="O9" t="n">
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4275646</v>
+        <v>1.4272374</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25132707</v>
+        <v>0.2512685</v>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23596437</v>
+        <v>0.23663652</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
         <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31319085</v>
+        <v>0.31401938</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3710379</v>
+        <v>0.37191612</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.764356</v>
+        <v>3.7729259</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2656493</v>
+        <v>1.2638068</v>
       </c>
       <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.23675056</v>
+      </c>
+      <c r="U10" t="n">
         <v>10</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.23712403</v>
-      </c>
-      <c r="U10" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25390625</v>
+        <v>0.25311542</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3239566</v>
+        <v>0.3229757</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4165296</v>
+        <v>0.41593462</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="M11" t="n">
         <v>22</v>
       </c>
       <c r="N11" t="n">
-        <v>5.470074</v>
+        <v>5.4639473</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5190679</v>
+        <v>1.518158</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28750998</v>
+        <v>0.28738597</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23822258</v>
+        <v>0.23773508</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G12" t="n">
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31402382</v>
+        <v>0.3134111</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39600906</v>
+        <v>0.39513493</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="M12" t="n">
         <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6818182</v>
+        <v>3.6770427</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2264891</v>
+        <v>1.2241246</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23287958</v>
+        <v>0.23251458</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23991726</v>
+        <v>0.24030371</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31468144</v>
+        <v>0.31500825</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40703207</v>
+        <v>0.40837267</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.50938</v>
+        <v>4.5128074</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3522668</v>
+        <v>1.3505821</v>
       </c>
       <c r="S13" t="n">
         <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23778705</v>
+        <v>0.23813471</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24707091</v>
+        <v>0.24663402</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31611</v>
+        <v>0.31606883</v>
       </c>
       <c r="I14" t="n">
         <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40184996</v>
+        <v>0.40146878</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6892138</v>
+        <v>4.6701193</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q14" t="n">
         <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3922695</v>
+        <v>1.3928016</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25841543</v>
+        <v>0.25830108</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,46 +1417,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23305613</v>
+        <v>0.23437178</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E15" t="n">
         <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G15" t="n">
         <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30736253</v>
+        <v>0.30829015</v>
       </c>
       <c r="I15" t="n">
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.36860707</v>
+        <v>0.37053847</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1366</v>
+        <v>1377</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.220299</v>
+        <v>4.197656</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
         <v>150</v>
@@ -1465,13 +1465,13 @@
         <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3422502</v>
+        <v>1.3382813</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23559003</v>
+        <v>0.23490213</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25593394</v>
+        <v>0.25584736</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3357598</v>
+        <v>0.33598554</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.41898865</v>
+        <v>0.4193681</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7039456</v>
+        <v>3.6920083</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1672329</v>
+        <v>1.1652828</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22044258</v>
+        <v>0.22005862</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24709061</v>
+        <v>0.24731848</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>149</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32579517</v>
+        <v>0.32547945</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39879468</v>
+        <v>0.3989274</v>
       </c>
       <c r="K17" t="n">
         <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>1191</v>
+        <v>1200</v>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9994767</v>
+        <v>4.02053</v>
       </c>
       <c r="O17" t="n">
         <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.269563</v>
+        <v>1.2707901</v>
       </c>
       <c r="S17" t="n">
         <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23414023</v>
+        <v>0.23414837</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25599837</v>
+        <v>0.2565086</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3392283</v>
+        <v>0.33971632</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39873934</v>
+        <v>0.39919272</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="M18" t="n">
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5410976</v>
+        <v>3.5346458</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1666,13 +1666,13 @@
         <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1865499</v>
+        <v>1.185886</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22266194</v>
+        <v>0.22249793</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24557431</v>
+        <v>0.24514017</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31962547</v>
+        <v>0.31916058</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40675175</v>
+        <v>0.4065889</v>
       </c>
       <c r="K19" t="n">
         <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6642165</v>
+        <v>4.645464</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.377527</v>
+        <v>1.3733056</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25148475</v>
+        <v>0.25091577</v>
       </c>
       <c r="U19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2369453</v>
+        <v>0.2369338</v>
       </c>
       <c r="C20" t="n">
         <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G20" t="n">
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3069344</v>
+        <v>0.30719557</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39153767</v>
+        <v>0.3927034</v>
       </c>
       <c r="K20" t="n">
         <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>4.118763</v>
+        <v>4.124903</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P20" t="n">
         <v>161</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2972974</v>
+        <v>1.2967743</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23858495</v>
+        <v>0.23907718</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23350254</v>
+        <v>0.23371165</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G21" t="n">
         <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31145382</v>
+        <v>0.31171745</v>
       </c>
       <c r="I21" t="n">
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40630287</v>
+        <v>0.4064733</v>
       </c>
       <c r="K21" t="n">
         <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.225352</v>
+        <v>3.2237763</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1674491</v>
+        <v>1.1631702</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22353189</v>
+        <v>0.22291929</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24160099</v>
+        <v>0.24191888</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31173414</v>
+        <v>0.31182003</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3996267</v>
+        <v>0.40045294</v>
       </c>
       <c r="K22" t="n">
         <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9627216</v>
+        <v>3.976961</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2708551</v>
+        <v>1.2736216</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2444217</v>
+        <v>0.24476945</v>
       </c>
       <c r="U22" t="n">
         <v>17</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25176945</v>
+        <v>0.25325847</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3298006</v>
+        <v>0.33083913</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4010111</v>
+        <v>0.40304792</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.176989</v>
+        <v>4.1688113</v>
       </c>
       <c r="O23" t="n">
         <v>17</v>
       </c>
       <c r="P23" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3060378</v>
+        <v>1.3015954</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23709644</v>
+        <v>0.23677221</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23633678</v>
+        <v>0.23625682</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
         <v>159</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31362614</v>
+        <v>0.31368893</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38636842</v>
+        <v>0.38543853</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8954523</v>
+        <v>3.8961847</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q24" t="n">
         <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2859383</v>
+        <v>1.2831559</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24069427</v>
+        <v>0.2404485</v>
       </c>
       <c r="U24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24776241</v>
+        <v>0.2474727</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3087447</v>
+        <v>0.30852628</v>
       </c>
       <c r="I25" t="n">
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4068348</v>
+        <v>0.40699556</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="M25" t="n">
         <v>9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.36982</v>
+        <v>4.3462734</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
@@ -2135,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3588741</v>
+        <v>1.3579192</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24788266</v>
+        <v>0.24728094</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22923657</v>
+        <v>0.22939217</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G26" t="n">
         <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31019723</v>
+        <v>0.30986696</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37416106</v>
+        <v>0.3744796</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.197955</v>
+        <v>4.23874</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2498689</v>
+        <v>1.2535797</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25041288</v>
+        <v>0.25071692</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24367863</v>
+        <v>0.24311183</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
@@ -2239,43 +2239,43 @@
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3167939</v>
+        <v>0.3166065</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38662317</v>
+        <v>0.38512966</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2994075</v>
+        <v>4.286812</v>
       </c>
       <c r="O27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3527442</v>
+        <v>1.3513445</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2545196</v>
+        <v>0.25418937</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,43 +2288,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2601829</v>
+        <v>0.26056483</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3283582</v>
+        <v>0.32895467</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40295094</v>
+        <v>0.4050711</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L28" t="n">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8198903</v>
+        <v>3.8001556</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
@@ -2336,16 +2336,16 @@
         <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1542678</v>
+        <v>1.1508554</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23171493</v>
+        <v>0.23121507</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24310201</v>
+        <v>0.24346744</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G29" t="n">
         <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31732386</v>
+        <v>0.31788692</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39987457</v>
+        <v>0.400871</v>
       </c>
       <c r="K29" t="n">
         <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>1215</v>
+        <v>1231</v>
       </c>
       <c r="M29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2991815</v>
+        <v>4.2970634</v>
       </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3126485</v>
+        <v>1.3112217</v>
       </c>
       <c r="S29" t="n">
         <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24984603</v>
+        <v>0.24984716</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24765019</v>
+        <v>0.24812335</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G30" t="n">
         <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30917516</v>
+        <v>0.3093353</v>
       </c>
       <c r="I30" t="n">
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38291785</v>
+        <v>0.3836478</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9309542</v>
+        <v>3.9175656</v>
       </c>
       <c r="O30" t="n">
         <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2986811</v>
+        <v>1.2950693</v>
       </c>
       <c r="S30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23643893</v>
+        <v>0.23611683</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,43 +2489,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24819277</v>
+        <v>0.24790587</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32408732</v>
+        <v>0.3234928</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42811245</v>
+        <v>0.42879936</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1221</v>
+        <v>1232</v>
       </c>
       <c r="M31" t="n">
         <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7156105</v>
+        <v>4.721198</v>
       </c>
       <c r="O31" t="n">
         <v>28</v>
@@ -2537,13 +2537,13 @@
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3910356</v>
+        <v>1.390937</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2552335</v>
+        <v>0.25505507</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.20103092</v>
+        <v>0.21105528</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -2818,46 +2818,46 @@
         <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>0.26168224</v>
+        <v>0.28318584</v>
       </c>
       <c r="I2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.30927834</v>
+        <v>0.32663316</v>
       </c>
       <c r="K2" t="n">
         <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9454546</v>
+        <v>2.0526316</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1272727</v>
+        <v>1.0175439</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>0.23039216</v>
+        <v>0.2009804</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.26612905</v>
+        <v>0.25</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.34172663</v>
+        <v>0.30943397</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>0.48790324</v>
+        <v>0.48770493</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2786884</v>
+        <v>3.6290324</v>
       </c>
       <c r="O3" t="n">
         <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.409836</v>
+        <v>1.3225807</v>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26180258</v>
+        <v>0.25531915</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2934,61 +2934,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.22</v>
+        <v>0.20707071</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2764977</v>
+        <v>0.26511627</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.34848484</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.5961537</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>1.137255</v>
+        <v>1.0384616</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.21052632</v>
+        <v>0.20103092</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21030043</v>
+        <v>0.20600858</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2857143</v>
+        <v>0.2818533</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>0.32618025</v>
+        <v>0.3304721</v>
       </c>
       <c r="K5" t="n">
+        <v>27</v>
+      </c>
+      <c r="L5" t="n">
+        <v>70</v>
+      </c>
+      <c r="M5" t="n">
         <v>28</v>
       </c>
-      <c r="L5" t="n">
-        <v>71</v>
-      </c>
-      <c r="M5" t="n">
-        <v>29</v>
-      </c>
       <c r="N5" t="n">
-        <v>3.3926702</v>
+        <v>3.757732</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.209424</v>
+        <v>1.2525774</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="n">
-        <v>0.22857143</v>
+        <v>0.23387097</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2345679</v>
+        <v>0.21276596</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31365314</v>
+        <v>0.3018868</v>
       </c>
       <c r="I6" t="n">
         <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4238683</v>
+        <v>0.3744681</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4285715</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2063493</v>
+        <v>1.1746032</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.23504274</v>
+        <v>0.24242425</v>
       </c>
       <c r="U6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22222222</v>
+        <v>0.2246696</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
@@ -3150,49 +3150,49 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>0.31128404</v>
+        <v>0.32061067</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>0.36888888</v>
+        <v>0.36563876</v>
       </c>
       <c r="K7" t="n">
         <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
+        <v>14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.8423915</v>
+      </c>
+      <c r="O7" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
         <v>12</v>
       </c>
-      <c r="N7" t="n">
-        <v>5.7540984</v>
-      </c>
-      <c r="O7" t="n">
-        <v>29</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>16</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.4590164</v>
+        <v>1.4347826</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T7" t="n">
-        <v>0.25541127</v>
+        <v>0.25108224</v>
       </c>
       <c r="U7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.21428572</v>
+        <v>0.20618556</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31555554</v>
+        <v>0.28372094</v>
       </c>
       <c r="I8" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.38659793</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>57</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.326923</v>
+      </c>
+      <c r="O8" t="n">
         <v>17</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.38265306</v>
-      </c>
-      <c r="K8" t="n">
-        <v>19</v>
-      </c>
-      <c r="L8" t="n">
-        <v>56</v>
-      </c>
-      <c r="M8" t="n">
-        <v>16</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.9423077</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0769231</v>
+        <v>1.3076923</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>0.19791667</v>
+        <v>0.25980392</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.29064038</v>
+        <v>0.27450982</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3580786</v>
+        <v>0.34210527</v>
       </c>
       <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4852941</v>
+      </c>
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.49261084</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.8461537</v>
+      </c>
+      <c r="O9" t="n">
         <v>19</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.754717</v>
-      </c>
-      <c r="O9" t="n">
-        <v>17</v>
-      </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4528302</v>
+        <v>1.4807693</v>
       </c>
       <c r="S9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T9" t="n">
-        <v>0.22335026</v>
+        <v>0.22564103</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2248062</v>
+        <v>0.23484848</v>
       </c>
       <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I10" t="n">
         <v>20</v>
       </c>
-      <c r="D10" t="n">
-        <v>27</v>
-      </c>
-      <c r="E10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="J10" t="n">
+        <v>0.3598485</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" t="n">
+        <v>56</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.9315066</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23</v>
+      </c>
+      <c r="P10" t="n">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.2846975</v>
-      </c>
-      <c r="I10" t="n">
-        <v>26</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.36821705</v>
-      </c>
-      <c r="K10" t="n">
-        <v>21</v>
-      </c>
-      <c r="L10" t="n">
-        <v>53</v>
-      </c>
-      <c r="M10" t="n">
-        <v>13</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.3150687</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>14</v>
       </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>13</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.3835616</v>
+        <v>1.4520547</v>
       </c>
       <c r="S10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2508834</v>
+        <v>0.25874126</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.29444444</v>
+        <v>0.26553673</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
         <v>11</v>
@@ -3418,49 +3418,49 @@
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3469388</v>
+        <v>0.31413612</v>
       </c>
       <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4463277</v>
+      </c>
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.49444443</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5531917</v>
+        <v>6.0652175</v>
       </c>
       <c r="O11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.468085</v>
+        <v>1.5217391</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2857143</v>
+        <v>0.2956989</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.25</v>
+        <v>0.2421875</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>0.30985916</v>
+        <v>0.30107528</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3846154</v>
+        <v>0.3828125</v>
       </c>
       <c r="K12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M12" t="n">
         <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5927835</v>
+        <v>3.1522841</v>
       </c>
       <c r="O12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2525774</v>
+        <v>1.0659899</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2375</v>
+        <v>0.2112069</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2113402</v>
+        <v>0.24257426</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="n">
-        <v>27</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>25</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.28703704</v>
+        <v>0.3063063</v>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.34020618</v>
+        <v>0.4009901</v>
       </c>
       <c r="K13" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
         <v>2.290909</v>
       </c>
       <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
         <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.0909091</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>0.19689119</v>
+        <v>0.20618556</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.23175965</v>
+        <v>0.23012552</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
         <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31558937</v>
+        <v>0.32234433</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4248927</v>
+        <v>0.42677826</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>4.78125</v>
+        <v>4.2272725</v>
       </c>
       <c r="O14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.359375</v>
+        <v>1.4090909</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28286853</v>
+        <v>0.28235295</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2</v>
+        <v>0.22660099</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.27314815</v>
+      </c>
+      <c r="I15" t="n">
+        <v>27</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3497537</v>
+      </c>
+      <c r="K15" t="n">
+        <v>23</v>
+      </c>
+      <c r="L15" t="n">
+        <v>68</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.4230769</v>
+      </c>
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.24528302</v>
-      </c>
-      <c r="I15" t="n">
-        <v>30</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>30</v>
-      </c>
-      <c r="L15" t="n">
-        <v>65</v>
-      </c>
-      <c r="M15" t="n">
-        <v>26</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.4615386</v>
-      </c>
-      <c r="O15" t="n">
-        <v>9</v>
-      </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3269231</v>
+        <v>1.1153846</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>0.26020408</v>
+        <v>0.21808511</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -3738,34 +3738,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2236842</v>
+        <v>0.22171946</v>
       </c>
       <c r="C16" t="n">
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3490909</v>
+        <v>0.34962407</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.35964912</v>
+        <v>0.3800905</v>
       </c>
       <c r="K16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L16" t="n">
         <v>61</v>
@@ -3774,28 +3774,28 @@
         <v>22</v>
       </c>
       <c r="N16" t="n">
-        <v>5.203125</v>
+        <v>3.796875</v>
       </c>
       <c r="O16" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
         <v>10</v>
       </c>
-      <c r="Q16" t="n">
-        <v>23</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.375</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>0.28</v>
+        <v>0.25514403</v>
       </c>
       <c r="U16" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.23275863</v>
+        <v>0.23829788</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3219697</v>
+        <v>0.3181818</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>0.44827586</v>
+        <v>0.43829787</v>
       </c>
       <c r="K17" t="n">
         <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>5.516129</v>
+        <v>6.096774</v>
       </c>
       <c r="O17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6451613</v>
+        <v>1.7096775</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>0.29098362</v>
+        <v>0.29554656</v>
       </c>
       <c r="U17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.26859504</v>
+        <v>0.2644628</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3607143</v>
+        <v>0.35714287</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.41735536</v>
+        <v>0.3966942</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N18" t="n">
-        <v>4.95</v>
+        <v>4.8688526</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>10</v>
       </c>
       <c r="Q18" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.409836</v>
+      </c>
+      <c r="S18" t="n">
         <v>23</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>21</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.24017467</v>
+        <v>0.24242425</v>
       </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.23474178</v>
+        <v>0.20487805</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32786885</v>
+        <v>0.29310346</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>0.38967136</v>
+        <v>0.32682925</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N19" t="n">
         <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3888888</v>
+        <v>1.3518518</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24884793</v>
+        <v>0.23943663</v>
       </c>
       <c r="U19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2596154</v>
+        <v>0.2783019</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.35833332</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.504717</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>40</v>
       </c>
-      <c r="E20" t="n">
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
         <v>5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.34188035</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.45192307</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>43</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.264151</v>
       </c>
       <c r="O20" t="n">
         <v>24</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R20" t="n">
-        <v>1.245283</v>
+        <v>1.1481482</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>0.25728154</v>
+        <v>0.2415459</v>
       </c>
       <c r="U20" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -4073,40 +4073,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.26857144</v>
+        <v>0.24698795</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
+        <v>21</v>
+      </c>
+      <c r="E21" t="n">
         <v>23</v>
       </c>
-      <c r="E21" t="n">
-        <v>24</v>
-      </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3401015</v>
+        <v>0.3262032</v>
       </c>
       <c r="I21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3192771</v>
+      </c>
+      <c r="K21" t="n">
+        <v>30</v>
+      </c>
+      <c r="L21" t="n">
+        <v>52</v>
+      </c>
+      <c r="M21" t="n">
         <v>11</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.34857142</v>
-      </c>
-      <c r="K21" t="n">
-        <v>25</v>
-      </c>
-      <c r="L21" t="n">
-        <v>54</v>
-      </c>
-      <c r="M21" t="n">
-        <v>14</v>
       </c>
       <c r="N21" t="n">
         <v>2.3823528</v>
@@ -4115,19 +4115,19 @@
         <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8382353</v>
+        <v>0.7279412</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.17610063</v>
+        <v>0.1474359</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.21875</v>
+        <v>0.20526315</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.25853658</v>
+      </c>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3736842</v>
+      </c>
+      <c r="K22" t="n">
         <v>18</v>
-      </c>
-      <c r="E22" t="n">
-        <v>26</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>23</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.2783019</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.35416666</v>
-      </c>
-      <c r="K22" t="n">
-        <v>24</v>
       </c>
       <c r="L22" t="n">
         <v>47</v>
@@ -4176,28 +4176,28 @@
         <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3773584</v>
+        <v>3.2264152</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8113208</v>
+        <v>0.9622642</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0.17989418</v>
+        <v>0.2</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25</v>
+        <v>0.24736843</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -4225,46 +4225,46 @@
         <v>28</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34684685</v>
+        <v>0.33179724</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>0.33854166</v>
+        <v>0.3631579</v>
       </c>
       <c r="K23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9272728</v>
+        <v>2.4545455</v>
       </c>
       <c r="O23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
       </c>
       <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.90909094</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.2363636</v>
-      </c>
-      <c r="S23" t="n">
-        <v>11</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23115578</v>
+        <v>0.18848167</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2054054</v>
+        <v>0.2044199</v>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28846154</v>
+        <v>0.28780487</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4054054</v>
+        <v>0.3480663</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M24" t="n">
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5660377</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2075472</v>
+        <v>1.1111112</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
       </c>
       <c r="T24" t="n">
-        <v>0.22916667</v>
+        <v>0.21938775</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25619835</v>
+        <v>0.22413793</v>
       </c>
       <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>31</v>
+      </c>
+      <c r="E25" t="n">
         <v>12</v>
       </c>
-      <c r="D25" t="n">
-        <v>41</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3393502</v>
+        <v>0.29885057</v>
       </c>
       <c r="I25" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.40086207</v>
+      </c>
+      <c r="K25" t="n">
         <v>12</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.4214876</v>
-      </c>
-      <c r="K25" t="n">
-        <v>10</v>
-      </c>
       <c r="L25" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M25" t="n">
         <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>5.0265956</v>
+        <v>3.4285715</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4840425</v>
+        <v>1.2857143</v>
       </c>
       <c r="S25" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25514403</v>
+        <v>0.20779221</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2761905</v>
+        <v>0.25728154</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H26" t="n">
-        <v>0.36514524</v>
+        <v>0.3390558</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3857143</v>
+        <v>0.33495146</v>
       </c>
       <c r="K26" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
         <v>55</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>5.3333335</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2962962</v>
+        <v>1.3518518</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T26" t="n">
-        <v>0.27102804</v>
+        <v>0.27230048</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -4475,61 +4475,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3018868</v>
+        <v>0.27799228</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" t="n">
         <v>12</v>
       </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
       <c r="H27" t="n">
-        <v>0.34812286</v>
+        <v>0.33449477</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.49056605</v>
+        <v>0.4092664</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L27" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M27" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>5.6544504</v>
+        <v>5.1702127</v>
       </c>
       <c r="O27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5706806</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T27" t="n">
-        <v>0.27235773</v>
+        <v>0.26666668</v>
       </c>
       <c r="U27" t="n">
         <v>25</v>
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26190478</v>
+        <v>0.24766356</v>
       </c>
       <c r="C28" t="n">
         <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>0.31304348</v>
+        <v>0.31512606</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40952381</v>
+        <v>0.42056075</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.09434</v>
+        <v>4.924528</v>
       </c>
       <c r="O28" t="n">
         <v>22</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3584906</v>
+        <v>1.3396226</v>
       </c>
       <c r="S28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T28" t="n">
-        <v>0.24878049</v>
+        <v>0.25603864</v>
       </c>
       <c r="U28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -4609,43 +4609,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.27</v>
+        <v>0.25853658</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>13</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.32456142</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.47804877</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>53</v>
+      </c>
+      <c r="M29" t="n">
         <v>12</v>
       </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.32735425</v>
-      </c>
-      <c r="I29" t="n">
-        <v>14</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6</v>
-      </c>
       <c r="N29" t="n">
-        <v>5.072727</v>
+        <v>4.909091</v>
       </c>
       <c r="O29" t="n">
         <v>21</v>
@@ -4654,16 +4654,16 @@
         <v>11</v>
       </c>
       <c r="Q29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5272727</v>
+        <v>1.3818182</v>
       </c>
       <c r="S29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2764977</v>
+        <v>0.26728112</v>
       </c>
       <c r="U29" t="n">
         <v>26</v>
@@ -4676,61 +4676,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.28</v>
+        <v>0.30588236</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
         <v>9</v>
       </c>
-      <c r="F30" t="n">
-        <v>7</v>
-      </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3429603</v>
+        <v>0.36298934</v>
       </c>
       <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.45490196</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>40</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.0648649</v>
+      </c>
+      <c r="O30" t="n">
         <v>8</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="K30" t="n">
-        <v>13</v>
-      </c>
-      <c r="L30" t="n">
-        <v>48</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
         <v>8</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.7087913</v>
-      </c>
-      <c r="O30" t="n">
-        <v>11</v>
-      </c>
-      <c r="P30" t="n">
-        <v>9</v>
-      </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1703297</v>
+        <v>1.0864865</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>0.21145375</v>
+        <v>0.20175439</v>
       </c>
       <c r="U30" t="n">
         <v>6</v>
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23880596</v>
+        <v>0.215</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
+        <v>27</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2685185</v>
+      </c>
+      <c r="I31" t="n">
         <v>28</v>
       </c>
-      <c r="H31" t="n">
-        <v>0.3080357</v>
-      </c>
-      <c r="I31" t="n">
-        <v>22</v>
-      </c>
       <c r="J31" t="n">
-        <v>0.3681592</v>
+        <v>0.37</v>
       </c>
       <c r="K31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>6.12</v>
+        <v>6.244898</v>
       </c>
       <c r="O31" t="n">
         <v>30</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.5102041</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2538071</v>
+        <v>0.25263157</v>
       </c>
       <c r="U31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24202128</v>
+        <v>0.2422272</v>
       </c>
       <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>648</v>
+      </c>
+      <c r="E2" t="n">
         <v>18</v>
       </c>
-      <c r="D2" t="n">
-        <v>646</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17</v>
-      </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31421265</v>
+        <v>0.31446198</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39320785</v>
+        <v>0.39300954</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0946884</v>
+        <v>4.097169</v>
       </c>
       <c r="O2" t="n">
         <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q2" t="n">
         <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2786759</v>
+        <v>1.2785004</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24822406</v>
+        <v>0.24818403</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24571313</v>
+        <v>0.24513541</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31873304</v>
+        <v>0.3180918</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40346983</v>
+        <v>0.40260783</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.388846</v>
+        <v>5.3515387</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4918668</v>
+        <v>1.4884615</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26878726</v>
+        <v>0.26832643</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,64 +680,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24662852</v>
+        <v>0.24583502</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3099426</v>
+        <v>0.30922142</v>
       </c>
       <c r="I4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.409481</v>
+        <v>0.40857375</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.569207</v>
+        <v>3.5930502</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q4" t="n">
         <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2457231</v>
+        <v>1.2471043</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23201664</v>
+        <v>0.23250052</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23374486</v>
+        <v>0.23421215</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31573197</v>
+        <v>0.31609404</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39382717</v>
+        <v>0.3940323</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.142674</v>
+        <v>4.148563</v>
       </c>
       <c r="O5" t="n">
         <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3417008</v>
+        <v>1.3408802</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25330928</v>
+        <v>0.25328556</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24790859</v>
+        <v>0.24777147</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G6" t="n">
         <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32219398</v>
+        <v>0.32184738</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40399918</v>
+        <v>0.40397084</v>
       </c>
       <c r="K6" t="n">
         <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6087737</v>
+        <v>3.625223</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2360184</v>
+        <v>1.2382165</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24194206</v>
+        <v>0.24280502</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2510943</v>
+        <v>0.25059336</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -899,46 +899,46 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33912438</v>
+        <v>0.33891574</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.42996418</v>
+        <v>0.42879745</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>4.203221</v>
+        <v>4.21875</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.268405</v>
+        <v>1.2690549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2450264</v>
+        <v>0.24511187</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23619442</v>
+        <v>0.23623665</v>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31838155</v>
+        <v>0.31854546</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40661842</v>
+        <v>0.40653247</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>1313</v>
+        <v>1327</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.145752</v>
+        <v>4.144737</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3102105</v>
+        <v>1.3111455</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2410437</v>
+        <v>0.24141477</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2299565</v>
+        <v>0.22967689</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30871248</v>
+        <v>0.3081289</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3981769</v>
+        <v>0.39740688</v>
       </c>
       <c r="K9" t="n">
         <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>1383</v>
+        <v>1396</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6645913</v>
+        <v>4.7331786</v>
       </c>
       <c r="O9" t="n">
+        <v>27</v>
+      </c>
+      <c r="P9" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q9" t="n">
         <v>26</v>
       </c>
-      <c r="P9" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>25</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.4272374</v>
+        <v>1.4338747</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2512685</v>
+        <v>0.25216517</v>
       </c>
       <c r="U9" t="n">
         <v>24</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23663652</v>
+        <v>0.23673469</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G10" t="n">
         <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31401938</v>
+        <v>0.31409907</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37191612</v>
+        <v>0.37244898</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7729259</v>
+        <v>3.8049529</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2638068</v>
+        <v>1.2660199</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23675056</v>
+        <v>0.23719512</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25311542</v>
+        <v>0.25253755</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G11" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3229757</v>
+        <v>0.32243416</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41593462</v>
+        <v>0.41555014</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1259</v>
+        <v>1270</v>
       </c>
       <c r="M11" t="n">
         <v>22</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4639473</v>
+        <v>5.4720187</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.518158</v>
+        <v>1.516475</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28738597</v>
+        <v>0.28700966</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23773508</v>
+        <v>0.23775655</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3134111</v>
+        <v>0.31397033</v>
       </c>
       <c r="I12" t="n">
         <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39513493</v>
+        <v>0.39524487</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>1265</v>
+        <v>1275</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6770427</v>
+        <v>3.6653786</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2241246</v>
+        <v>1.2210201</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23251458</v>
+        <v>0.23210591</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24030371</v>
+        <v>0.24093686</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31500825</v>
+        <v>0.315071</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40837267</v>
+        <v>0.40977597</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5128074</v>
+        <v>4.5474415</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3505821</v>
+        <v>1.3545898</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23813471</v>
+        <v>0.23883975</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24663402</v>
+        <v>0.24660312</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31606883</v>
+        <v>0.31604803</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40146878</v>
+        <v>0.40174407</v>
       </c>
       <c r="K14" t="n">
         <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6701193</v>
+        <v>4.6446385</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3928016</v>
+        <v>1.3931601</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25830108</v>
+        <v>0.2583974</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23437178</v>
+        <v>0.23529412</v>
       </c>
       <c r="C15" t="n">
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" t="n">
+        <v>141</v>
+      </c>
+      <c r="G15" t="n">
+        <v>27</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.30906418</v>
+      </c>
+      <c r="I15" t="n">
+        <v>26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.37261733</v>
+      </c>
+      <c r="K15" t="n">
         <v>29</v>
       </c>
-      <c r="F15" t="n">
-        <v>138</v>
-      </c>
-      <c r="G15" t="n">
-        <v>28</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.30829015</v>
-      </c>
-      <c r="I15" t="n">
-        <v>29</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.37053847</v>
-      </c>
-      <c r="K15" t="n">
-        <v>30</v>
-      </c>
       <c r="L15" t="n">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.197656</v>
+        <v>4.196276</v>
       </c>
       <c r="O15" t="n">
         <v>18</v>
       </c>
       <c r="P15" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q15" t="n">
         <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3382813</v>
+        <v>1.3366951</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23490213</v>
+        <v>0.23485632</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25584736</v>
+        <v>0.25671825</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33598554</v>
+        <v>0.33692142</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4193681</v>
+        <v>0.42223126</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6920083</v>
+        <v>3.67328</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1652828</v>
+        <v>1.162587</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22005862</v>
+        <v>0.21984193</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24731848</v>
+        <v>0.24902962</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32547945</v>
+        <v>0.32706222</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3989274</v>
+        <v>0.40122575</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4.02053</v>
+        <v>4.097032</v>
       </c>
       <c r="O17" t="n">
         <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q17" t="n">
         <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2707901</v>
+        <v>1.2781936</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23414837</v>
+        <v>0.23525786</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2565086</v>
+        <v>0.25651303</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33971632</v>
+        <v>0.33943984</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39919272</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" t="n">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="M18" t="n">
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5346458</v>
+        <v>3.5446928</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1663,16 +1663,16 @@
         <v>156</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.185886</v>
+        <v>1.1853733</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22249793</v>
+        <v>0.22215372</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24514017</v>
+        <v>0.24466138</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31916058</v>
+        <v>0.31870124</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4065889</v>
+        <v>0.40634534</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.645464</v>
+        <v>4.665544</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3733056</v>
+        <v>1.3764249</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25091577</v>
+        <v>0.2508598</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2369338</v>
+        <v>0.23800813</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G20" t="n">
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30719557</v>
+        <v>0.30859232</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3927034</v>
+        <v>0.3941057</v>
       </c>
       <c r="K20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L20" t="n">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="M20" t="n">
         <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>4.124903</v>
+        <v>4.1932344</v>
       </c>
       <c r="O20" t="n">
+        <v>17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q20" t="n">
         <v>14</v>
       </c>
-      <c r="P20" t="n">
-        <v>161</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>13</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.2967743</v>
+        <v>1.3062532</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23907718</v>
+        <v>0.24084935</v>
       </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23371165</v>
+        <v>0.23366047</v>
       </c>
       <c r="C21" t="n">
         <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31171745</v>
+        <v>0.31160632</v>
       </c>
       <c r="I21" t="n">
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4064733</v>
+        <v>0.40780956</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2237763</v>
+        <v>3.2083333</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1631702</v>
+        <v>1.1612654</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22291929</v>
+        <v>0.22252233</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24191888</v>
+        <v>0.24259146</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31182003</v>
+        <v>0.31246567</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40045294</v>
+        <v>0.40138975</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L22" t="n">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.976961</v>
+        <v>3.9979434</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2736216</v>
+        <v>1.274036</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24476945</v>
+        <v>0.24536291</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25325847</v>
+        <v>0.25353515</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G23" t="n">
         <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33083913</v>
+        <v>0.33109185</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40304792</v>
+        <v>0.4029078</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1688113</v>
+        <v>4.1538463</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3015954</v>
+        <v>1.3010478</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23677221</v>
+        <v>0.23681006</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23625682</v>
+        <v>0.23771857</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31368893</v>
+        <v>0.3148251</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38543853</v>
+        <v>0.38780183</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8961847</v>
+        <v>3.8829896</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q24" t="n">
         <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2831559</v>
+        <v>1.2796391</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2404485</v>
+        <v>0.23973592</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2474727</v>
+        <v>0.24789073</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>166</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30852628</v>
+        <v>0.30880204</v>
       </c>
       <c r="I25" t="n">
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40699556</v>
+        <v>0.40699077</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="M25" t="n">
         <v>9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3462734</v>
+        <v>4.3438706</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3579192</v>
+        <v>1.3569776</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24728094</v>
+        <v>0.24729867</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22939217</v>
+        <v>0.22920977</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
@@ -2172,43 +2172,43 @@
         <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>0.30986696</v>
+        <v>0.30964187</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3744796</v>
+        <v>0.3740174</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>4.23874</v>
+        <v>4.2231126</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q26" t="n">
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2535797</v>
+        <v>1.2525853</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25071692</v>
+        <v>0.2504578</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24311183</v>
+        <v>0.2431562</v>
       </c>
       <c r="C27" t="n">
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G27" t="n">
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3166065</v>
+        <v>0.3167802</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38512966</v>
+        <v>0.38506442</v>
       </c>
       <c r="K27" t="n">
         <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.286812</v>
+        <v>4.30873</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P27" t="n">
         <v>146</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3513445</v>
+        <v>1.351489</v>
       </c>
       <c r="S27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25418937</v>
+        <v>0.2545637</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26056483</v>
+        <v>0.26085177</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G28" t="n">
         <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32895467</v>
+        <v>0.3292302</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4050711</v>
+        <v>0.40499592</v>
       </c>
       <c r="K28" t="n">
         <v>11</v>
       </c>
       <c r="L28" t="n">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8001556</v>
+        <v>3.7876449</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q28" t="n">
         <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1508554</v>
+        <v>1.1474904</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23121507</v>
+        <v>0.2305001</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,46 +2355,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24346744</v>
+        <v>0.24325438</v>
       </c>
       <c r="C29" t="n">
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G29" t="n">
         <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31788692</v>
+        <v>0.31762105</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.400871</v>
+        <v>0.4008239</v>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="M29" t="n">
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2970634</v>
+        <v>4.2912974</v>
       </c>
       <c r="O29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P29" t="n">
         <v>175</v>
@@ -2403,13 +2403,13 @@
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3112217</v>
+        <v>1.3100573</v>
       </c>
       <c r="S29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24984716</v>
+        <v>0.24954426</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24812335</v>
+        <v>0.24778226</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
         <v>589</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>140</v>
       </c>
       <c r="G30" t="n">
+        <v>28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.30905765</v>
+      </c>
+      <c r="I30" t="n">
         <v>27</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.3093353</v>
-      </c>
-      <c r="I30" t="n">
-        <v>26</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.3836478</v>
+        <v>0.38266128</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1044</v>
+        <v>1053</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9175656</v>
+        <v>3.9073508</v>
       </c>
       <c r="O30" t="n">
         <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q30" t="n">
         <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2950693</v>
+        <v>1.2917305</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23611683</v>
+        <v>0.23558283</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24790587</v>
+        <v>0.24717543</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3234928</v>
+        <v>0.32278594</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42879936</v>
+        <v>0.42755204</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.721198</v>
+        <v>4.7541986</v>
       </c>
       <c r="O31" t="n">
         <v>28</v>
       </c>
       <c r="P31" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.390937</v>
+        <v>1.3969465</v>
       </c>
       <c r="S31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25505507</v>
+        <v>0.25630838</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.21105528</v>
+        <v>0.23529412</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.28318584</v>
+        <v>0.3148936</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>0.32663316</v>
+        <v>0.3480392</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.0526316</v>
+        <v>2.732143</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0175439</v>
+        <v>1.125</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2009804</v>
+        <v>0.22058824</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.25</v>
+        <v>0.21982759</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.27309236</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4051724</v>
+      </c>
+      <c r="K3" t="n">
         <v>16</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.30943397</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.48770493</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6290324</v>
+        <v>3.3387096</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3225807</v>
+        <v>1.3064516</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25531915</v>
+        <v>0.24892704</v>
       </c>
       <c r="U3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.20707071</v>
+        <v>0.17460318</v>
       </c>
       <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
         <v>25</v>
       </c>
-      <c r="D4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.26511627</v>
+        <v>0.2254902</v>
       </c>
       <c r="I4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>0.34848484</v>
+        <v>0.3015873</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.8076923</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" t="n">
         <v>10</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.5961537</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>9</v>
-      </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0384616</v>
+        <v>1.2115384</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>0.20103092</v>
+        <v>0.23737374</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.20600858</v>
+        <v>0.21524663</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2818533</v>
+        <v>0.29482073</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3304721</v>
+        <v>0.35874438</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>3.757732</v>
+        <v>3.857143</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2525774</v>
+        <v>1.2380953</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23387097</v>
+        <v>0.22727273</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.21276596</v>
+        <v>0.19742489</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.29166666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.35193133</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L6" t="n">
+        <v>69</v>
+      </c>
+      <c r="M6" t="n">
+        <v>27</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.857143</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1269841</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.24778761</v>
+      </c>
+      <c r="U6" t="n">
         <v>18</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3018868</v>
-      </c>
-      <c r="I6" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.3744681</v>
-      </c>
-      <c r="K6" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" t="n">
-        <v>66</v>
-      </c>
-      <c r="M6" t="n">
-        <v>26</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1746032</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.24242425</v>
-      </c>
-      <c r="U6" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2246696</v>
+        <v>0.22321428</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32061067</v>
+        <v>0.32307693</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>0.36563876</v>
+        <v>0.35267857</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8423915</v>
+        <v>4.475138</v>
       </c>
       <c r="O7" t="n">
+        <v>19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
         <v>18</v>
       </c>
-      <c r="P7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>1.3259668</v>
+      </c>
+      <c r="S7" t="n">
+        <v>19</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.23348017</v>
+      </c>
+      <c r="U7" t="n">
         <v>12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4347826</v>
-      </c>
-      <c r="S7" t="n">
-        <v>24</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.25108224</v>
-      </c>
-      <c r="U7" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20618556</v>
+        <v>0.22727273</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.28372094</v>
+        <v>0.30454546</v>
       </c>
       <c r="I8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>0.38659793</v>
+        <v>0.41919193</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.326923</v>
+        <v>4.5849056</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3076923</v>
+        <v>1.3396226</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.25980392</v>
+        <v>0.2705314</v>
       </c>
       <c r="U8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.27450982</v>
+        <v>0.25742576</v>
       </c>
       <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>36</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.34210527</v>
+        <v>0.32589287</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4852941</v>
+        <v>0.43564355</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8461537</v>
+        <v>6.882353</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4807693</v>
+        <v>1.6862745</v>
       </c>
       <c r="S9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.22564103</v>
+        <v>0.25373134</v>
       </c>
       <c r="U9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23484848</v>
+        <v>0.24253732</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0.3131313</v>
       </c>
       <c r="I10" t="n">
+        <v>18</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3880597</v>
+      </c>
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.3598485</v>
-      </c>
-      <c r="K10" t="n">
-        <v>22</v>
-      </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
         <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9315066</v>
+        <v>5.25</v>
       </c>
       <c r="O10" t="n">
         <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4520547</v>
+        <v>1.4166666</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T10" t="n">
-        <v>0.25874126</v>
+        <v>0.24909747</v>
       </c>
       <c r="U10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.26553673</v>
+        <v>0.24096386</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.29834256</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.42771083</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>17</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.31413612</v>
-      </c>
-      <c r="I11" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4463277</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>56</v>
-      </c>
-      <c r="M11" t="n">
-        <v>16</v>
-      </c>
       <c r="N11" t="n">
-        <v>6.0652175</v>
+        <v>6.9069767</v>
       </c>
       <c r="O11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5217391</v>
+        <v>1.5581396</v>
       </c>
       <c r="S11" t="n">
+        <v>27</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.29885057</v>
+      </c>
+      <c r="U11" t="n">
         <v>29</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.2956989</v>
-      </c>
-      <c r="U11" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2421875</v>
+        <v>0.23305085</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.30107528</v>
+        <v>0.30152673</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3828125</v>
+        <v>0.3644068</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M12" t="n">
         <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1522841</v>
+        <v>3.0159574</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.0212766</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.20737328</v>
+      </c>
+      <c r="U12" t="n">
         <v>6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>10</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.0659899</v>
-      </c>
-      <c r="S12" t="n">
-        <v>7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.2112069</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24257426</v>
+        <v>0.2596154</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3080357</v>
+      </c>
+      <c r="I13" t="n">
         <v>20</v>
       </c>
-      <c r="F13" t="n">
+      <c r="J13" t="n">
+        <v>0.45673078</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>49</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.8333333</v>
+      </c>
+      <c r="O13" t="n">
+        <v>14</v>
+      </c>
+      <c r="P13" t="n">
         <v>6</v>
       </c>
-      <c r="G13" t="n">
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2037038</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.24378109</v>
+      </c>
+      <c r="U13" t="n">
         <v>17</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3063063</v>
-      </c>
-      <c r="I13" t="n">
-        <v>17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.4009901</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11</v>
-      </c>
-      <c r="L13" t="n">
-        <v>48</v>
-      </c>
-      <c r="M13" t="n">
-        <v>8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.290909</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.20618556</v>
-      </c>
-      <c r="U13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.23012552</v>
+        <v>0.22844827</v>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.32234433</v>
+        <v>0.31558937</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.42677826</v>
+        <v>0.40948275</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.2727273</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" t="n">
         <v>6</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.2272725</v>
-      </c>
-      <c r="O14" t="n">
-        <v>16</v>
-      </c>
-      <c r="P14" t="n">
-        <v>8</v>
-      </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4090909</v>
+        <v>1.3787879</v>
       </c>
       <c r="S14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28235295</v>
+        <v>0.27309236</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.22660099</v>
+        <v>0.26865673</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.32258064</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.41293532</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>60</v>
+      </c>
+      <c r="M15" t="n">
+        <v>22</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.2941177</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.0784314</v>
+      </c>
+      <c r="S15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="n">
-        <v>23</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.27314815</v>
-      </c>
-      <c r="I15" t="n">
-        <v>27</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.3497537</v>
-      </c>
-      <c r="K15" t="n">
-        <v>23</v>
-      </c>
-      <c r="L15" t="n">
-        <v>68</v>
-      </c>
-      <c r="M15" t="n">
-        <v>27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.4230769</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.1153846</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.21808511</v>
+        <v>0.2021858</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.22171946</v>
+        <v>0.23636363</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
+        <v>0.35496184</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.42727274</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>58</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
         <v>7</v>
       </c>
-      <c r="G16" t="n">
+      <c r="P16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.2063493</v>
+      </c>
+      <c r="S16" t="n">
         <v>12</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.34962407</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.3800905</v>
-      </c>
-      <c r="K16" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" t="n">
-        <v>61</v>
-      </c>
-      <c r="M16" t="n">
-        <v>22</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.796875</v>
-      </c>
-      <c r="O16" t="n">
-        <v>15</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>10</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>13</v>
-      </c>
       <c r="T16" t="n">
-        <v>0.25514403</v>
+        <v>0.24789916</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.23829788</v>
+        <v>0.25925925</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.34306568</v>
+      </c>
+      <c r="I17" t="n">
         <v>5</v>
       </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.3181818</v>
-      </c>
-      <c r="I17" t="n">
-        <v>13</v>
-      </c>
       <c r="J17" t="n">
-        <v>0.43829787</v>
+        <v>0.44032922</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N17" t="n">
-        <v>6.096774</v>
+        <v>7.403226</v>
       </c>
       <c r="O17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7096775</v>
+        <v>1.8064516</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>0.29554656</v>
+        <v>0.31349206</v>
       </c>
       <c r="U17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2644628</v>
+        <v>0.24789916</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>0.35714287</v>
+        <v>0.3345588</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3966942</v>
+        <v>0.39915967</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N18" t="n">
         <v>4.8688526</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.409836</v>
+        <v>1.3934426</v>
       </c>
       <c r="S18" t="n">
         <v>23</v>
       </c>
       <c r="T18" t="n">
-        <v>0.24242425</v>
+        <v>0.24122807</v>
       </c>
       <c r="U18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.20487805</v>
+        <v>0.2</v>
       </c>
       <c r="C19" t="n">
+        <v>28</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E19" t="n">
         <v>29</v>
       </c>
-      <c r="D19" t="n">
-        <v>21</v>
-      </c>
-      <c r="E19" t="n">
-        <v>23</v>
-      </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H19" t="n">
-        <v>0.29310346</v>
+        <v>0.28169015</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>0.32682925</v>
+        <v>0.35263157</v>
       </c>
       <c r="K19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L19" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P19" t="n">
         <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3518518</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>0.23943663</v>
+        <v>0.22797927</v>
       </c>
       <c r="U19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2783019</v>
+        <v>0.28301886</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.35833332</v>
+        <v>0.36885247</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.504717</v>
+        <v>0.5141509</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>6.6666665</v>
       </c>
       <c r="O20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1481482</v>
+        <v>1.425926</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2415459</v>
+        <v>0.28636363</v>
       </c>
       <c r="U20" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24698795</v>
+        <v>0.22929937</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.32222223</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.36942676</v>
+      </c>
+      <c r="K21" t="n">
+        <v>22</v>
+      </c>
+      <c r="L21" t="n">
+        <v>47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.2330828</v>
+      </c>
+      <c r="O21" t="n">
         <v>2</v>
       </c>
-      <c r="G21" t="n">
-        <v>29</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.3262032</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="P21" t="n">
         <v>9</v>
       </c>
-      <c r="J21" t="n">
-        <v>0.3192771</v>
-      </c>
-      <c r="K21" t="n">
-        <v>30</v>
-      </c>
-      <c r="L21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M21" t="n">
-        <v>11</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.3823528</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7279412</v>
+        <v>0.8345865</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1474359</v>
+        <v>0.15686275</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.20526315</v>
+        <v>0.24365482</v>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.25853658</v>
+        <v>0.2990654</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3736842</v>
+        <v>0.43654823</v>
       </c>
       <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>50</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.1666665</v>
+      </c>
+      <c r="O22" t="n">
         <v>18</v>
       </c>
-      <c r="L22" t="n">
-        <v>47</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>18</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.1111112</v>
+      </c>
+      <c r="S22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.2264152</v>
-      </c>
-      <c r="O22" t="n">
-        <v>10</v>
-      </c>
-      <c r="P22" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>14</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.9622642</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
       <c r="T22" t="n">
-        <v>0.2</v>
+        <v>0.23529412</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -4207,46 +4207,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.24736843</v>
+        <v>0.2620321</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33179724</v>
+        <v>0.342723</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3631579</v>
+        <v>0.37967914</v>
       </c>
       <c r="K23" t="n">
         <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4545455</v>
+        <v>2.1666667</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -4255,16 +4255,16 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.90909094</v>
+        <v>0.9259259</v>
       </c>
       <c r="S23" t="n">
         <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>0.18848167</v>
+        <v>0.19371727</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2044199</v>
+        <v>0.24598931</v>
       </c>
       <c r="C24" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
         <v>12</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28780487</v>
+        <v>0.31904763</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3480663</v>
+        <v>0.4171123</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.6181817</v>
+      </c>
+      <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>12</v>
-      </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1111112</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>0.21938775</v>
+        <v>0.19170985</v>
       </c>
       <c r="U24" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.22413793</v>
+        <v>0.23809524</v>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.30859375</v>
+      </c>
+      <c r="I25" t="n">
+        <v>19</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4069264</v>
+      </c>
+      <c r="K25" t="n">
+        <v>14</v>
+      </c>
+      <c r="L25" t="n">
+        <v>61</v>
+      </c>
+      <c r="M25" t="n">
+        <v>23</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.6290324</v>
+      </c>
+      <c r="O25" t="n">
         <v>12</v>
       </c>
-      <c r="F25" t="n">
+      <c r="P25" t="n">
         <v>10</v>
       </c>
-      <c r="G25" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.29885057</v>
-      </c>
-      <c r="I25" t="n">
-        <v>21</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.40086207</v>
-      </c>
-      <c r="K25" t="n">
-        <v>12</v>
-      </c>
-      <c r="L25" t="n">
-        <v>58</v>
-      </c>
-      <c r="M25" t="n">
-        <v>19</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.4285715</v>
-      </c>
-      <c r="O25" t="n">
-        <v>11</v>
-      </c>
-      <c r="P25" t="n">
-        <v>9</v>
-      </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2857143</v>
+        <v>1.2741935</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T25" t="n">
-        <v>0.20779221</v>
+        <v>0.21238938</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.25728154</v>
+        <v>0.2361809</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
       </c>
       <c r="G26" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.31390134</v>
+      </c>
+      <c r="I26" t="n">
+        <v>17</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.32663316</v>
+      </c>
+      <c r="K26" t="n">
         <v>29</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.3390558</v>
-      </c>
-      <c r="I26" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.33495146</v>
-      </c>
-      <c r="K26" t="n">
-        <v>26</v>
-      </c>
       <c r="L26" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3333335</v>
+        <v>5.1666665</v>
       </c>
       <c r="O26" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="n">
         <v>30</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3518518</v>
+        <v>1.2962962</v>
       </c>
       <c r="S26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T26" t="n">
-        <v>0.27230048</v>
+        <v>0.25358853</v>
       </c>
       <c r="U26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.27799228</v>
+        <v>0.27952754</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.33449477</v>
+        <v>0.34385964</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4092664</v>
+        <v>0.39370078</v>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L27" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N27" t="n">
-        <v>5.1702127</v>
+        <v>5.6373625</v>
       </c>
       <c r="O27" t="n">
         <v>25</v>
       </c>
       <c r="P27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.4505494</v>
       </c>
       <c r="S27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T27" t="n">
-        <v>0.26666668</v>
+        <v>0.27038628</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.24766356</v>
+        <v>0.26291078</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>0.31512606</v>
+        <v>0.33333334</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.42056075</v>
+        <v>0.43192488</v>
       </c>
       <c r="K28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.924528</v>
+        <v>4.075472</v>
       </c>
       <c r="O28" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
         <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3396226</v>
+        <v>1.1132076</v>
       </c>
       <c r="S28" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>0.25603864</v>
+        <v>0.21649484</v>
       </c>
       <c r="U28" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.25853658</v>
+        <v>0.25365853</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
         <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32456142</v>
+        <v>0.3231441</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>0.47804877</v>
+        <v>0.47317073</v>
       </c>
       <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>52</v>
+      </c>
+      <c r="M29" t="n">
+        <v>13</v>
+      </c>
+      <c r="N29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" t="n">
-        <v>53</v>
-      </c>
-      <c r="M29" t="n">
-        <v>12</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.909091</v>
-      </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3818182</v>
+        <v>1.2222222</v>
       </c>
       <c r="S29" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T29" t="n">
-        <v>0.26728112</v>
+        <v>0.2415459</v>
       </c>
       <c r="U29" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.30588236</v>
+        <v>0.28278688</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.34686348</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4057377</v>
+      </c>
+      <c r="K30" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>41</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.412088</v>
+      </c>
+      <c r="O30" t="n">
+        <v>11</v>
+      </c>
+      <c r="P30" t="n">
         <v>9</v>
       </c>
-      <c r="G30" t="n">
-        <v>9</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.36298934</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.45490196</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>40</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.0648649</v>
-      </c>
-      <c r="O30" t="n">
-        <v>8</v>
-      </c>
-      <c r="P30" t="n">
-        <v>8</v>
-      </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.0864865</v>
+        <v>1.1043956</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T30" t="n">
-        <v>0.20175439</v>
+        <v>0.19642857</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.215</v>
+        <v>0.22277227</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2685185</v>
+        <v>0.27853882</v>
       </c>
       <c r="I31" t="n">
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>0.37</v>
+        <v>0.3910891</v>
       </c>
       <c r="K31" t="n">
         <v>19</v>
       </c>
       <c r="L31" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N31" t="n">
-        <v>6.244898</v>
+        <v>6.375</v>
       </c>
       <c r="O31" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
         <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5102041</v>
+        <v>1.5833334</v>
       </c>
       <c r="S31" t="n">
         <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25263157</v>
+        <v>0.27748692</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -549,7 +549,7 @@
         <v>0.2422272</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>648</v>
@@ -634,13 +634,13 @@
         <v>0.3180918</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
         <v>0.40260783</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
         <v>1256</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24583502</v>
+        <v>0.24580893</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
@@ -698,46 +698,46 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.30922142</v>
+        <v>0.30886123</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40857375</v>
+        <v>0.40820035</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5930502</v>
+        <v>3.5751534</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q4" t="n">
         <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2471043</v>
+        <v>1.2446319</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23250052</v>
+        <v>0.2320476</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -750,13 +750,13 @@
         <v>0.23421215</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>661</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>176</v>
@@ -786,7 +786,7 @@
         <v>4.148563</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
         <v>157</v>
@@ -914,13 +914,13 @@
         <v>1243</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
         <v>4.21875</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
         <v>221</v>
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23623665</v>
+        <v>0.23524606</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
         <v>685</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
         <v>190</v>
@@ -966,43 +966,43 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31854546</v>
+        <v>0.31748328</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40653247</v>
+        <v>0.4047376</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>1327</v>
+        <v>1338</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.144737</v>
+        <v>4.1299</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3111455</v>
+        <v>1.3082244</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24141477</v>
+        <v>0.2412666</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1121,13 +1121,13 @@
         <v>3.8049529</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
         <v>163</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
         <v>1.2660199</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25253755</v>
+        <v>0.2523176</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G11" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32243416</v>
+        <v>0.32239452</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41555014</v>
+        <v>0.41535673</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4720187</v>
+        <v>5.508056</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.516475</v>
+        <v>1.5194907</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28700966</v>
+        <v>0.28725278</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1231,7 +1231,7 @@
         <v>164</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
         <v>0.31397033</v>
@@ -1249,7 +1249,7 @@
         <v>1275</v>
       </c>
       <c r="M12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
         <v>3.6653786</v>
@@ -1264,16 +1264,16 @@
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2210201</v>
+        <v>1.2217929</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23210591</v>
+        <v>0.23231278</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24093686</v>
+        <v>0.2409468</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.315071</v>
+        <v>0.31500903</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40977597</v>
+        <v>0.40967023</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5474415</v>
+        <v>4.5229826</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3545898</v>
+        <v>1.3483145</v>
       </c>
       <c r="S13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23883975</v>
+        <v>0.2380855</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1365,7 +1365,7 @@
         <v>154</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
         <v>0.31604803</v>
@@ -1420,7 +1420,7 @@
         <v>0.23529412</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
         <v>591</v>
@@ -1438,7 +1438,7 @@
         <v>0.30906418</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
         <v>0.37261733</v>
@@ -1529,13 +1529,13 @@
         <v>163</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
         <v>1.162587</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
         <v>0.21984193</v>
@@ -1578,7 +1578,7 @@
         <v>0.40122575</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
         <v>1207</v>
@@ -1645,7 +1645,7 @@
         <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L18" t="n">
         <v>1238</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24466138</v>
+        <v>0.24486476</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
@@ -1703,16 +1703,16 @@
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31870124</v>
+        <v>0.31888264</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40634534</v>
+        <v>0.4065487</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
         <v>1157</v>
@@ -1797,7 +1797,7 @@
         <v>163</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
         <v>1.3062532</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23366047</v>
+        <v>0.23429401</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31160632</v>
+        <v>0.31225806</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40780956</v>
+        <v>0.40887415</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2083333</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.1632184</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.1612654</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
       <c r="T21" t="n">
-        <v>0.22252233</v>
+        <v>0.22252011</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24259146</v>
+        <v>0.24182077</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>173</v>
@@ -1904,43 +1904,43 @@
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31246567</v>
+        <v>0.31154406</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40138975</v>
+        <v>0.3999187</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L22" t="n">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9979434</v>
+        <v>3.9841716</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.274036</v>
+        <v>1.2736789</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24536291</v>
+        <v>0.24534348</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25353515</v>
+        <v>0.25331485</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G23" t="n">
         <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33109185</v>
+        <v>0.33057705</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4029078</v>
+        <v>0.40253314</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1538463</v>
+        <v>4.1253805</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
         <v>141</v>
@@ -2001,13 +2001,13 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3010478</v>
+        <v>1.2951776</v>
       </c>
       <c r="S23" t="n">
         <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23681006</v>
+        <v>0.23582812</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -2035,7 +2035,7 @@
         <v>161</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
         <v>0.3148251</v>
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22920977</v>
+        <v>0.22875951</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G26" t="n">
         <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>0.30964187</v>
+        <v>0.30922374</v>
       </c>
       <c r="I26" t="n">
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3740174</v>
+        <v>0.37337998</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="M26" t="n">
+        <v>24</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.214634</v>
+      </c>
+      <c r="O26" t="n">
+        <v>19</v>
+      </c>
+      <c r="P26" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q26" t="n">
         <v>23</v>
       </c>
-      <c r="N26" t="n">
-        <v>4.2231126</v>
-      </c>
-      <c r="O26" t="n">
-        <v>20</v>
-      </c>
-      <c r="P26" t="n">
-        <v>179</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>22</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.2525853</v>
+        <v>1.2500641</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2504578</v>
+        <v>0.24984828</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2224,13 +2224,13 @@
         <v>0.2431562</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
         <v>668</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
         <v>156</v>
@@ -2272,7 +2272,7 @@
         <v>1.351489</v>
       </c>
       <c r="S27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T27" t="n">
         <v>0.2545637</v>
@@ -2288,46 +2288,46 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26085177</v>
+        <v>0.2602238</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G28" t="n">
         <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3292302</v>
+        <v>0.32864708</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40499592</v>
+        <v>0.4040692</v>
       </c>
       <c r="K28" t="n">
         <v>11</v>
       </c>
       <c r="L28" t="n">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7876449</v>
+        <v>3.8058326</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
         <v>182</v>
@@ -2336,13 +2336,13 @@
         <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1474904</v>
+        <v>1.1458174</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2305001</v>
+        <v>0.23056465</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24325438</v>
+        <v>0.24267869</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G29" t="n">
         <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31762105</v>
+        <v>0.31734994</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4008239</v>
+        <v>0.39995903</v>
       </c>
       <c r="K29" t="n">
         <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2912974</v>
+        <v>4.2925944</v>
       </c>
       <c r="O29" t="n">
         <v>21</v>
       </c>
       <c r="P29" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3100573</v>
+        <v>1.3065768</v>
       </c>
       <c r="S29" t="n">
         <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24954426</v>
+        <v>0.24899274</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2443,7 +2443,7 @@
         <v>0.30905765</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
         <v>0.38266128</v>
@@ -2504,7 +2504,7 @@
         <v>198</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>0.32278594</v>
@@ -2803,49 +2803,49 @@
         <v>0.23529412</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
         <v>0.3148936</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
         <v>0.3480392</v>
       </c>
       <c r="K2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
         <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
         <v>2.732143</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1.125</v>
@@ -2857,7 +2857,7 @@
         <v>0.22058824</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.21982759</v>
+        <v>0.19170985</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.27309236</v>
+        <v>0.24271844</v>
       </c>
       <c r="I3" t="n">
         <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4051724</v>
+        <v>0.373057</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3387096</v>
+        <v>3.2264152</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3064516</v>
+        <v>1.2075472</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
-        <v>0.24892704</v>
+        <v>0.24873096</v>
       </c>
       <c r="U3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.17460318</v>
+        <v>0.18348624</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2254902</v>
+        <v>0.2274678</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3015873</v>
+        <v>0.30733946</v>
       </c>
       <c r="K4" t="n">
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8076923</v>
+        <v>3.3934426</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2115384</v>
+        <v>1.1639345</v>
       </c>
       <c r="S4" t="n">
         <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23737374</v>
+        <v>0.22707424</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21524663</v>
+        <v>0.21465969</v>
       </c>
       <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.30092594</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.33507854</v>
+      </c>
+      <c r="K5" t="n">
         <v>27</v>
       </c>
-      <c r="D5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="L5" t="n">
+        <v>60</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2777778</v>
+      </c>
+      <c r="S5" t="n">
         <v>19</v>
       </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.29482073</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.35874438</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24</v>
-      </c>
-      <c r="L5" t="n">
-        <v>73</v>
-      </c>
-      <c r="M5" t="n">
-        <v>29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.857143</v>
-      </c>
-      <c r="O5" t="n">
-        <v>15</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>25</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.2380953</v>
-      </c>
-      <c r="S5" t="n">
-        <v>15</v>
-      </c>
       <c r="T5" t="n">
-        <v>0.22727273</v>
+        <v>0.23076923</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.19742489</v>
+        <v>0.1959799</v>
       </c>
       <c r="C6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2920354</v>
+      </c>
+      <c r="I6" t="n">
+        <v>23</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3115578</v>
+      </c>
+      <c r="K6" t="n">
         <v>29</v>
       </c>
-      <c r="D6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="L6" t="n">
+        <v>59</v>
+      </c>
+      <c r="M6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.29166666</v>
-      </c>
-      <c r="I6" t="n">
-        <v>26</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.35193133</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27</v>
-      </c>
-      <c r="L6" t="n">
-        <v>69</v>
-      </c>
-      <c r="M6" t="n">
-        <v>27</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.857143</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1269841</v>
+        <v>1.1481482</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24778761</v>
+        <v>0.2525773</v>
       </c>
       <c r="U6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22321428</v>
+        <v>0.23737374</v>
       </c>
       <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
         <v>24</v>
       </c>
-      <c r="D7" t="n">
-        <v>29</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>22</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.32307693</v>
+        <v>0.34334764</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.35267857</v>
+        <v>0.36363637</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.0844154</v>
+      </c>
+      <c r="O7" t="n">
+        <v>21</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="n">
         <v>16</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.475138</v>
-      </c>
-      <c r="O7" t="n">
-        <v>19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>18</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.3259668</v>
+        <v>1.4415585</v>
       </c>
       <c r="S7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23348017</v>
+        <v>0.24615385</v>
       </c>
       <c r="U7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.22727273</v>
+        <v>0.20618556</v>
       </c>
       <c r="C8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" t="n">
         <v>23</v>
       </c>
-      <c r="D8" t="n">
-        <v>25</v>
-      </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.30454546</v>
+        <v>0.28703704</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41919193</v>
+        <v>0.4072165</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5849056</v>
+        <v>3.8333333</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
         <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3396226</v>
+        <v>1.2592592</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2705314</v>
+        <v>0.2657005</v>
       </c>
       <c r="U8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -3272,13 +3272,13 @@
         <v>0.25742576</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -3290,19 +3290,19 @@
         <v>0.32589287</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
         <v>0.43564355</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>67</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N9" t="n">
         <v>6.882353</v>
@@ -3314,7 +3314,7 @@
         <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
         <v>1.6862745</v>
@@ -3326,7 +3326,7 @@
         <v>0.25373134</v>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24253732</v>
+        <v>0.2446352</v>
       </c>
       <c r="C10" t="n">
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3131313</v>
+        <v>0.30588236</v>
       </c>
       <c r="I10" t="n">
         <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3880597</v>
+        <v>0.40772533</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>5.25</v>
+        <v>5.142857</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P10" t="n">
         <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4166666</v>
+        <v>1.3333334</v>
       </c>
       <c r="S10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T10" t="n">
-        <v>0.24909747</v>
+        <v>0.24793388</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.24096386</v>
+        <v>0.23762377</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3018018</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.42079207</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>62</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.5882354</v>
+      </c>
+      <c r="O11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.627451</v>
+      </c>
+      <c r="S11" t="n">
         <v>28</v>
       </c>
-      <c r="E11" t="n">
-        <v>16</v>
-      </c>
-      <c r="F11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.29834256</v>
-      </c>
-      <c r="I11" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.42771083</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>50</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.9069767</v>
-      </c>
-      <c r="O11" t="n">
-        <v>29</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.5581396</v>
-      </c>
-      <c r="S11" t="n">
-        <v>27</v>
-      </c>
       <c r="T11" t="n">
-        <v>0.29885057</v>
+        <v>0.3028846</v>
       </c>
       <c r="U11" t="n">
         <v>29</v>
@@ -3473,25 +3473,25 @@
         <v>0.23305085</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
         <v>31</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
         <v>0.30152673</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
         <v>0.3644068</v>
@@ -3509,25 +3509,25 @@
         <v>3.0159574</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
         <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
         <v>1.0212766</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
         <v>0.20737328</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2596154</v>
+        <v>0.2583732</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
         <v>17</v>
@@ -3552,49 +3552,49 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3080357</v>
+        <v>0.30357143</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0.45673078</v>
+        <v>0.4401914</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8333333</v>
+        <v>3.6666667</v>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
         <v>6</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2037038</v>
+        <v>1.1111112</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24378109</v>
+        <v>0.22959183</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.22844827</v>
+        <v>0.21212122</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
         <v>9</v>
       </c>
-      <c r="G14" t="n">
-        <v>7</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.31558937</v>
+        <v>0.3114035</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40948275</v>
+        <v>0.37878788</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2727273</v>
+        <v>3.3157895</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3787879</v>
+        <v>1.4561404</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.27309236</v>
+        <v>0.28703704</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -3674,31 +3674,31 @@
         <v>0.26865673</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
         <v>0.32258064</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
         <v>0.41293532</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>60</v>
@@ -3716,13 +3716,13 @@
         <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
         <v>1.0784314</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="n">
         <v>0.2021858</v>
@@ -3738,13 +3738,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23636363</v>
+        <v>0.24338624</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -3753,49 +3753,49 @@
         <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35496184</v>
+        <v>0.3542601</v>
       </c>
       <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.45502645</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.42727274</v>
-      </c>
-      <c r="K16" t="n">
-        <v>9</v>
-      </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>3.1666667</v>
       </c>
       <c r="O16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
         <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2063493</v>
+        <v>1.1666666</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24789916</v>
+        <v>0.23267327</v>
       </c>
       <c r="U16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -3805,61 +3805,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25925925</v>
+        <v>0.27142859</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.35714287</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.44285715</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>47</v>
+      </c>
+      <c r="M17" t="n">
         <v>9</v>
       </c>
-      <c r="G17" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.34306568</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.44032922</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>57</v>
-      </c>
-      <c r="M17" t="n">
-        <v>19</v>
-      </c>
       <c r="N17" t="n">
-        <v>7.403226</v>
+        <v>7.3333335</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8064516</v>
+        <v>1.8518518</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>0.31349206</v>
+        <v>0.3119266</v>
       </c>
       <c r="U17" t="n">
         <v>30</v>
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.24789916</v>
+        <v>0.26213592</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.35564855</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4223301</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>62</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.264151</v>
+      </c>
+      <c r="O18" t="n">
+        <v>23</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q18" t="n">
         <v>16</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.3345588</v>
-      </c>
-      <c r="I18" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.39915967</v>
-      </c>
-      <c r="K18" t="n">
-        <v>17</v>
-      </c>
-      <c r="L18" t="n">
-        <v>72</v>
-      </c>
-      <c r="M18" t="n">
-        <v>28</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8688526</v>
-      </c>
-      <c r="O18" t="n">
-        <v>21</v>
-      </c>
-      <c r="P18" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>18</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.3934426</v>
+        <v>1.5283018</v>
       </c>
       <c r="S18" t="n">
+        <v>26</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.25742576</v>
+      </c>
+      <c r="U18" t="n">
         <v>23</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.24122807</v>
-      </c>
-      <c r="U18" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3942,37 +3942,37 @@
         <v>0.2</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" t="n">
         <v>0.28169015</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
         <v>0.35263157</v>
       </c>
       <c r="K19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L19" t="n">
         <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
         <v>5.58</v>
@@ -3984,19 +3984,19 @@
         <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R19" t="n">
         <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T19" t="n">
         <v>0.22797927</v>
       </c>
       <c r="U19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -4009,7 +4009,7 @@
         <v>0.28301886</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>50</v>
@@ -4039,7 +4039,7 @@
         <v>41</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>6.6666665</v>
@@ -4051,19 +4051,19 @@
         <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R20" t="n">
         <v>1.425926</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T20" t="n">
         <v>0.28636363</v>
       </c>
       <c r="U20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.22929937</v>
+        <v>0.2460733</v>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32222223</v>
+        <v>0.33636364</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.36942676</v>
+        <v>0.40314135</v>
       </c>
       <c r="K21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2330828</v>
+        <v>2.19375</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8345865</v>
+        <v>0.9375</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.15686275</v>
+        <v>0.16931216</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24365482</v>
+        <v>0.22666667</v>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2990654</v>
+        <v>0.2798354</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>0.43654823</v>
+        <v>0.4</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1666665</v>
+        <v>3.857143</v>
       </c>
       <c r="O22" t="n">
         <v>18</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1111112</v>
+        <v>1.1269841</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>0.23529412</v>
+        <v>0.23628692</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -4207,43 +4207,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2620321</v>
+        <v>0.2642487</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
+        <v>28</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
         <v>24</v>
       </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>29</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.342723</v>
+        <v>0.3222749</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>0.37967914</v>
+        <v>0.39896372</v>
       </c>
       <c r="K23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L23" t="n">
         <v>37</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1666667</v>
+        <v>1.8333334</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -4255,13 +4255,13 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9259259</v>
+        <v>0.8703704</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.19371727</v>
+        <v>0.19170985</v>
       </c>
       <c r="U23" t="n">
         <v>3</v>
@@ -4277,49 +4277,49 @@
         <v>0.24598931</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
         <v>0.31904763</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J24" t="n">
         <v>0.4171123</v>
       </c>
       <c r="K24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L24" t="n">
         <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>2.6181817</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -4331,7 +4331,7 @@
         <v>0.19170985</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.23809524</v>
+        <v>0.25980392</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30859375</v>
+        <v>0.31838566</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4069264</v>
+        <v>0.44607842</v>
       </c>
       <c r="K25" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6290324</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P25" t="n">
         <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2741935</v>
+        <v>1.2407408</v>
       </c>
       <c r="S25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T25" t="n">
-        <v>0.21238938</v>
+        <v>0.215</v>
       </c>
       <c r="U25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2361809</v>
+        <v>0.22105263</v>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
         <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31390134</v>
+        <v>0.28365386</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.32663316</v>
+        <v>0.32105264</v>
       </c>
       <c r="K26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
         <v>15</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1666665</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="n">
         <v>30</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2962962</v>
+        <v>1.1296296</v>
       </c>
       <c r="S26" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25358853</v>
+        <v>0.21717171</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.27952754</v>
+        <v>0.2706422</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
@@ -4490,28 +4490,28 @@
         <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>0.34385964</v>
+        <v>0.34008098</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39370078</v>
+        <v>0.39908257</v>
       </c>
       <c r="K27" t="n">
         <v>18</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>5.6373625</v>
+        <v>6.0191083</v>
       </c>
       <c r="O27" t="n">
         <v>25</v>
@@ -4520,19 +4520,19 @@
         <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4505494</v>
+        <v>1.4140128</v>
       </c>
       <c r="S27" t="n">
+        <v>22</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.28217822</v>
+      </c>
+      <c r="U27" t="n">
         <v>26</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.27038628</v>
-      </c>
-      <c r="U27" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26291078</v>
+        <v>0.27102804</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33333334</v>
+        <v>0.3375</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>0.43192488</v>
+        <v>0.45327103</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>41</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.075472</v>
+        <v>3.5660377</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1132076</v>
+        <v>1.018868</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.21649484</v>
+        <v>0.20725389</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.25365853</v>
+        <v>0.23152709</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>13</v>
@@ -4627,46 +4627,46 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3231441</v>
+        <v>0.3114035</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>0.47317073</v>
+        <v>0.43842363</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M29" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.754717</v>
       </c>
       <c r="O29" t="n">
+        <v>20</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>14</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.226415</v>
+      </c>
+      <c r="S29" t="n">
         <v>16</v>
       </c>
-      <c r="P29" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.2222222</v>
-      </c>
-      <c r="S29" t="n">
-        <v>14</v>
-      </c>
       <c r="T29" t="n">
-        <v>0.2415459</v>
+        <v>0.25</v>
       </c>
       <c r="U29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.28278688</v>
+        <v>0.28708133</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H30" t="n">
-        <v>0.34686348</v>
+        <v>0.33628318</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4057377</v>
+        <v>0.42105263</v>
       </c>
       <c r="K30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.412088</v>
+        <v>3.483871</v>
       </c>
       <c r="O30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
         <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1043956</v>
+        <v>1.0451612</v>
       </c>
       <c r="S30" t="n">
         <v>6</v>
       </c>
       <c r="T30" t="n">
-        <v>0.19642857</v>
+        <v>0.1904762</v>
       </c>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4746,19 +4746,19 @@
         <v>0.22277227</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
         <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H31" t="n">
         <v>0.27853882</v>
@@ -4770,13 +4770,13 @@
         <v>0.3910891</v>
       </c>
       <c r="K31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L31" t="n">
         <v>62</v>
       </c>
       <c r="M31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>6.375</v>
@@ -4788,19 +4788,19 @@
         <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
         <v>1.5833334</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
         <v>0.27748692</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2422272</v>
+        <v>0.24273607</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31446198</v>
+        <v>0.31520173</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39300954</v>
+        <v>0.3946731</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.097169</v>
+        <v>4.075988</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>165</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2785004</v>
+        <v>1.2765957</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24818403</v>
+        <v>0.24769354</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24513541</v>
+        <v>0.24597014</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G3" t="n">
         <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3180918</v>
+        <v>0.31856352</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40260783</v>
+        <v>0.4037811</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3515387</v>
+        <v>5.331298</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4884615</v>
+        <v>1.4870229</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26832643</v>
+        <v>0.2681827</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,43 +680,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24580893</v>
+        <v>0.24604288</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.30886123</v>
+        <v>0.30918664</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40820035</v>
+        <v>0.40873572</v>
       </c>
       <c r="K4" t="n">
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5751534</v>
+        <v>3.5657794</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -728,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2446319</v>
+        <v>1.2425855</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2320476</v>
+        <v>0.23167752</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23421215</v>
+        <v>0.234638</v>
       </c>
       <c r="C5" t="n">
         <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31609404</v>
+        <v>0.316158</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3940323</v>
+        <v>0.3946461</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.148563</v>
+        <v>4.147549</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3408802</v>
+        <v>1.3415866</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25328556</v>
+        <v>0.25340977</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24777147</v>
+        <v>0.24763629</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32184738</v>
+        <v>0.32150537</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40397084</v>
+        <v>0.4037417</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>1195</v>
+        <v>1205</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.625223</v>
+        <v>3.6209514</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
@@ -862,13 +862,13 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2382165</v>
+        <v>1.2411437</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24280502</v>
+        <v>0.2431562</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25059336</v>
+        <v>0.25196385</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33891574</v>
+        <v>0.3397326</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.42879745</v>
+        <v>0.43087196</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" t="n">
-        <v>4.21875</v>
+        <v>4.203634</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2690549</v>
+        <v>1.2679788</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24511187</v>
+        <v>0.24489388</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,43 +948,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23524606</v>
+        <v>0.2354492</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31748328</v>
+        <v>0.31814104</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4047376</v>
+        <v>0.40519163</v>
       </c>
       <c r="K8" t="n">
         <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1299</v>
+        <v>4.152788</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
@@ -993,16 +993,16 @@
         <v>164</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3082244</v>
+        <v>1.3116883</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2412666</v>
+        <v>0.24219067</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22967689</v>
+        <v>0.22888117</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
         <v>611</v>
@@ -1033,46 +1033,46 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3081289</v>
+        <v>0.30724427</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39740688</v>
+        <v>0.39558193</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7331786</v>
+        <v>4.8424287</v>
       </c>
       <c r="O9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4338747</v>
+        <v>1.4442736</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25216517</v>
+        <v>0.25444022</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1082,46 +1082,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23673469</v>
+        <v>0.23657005</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31409907</v>
+        <v>0.31423423</v>
       </c>
       <c r="I10" t="n">
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37244898</v>
+        <v>0.37259275</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1175</v>
+        <v>1184</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8049529</v>
+        <v>3.7925963</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
         <v>163</v>
@@ -1130,16 +1130,16 @@
         <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2660199</v>
+        <v>1.2634382</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23719512</v>
+        <v>0.23692183</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2523176</v>
+        <v>0.252501</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -1167,43 +1167,43 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32239452</v>
+        <v>0.32234958</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41535673</v>
+        <v>0.41436574</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.508056</v>
+        <v>5.508781</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5194907</v>
+        <v>1.5178202</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28725278</v>
+        <v>0.28652123</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,43 +1216,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23775655</v>
+        <v>0.23746969</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31397033</v>
+        <v>0.31420863</v>
       </c>
       <c r="I12" t="n">
         <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39524487</v>
+        <v>0.39591753</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6653786</v>
+        <v>3.6469686</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
@@ -1264,13 +1264,13 @@
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2217929</v>
+        <v>1.2225633</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23231278</v>
+        <v>0.23264886</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2409468</v>
+        <v>0.24115756</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>193</v>
@@ -1301,43 +1301,43 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31500903</v>
+        <v>0.31488138</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40967023</v>
+        <v>0.40896302</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5229826</v>
+        <v>4.514844</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3483145</v>
+        <v>1.3443289</v>
       </c>
       <c r="S13" t="n">
         <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2380855</v>
+        <v>0.23759153</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24660312</v>
+        <v>0.2469285</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
@@ -1368,43 +1368,43 @@
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31604803</v>
+        <v>0.31653115</v>
       </c>
       <c r="I14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4018127</v>
+      </c>
+      <c r="K14" t="n">
         <v>16</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.40174407</v>
-      </c>
-      <c r="K14" t="n">
-        <v>15</v>
-      </c>
       <c r="L14" t="n">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6446385</v>
+        <v>4.6264043</v>
       </c>
       <c r="O14" t="n">
         <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q14" t="n">
         <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3931601</v>
+        <v>1.3912154</v>
       </c>
       <c r="S14" t="n">
         <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2583974</v>
+        <v>0.25818765</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,46 +1417,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23529412</v>
+        <v>0.23471883</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E15" t="n">
         <v>28</v>
       </c>
       <c r="F15" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G15" t="n">
         <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30906418</v>
+        <v>0.3087886</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37261733</v>
+        <v>0.37204564</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1382</v>
+        <v>1393</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.196276</v>
+        <v>4.1981497</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P15" t="n">
         <v>152</v>
@@ -1465,13 +1465,13 @@
         <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3366951</v>
+        <v>1.3369313</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23485632</v>
+        <v>0.23464146</v>
       </c>
       <c r="U15" t="n">
         <v>7</v>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25671825</v>
+        <v>0.25662285</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33692142</v>
+        <v>0.33689648</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42223126</v>
+        <v>0.42204246</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.67328</v>
+        <v>3.6548107</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
@@ -1532,13 +1532,13 @@
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.162587</v>
+        <v>1.1637666</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21984193</v>
+        <v>0.2201115</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24902962</v>
+        <v>0.24929006</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
         <v>151</v>
@@ -1569,43 +1569,43 @@
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32706222</v>
+        <v>0.32710615</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40122575</v>
+        <v>0.4010142</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>1207</v>
+        <v>1218</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4.097032</v>
+        <v>4.1102</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q17" t="n">
         <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2781936</v>
+        <v>1.279344</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23525786</v>
+        <v>0.23530613</v>
       </c>
       <c r="U17" t="n">
         <v>8</v>
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25651303</v>
+        <v>0.2587371</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33943984</v>
+        <v>0.34090117</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.40409055</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="M18" t="n">
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5446928</v>
+        <v>3.534174</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1666,13 +1666,13 @@
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1853733</v>
+        <v>1.1810845</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22215372</v>
+        <v>0.22140522</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24486476</v>
+        <v>0.24454325</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
@@ -1703,46 +1703,46 @@
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31888264</v>
+        <v>0.3186734</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4065487</v>
+        <v>0.40541634</v>
       </c>
       <c r="K19" t="n">
         <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.665544</v>
+        <v>4.667867</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3764249</v>
+        <v>1.3768973</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2508598</v>
+        <v>0.2506029</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23800813</v>
+        <v>0.23788369</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G20" t="n">
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30859232</v>
+        <v>0.30864197</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3941057</v>
+        <v>0.39357835</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>1232</v>
+        <v>1241</v>
       </c>
       <c r="M20" t="n">
         <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1932344</v>
+        <v>4.208864</v>
       </c>
       <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q20" t="n">
         <v>17</v>
       </c>
-      <c r="P20" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>13</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3062532</v>
+        <v>1.3089659</v>
       </c>
       <c r="S20" t="n">
         <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24084935</v>
+        <v>0.24181563</v>
       </c>
       <c r="U20" t="n">
         <v>14</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23429401</v>
+        <v>0.23533045</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="E21" t="n">
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31225806</v>
+        <v>0.31282052</v>
       </c>
       <c r="I21" t="n">
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40887415</v>
+        <v>0.40992382</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.19863</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1632184</v>
+        <v>1.1643835</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22252011</v>
+        <v>0.22249539</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24182077</v>
+        <v>0.2413793</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
         <v>173</v>
@@ -1904,43 +1904,43 @@
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31154406</v>
+        <v>0.31129178</v>
       </c>
       <c r="I22" t="n">
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3999187</v>
+        <v>0.3986691</v>
       </c>
       <c r="K22" t="n">
         <v>19</v>
       </c>
       <c r="L22" t="n">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9841716</v>
+        <v>3.9792352</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2736789</v>
+        <v>1.2739934</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24534348</v>
+        <v>0.24557918</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25331485</v>
+        <v>0.2530476</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G23" t="n">
         <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33057705</v>
+        <v>0.33024475</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40253314</v>
+        <v>0.40228078</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1253805</v>
+        <v>4.1821394</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2951776</v>
+        <v>1.3009586</v>
       </c>
       <c r="S23" t="n">
         <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23582812</v>
+        <v>0.23733227</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23771857</v>
+        <v>0.23828205</v>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D24" t="n">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -2038,43 +2038,43 @@
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3148251</v>
+        <v>0.31527728</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38780183</v>
+        <v>0.38901508</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8829896</v>
+        <v>3.890709</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q24" t="n">
         <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2796391</v>
+        <v>1.2800102</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23973592</v>
+        <v>0.23934427</v>
       </c>
       <c r="U24" t="n">
         <v>13</v>
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24789073</v>
+        <v>0.2474556</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" t="n">
         <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30880204</v>
+        <v>0.3087942</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40699077</v>
+        <v>0.40650567</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1177</v>
+        <v>1188</v>
       </c>
       <c r="M25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3438706</v>
+        <v>4.3621745</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
@@ -2135,16 +2135,16 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3569776</v>
+        <v>1.3598775</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24729867</v>
+        <v>0.24777508</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -2154,64 +2154,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22875951</v>
+        <v>0.22893287</v>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G26" t="n">
         <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>0.30922374</v>
+        <v>0.30916998</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37337998</v>
+        <v>0.37380126</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.214634</v>
+        <v>4.220041</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q26" t="n">
         <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2500641</v>
+        <v>1.253697</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24984828</v>
+        <v>0.25065222</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2431562</v>
+        <v>0.24385369</v>
       </c>
       <c r="C27" t="n">
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
@@ -2236,46 +2236,46 @@
         <v>156</v>
       </c>
       <c r="G27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3167802</v>
+        <v>0.31730768</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38506442</v>
+        <v>0.38576853</v>
       </c>
       <c r="K27" t="n">
         <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.30873</v>
+        <v>4.299798</v>
       </c>
       <c r="O27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.351489</v>
+        <v>1.3536401</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2545637</v>
+        <v>0.25463238</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2602238</v>
+        <v>0.25981385</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32864708</v>
+        <v>0.32830942</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4040692</v>
+        <v>0.4044921</v>
       </c>
       <c r="K28" t="n">
         <v>11</v>
       </c>
       <c r="L28" t="n">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8058326</v>
+        <v>3.7865853</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
         <v>182</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1458174</v>
+        <v>1.1455792</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23056465</v>
+        <v>0.23084739</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24267869</v>
+        <v>0.24221453</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
         <v>171</v>
@@ -2373,43 +2373,43 @@
         <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31734994</v>
+        <v>0.31727272</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39995903</v>
+        <v>0.39873806</v>
       </c>
       <c r="K29" t="n">
         <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="M29" t="n">
         <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2925944</v>
+        <v>4.3286157</v>
       </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3065768</v>
+        <v>1.3116314</v>
       </c>
       <c r="S29" t="n">
         <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24899274</v>
+        <v>0.24964993</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24778226</v>
+        <v>0.24794877</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30905765</v>
+        <v>0.30917346</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38266128</v>
+        <v>0.38343006</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1053</v>
+        <v>1062</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9073508</v>
+        <v>3.928517</v>
       </c>
       <c r="O30" t="n">
         <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q30" t="n">
         <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2917305</v>
+        <v>1.2927756</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23558283</v>
+        <v>0.23599838</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,16 +2489,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24717543</v>
+        <v>0.24669951</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>198</v>
@@ -2507,43 +2507,43 @@
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32278594</v>
+        <v>0.32250133</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42755204</v>
+        <v>0.42640394</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7541986</v>
+        <v>4.742229</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3969465</v>
+        <v>1.3927218</v>
       </c>
       <c r="S31" t="n">
         <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25630838</v>
+        <v>0.2556302</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23529412</v>
+        <v>0.26540285</v>
       </c>
       <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
         <v>18</v>
       </c>
-      <c r="D2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.3148936</v>
+        <v>0.3360996</v>
       </c>
       <c r="I2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.40758294</v>
+      </c>
+      <c r="K2" t="n">
         <v>15</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.3480392</v>
-      </c>
-      <c r="K2" t="n">
-        <v>26</v>
-      </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.732143</v>
+        <v>2.368421</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.125</v>
+        <v>1.1403508</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>0.22058824</v>
+        <v>0.20975609</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.19170985</v>
+        <v>0.20304568</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24271844</v>
+        <v>0.24880382</v>
       </c>
       <c r="I3" t="n">
         <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>0.373057</v>
+        <v>0.35025382</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2264152</v>
+        <v>2.6666667</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2075472</v>
+        <v>1.1666666</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>0.24873096</v>
+        <v>0.2413793</v>
       </c>
       <c r="U3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.18348624</v>
+        <v>0.19282511</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
-        <v>28</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>24</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.2274678</v>
+        <v>0.2375</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>0.30733946</v>
+        <v>0.32735425</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>48</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3934426</v>
+        <v>3.4285715</v>
       </c>
       <c r="O4" t="n">
         <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1639345</v>
+        <v>1.1904762</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22707424</v>
+        <v>0.22553192</v>
       </c>
       <c r="U4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21465969</v>
+        <v>0.23232323</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.31390134</v>
+      </c>
+      <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3838384</v>
+      </c>
+      <c r="K5" t="n">
+        <v>19</v>
+      </c>
+      <c r="L5" t="n">
+        <v>68</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>29</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.30092594</v>
-      </c>
-      <c r="I5" t="n">
-        <v>22</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.33507854</v>
-      </c>
-      <c r="K5" t="n">
-        <v>27</v>
-      </c>
-      <c r="L5" t="n">
-        <v>60</v>
-      </c>
-      <c r="M5" t="n">
-        <v>22</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2777778</v>
+        <v>1.3518518</v>
       </c>
       <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U5" t="n">
         <v>19</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.23076923</v>
-      </c>
-      <c r="U5" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1959799</v>
+        <v>0.20895523</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2920354</v>
+        <v>0.29333332</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3115578</v>
+        <v>0.33333334</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1481482</v>
+        <v>1.2962962</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2525773</v>
+        <v>0.26903552</v>
       </c>
       <c r="U6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.23737374</v>
+        <v>0.27</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34334764</v>
+        <v>0.35897437</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.36363637</v>
+        <v>0.425</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>5.0844154</v>
+        <v>5.2597404</v>
       </c>
       <c r="O7" t="n">
+        <v>22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
         <v>21</v>
       </c>
-      <c r="P7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>16</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.4415585</v>
+        <v>1.5194806</v>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24615385</v>
+        <v>0.25888324</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -3202,34 +3202,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20618556</v>
+        <v>0.21717171</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.28703704</v>
+        <v>0.3141593</v>
       </c>
       <c r="I8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4072165</v>
+        <v>0.4040404</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>66</v>
@@ -3238,28 +3238,28 @@
         <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8333333</v>
+        <v>4.924528</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2592592</v>
+        <v>1.3584906</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2657005</v>
+        <v>0.28846154</v>
       </c>
       <c r="U8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.25742576</v>
+        <v>0.2361809</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.29816514</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.38190955</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>64</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9</v>
+      </c>
+      <c r="O9" t="n">
         <v>30</v>
       </c>
-      <c r="E9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.32589287</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.43564355</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>67</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S9" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.29951692</v>
+      </c>
+      <c r="U9" t="n">
         <v>29</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.882353</v>
-      </c>
-      <c r="O9" t="n">
-        <v>28</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>16</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.6862745</v>
-      </c>
-      <c r="S9" t="n">
-        <v>29</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.25373134</v>
-      </c>
-      <c r="U9" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2446352</v>
+        <v>0.2361809</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>0.30588236</v>
+        <v>0.3090909</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.40772533</v>
+        <v>0.38190955</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>5.142857</v>
+        <v>4.924528</v>
       </c>
       <c r="O10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3333334</v>
+        <v>1.2830188</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T10" t="n">
-        <v>0.24793388</v>
+        <v>0.23115578</v>
       </c>
       <c r="U10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.23762377</v>
+        <v>0.23529412</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3018018</v>
+        <v>0.29411766</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42079207</v>
+        <v>0.3627451</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5882354</v>
+        <v>7.74</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.627451</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
         <v>28</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3028846</v>
+        <v>0.295</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23305085</v>
+        <v>0.21164021</v>
       </c>
       <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.30733946</v>
+      </c>
+      <c r="I12" t="n">
         <v>19</v>
       </c>
-      <c r="D12" t="n">
-        <v>31</v>
-      </c>
-      <c r="E12" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.30152673</v>
-      </c>
-      <c r="I12" t="n">
-        <v>21</v>
-      </c>
       <c r="J12" t="n">
-        <v>0.3644068</v>
+        <v>0.3968254</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0159574</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0212766</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.20737328</v>
+        <v>0.20430107</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2583732</v>
+        <v>0.26291078</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.30837005</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.42723006</v>
+      </c>
+      <c r="K13" t="n">
         <v>9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.30357143</v>
-      </c>
-      <c r="I13" t="n">
-        <v>19</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.4401914</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6666667</v>
+        <v>4.05</v>
       </c>
       <c r="O13" t="n">
         <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1111112</v>
+        <v>1.0500001</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22959183</v>
+        <v>0.23589744</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.21212122</v>
+        <v>0.22885571</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3114035</v>
+        <v>0.33333334</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>0.37878788</v>
+        <v>0.37810946</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3157895</v>
+        <v>2.2105262</v>
       </c>
       <c r="O14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4561404</v>
+        <v>1.3508772</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28703704</v>
+        <v>0.26760563</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.26865673</v>
+        <v>0.27</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>0.32258064</v>
+        <v>0.33333334</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>0.41293532</v>
+        <v>0.435</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2941177</v>
+        <v>2.8235295</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
         <v>6</v>
       </c>
       <c r="Q15" t="n">
+        <v>11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.137255</v>
+      </c>
+      <c r="S15" t="n">
         <v>8</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.0784314</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.2021858</v>
+        <v>0.20430107</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3738,43 +3738,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.24338624</v>
+        <v>0.25520834</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3542601</v>
+        <v>0.3640351</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.45502645</v>
+        <v>0.46354166</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1666667</v>
+        <v>2.8333333</v>
       </c>
       <c r="O16" t="n">
         <v>8</v>
@@ -3783,19 +3783,19 @@
         <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
         <v>1.1666666</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T16" t="n">
-        <v>0.23267327</v>
+        <v>0.22885571</v>
       </c>
       <c r="U16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -3805,61 +3805,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.27142859</v>
+        <v>0.29439253</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>0.35714287</v>
+        <v>0.37704918</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.44285715</v>
+        <v>0.46728972</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
         <v>7.3333335</v>
       </c>
       <c r="O17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P17" t="n">
         <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8518518</v>
+        <v>1.8148148</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3119266</v>
+        <v>0.30875576</v>
       </c>
       <c r="U17" t="n">
         <v>30</v>
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.26213592</v>
+        <v>0.30660376</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.38016528</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>57</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4150944</v>
+      </c>
+      <c r="O18" t="n">
+        <v>19</v>
+      </c>
+      <c r="P18" t="n">
         <v>6</v>
       </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.35564855</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.4223301</v>
-      </c>
-      <c r="K18" t="n">
-        <v>9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>62</v>
-      </c>
-      <c r="M18" t="n">
-        <v>25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.264151</v>
-      </c>
-      <c r="O18" t="n">
-        <v>23</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8</v>
-      </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5283018</v>
+        <v>1.3773584</v>
       </c>
       <c r="S18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T18" t="n">
-        <v>0.25742576</v>
+        <v>0.2361809</v>
       </c>
       <c r="U18" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3939,61 +3939,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2</v>
+        <v>0.19251336</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>0.28169015</v>
+        <v>0.27962086</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>0.35263157</v>
+        <v>0.3315508</v>
       </c>
       <c r="K19" t="n">
+        <v>28</v>
+      </c>
+      <c r="L19" t="n">
+        <v>45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.647059</v>
+      </c>
+      <c r="O19" t="n">
         <v>25</v>
       </c>
-      <c r="L19" t="n">
-        <v>43</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="O19" t="n">
-        <v>24</v>
-      </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.4509804</v>
       </c>
       <c r="S19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.22797927</v>
+        <v>0.22959183</v>
       </c>
       <c r="U19" t="n">
         <v>12</v>
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.28301886</v>
+        <v>0.2761905</v>
       </c>
       <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44</v>
+      </c>
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="D20" t="n">
-        <v>50</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
       <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3647541</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.45238096</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46</v>
+      </c>
+      <c r="M20" t="n">
         <v>13</v>
       </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.36885247</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5141509</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>41</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
       <c r="N20" t="n">
-        <v>6.6666665</v>
+        <v>6.792453</v>
       </c>
       <c r="O20" t="n">
         <v>27</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R20" t="n">
-        <v>1.425926</v>
+        <v>1.3773584</v>
       </c>
       <c r="S20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T20" t="n">
-        <v>0.28636363</v>
+        <v>0.2962963</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2460733</v>
+        <v>0.28350514</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.36486486</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.45360824</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>44</v>
+      </c>
+      <c r="M21" t="n">
         <v>9</v>
       </c>
-      <c r="F21" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>15</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.33636364</v>
-      </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.40314135</v>
-      </c>
-      <c r="K21" t="n">
-        <v>16</v>
-      </c>
-      <c r="L21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M21" t="n">
-        <v>15</v>
-      </c>
       <c r="N21" t="n">
-        <v>2.19375</v>
+        <v>2.3773584</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
         <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9375</v>
+        <v>1.018868</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.16931216</v>
+        <v>0.17460318</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22666667</v>
+        <v>0.22510822</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2798354</v>
+        <v>0.2857143</v>
       </c>
       <c r="I22" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.37662336</v>
+      </c>
+      <c r="K22" t="n">
+        <v>23</v>
+      </c>
+      <c r="L22" t="n">
+        <v>58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>21</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.6185567</v>
+      </c>
+      <c r="O22" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q22" t="n">
         <v>27</v>
       </c>
-      <c r="J22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="R22" t="n">
+        <v>1.1288661</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.24380165</v>
+      </c>
+      <c r="U22" t="n">
         <v>17</v>
-      </c>
-      <c r="L22" t="n">
-        <v>59</v>
-      </c>
-      <c r="M22" t="n">
-        <v>20</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.857143</v>
-      </c>
-      <c r="O22" t="n">
-        <v>18</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>23</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1269841</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.23628692</v>
-      </c>
-      <c r="U22" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2642487</v>
+        <v>0.26633167</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
         <v>18</v>
       </c>
-      <c r="E23" t="n">
-        <v>28</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>24</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.3222749</v>
+        <v>0.31944445</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>0.39896372</v>
+        <v>0.4120603</v>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.8333334</v>
+        <v>3.9056604</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8703704</v>
+        <v>1.1132076</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>0.19170985</v>
+        <v>0.24623115</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24598931</v>
+        <v>0.26804122</v>
       </c>
       <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>29</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" t="n">
         <v>13</v>
       </c>
-      <c r="D24" t="n">
-        <v>25</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
+        <v>0.34246576</v>
+      </c>
+      <c r="I24" t="n">
         <v>8</v>
       </c>
-      <c r="G24" t="n">
-        <v>9</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.31904763</v>
-      </c>
-      <c r="I24" t="n">
-        <v>13</v>
-      </c>
       <c r="J24" t="n">
-        <v>0.4171123</v>
+        <v>0.45360824</v>
       </c>
       <c r="K24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6181817</v>
+        <v>3.3333333</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>1.1111112</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>0.19170985</v>
+        <v>0.1948718</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25980392</v>
+        <v>0.2361809</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
         <v>9</v>
@@ -4356,46 +4356,46 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>0.31838566</v>
+        <v>0.29816514</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>0.44607842</v>
+        <v>0.42211056</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L25" t="n">
         <v>52</v>
       </c>
       <c r="M25" t="n">
+        <v>17</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.4363637</v>
+      </c>
+      <c r="O25" t="n">
+        <v>12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2727273</v>
+      </c>
+      <c r="S25" t="n">
         <v>15</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>13</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>23</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.2407408</v>
-      </c>
-      <c r="S25" t="n">
-        <v>17</v>
-      </c>
       <c r="T25" t="n">
-        <v>0.215</v>
+        <v>0.22439024</v>
       </c>
       <c r="U25" t="n">
         <v>8</v>
@@ -4408,16 +4408,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22105263</v>
+        <v>0.21428572</v>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -4426,46 +4426,46 @@
         <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>0.28365386</v>
+        <v>0.2688679</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>0.32105264</v>
+        <v>0.31632653</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>4.1666665</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1296296</v>
+        <v>1.1666666</v>
       </c>
       <c r="S26" t="n">
         <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>0.21717171</v>
+        <v>0.22772278</v>
       </c>
       <c r="U26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2706422</v>
+        <v>0.28899083</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>35</v>
@@ -4487,52 +4487,52 @@
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H27" t="n">
-        <v>0.34008098</v>
+        <v>0.35510203</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39908257</v>
+        <v>0.4174312</v>
       </c>
       <c r="K27" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N27" t="n">
-        <v>6.0191083</v>
+        <v>5.503185</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P27" t="n">
         <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4140128</v>
+        <v>1.4331211</v>
       </c>
       <c r="S27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T27" t="n">
-        <v>0.28217822</v>
+        <v>0.27722773</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.27102804</v>
+        <v>0.25123152</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3231441</v>
+      </c>
+      <c r="I28" t="n">
+        <v>12</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.43842363</v>
+      </c>
+      <c r="K28" t="n">
+        <v>7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>39</v>
+      </c>
+      <c r="M28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="N28" t="n">
+        <v>2.7169812</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>11</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9811321</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.21428572</v>
+      </c>
+      <c r="U28" t="n">
         <v>7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.45327103</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>41</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.5660377</v>
-      </c>
-      <c r="O28" t="n">
-        <v>15</v>
-      </c>
-      <c r="P28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>16</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.018868</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.20725389</v>
-      </c>
-      <c r="U28" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -4609,61 +4609,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.23152709</v>
+        <v>0.22167487</v>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3114035</v>
+        <v>0.30701753</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>0.43842363</v>
+        <v>0.4039409</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M29" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N29" t="n">
-        <v>4.754717</v>
+        <v>5.3653846</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P29" t="n">
         <v>7</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R29" t="n">
-        <v>1.226415</v>
+        <v>1.3269231</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.25</v>
+        <v>0.25373134</v>
       </c>
       <c r="U29" t="n">
         <v>20</v>
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.28708133</v>
+        <v>0.27403846</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
         <v>7</v>
       </c>
-      <c r="G30" t="n">
-        <v>15</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.33628318</v>
+        <v>0.32142857</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>0.42105263</v>
+        <v>0.41826922</v>
       </c>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.483871</v>
+        <v>4.354839</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P30" t="n">
         <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
-        <v>1.0451612</v>
+        <v>1.1419355</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1904762</v>
+        <v>0.20918368</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -4743,43 +4743,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.22277227</v>
+        <v>0.20408164</v>
       </c>
       <c r="C31" t="n">
+        <v>27</v>
+      </c>
+      <c r="D31" t="n">
         <v>22</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>21</v>
-      </c>
-      <c r="E31" t="n">
-        <v>23</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
+        <v>27</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2718894</v>
+      </c>
+      <c r="I31" t="n">
+        <v>27</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3622449</v>
+      </c>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" t="n">
+        <v>60</v>
+      </c>
+      <c r="M31" t="n">
         <v>24</v>
       </c>
-      <c r="H31" t="n">
-        <v>0.27853882</v>
-      </c>
-      <c r="I31" t="n">
-        <v>28</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.3910891</v>
-      </c>
-      <c r="K31" t="n">
-        <v>20</v>
-      </c>
-      <c r="L31" t="n">
-        <v>62</v>
-      </c>
-      <c r="M31" t="n">
-        <v>25</v>
-      </c>
       <c r="N31" t="n">
-        <v>6.375</v>
+        <v>6.0612245</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
@@ -4788,19 +4788,19 @@
         <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5833334</v>
+        <v>1.5102041</v>
       </c>
       <c r="S31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.27748692</v>
+        <v>0.2736842</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24273607</v>
+        <v>0.24238172</v>
       </c>
       <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>659</v>
+      </c>
+      <c r="E2" t="n">
         <v>17</v>
-      </c>
-      <c r="D2" t="n">
-        <v>657</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16</v>
       </c>
       <c r="F2" t="n">
         <v>145</v>
@@ -564,43 +564,43 @@
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31520173</v>
+        <v>0.31478167</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3946731</v>
+        <v>0.39374498</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>1079</v>
+        <v>1089</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.075988</v>
+        <v>4.0890565</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2765957</v>
+        <v>1.2784905</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24769354</v>
+        <v>0.24840765</v>
       </c>
       <c r="U2" t="n">
         <v>19</v>
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24597014</v>
+        <v>0.24535389</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>180</v>
@@ -631,43 +631,43 @@
         <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31856352</v>
+        <v>0.3179478</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4037811</v>
+        <v>0.40213522</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.331298</v>
+        <v>5.4109173</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4870229</v>
+        <v>1.4988627</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2681827</v>
+        <v>0.270202</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24604288</v>
+        <v>0.24686691</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.30918664</v>
+        <v>0.31021437</v>
       </c>
       <c r="I4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40873572</v>
+        <v>0.410185</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5657794</v>
+        <v>3.555136</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2425855</v>
+        <v>1.239426</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23167752</v>
+        <v>0.23159385</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.234638</v>
+        <v>0.23423968</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.316158</v>
+        <v>0.31579885</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3946461</v>
+        <v>0.3941591</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.147549</v>
+        <v>4.170015</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3415866</v>
+        <v>1.345555</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25340977</v>
+        <v>0.25402752</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24763629</v>
+        <v>0.24805117</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
         <v>154</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32150537</v>
+        <v>0.32169577</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4037417</v>
+        <v>0.40395764</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6209514</v>
+        <v>3.6031666</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2411437</v>
+        <v>1.2372456</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2431562</v>
+        <v>0.2426</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25196385</v>
+        <v>0.25161165</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3397326</v>
+        <v>0.33969662</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43087196</v>
+        <v>0.43094355</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>4.203634</v>
+        <v>4.1887217</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2679788</v>
+        <v>1.2676692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24489388</v>
+        <v>0.24443118</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2354492</v>
+        <v>0.23514004</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31814104</v>
+        <v>0.31861088</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40519163</v>
+        <v>0.4043925</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>1345</v>
+        <v>1357</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.152788</v>
+        <v>4.1585736</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3116883</v>
+        <v>1.3133535</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24219067</v>
+        <v>0.24214344</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22888117</v>
+        <v>0.22991072</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30724427</v>
+        <v>0.3079841</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39558193</v>
+        <v>0.39732143</v>
       </c>
       <c r="K9" t="n">
         <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>1404</v>
+        <v>1415</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8424287</v>
+        <v>4.89534</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4442736</v>
+        <v>1.4507258</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25444022</v>
+        <v>0.25529808</v>
       </c>
       <c r="U9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23657005</v>
+        <v>0.23605236</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
@@ -1100,43 +1100,43 @@
         <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31423423</v>
+        <v>0.3136974</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37259275</v>
+        <v>0.3713998</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7925963</v>
+        <v>3.796875</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2634382</v>
+        <v>1.2626009</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23692183</v>
+        <v>0.23685268</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.252501</v>
+        <v>0.25307906</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G11" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32234958</v>
+        <v>0.32302222</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41436574</v>
+        <v>0.4155741</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1287</v>
+        <v>1296</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.508781</v>
+        <v>5.551078</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5178202</v>
+        <v>1.5277208</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28652123</v>
+        <v>0.28778508</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23746969</v>
+        <v>0.23917402</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31420863</v>
+        <v>0.3159772</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39591753</v>
+        <v>0.39855653</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6469686</v>
+        <v>3.6699696</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2225633</v>
+        <v>1.2248476</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23264886</v>
+        <v>0.2333877</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24115756</v>
+        <v>0.24061501</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31488138</v>
+        <v>0.31434184</v>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40896302</v>
+        <v>0.40814698</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1212</v>
+        <v>1226</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.514844</v>
+        <v>4.5079446</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3443289</v>
+        <v>1.3445145</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23759153</v>
+        <v>0.2377099</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,43 +1350,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2469285</v>
+        <v>0.24634781</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G14" t="n">
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31653115</v>
+        <v>0.31573275</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4018127</v>
+        <v>0.4010406</v>
       </c>
       <c r="K14" t="n">
         <v>16</v>
       </c>
       <c r="L14" t="n">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6264043</v>
+        <v>4.6324873</v>
       </c>
       <c r="O14" t="n">
         <v>25</v>
@@ -1398,13 +1398,13 @@
         <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3912154</v>
+        <v>1.3911167</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25818765</v>
+        <v>0.25853464</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23471883</v>
+        <v>0.23396073</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3087886</v>
+        <v>0.30848747</v>
       </c>
       <c r="I15" t="n">
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37204564</v>
+        <v>0.3715847</v>
       </c>
       <c r="K15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L15" t="n">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1981497</v>
+        <v>4.202603</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>152</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3369313</v>
+        <v>1.338862</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23464146</v>
+        <v>0.23501834</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25662285</v>
+        <v>0.25582796</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33689648</v>
+        <v>0.33634272</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42204246</v>
+        <v>0.42142284</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6548107</v>
+        <v>3.6599696</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1637666</v>
+        <v>1.1658189</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2201115</v>
+        <v>0.2201929</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24929006</v>
+        <v>0.24919355</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32710615</v>
+        <v>0.32744467</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4010142</v>
+        <v>0.40080646</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>1218</v>
+        <v>1227</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1102</v>
+        <v>4.1025705</v>
       </c>
       <c r="O17" t="n">
         <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.279344</v>
+        <v>1.2774243</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23530613</v>
+        <v>0.234638</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2587371</v>
+        <v>0.25955853</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34090117</v>
+        <v>0.34176776</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40409055</v>
+        <v>0.40599132</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="M18" t="n">
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.534174</v>
+        <v>3.5711422</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1810845</v>
+        <v>1.1858717</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22140522</v>
+        <v>0.2224924</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24454325</v>
+        <v>0.2444266</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3186734</v>
+        <v>0.3187679</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40541634</v>
+        <v>0.40510142</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.667867</v>
+        <v>4.6563616</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
@@ -1733,13 +1733,13 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3768973</v>
+        <v>1.3727645</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2506029</v>
+        <v>0.25</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23788369</v>
+        <v>0.23878205</v>
       </c>
       <c r="C20" t="n">
+        <v>23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>643</v>
+      </c>
+      <c r="E20" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" t="n">
+        <v>188</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3091892</v>
+      </c>
+      <c r="I20" t="n">
+        <v>27</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.39723557</v>
+      </c>
+      <c r="K20" t="n">
         <v>22</v>
       </c>
-      <c r="D20" t="n">
-        <v>631</v>
-      </c>
-      <c r="E20" t="n">
-        <v>22</v>
-      </c>
-      <c r="F20" t="n">
-        <v>182</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.30864197</v>
-      </c>
-      <c r="I20" t="n">
-        <v>29</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.39357835</v>
-      </c>
-      <c r="K20" t="n">
-        <v>24</v>
-      </c>
       <c r="L20" t="n">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="M20" t="n">
         <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>4.208864</v>
+        <v>4.193777</v>
       </c>
       <c r="O20" t="n">
         <v>19</v>
       </c>
       <c r="P20" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q20" t="n">
         <v>17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3089659</v>
+        <v>1.3060967</v>
       </c>
       <c r="S20" t="n">
         <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24181563</v>
+        <v>0.24162011</v>
       </c>
       <c r="U20" t="n">
         <v>14</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23533045</v>
+        <v>0.23517382</v>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E21" t="n">
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31282052</v>
+        <v>0.31234074</v>
       </c>
       <c r="I21" t="n">
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40992382</v>
+        <v>0.40940696</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.19863</v>
+        <v>3.2585034</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1643835</v>
+        <v>1.1685563</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22249539</v>
+        <v>0.2235318</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2413793</v>
+        <v>0.24123423</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E22" t="n">
         <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31129178</v>
+        <v>0.31075984</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3986691</v>
+        <v>0.3987177</v>
       </c>
       <c r="K22" t="n">
         <v>19</v>
       </c>
       <c r="L22" t="n">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9792352</v>
+        <v>3.9959729</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2739934</v>
+        <v>1.2798892</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24557918</v>
+        <v>0.24639969</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2530476</v>
+        <v>0.25253907</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33024475</v>
+        <v>0.32991838</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40228078</v>
+        <v>0.4013672</v>
       </c>
       <c r="K23" t="n">
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1821394</v>
+        <v>4.184052</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3009586</v>
+        <v>1.2991474</v>
       </c>
       <c r="S23" t="n">
         <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23733227</v>
+        <v>0.2370518</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23828205</v>
+        <v>0.23904137</v>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G24" t="n">
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31527728</v>
+        <v>0.31609613</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38901508</v>
+        <v>0.39020893</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.890709</v>
+        <v>3.9051855</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2800102</v>
+        <v>1.2773259</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23934427</v>
+        <v>0.23931624</v>
       </c>
       <c r="U24" t="n">
         <v>13</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2474556</v>
+        <v>0.24737364</v>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3087942</v>
+        <v>0.30834386</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40650567</v>
+        <v>0.40773043</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3621745</v>
+        <v>4.373384</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3598775</v>
+        <v>1.365019</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24777508</v>
+        <v>0.2484447</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2154,46 +2154,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22893287</v>
+        <v>0.23140663</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H26" t="n">
-        <v>0.30916998</v>
+        <v>0.3115019</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37380126</v>
+        <v>0.37873888</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>4.220041</v>
+        <v>4.191188</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
         <v>182</v>
@@ -2202,16 +2202,16 @@
         <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.253697</v>
+        <v>1.2512028</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25065222</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -2221,64 +2221,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24385369</v>
+        <v>0.24379592</v>
       </c>
       <c r="C27" t="n">
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31730768</v>
+        <v>0.31748277</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38576853</v>
+        <v>0.3857455</v>
       </c>
       <c r="K27" t="n">
         <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.299798</v>
+        <v>4.311323</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3536401</v>
+        <v>1.3542557</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25463238</v>
+        <v>0.25420707</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25981385</v>
+        <v>0.25981084</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E28" t="n">
         <v>13</v>
@@ -2306,43 +2306,43 @@
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32830942</v>
+        <v>0.32839862</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4044921</v>
+        <v>0.4039042</v>
       </c>
       <c r="K28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7865853</v>
+        <v>3.7744133</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1455792</v>
+        <v>1.1438304</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23084739</v>
+        <v>0.23036544</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24221453</v>
+        <v>0.24298121</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G29" t="n">
         <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31727272</v>
+        <v>0.31768954</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39873806</v>
+        <v>0.39971724</v>
       </c>
       <c r="K29" t="n">
         <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="M29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3286157</v>
+        <v>4.3125477</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
@@ -2403,13 +2403,13 @@
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3116314</v>
+        <v>1.3087145</v>
       </c>
       <c r="S29" t="n">
         <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24964993</v>
+        <v>0.24925461</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24794877</v>
+        <v>0.2486078</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G30" t="n">
         <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30917346</v>
+        <v>0.3102453</v>
       </c>
       <c r="I30" t="n">
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38343006</v>
+        <v>0.38484487</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>1062</v>
+        <v>1072</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.928517</v>
+        <v>3.915408</v>
       </c>
       <c r="O30" t="n">
         <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q30" t="n">
         <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2927756</v>
+        <v>1.2915407</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23599838</v>
+        <v>0.23559049</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24669951</v>
+        <v>0.2469691</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -2507,46 +2507,46 @@
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32250133</v>
+        <v>0.32269874</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42640394</v>
+        <v>0.42608526</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1249</v>
+        <v>1258</v>
       </c>
       <c r="M31" t="n">
         <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.742229</v>
+        <v>4.7404065</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q31" t="n">
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3927218</v>
+        <v>1.3905191</v>
       </c>
       <c r="S31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2556302</v>
+        <v>0.25475958</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.26540285</v>
+        <v>0.26086956</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
         <v>28</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.38647342</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>44</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.892857</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.2142857</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2292683</v>
+      </c>
+      <c r="U2" t="n">
         <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3360996</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.40758294</v>
-      </c>
-      <c r="K2" t="n">
-        <v>15</v>
-      </c>
-      <c r="L2" t="n">
-        <v>42</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.368421</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.1403508</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.20975609</v>
-      </c>
-      <c r="U2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.20304568</v>
+        <v>0.18461539</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24880382</v>
+        <v>0.23923445</v>
       </c>
       <c r="I3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>0.35025382</v>
+        <v>0.2923077</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6666667</v>
+        <v>5.1666665</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1666666</v>
+        <v>1.537037</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2413793</v>
+        <v>0.3027523</v>
       </c>
       <c r="U3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.19282511</v>
+        <v>0.2236842</v>
       </c>
       <c r="C4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" t="n">
         <v>29</v>
       </c>
-      <c r="D4" t="n">
-        <v>19</v>
-      </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2375</v>
+        <v>0.276</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>0.32735425</v>
+        <v>0.36842105</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4285715</v>
+        <v>3.09375</v>
       </c>
       <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
         <v>11</v>
       </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1904762</v>
+        <v>1.0625</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22553192</v>
+        <v>0.21794872</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23232323</v>
+        <v>0.23267327</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31390134</v>
+        <v>0.30973452</v>
       </c>
       <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3910891</v>
+      </c>
+      <c r="K5" t="n">
         <v>16</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.3838384</v>
-      </c>
-      <c r="K5" t="n">
-        <v>19</v>
-      </c>
       <c r="L5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
         <v>30</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.4150944</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3518518</v>
+        <v>1.4150944</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.2657005</v>
       </c>
       <c r="U5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -3068,61 +3068,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.20895523</v>
+        <v>0.21827412</v>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29333332</v>
+        <v>0.29357797</v>
       </c>
       <c r="I6" t="n">
         <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>0.33333334</v>
+        <v>0.3604061</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.1666667</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2962962</v>
+        <v>1.2222222</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T6" t="n">
-        <v>0.26903552</v>
+        <v>0.26633167</v>
       </c>
       <c r="U6" t="n">
         <v>23</v>
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27</v>
+        <v>0.2408377</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
-        <v>0.35897437</v>
+        <v>0.33482143</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>0.425</v>
+        <v>0.41361257</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.733766</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20</v>
+      </c>
+      <c r="P7" t="n">
         <v>8</v>
       </c>
-      <c r="N7" t="n">
-        <v>5.2597404</v>
-      </c>
-      <c r="O7" t="n">
-        <v>22</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9</v>
-      </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5194806</v>
+        <v>1.4805195</v>
       </c>
       <c r="S7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T7" t="n">
-        <v>0.25888324</v>
+        <v>0.255</v>
       </c>
       <c r="U7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -3202,34 +3202,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.21717171</v>
+        <v>0.21827412</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3390558</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.38071066</v>
+      </c>
+      <c r="K8" t="n">
         <v>22</v>
-      </c>
-      <c r="E8" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3141593</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.4040404</v>
-      </c>
-      <c r="K8" t="n">
-        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>66</v>
@@ -3238,28 +3238,28 @@
         <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>4.924528</v>
+        <v>4.754717</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8" t="n">
         <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3584906</v>
+        <v>1.4339622</v>
       </c>
       <c r="S8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T8" t="n">
-        <v>0.28846154</v>
+        <v>0.28985506</v>
       </c>
       <c r="U8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2361809</v>
+        <v>0.24019608</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.29816514</v>
+        <v>0.30666667</v>
       </c>
       <c r="I9" t="n">
         <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38190955</v>
+        <v>0.38235295</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M9" t="n">
         <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>11.020409</v>
       </c>
       <c r="O9" t="n">
         <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>1.88</v>
+        <v>2.0816326</v>
       </c>
       <c r="S9" t="n">
         <v>30</v>
       </c>
       <c r="T9" t="n">
-        <v>0.29951692</v>
+        <v>0.3222749</v>
       </c>
       <c r="U9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2361809</v>
+        <v>0.24019608</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
       </c>
       <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3141593</v>
+      </c>
+      <c r="I10" t="n">
         <v>18</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.3090909</v>
-      </c>
-      <c r="I10" t="n">
-        <v>17</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.38190955</v>
+        <v>0.3872549</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>4.924528</v>
+        <v>4.673077</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2115384</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.21761657</v>
+      </c>
+      <c r="U10" t="n">
         <v>6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2830188</v>
-      </c>
-      <c r="S10" t="n">
-        <v>16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.23115578</v>
-      </c>
-      <c r="U10" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.23529412</v>
+        <v>0.23671497</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>0.29411766</v>
+        <v>0.29464287</v>
       </c>
       <c r="I11" t="n">
         <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3627451</v>
+        <v>0.4009662</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N11" t="n">
-        <v>7.74</v>
+        <v>8.632652999999999</v>
       </c>
       <c r="O11" t="n">
         <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.8571428</v>
       </c>
       <c r="S11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T11" t="n">
-        <v>0.295</v>
+        <v>0.31683168</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.21164021</v>
+        <v>0.24479167</v>
       </c>
       <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.34666666</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.44270834</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M12" t="n">
         <v>25</v>
       </c>
-      <c r="D12" t="n">
-        <v>28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="N12" t="n">
+        <v>3.1666667</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
         <v>7</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.30733946</v>
-      </c>
-      <c r="I12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3968254</v>
-      </c>
-      <c r="K12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M12" t="n">
-        <v>29</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>5</v>
-      </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>1.1851852</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>0.20430107</v>
+        <v>0.24102564</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.26291078</v>
+        <v>0.25120774</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3018018</v>
+      </c>
+      <c r="I13" t="n">
+        <v>22</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.42028984</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>58</v>
+      </c>
+      <c r="M13" t="n">
         <v>24</v>
       </c>
-      <c r="F13" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.30837005</v>
-      </c>
-      <c r="I13" t="n">
-        <v>18</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.42723006</v>
-      </c>
-      <c r="K13" t="n">
-        <v>9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>54</v>
-      </c>
-      <c r="M13" t="n">
-        <v>18</v>
-      </c>
       <c r="N13" t="n">
-        <v>4.05</v>
+        <v>4.2077923</v>
       </c>
       <c r="O13" t="n">
+        <v>14</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.0909091</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.24193548</v>
+      </c>
+      <c r="U13" t="n">
         <v>16</v>
-      </c>
-      <c r="P13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>17</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.0500001</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.23589744</v>
-      </c>
-      <c r="U13" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3604,46 +3604,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.22885571</v>
+        <v>0.22</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" t="n">
-        <v>0.33333334</v>
+        <v>0.32034633</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.37810946</v>
+        <v>0.37</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2105262</v>
+        <v>2.5714285</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>4</v>
@@ -3652,16 +3652,16 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3508772</v>
+        <v>1.2857143</v>
       </c>
       <c r="S14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26760563</v>
+        <v>0.26213592</v>
       </c>
       <c r="U14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -3671,16 +3671,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.27</v>
+        <v>0.23589744</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" t="n">
         <v>23</v>
-      </c>
-      <c r="E15" t="n">
-        <v>19</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -3689,46 +3689,46 @@
         <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33333334</v>
+        <v>0.32126698</v>
       </c>
       <c r="I15" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4051282</v>
+      </c>
+      <c r="K15" t="n">
+        <v>13</v>
+      </c>
+      <c r="L15" t="n">
+        <v>56</v>
+      </c>
+      <c r="M15" t="n">
+        <v>21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.5064936</v>
+      </c>
+      <c r="O15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>59</v>
-      </c>
-      <c r="M15" t="n">
-        <v>23</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.8235295</v>
-      </c>
-      <c r="O15" t="n">
-        <v>7</v>
-      </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.137255</v>
+        <v>1.1883117</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>0.20430107</v>
+        <v>0.21243523</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25520834</v>
+        <v>0.23958333</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3640351</v>
+        <v>0.3508772</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
         <v>0.46354166</v>
       </c>
       <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.8867924</v>
+      </c>
+      <c r="O16" t="n">
         <v>3</v>
       </c>
-      <c r="L16" t="n">
-        <v>51</v>
-      </c>
-      <c r="M16" t="n">
-        <v>15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.8333333</v>
-      </c>
-      <c r="O16" t="n">
-        <v>8</v>
-      </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1666666</v>
+        <v>1.1886792</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22885571</v>
+        <v>0.22564103</v>
       </c>
       <c r="U16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.29439253</v>
+        <v>0.3004695</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.37759337</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.45539907</v>
+      </c>
+      <c r="K17" t="n">
         <v>7</v>
       </c>
-      <c r="G17" t="n">
-        <v>13</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.37704918</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.46728972</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>7.3333335</v>
+        <v>6.8333335</v>
       </c>
       <c r="O17" t="n">
         <v>28</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8148148</v>
+        <v>1.6296296</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T17" t="n">
-        <v>0.30875576</v>
+        <v>0.2735849</v>
       </c>
       <c r="U17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.30660376</v>
+        <v>0.3287037</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.38016528</v>
+        <v>0.4048583</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.5509259</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4150944</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3773584</v>
+        <v>1.425926</v>
       </c>
       <c r="S18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2361809</v>
+        <v>0.24019608</v>
       </c>
       <c r="U18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.19251336</v>
+        <v>0.19125684</v>
       </c>
       <c r="C19" t="n">
+        <v>29</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" t="n">
         <v>30</v>
-      </c>
-      <c r="D19" t="n">
-        <v>18</v>
-      </c>
-      <c r="E19" t="n">
-        <v>29</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
       </c>
       <c r="G19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.28708133</v>
+      </c>
+      <c r="I19" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.32240438</v>
+      </c>
+      <c r="K19" t="n">
+        <v>29</v>
+      </c>
+      <c r="L19" t="n">
+        <v>53</v>
+      </c>
+      <c r="M19" t="n">
         <v>18</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.27962086</v>
-      </c>
-      <c r="I19" t="n">
-        <v>26</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.3315508</v>
-      </c>
-      <c r="K19" t="n">
-        <v>28</v>
-      </c>
-      <c r="L19" t="n">
-        <v>45</v>
-      </c>
-      <c r="M19" t="n">
-        <v>12</v>
-      </c>
       <c r="N19" t="n">
-        <v>5.647059</v>
+        <v>5.470588</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4509804</v>
+        <v>1.4313725</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>0.22959183</v>
+        <v>0.22564103</v>
       </c>
       <c r="U19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2761905</v>
+        <v>0.30875576</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3647541</v>
+        <v>0.38554215</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.45238096</v>
+        <v>0.5529954</v>
       </c>
       <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>44</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.6037736</v>
+      </c>
+      <c r="O20" t="n">
+        <v>26</v>
+      </c>
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="L20" t="n">
-        <v>46</v>
-      </c>
-      <c r="M20" t="n">
-        <v>13</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.792453</v>
-      </c>
-      <c r="O20" t="n">
-        <v>27</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>11</v>
       </c>
-      <c r="Q20" t="n">
-        <v>27</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3773584</v>
+        <v>1.3018868</v>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2962963</v>
+        <v>0.28504673</v>
       </c>
       <c r="U20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.28350514</v>
+        <v>0.27319586</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3364486</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.45876288</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>43</v>
+      </c>
+      <c r="M21" t="n">
         <v>5</v>
       </c>
-      <c r="F21" t="n">
+      <c r="N21" t="n">
+        <v>4.245283</v>
+      </c>
+      <c r="O21" t="n">
+        <v>16</v>
+      </c>
+      <c r="P21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>30</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.1509434</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.22110553</v>
+      </c>
+      <c r="U21" t="n">
         <v>8</v>
-      </c>
-      <c r="G21" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.36486486</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.45360824</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>44</v>
-      </c>
-      <c r="M21" t="n">
-        <v>9</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.3773584</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>24</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.018868</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.17460318</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22510822</v>
+        <v>0.2173913</v>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E22" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>7</v>
       </c>
-      <c r="G22" t="n">
-        <v>13</v>
-      </c>
       <c r="H22" t="n">
-        <v>0.2857143</v>
+        <v>0.26422763</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>0.37662336</v>
+        <v>0.37391305</v>
       </c>
       <c r="K22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L22" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M22" t="n">
         <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6185567</v>
+        <v>4.2408376</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P22" t="n">
         <v>11</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1288661</v>
+        <v>1.3193717</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24380165</v>
+        <v>0.27125505</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.26633167</v>
+        <v>0.25373134</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H23" t="n">
-        <v>0.31944445</v>
+        <v>0.3105023</v>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4120603</v>
+        <v>0.3880597</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9056604</v>
+        <v>3.6346154</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1132076</v>
+        <v>1.0576923</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24623115</v>
+        <v>0.22340426</v>
       </c>
       <c r="U23" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.26804122</v>
+        <v>0.30541873</v>
       </c>
       <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.37117904</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5073892</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="D24" t="n">
-        <v>29</v>
-      </c>
-      <c r="E24" t="n">
-        <v>11</v>
-      </c>
-      <c r="F24" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" t="n">
-        <v>13</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.34246576</v>
-      </c>
-      <c r="I24" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.45360824</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>41</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.3333333</v>
-      </c>
-      <c r="O24" t="n">
-        <v>10</v>
-      </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1111112</v>
+        <v>0.962963</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1948718</v>
+        <v>0.18877551</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4341,34 +4341,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2361809</v>
+        <v>0.22727273</v>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
-        <v>0.29816514</v>
+        <v>0.28372094</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0.42211056</v>
+        <v>0.37878788</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L25" t="n">
         <v>52</v>
@@ -4377,28 +4377,28 @@
         <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4363637</v>
+        <v>3.9272728</v>
       </c>
       <c r="O25" t="n">
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2727273</v>
+        <v>1.4545455</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.22439024</v>
+        <v>0.25592417</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.21428572</v>
+        <v>0.27962086</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I26" t="n">
+        <v>13</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.45971563</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>49</v>
+      </c>
+      <c r="M26" t="n">
+        <v>15</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.3333333</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>19</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1296296</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U26" t="n">
         <v>3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.2688679</v>
-      </c>
-      <c r="I26" t="n">
-        <v>28</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.31632653</v>
-      </c>
-      <c r="K26" t="n">
-        <v>30</v>
-      </c>
-      <c r="L26" t="n">
-        <v>54</v>
-      </c>
-      <c r="M26" t="n">
-        <v>18</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.1666665</v>
-      </c>
-      <c r="O26" t="n">
-        <v>17</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>24</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.1666666</v>
-      </c>
-      <c r="S26" t="n">
-        <v>11</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.22772278</v>
-      </c>
-      <c r="U26" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.28899083</v>
+        <v>0.27102804</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3510204</v>
+      </c>
+      <c r="I27" t="n">
         <v>5</v>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>27</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.35510203</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
+        <v>0.38317758</v>
+      </c>
+      <c r="K27" t="n">
+        <v>20</v>
+      </c>
+      <c r="L27" t="n">
+        <v>45</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="O27" t="n">
+        <v>19</v>
+      </c>
+      <c r="P27" t="n">
         <v>7</v>
       </c>
-      <c r="J27" t="n">
-        <v>0.4174312</v>
-      </c>
-      <c r="K27" t="n">
-        <v>13</v>
-      </c>
-      <c r="L27" t="n">
-        <v>44</v>
-      </c>
-      <c r="M27" t="n">
-        <v>9</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.503185</v>
-      </c>
-      <c r="O27" t="n">
-        <v>24</v>
-      </c>
-      <c r="P27" t="n">
-        <v>6</v>
-      </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4331211</v>
+        <v>1.36875</v>
       </c>
       <c r="S27" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.27722773</v>
+        <v>0.25373134</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25123152</v>
+        <v>0.24870466</v>
       </c>
       <c r="C28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.32579187</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4041451</v>
+      </c>
+      <c r="K28" t="n">
         <v>14</v>
       </c>
-      <c r="D28" t="n">
-        <v>30</v>
-      </c>
-      <c r="E28" t="n">
-        <v>9</v>
-      </c>
-      <c r="F28" t="n">
-        <v>11</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.3231441</v>
-      </c>
-      <c r="I28" t="n">
-        <v>12</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.43842363</v>
-      </c>
-      <c r="K28" t="n">
-        <v>7</v>
-      </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7169812</v>
+        <v>2.5961537</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9811321</v>
+        <v>1.0384616</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0.21428572</v>
+        <v>0.21465969</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.22167487</v>
+        <v>0.25490198</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0.30701753</v>
+        <v>0.34199134</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4039409</v>
+        <v>0.4362745</v>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M29" t="n">
         <v>26</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3653846</v>
+        <v>4.9411764</v>
       </c>
       <c r="O29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3269231</v>
+        <v>1.254902</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T29" t="n">
-        <v>0.25373134</v>
+        <v>0.23979592</v>
       </c>
       <c r="U29" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -4676,46 +4676,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.27403846</v>
+        <v>0.275</v>
       </c>
       <c r="C30" t="n">
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.33484164</v>
+      </c>
+      <c r="I30" t="n">
+        <v>11</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.32142857</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="L30" t="n">
+        <v>43</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.180645</v>
+      </c>
+      <c r="O30" t="n">
         <v>13</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.41826922</v>
-      </c>
-      <c r="K30" t="n">
-        <v>12</v>
-      </c>
-      <c r="L30" t="n">
-        <v>37</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.354839</v>
-      </c>
-      <c r="O30" t="n">
-        <v>18</v>
       </c>
       <c r="P30" t="n">
         <v>9</v>
@@ -4724,16 +4724,16 @@
         <v>21</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1419355</v>
+        <v>1.1612903</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>0.20918368</v>
+        <v>0.20304568</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.20408164</v>
+        <v>0.21105528</v>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" t="n">
         <v>22</v>
-      </c>
-      <c r="E31" t="n">
-        <v>21</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2718894</v>
+        <v>0.28181818</v>
       </c>
       <c r="I31" t="n">
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3622449</v>
+        <v>0.36180905</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L31" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N31" t="n">
-        <v>6.0612245</v>
+        <v>5.647059</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
         <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5102041</v>
+        <v>1.4705882</v>
       </c>
       <c r="S31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2736842</v>
+        <v>0.25520834</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24238172</v>
+        <v>0.24303344</v>
       </c>
       <c r="C2" t="n">
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31478167</v>
+        <v>0.3152657</v>
       </c>
       <c r="I2" t="n">
         <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39374498</v>
+        <v>0.3951035</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0890565</v>
+        <v>4.0884557</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2784905</v>
+        <v>1.278111</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24840765</v>
+        <v>0.24856748</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24535389</v>
+        <v>0.24557957</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G3" t="n">
         <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3179478</v>
+        <v>0.31870264</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40213522</v>
+        <v>0.4037328</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4109173</v>
+        <v>5.4216866</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4988627</v>
+        <v>1.502259</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.270202</v>
+        <v>0.27064043</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24686691</v>
+        <v>0.24743286</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31021437</v>
+        <v>0.31074557</v>
       </c>
       <c r="I4" t="n">
         <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.410185</v>
+        <v>0.41015008</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1202</v>
+        <v>1211</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.555136</v>
+        <v>3.591898</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.239426</v>
+        <v>1.2453114</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23159385</v>
+        <v>0.2328987</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23423968</v>
+        <v>0.2344</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>179</v>
@@ -765,46 +765,46 @@
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31579885</v>
+        <v>0.31616214</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3941591</v>
+        <v>0.3934</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>1384</v>
+        <v>1399</v>
       </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.170015</v>
+        <v>4.1989517</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.345555</v>
+        <v>1.3487269</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25402752</v>
+        <v>0.25429353</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -814,46 +814,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24805117</v>
+        <v>0.24811283</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32169577</v>
+        <v>0.3219469</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40395764</v>
+        <v>0.4038538</v>
       </c>
       <c r="K6" t="n">
         <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6031666</v>
+        <v>3.5856216</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>147</v>
@@ -862,13 +862,13 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2372456</v>
+        <v>1.2363954</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2426</v>
+        <v>0.24205087</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,43 +881,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25161165</v>
+        <v>0.25111672</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33969662</v>
+        <v>0.3394884</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43094355</v>
+        <v>0.4301806</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1887217</v>
+        <v>4.1874533</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
@@ -929,13 +929,13 @@
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2676692</v>
+        <v>1.2696042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24443118</v>
+        <v>0.24456736</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23514004</v>
+        <v>0.23457532</v>
       </c>
       <c r="C8" t="n">
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -966,25 +966,25 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31861088</v>
+        <v>0.3182301</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4043925</v>
+        <v>0.4034455</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>1357</v>
+        <v>1366</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1585736</v>
+        <v>4.1334844</v>
       </c>
       <c r="O8" t="n">
         <v>14</v>
@@ -993,16 +993,16 @@
         <v>165</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3133535</v>
+        <v>1.3084464</v>
       </c>
       <c r="S8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24214344</v>
+        <v>0.24153815</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22991072</v>
+        <v>0.2299476</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3079841</v>
+        <v>0.3078579</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39732143</v>
+        <v>0.39721885</v>
       </c>
       <c r="K9" t="n">
         <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.89534</v>
+        <v>4.8823977</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4507258</v>
+        <v>1.4476479</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25529808</v>
+        <v>0.25502166</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,61 +1082,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23605236</v>
+        <v>0.23701039</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3136974</v>
+        <v>0.31456482</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3713998</v>
+        <v>0.3739009</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.796875</v>
+        <v>3.784731</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q10" t="n">
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2626009</v>
+        <v>1.2600751</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23685268</v>
+        <v>0.23649053</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25307906</v>
+        <v>0.25251728</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G11" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32302222</v>
+        <v>0.3223754</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4155741</v>
+        <v>0.4148075</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1296</v>
+        <v>1307</v>
       </c>
       <c r="M11" t="n">
         <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.551078</v>
+        <v>5.572194</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5277208</v>
+        <v>1.529847</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28778508</v>
+        <v>0.28760806</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23917402</v>
+        <v>0.2392907</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G12" t="n">
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3159772</v>
+        <v>0.31645122</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39855653</v>
+        <v>0.39948198</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6699696</v>
+        <v>3.651779</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2248476</v>
+        <v>1.2210447</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2333877</v>
+        <v>0.23293498</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24061501</v>
+        <v>0.23992856</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31434184</v>
+        <v>0.31405252</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40814698</v>
+        <v>0.40841436</v>
       </c>
       <c r="K13" t="n">
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5079446</v>
+        <v>4.548508</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3445145</v>
+        <v>1.3492104</v>
       </c>
       <c r="S13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2377099</v>
+        <v>0.23881195</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24634781</v>
+        <v>0.24577451</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
         <v>155</v>
@@ -1368,43 +1368,43 @@
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31573275</v>
+        <v>0.31555477</v>
       </c>
       <c r="I14" t="n">
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4010406</v>
+        <v>0.399483</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
-        <v>1160</v>
+        <v>1172</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6324873</v>
+        <v>4.6316853</v>
       </c>
       <c r="O14" t="n">
         <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q14" t="n">
         <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3911167</v>
+        <v>1.3910191</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25853464</v>
+        <v>0.25853175</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,46 +1417,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23396073</v>
+        <v>0.23335345</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G15" t="n">
         <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30848747</v>
+        <v>0.30823275</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3715847</v>
+        <v>0.3717562</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1403</v>
+        <v>1416</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.202603</v>
+        <v>4.218108</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
         <v>152</v>
@@ -1465,16 +1465,16 @@
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.338862</v>
+        <v>1.3421253</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23501834</v>
+        <v>0.23593687</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25582796</v>
+        <v>0.25588822</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33634272</v>
+        <v>0.3367311</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42142284</v>
+        <v>0.4215569</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6599696</v>
+        <v>3.678716</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q16" t="n">
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1658189</v>
+        <v>1.167088</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2201929</v>
+        <v>0.22054628</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24919355</v>
+        <v>0.24934909</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32744467</v>
+        <v>0.327363</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40080646</v>
+        <v>0.40076107</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1025705</v>
+        <v>4.1018705</v>
       </c>
       <c r="O17" t="n">
         <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2774243</v>
+        <v>1.2793226</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.234638</v>
+        <v>0.23484391</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25955853</v>
+        <v>0.25925925</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34176776</v>
+        <v>0.341434</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40599132</v>
+        <v>0.40603566</v>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5711422</v>
+        <v>3.5740235</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1858717</v>
+        <v>1.186116</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2224924</v>
+        <v>0.22258</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2444266</v>
+        <v>0.24401437</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E19" t="n">
         <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3187679</v>
+        <v>0.31820607</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40510142</v>
+        <v>0.4046289</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>1177</v>
+        <v>1188</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6563616</v>
+        <v>4.6861205</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3727645</v>
+        <v>1.3770617</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25</v>
+        <v>0.2508421</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23878205</v>
+        <v>0.237953</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
@@ -1770,43 +1770,43 @@
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3091892</v>
+        <v>0.30831245</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39723557</v>
+        <v>0.3956591</v>
       </c>
       <c r="K20" t="n">
         <v>22</v>
       </c>
       <c r="L20" t="n">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="M20" t="n">
+        <v>17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.182047</v>
+      </c>
+      <c r="O20" t="n">
         <v>16</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.193777</v>
-      </c>
-      <c r="O20" t="n">
-        <v>19</v>
-      </c>
       <c r="P20" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3060967</v>
+        <v>1.3034952</v>
       </c>
       <c r="S20" t="n">
         <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24162011</v>
+        <v>0.24101648</v>
       </c>
       <c r="U20" t="n">
         <v>14</v>
@@ -1819,43 +1819,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23517382</v>
+        <v>0.234588</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31234074</v>
+        <v>0.31196815</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40940696</v>
+        <v>0.40915564</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1353</v>
+        <v>1362</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2585034</v>
+        <v>3.2364864</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1864,16 +1864,16 @@
         <v>154</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1685563</v>
+        <v>1.1644144</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2235318</v>
+        <v>0.22278328</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24123423</v>
+        <v>0.24244833</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31075984</v>
+        <v>0.31170914</v>
       </c>
       <c r="I22" t="n">
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3987177</v>
+        <v>0.40023848</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="M22" t="n">
         <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9959729</v>
+        <v>3.996</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2798892</v>
+        <v>1.28325</v>
       </c>
       <c r="S22" t="n">
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24639969</v>
+        <v>0.24696435</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25253907</v>
+        <v>0.25261933</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
@@ -1971,43 +1971,43 @@
         <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>0.32991838</v>
+        <v>0.33011383</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4013672</v>
+        <v>0.4008537</v>
       </c>
       <c r="K23" t="n">
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="M23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.184052</v>
+        <v>4.17609</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P23" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2991474</v>
+        <v>1.2986301</v>
       </c>
       <c r="S23" t="n">
         <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2370518</v>
+        <v>0.23663366</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23904137</v>
+        <v>0.23917022</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E24" t="n">
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G24" t="n">
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31609613</v>
+        <v>0.3158466</v>
       </c>
       <c r="I24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39020893</v>
+        <v>0.390482</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="M24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9051855</v>
+        <v>3.9058318</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2773259</v>
+        <v>1.278465</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23931624</v>
+        <v>0.23939393</v>
       </c>
       <c r="U24" t="n">
         <v>13</v>
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24737364</v>
+        <v>0.24739225</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30834386</v>
+        <v>0.30846307</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40773043</v>
+        <v>0.40720332</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1196</v>
+        <v>1205</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.373384</v>
+        <v>4.384441</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.365019</v>
+        <v>1.363293</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2484447</v>
+        <v>0.24850538</v>
       </c>
       <c r="U25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23140663</v>
+        <v>0.23214285</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3115019</v>
+        <v>0.31232193</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37873888</v>
+        <v>0.38001606</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="M26" t="n">
         <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>4.191188</v>
+        <v>4.220237</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q26" t="n">
         <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2512028</v>
+        <v>1.254971</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.2501981</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2221,43 +2221,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24379592</v>
+        <v>0.24318989</v>
       </c>
       <c r="C27" t="n">
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
         <v>157</v>
       </c>
       <c r="G27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31748277</v>
+        <v>0.316567</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3857455</v>
+        <v>0.38472167</v>
       </c>
       <c r="K27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1174</v>
+        <v>1183</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.311323</v>
+        <v>4.289027</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
@@ -2269,16 +2269,16 @@
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3542557</v>
+        <v>1.3518704</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25420707</v>
+        <v>0.25354332</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25981084</v>
+        <v>0.26073068</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G28" t="n">
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32839862</v>
+        <v>0.3289733</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4039042</v>
+        <v>0.40686765</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7744133</v>
+        <v>3.77594</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q28" t="n">
         <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1438304</v>
+        <v>1.143609</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23036544</v>
+        <v>0.22973515</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24298121</v>
+        <v>0.24318364</v>
       </c>
       <c r="C29" t="n">
         <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G29" t="n">
         <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31768954</v>
+        <v>0.3174973</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39971724</v>
+        <v>0.39955893</v>
       </c>
       <c r="K29" t="n">
         <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3125477</v>
+        <v>4.3241115</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3087145</v>
+        <v>1.3104061</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24925461</v>
+        <v>0.24985199</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,46 +2422,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2486078</v>
+        <v>0.24891347</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3102453</v>
+        <v>0.31076482</v>
       </c>
       <c r="I30" t="n">
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38484487</v>
+        <v>0.3866061</v>
       </c>
       <c r="K30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.915408</v>
+        <v>3.8957238</v>
       </c>
       <c r="O30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P30" t="n">
         <v>156</v>
@@ -2470,16 +2470,16 @@
         <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2915407</v>
+        <v>1.2940735</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23559049</v>
+        <v>0.23574145</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2469691</v>
+        <v>0.24776699</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -2504,49 +2504,49 @@
         <v>198</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32269874</v>
+        <v>0.32329005</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42608526</v>
+        <v>0.42640775</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="M31" t="n">
         <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7404065</v>
+        <v>4.735426</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q31" t="n">
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3905191</v>
+        <v>1.3886398</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25475958</v>
+        <v>0.2540488</v>
       </c>
       <c r="U31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24303344</v>
+        <v>0.24352638</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3152657</v>
+        <v>0.31586376</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3951035</v>
+        <v>0.3967187</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0884557</v>
+        <v>4.1079674</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.278111</v>
+        <v>1.2799702</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24856748</v>
+        <v>0.24906844</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -634,7 +634,7 @@
         <v>0.31870264</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
         <v>0.4037328</v>
@@ -680,64 +680,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24743286</v>
+        <v>0.24744898</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31074557</v>
+        <v>0.31101245</v>
       </c>
       <c r="I4" t="n">
         <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41015008</v>
+        <v>0.40973312</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.591898</v>
+        <v>3.6174498</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q4" t="n">
         <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2453114</v>
+        <v>1.2490679</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2328987</v>
+        <v>0.2333599</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2344</v>
+        <v>0.23455809</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31616214</v>
+        <v>0.31591907</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3934</v>
+        <v>0.39344588</v>
       </c>
       <c r="K5" t="n">
         <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1989517</v>
+        <v>4.1775355</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3487269</v>
+        <v>1.34788</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25429353</v>
+        <v>0.25387898</v>
       </c>
       <c r="U5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -847,7 +847,7 @@
         <v>1218</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
         <v>3.5856216</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25111672</v>
+        <v>0.25144732</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3394884</v>
+        <v>0.33984178</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4301806</v>
+        <v>0.43052876</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1874533</v>
+        <v>4.1795254</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2696042</v>
+        <v>1.2707715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24456736</v>
+        <v>0.24460149</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23457532</v>
+        <v>0.23473245</v>
       </c>
       <c r="C8" t="n">
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3182301</v>
+        <v>0.31881258</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4034455</v>
+        <v>0.4032226</v>
       </c>
       <c r="K8" t="n">
         <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>1366</v>
+        <v>1380</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1334844</v>
+        <v>4.105618</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q8" t="n">
         <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3084464</v>
+        <v>1.306367</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24153815</v>
+        <v>0.241345</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2299476</v>
+        <v>0.22936699</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3078579</v>
+        <v>0.30704728</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39721885</v>
+        <v>0.39623398</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>1423</v>
+        <v>1434</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8823977</v>
+        <v>4.876413</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4476479</v>
+        <v>1.4446119</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25502166</v>
+        <v>0.25416097</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,61 +1082,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23701039</v>
+        <v>0.23684733</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31456482</v>
+        <v>0.31421006</v>
       </c>
       <c r="I10" t="n">
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3739009</v>
+        <v>0.3736351</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.784731</v>
+        <v>3.786176</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q10" t="n">
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2600751</v>
+        <v>1.2620587</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23649053</v>
+        <v>0.23663366</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25251728</v>
+        <v>0.2532811</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G11" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3223754</v>
+        <v>0.32304454</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4148075</v>
+        <v>0.41665035</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.572194</v>
+        <v>5.5888014</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.529847</v>
+        <v>1.531543</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28760806</v>
+        <v>0.28800306</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2392907</v>
+        <v>0.23931962</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
         <v>169</v>
@@ -1234,46 +1234,46 @@
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31645122</v>
+        <v>0.31621528</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39948198</v>
+        <v>0.39873418</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.651779</v>
+        <v>3.6609023</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2210447</v>
+        <v>1.2233083</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23293498</v>
+        <v>0.23295112</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1286,13 +1286,13 @@
         <v>0.23992856</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
         <v>669</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
         <v>197</v>
@@ -1371,7 +1371,7 @@
         <v>0.31555477</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
         <v>0.399483</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23335345</v>
+        <v>0.23370652</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
@@ -1435,43 +1435,43 @@
         <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30823275</v>
+        <v>0.3083259</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3717562</v>
+        <v>0.37185127</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.218108</v>
+        <v>4.2166247</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3421253</v>
+        <v>1.3413098</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23593687</v>
+        <v>0.23593247</v>
       </c>
       <c r="U15" t="n">
         <v>9</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25588822</v>
+        <v>0.2550109</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3367311</v>
+        <v>0.33624455</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4215569</v>
+        <v>0.42091686</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.678716</v>
+        <v>3.6605573</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q16" t="n">
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.167088</v>
+        <v>1.1629425</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22054628</v>
+        <v>0.22001621</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24934909</v>
+        <v>0.24985093</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.327363</v>
+        <v>0.3274648</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40076107</v>
+        <v>0.4023057</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="M17" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.130369</v>
+      </c>
+      <c r="O17" t="n">
         <v>14</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.1018705</v>
-      </c>
-      <c r="O17" t="n">
-        <v>13</v>
-      </c>
       <c r="P17" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2793226</v>
+        <v>1.2825923</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23484391</v>
+        <v>0.2354</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1651,7 +1651,7 @@
         <v>1259</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N18" t="n">
         <v>3.5740235</v>
@@ -1675,7 +1675,7 @@
         <v>0.22258</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24401437</v>
+        <v>0.24355926</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E19" t="n">
         <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31820607</v>
+        <v>0.31795686</v>
       </c>
       <c r="I19" t="n">
         <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4046289</v>
+        <v>0.40408245</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6861205</v>
+        <v>4.708669</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3770617</v>
+        <v>1.375252</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2508421</v>
+        <v>0.2508855</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.237953</v>
+        <v>0.23763356</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G20" t="n">
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30831245</v>
+        <v>0.3082399</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3956591</v>
+        <v>0.3949347</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="M20" t="n">
+        <v>19</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.160589</v>
+      </c>
+      <c r="O20" t="n">
+        <v>15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q20" t="n">
         <v>17</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.182047</v>
-      </c>
-      <c r="O20" t="n">
-        <v>16</v>
-      </c>
-      <c r="P20" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>18</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3034952</v>
+        <v>1.3021978</v>
       </c>
       <c r="S20" t="n">
         <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24101648</v>
+        <v>0.24112776</v>
       </c>
       <c r="U20" t="n">
         <v>14</v>
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.234588</v>
+        <v>0.23474747</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31196815</v>
+        <v>0.31174672</v>
       </c>
       <c r="I21" t="n">
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40915564</v>
+        <v>0.410101</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1362</v>
+        <v>1371</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2364864</v>
+        <v>3.2214766</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1644144</v>
+        <v>1.1640567</v>
       </c>
       <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.22246741</v>
+      </c>
+      <c r="U21" t="n">
         <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.22278328</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1919,7 +1919,7 @@
         <v>1238</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
         <v>3.996</v>
@@ -1937,7 +1937,7 @@
         <v>1.28325</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
         <v>0.24696435</v>
@@ -1956,7 +1956,7 @@
         <v>0.25261933</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
         <v>718</v>
@@ -1980,7 +1980,7 @@
         <v>0.4008537</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L23" t="n">
         <v>1395</v>
@@ -1992,7 +1992,7 @@
         <v>4.17609</v>
       </c>
       <c r="O23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
         <v>145</v>
@@ -2010,7 +2010,7 @@
         <v>0.23663366</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23917022</v>
+        <v>0.23995964</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3158466</v>
+        <v>0.31633753</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" t="n">
-        <v>0.390482</v>
+        <v>0.39172554</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9058318</v>
+        <v>3.9267802</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q24" t="n">
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.278465</v>
+        <v>1.28335</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23939393</v>
+        <v>0.24028055</v>
       </c>
       <c r="U24" t="n">
         <v>13</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24739225</v>
+        <v>0.24706572</v>
       </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -2105,25 +2105,25 @@
         <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30846307</v>
+        <v>0.30832148</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40720332</v>
+        <v>0.40610328</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L25" t="n">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.384441</v>
+        <v>4.3716216</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
@@ -2135,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.363293</v>
+        <v>1.3641142</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24850538</v>
+        <v>0.24861331</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23214285</v>
+        <v>0.2321642</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31232193</v>
+        <v>0.31222358</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38001606</v>
+        <v>0.38043046</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1301</v>
+        <v>1312</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.220237</v>
+        <v>4.2354264</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
@@ -2202,13 +2202,13 @@
         <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.254971</v>
+        <v>1.2556918</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2501981</v>
+        <v>0.250443</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24318989</v>
+        <v>0.2433281</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
         <v>157</v>
@@ -2239,25 +2239,25 @@
         <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.316567</v>
+        <v>0.31678322</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38472167</v>
+        <v>0.38422292</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.289027</v>
+        <v>4.26703</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
@@ -2269,13 +2269,13 @@
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3518704</v>
+        <v>1.3502601</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25354332</v>
+        <v>0.25317943</v>
       </c>
       <c r="U27" t="n">
         <v>24</v>
@@ -2297,7 +2297,7 @@
         <v>682</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
         <v>161</v>
@@ -2315,7 +2315,7 @@
         <v>0.40686765</v>
       </c>
       <c r="K28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
         <v>1031</v>
@@ -2358,19 +2358,19 @@
         <v>0.24318364</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
         <v>624</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>173</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" t="n">
         <v>0.3174973</v>
@@ -2422,43 +2422,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24891347</v>
+        <v>0.2488226</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31076482</v>
+        <v>0.31104392</v>
       </c>
       <c r="I30" t="n">
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3866061</v>
+        <v>0.38638148</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8957238</v>
+        <v>3.909836</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
@@ -2467,16 +2467,16 @@
         <v>156</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2940735</v>
+        <v>1.2935916</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23574145</v>
+        <v>0.23579659</v>
       </c>
       <c r="U30" t="n">
         <v>8</v>
@@ -2522,7 +2522,7 @@
         <v>1265</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
         <v>4.735426</v>
@@ -2546,7 +2546,7 @@
         <v>0.2540488</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24352638</v>
+        <v>0.24328563</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31586376</v>
+        <v>0.3157158</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3967187</v>
+        <v>0.3961968</v>
       </c>
       <c r="K2" t="n">
         <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>1105</v>
+        <v>1119</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1079674</v>
+        <v>4.094535</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2799702</v>
+        <v>1.27548</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24906844</v>
+        <v>0.24824767</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24557957</v>
+        <v>0.24487405</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -628,46 +628,46 @@
         <v>183</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31870264</v>
+        <v>0.3176718</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4037328</v>
+        <v>0.4022652</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>1276</v>
+        <v>1288</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4216866</v>
+        <v>5.395958</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.502259</v>
+        <v>1.498503</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27064043</v>
+        <v>0.27028582</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,43 +680,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24744898</v>
+        <v>0.2475151</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31101245</v>
+        <v>0.31104445</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40973312</v>
+        <v>0.4106412</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6174498</v>
+        <v>3.6066666</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -725,16 +725,16 @@
         <v>167</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2490679</v>
+        <v>1.2474074</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2333599</v>
+        <v>0.23291741</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23455809</v>
+        <v>0.23428571</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31591907</v>
+        <v>0.3152288</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39344588</v>
+        <v>0.3942857</v>
       </c>
       <c r="K5" t="n">
         <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>1411</v>
+        <v>1428</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1775355</v>
+        <v>4.1635513</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34788</v>
+        <v>1.3494835</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25387898</v>
+        <v>0.25408733</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24811283</v>
+        <v>0.24772996</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3219469</v>
+        <v>0.32166725</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4038538</v>
+        <v>0.40307936</v>
       </c>
       <c r="K6" t="n">
         <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>1218</v>
+        <v>1233</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5856216</v>
+        <v>3.591067</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -862,13 +862,13 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2363954</v>
+        <v>1.2364764</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24205087</v>
+        <v>0.24199921</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25144732</v>
+        <v>0.25091118</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -896,46 +896,46 @@
         <v>208</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33984178</v>
+        <v>0.33930066</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43052876</v>
+        <v>0.4289277</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1795254</v>
+        <v>4.191599</v>
       </c>
       <c r="O7" t="n">
         <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2707715</v>
+        <v>1.2711865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24460149</v>
+        <v>0.24468708</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23473245</v>
+        <v>0.23482902</v>
       </c>
       <c r="C8" t="n">
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -966,46 +966,46 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31881258</v>
+        <v>0.31914893</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4032226</v>
+        <v>0.40284643</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.105618</v>
+        <v>4.119325</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.306367</v>
+        <v>1.3061275</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.241345</v>
+        <v>0.24135205</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22936699</v>
+        <v>0.2286397</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
@@ -1024,7 +1024,7 @@
         <v>625</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
@@ -1033,43 +1033,43 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30704728</v>
+        <v>0.30636865</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39623398</v>
+        <v>0.39474207</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>1434</v>
+        <v>1445</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.876413</v>
+        <v>4.870509</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4446119</v>
+        <v>1.4446108</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25416097</v>
+        <v>0.2541845</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23684733</v>
+        <v>0.23688363</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31421006</v>
+        <v>0.3141554</v>
       </c>
       <c r="I10" t="n">
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3736351</v>
+        <v>0.37475345</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.786176</v>
+        <v>3.8009386</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1127,16 +1127,16 @@
         <v>166</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2620587</v>
+        <v>1.2640158</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23663366</v>
+        <v>0.23671784</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2532811</v>
+        <v>0.2545207</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32304454</v>
+        <v>0.32404667</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41665035</v>
+        <v>0.4188217</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5888014</v>
+        <v>5.571213</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.531543</v>
+        <v>1.5301963</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28800306</v>
+        <v>0.28812274</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,43 +1216,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23931962</v>
+        <v>0.23963858</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="E12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" t="n">
+        <v>171</v>
+      </c>
+      <c r="G12" t="n">
         <v>17</v>
       </c>
-      <c r="F12" t="n">
-        <v>169</v>
-      </c>
-      <c r="G12" t="n">
-        <v>18</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.31621528</v>
+        <v>0.31698376</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39873418</v>
+        <v>0.399725</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6609023</v>
+        <v>3.6430173</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1264,13 +1264,13 @@
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2233083</v>
+        <v>1.2218074</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23295112</v>
+        <v>0.2326139</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23992856</v>
+        <v>0.23939215</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31405252</v>
+        <v>0.31356978</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40841436</v>
+        <v>0.40872312</v>
       </c>
       <c r="K13" t="n">
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.548508</v>
+        <v>4.5313745</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3492104</v>
+        <v>1.3453686</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23881195</v>
+        <v>0.23813322</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24577451</v>
+        <v>0.24505928</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G14" t="n">
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31555477</v>
+        <v>0.3148936</v>
       </c>
       <c r="I14" t="n">
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>0.399483</v>
+        <v>0.3986166</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>1172</v>
+        <v>1186</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6316853</v>
+        <v>4.6308928</v>
       </c>
       <c r="O14" t="n">
         <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q14" t="n">
         <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3910191</v>
+        <v>1.3871615</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25853175</v>
+        <v>0.25789267</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,43 +1417,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23370652</v>
+        <v>0.23365785</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3082399</v>
+      </c>
+      <c r="I15" t="n">
         <v>29</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.3083259</v>
-      </c>
-      <c r="I15" t="n">
-        <v>27</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.37185127</v>
+        <v>0.37174648</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1423</v>
+        <v>1433</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2166247</v>
+        <v>4.194896</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
@@ -1465,16 +1465,16 @@
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3413098</v>
+        <v>1.3375031</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23593247</v>
+        <v>0.2357756</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2550109</v>
+        <v>0.2550296</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33624455</v>
+        <v>0.33663023</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42091686</v>
+        <v>0.42130178</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6605573</v>
+        <v>3.6359103</v>
       </c>
       <c r="O16" t="n">
         <v>5</v>
@@ -1529,16 +1529,16 @@
         <v>166</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1629425</v>
+        <v>1.1596011</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22001621</v>
+        <v>0.21933535</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24985093</v>
+        <v>0.24901342</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3274648</v>
+        <v>0.32669115</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4023057</v>
+        <v>0.40114444</v>
       </c>
       <c r="K17" t="n">
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1248</v>
+        <v>1259</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.130369</v>
+        <v>4.103139</v>
       </c>
       <c r="O17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q17" t="n">
         <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2825923</v>
+        <v>1.2825112</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2354</v>
+        <v>0.23522411</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25925925</v>
+        <v>0.25920156</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1636,43 +1636,43 @@
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.341434</v>
+        <v>0.3416638</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40603566</v>
+        <v>0.40584224</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5740235</v>
+        <v>3.5568464</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.186116</v>
+        <v>1.1870984</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22258</v>
+        <v>0.22297703</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24355926</v>
+        <v>0.24340291</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>175</v>
@@ -1703,43 +1703,43 @@
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31795686</v>
+        <v>0.31739894</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40408245</v>
+        <v>0.40350533</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.708669</v>
+        <v>4.70388</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.375252</v>
+        <v>1.3794744</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2508855</v>
+        <v>0.25156128</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23763356</v>
+        <v>0.23798312</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3082399</v>
+        <v>0.30857447</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3949347</v>
+        <v>0.3951344</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L20" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="M20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.160589</v>
+        <v>4.16002</v>
       </c>
       <c r="O20" t="n">
         <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3021978</v>
+        <v>1.2982413</v>
       </c>
       <c r="S20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24112776</v>
+        <v>0.24080595</v>
       </c>
       <c r="U20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -1819,43 +1819,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23474747</v>
+        <v>0.23557693</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31174672</v>
+        <v>0.31239966</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.410101</v>
+        <v>0.41105768</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2214766</v>
+        <v>3.2066667</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1867,13 +1867,13 @@
         <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1640567</v>
+        <v>1.1614815</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22246741</v>
+        <v>0.22244368</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24244833</v>
+        <v>0.24190363</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31170914</v>
+        <v>0.31119376</v>
       </c>
       <c r="I22" t="n">
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40023848</v>
+        <v>0.39968404</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="M22" t="n">
         <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>3.996</v>
+        <v>4.0124254</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28325</v>
+        <v>1.2837971</v>
       </c>
       <c r="S22" t="n">
         <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24696435</v>
+        <v>0.24732229</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25261933</v>
+        <v>0.25279385</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G23" t="n">
         <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33011383</v>
+        <v>0.33002058</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4008537</v>
+        <v>0.40057802</v>
       </c>
       <c r="K23" t="n">
         <v>16</v>
       </c>
       <c r="L23" t="n">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.17609</v>
+        <v>4.1815934</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
         <v>145</v>
@@ -2001,13 +2001,13 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2986301</v>
+        <v>1.3003464</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23663366</v>
+        <v>0.23671784</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23995964</v>
+        <v>0.24043278</v>
       </c>
       <c r="C24" t="n">
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E24" t="n">
         <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G24" t="n">
         <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31633753</v>
+        <v>0.31639022</v>
       </c>
       <c r="I24" t="n">
         <v>15</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39172554</v>
+        <v>0.39290723</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9267802</v>
+        <v>3.9638584</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="n">
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28335</v>
+        <v>1.2883848</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24028055</v>
+        <v>0.24164678</v>
       </c>
       <c r="U24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24706572</v>
+        <v>0.24747671</v>
       </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30832148</v>
+        <v>0.30887282</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40610328</v>
+        <v>0.40722048</v>
       </c>
       <c r="K25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1217</v>
+        <v>1228</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3716216</v>
+        <v>4.3624163</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3641142</v>
+        <v>1.360179</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24861331</v>
+        <v>0.24808033</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2321642</v>
+        <v>0.23203327</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
@@ -2172,43 +2172,43 @@
         <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31222358</v>
+        <v>0.31176367</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38043046</v>
+        <v>0.37992477</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2354264</v>
+        <v>4.223576</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q26" t="n">
         <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2556918</v>
+        <v>1.2549117</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.250443</v>
+        <v>0.25029355</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2221,64 +2221,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2433281</v>
+        <v>0.24283206</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G27" t="n">
         <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31678322</v>
+        <v>0.31624675</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38422292</v>
+        <v>0.38365516</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.26703</v>
+        <v>4.2918305</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3502601</v>
+        <v>1.3538387</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25317943</v>
+        <v>0.253543</v>
       </c>
       <c r="U27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2288,43 +2288,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26073068</v>
+        <v>0.2604208</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E28" t="n">
         <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G28" t="n">
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3289733</v>
+        <v>0.32846195</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40686765</v>
+        <v>0.40651053</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.77594</v>
+        <v>3.7572815</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
@@ -2333,16 +2333,16 @@
         <v>186</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.143609</v>
+        <v>1.1389096</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22973515</v>
+        <v>0.22911265</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24318364</v>
+        <v>0.24312475</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
         <v>173</v>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3174973</v>
+        <v>0.31741223</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39955893</v>
+        <v>0.39876446</v>
       </c>
       <c r="K29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3241115</v>
+        <v>4.3082933</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3104061</v>
+        <v>1.3082933</v>
       </c>
       <c r="S29" t="n">
         <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24985199</v>
+        <v>0.24946068</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2488226</v>
+        <v>0.2483915</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -2440,46 +2440,46 @@
         <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31104392</v>
+        <v>0.3106556</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38638148</v>
+        <v>0.38506532</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.909836</v>
+        <v>3.9370837</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2935916</v>
+        <v>1.2982975</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23579659</v>
+        <v>0.23614125</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2489,64 +2489,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24776699</v>
+        <v>0.2481174</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32329005</v>
+        <v>0.323575</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42640775</v>
+        <v>0.42749566</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.735426</v>
+        <v>4.7238307</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q31" t="n">
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3886398</v>
+        <v>1.3853006</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2540488</v>
+        <v>0.25344193</v>
       </c>
       <c r="U31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.26086956</v>
+        <v>0.27230048</v>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" t="n">
         <v>9</v>
       </c>
-      <c r="D2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.46948355</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>49</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.090909</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.38647342</v>
-      </c>
-      <c r="K2" t="n">
-        <v>19</v>
-      </c>
-      <c r="L2" t="n">
-        <v>44</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.892857</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.2142857</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13</v>
-      </c>
       <c r="T2" t="n">
-        <v>0.2292683</v>
+        <v>0.24880382</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.18461539</v>
+        <v>0.2195122</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -2885,46 +2885,46 @@
         <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23923445</v>
+        <v>0.2849162</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2923077</v>
+        <v>0.36585367</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1666665</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.537037</v>
+        <v>1.6888889</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3027523</v>
+        <v>0.3114754</v>
       </c>
       <c r="U3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2236842</v>
+        <v>0.2658228</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I4" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
+      <c r="J4" t="n">
+        <v>0.43459916</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.359375</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" t="n">
         <v>6</v>
       </c>
-      <c r="G4" t="n">
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.28125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.25104603</v>
+      </c>
+      <c r="U4" t="n">
         <v>19</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="I4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.36842105</v>
-      </c>
-      <c r="K4" t="n">
-        <v>26</v>
-      </c>
-      <c r="L4" t="n">
-        <v>44</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.09375</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>26</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.21794872</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23267327</v>
+        <v>0.24651162</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.30973452</v>
+        <v>0.30341882</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3910891</v>
+        <v>0.40465117</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4150944</v>
+        <v>4.6666665</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4150944</v>
+        <v>1.537037</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2657005</v>
+        <v>0.27230048</v>
       </c>
       <c r="U5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.21827412</v>
+        <v>0.24242425</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29357797</v>
+        <v>0.30555555</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3604061</v>
+        <v>0.37575758</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1666667</v>
+        <v>3.0681818</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2222222</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.26633167</v>
+        <v>0.24375</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2408377</v>
+        <v>0.24598931</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3438914</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.40106952</v>
+      </c>
+      <c r="K7" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" t="n">
+        <v>29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.9056604</v>
+      </c>
+      <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3396226</v>
+      </c>
+      <c r="S7" t="n">
         <v>19</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.33482143</v>
-      </c>
-      <c r="I7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.41361257</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" t="n">
-        <v>40</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.733766</v>
-      </c>
-      <c r="O7" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>19</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4805195</v>
-      </c>
-      <c r="S7" t="n">
-        <v>26</v>
-      </c>
       <c r="T7" t="n">
-        <v>0.255</v>
+        <v>0.2364532</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.21827412</v>
+        <v>0.20535715</v>
       </c>
       <c r="C8" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" t="n">
         <v>25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>24</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3345588</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.32142857</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27</v>
+      </c>
+      <c r="L8" t="n">
+        <v>79</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.5604396</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3390558</v>
-      </c>
-      <c r="I8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.38071066</v>
-      </c>
-      <c r="K8" t="n">
-        <v>22</v>
-      </c>
-      <c r="L8" t="n">
-        <v>66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.754717</v>
-      </c>
-      <c r="O8" t="n">
-        <v>21</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4339622</v>
+        <v>1.2197802</v>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>0.28985506</v>
+        <v>0.24782608</v>
       </c>
       <c r="U8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -3269,55 +3269,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24019608</v>
+        <v>0.19072165</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30666667</v>
+        <v>0.24038461</v>
       </c>
       <c r="I9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38235295</v>
+        <v>0.3041237</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>11.020409</v>
+        <v>10.058824</v>
       </c>
       <c r="O9" t="n">
         <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0816326</v>
+        <v>1.882353</v>
       </c>
       <c r="S9" t="n">
         <v>30</v>
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24019608</v>
+        <v>0.24271844</v>
       </c>
       <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3173913</v>
+      </c>
+      <c r="I10" t="n">
         <v>16</v>
       </c>
-      <c r="D10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="J10" t="n">
+        <v>0.44174758</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2692307</v>
+      </c>
+      <c r="S10" t="n">
         <v>13</v>
       </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>19</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3141593</v>
-      </c>
-      <c r="I10" t="n">
-        <v>18</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.3872549</v>
-      </c>
-      <c r="K10" t="n">
-        <v>18</v>
-      </c>
-      <c r="L10" t="n">
-        <v>47</v>
-      </c>
-      <c r="M10" t="n">
-        <v>13</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.673077</v>
-      </c>
-      <c r="O10" t="n">
-        <v>18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2115384</v>
-      </c>
-      <c r="S10" t="n">
-        <v>12</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.21761657</v>
+        <v>0.23589744</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.23671497</v>
+        <v>0.28225806</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>0.29464287</v>
+        <v>0.34558824</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4009662</v>
+        <v>0.47580644</v>
       </c>
       <c r="K11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
-        <v>8.632652999999999</v>
+        <v>8.068966</v>
       </c>
       <c r="O11" t="n">
         <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8571428</v>
+        <v>1.8103448</v>
       </c>
       <c r="S11" t="n">
         <v>29</v>
       </c>
       <c r="T11" t="n">
-        <v>0.31683168</v>
+        <v>0.30801687</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24479167</v>
+        <v>0.28643215</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.34666666</v>
+        <v>0.39834026</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.44270834</v>
+        <v>0.5125628</v>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1666667</v>
+        <v>2.8333333</v>
       </c>
       <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" t="n">
-        <v>7</v>
-      </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1851852</v>
+        <v>1.1481482</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>0.24102564</v>
+        <v>0.23</v>
       </c>
       <c r="U12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25120774</v>
+        <v>0.21649484</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2761905</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.41752577</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>48</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.0066223</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2119206</v>
+      </c>
+      <c r="S13" t="n">
         <v>7</v>
       </c>
-      <c r="H13" t="n">
-        <v>0.3018018</v>
-      </c>
-      <c r="I13" t="n">
-        <v>22</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.42028984</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11</v>
-      </c>
-      <c r="L13" t="n">
-        <v>58</v>
-      </c>
-      <c r="M13" t="n">
-        <v>24</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.2077923</v>
-      </c>
-      <c r="O13" t="n">
-        <v>14</v>
-      </c>
-      <c r="P13" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>11</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.0909091</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
       <c r="T13" t="n">
-        <v>0.24193548</v>
+        <v>0.23809524</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.22</v>
+        <v>0.19620253</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2784091</v>
+      </c>
+      <c r="I14" t="n">
+        <v>27</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.31012657</v>
+      </c>
+      <c r="K14" t="n">
+        <v>29</v>
+      </c>
+      <c r="L14" t="n">
+        <v>50</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.642857</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" t="n">
         <v>6</v>
       </c>
-      <c r="G14" t="n">
-        <v>19</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.32034633</v>
-      </c>
-      <c r="I14" t="n">
-        <v>17</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="K14" t="n">
-        <v>25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>48</v>
-      </c>
-      <c r="M14" t="n">
-        <v>14</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.5714285</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>4</v>
-      </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2857143</v>
+        <v>1.2142857</v>
       </c>
       <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.24528302</v>
+      </c>
+      <c r="U14" t="n">
         <v>16</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.26213592</v>
-      </c>
-      <c r="U14" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23589744</v>
+        <v>0.21505377</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>0.32126698</v>
+        <v>0.30697674</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4051282</v>
+        <v>0.4032258</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
         <v>56</v>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5064936</v>
+        <v>4.1273885</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1883117</v>
+        <v>1.3184713</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>0.21243523</v>
+        <v>0.25603864</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23958333</v>
+        <v>0.23469388</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.35193133</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.46938777</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.4230769</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.0384616</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.20634921</v>
+      </c>
+      <c r="U16" t="n">
         <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.3508772</v>
-      </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.46354166</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>45</v>
-      </c>
-      <c r="M16" t="n">
-        <v>11</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.8867924</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>11</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.1886792</v>
-      </c>
-      <c r="S16" t="n">
-        <v>11</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.22564103</v>
-      </c>
-      <c r="U16" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3004695</v>
+        <v>0.28636363</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>0.37759337</v>
+        <v>0.35365853</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.45539907</v>
+        <v>0.45</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
-        <v>6.8333335</v>
+        <v>6.018072</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>22</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.5542169</v>
+      </c>
+      <c r="S17" t="n">
+        <v>27</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.25925925</v>
+      </c>
+      <c r="U17" t="n">
         <v>21</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.6296296</v>
-      </c>
-      <c r="S17" t="n">
-        <v>28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.2735849</v>
-      </c>
-      <c r="U17" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3287037</v>
+        <v>0.33333334</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -3890,46 +3890,46 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4048583</v>
+        <v>0.3960396</v>
       </c>
       <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5888889</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.5509259</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="O18" t="n">
-        <v>23</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.425926</v>
-      </c>
-      <c r="S18" t="n">
-        <v>21</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.24019608</v>
+        <v>0.23076923</v>
       </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.19125684</v>
+        <v>0.19371727</v>
       </c>
       <c r="C19" t="n">
         <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" t="n">
-        <v>0.28708133</v>
+        <v>0.26666668</v>
       </c>
       <c r="I19" t="n">
+        <v>29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.31937173</v>
+      </c>
+      <c r="K19" t="n">
+        <v>28</v>
+      </c>
+      <c r="L19" t="n">
+        <v>52</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.1132073</v>
+      </c>
+      <c r="O19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.5283018</v>
+      </c>
+      <c r="S19" t="n">
         <v>25</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.32240438</v>
-      </c>
-      <c r="K19" t="n">
-        <v>29</v>
-      </c>
-      <c r="L19" t="n">
-        <v>53</v>
-      </c>
-      <c r="M19" t="n">
-        <v>18</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.470588</v>
-      </c>
-      <c r="O19" t="n">
-        <v>25</v>
-      </c>
-      <c r="P19" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>16</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4313725</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>0.26666668</v>
+      </c>
+      <c r="U19" t="n">
         <v>22</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.22564103</v>
-      </c>
-      <c r="U19" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -4006,61 +4006,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.30875576</v>
+        <v>0.2614679</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.33870968</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.44954127</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>47</v>
+      </c>
+      <c r="M20" t="n">
         <v>14</v>
       </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.38554215</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5529954</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>44</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7</v>
-      </c>
       <c r="N20" t="n">
-        <v>5.6037736</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3018868</v>
+        <v>1.3333334</v>
       </c>
       <c r="S20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T20" t="n">
-        <v>0.28504673</v>
+        <v>0.28037384</v>
       </c>
       <c r="U20" t="n">
         <v>26</v>
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.27319586</v>
+        <v>0.2735043</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3364486</v>
+        <v>0.32677165</v>
       </c>
       <c r="I21" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>48</v>
+      </c>
+      <c r="M21" t="n">
+        <v>16</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.857143</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
         <v>10</v>
       </c>
-      <c r="J21" t="n">
-        <v>0.45876288</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>43</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.245283</v>
-      </c>
-      <c r="O21" t="n">
-        <v>16</v>
-      </c>
-      <c r="P21" t="n">
-        <v>15</v>
-      </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1509434</v>
+        <v>1.1269841</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22110553</v>
+        <v>0.21276596</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2173913</v>
+        <v>0.2415459</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H22" t="n">
-        <v>0.26422763</v>
+        <v>0.29596412</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>0.37391305</v>
+        <v>0.38164252</v>
       </c>
       <c r="K22" t="n">
+        <v>21</v>
+      </c>
+      <c r="L22" t="n">
+        <v>44</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.863354</v>
+      </c>
+      <c r="O22" t="n">
+        <v>22</v>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>22</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.5279503</v>
+      </c>
+      <c r="S22" t="n">
         <v>24</v>
       </c>
-      <c r="L22" t="n">
-        <v>56</v>
-      </c>
-      <c r="M22" t="n">
-        <v>21</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.2408376</v>
-      </c>
-      <c r="O22" t="n">
-        <v>15</v>
-      </c>
-      <c r="P22" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>26</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3193717</v>
-      </c>
-      <c r="S22" t="n">
-        <v>18</v>
-      </c>
       <c r="T22" t="n">
-        <v>0.27125505</v>
+        <v>0.30660376</v>
       </c>
       <c r="U22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25373134</v>
+        <v>0.2413793</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
         <v>21</v>
       </c>
-      <c r="E23" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
+        <v>0.30941704</v>
+      </c>
+      <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.33990148</v>
+      </c>
+      <c r="K23" t="n">
+        <v>26</v>
+      </c>
+      <c r="L23" t="n">
+        <v>40</v>
+      </c>
+      <c r="M23" t="n">
         <v>6</v>
       </c>
-      <c r="G23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.3105023</v>
-      </c>
-      <c r="I23" t="n">
-        <v>19</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.3880597</v>
-      </c>
-      <c r="K23" t="n">
-        <v>17</v>
-      </c>
-      <c r="L23" t="n">
-        <v>30</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
       <c r="N23" t="n">
-        <v>3.6346154</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0576923</v>
+        <v>1.2692307</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>0.22340426</v>
+        <v>0.23529412</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.30541873</v>
+        <v>0.3288889</v>
       </c>
       <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>40</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.37551022</v>
+      </c>
+      <c r="I24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="n">
-        <v>35</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.37117904</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
       <c r="J24" t="n">
-        <v>0.5073892</v>
+        <v>0.5511111</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>5.6037736</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
+        <v>22</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4150944</v>
+      </c>
+      <c r="S24" t="n">
         <v>21</v>
       </c>
-      <c r="R24" t="n">
-        <v>0.962963</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
       <c r="T24" t="n">
-        <v>0.18877551</v>
+        <v>0.2688679</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.22727273</v>
+        <v>0.24757281</v>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>13</v>
       </c>
       <c r="H25" t="n">
-        <v>0.28372094</v>
+        <v>0.3171806</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>0.37878788</v>
+        <v>0.41262135</v>
       </c>
       <c r="K25" t="n">
+        <v>16</v>
+      </c>
+      <c r="L25" t="n">
+        <v>60</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.754717</v>
+      </c>
+      <c r="O25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4150944</v>
+      </c>
+      <c r="S25" t="n">
+        <v>21</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2669903</v>
+      </c>
+      <c r="U25" t="n">
         <v>23</v>
-      </c>
-      <c r="L25" t="n">
-        <v>52</v>
-      </c>
-      <c r="M25" t="n">
-        <v>17</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.9272728</v>
-      </c>
-      <c r="O25" t="n">
-        <v>12</v>
-      </c>
-      <c r="P25" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>11</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4545455</v>
-      </c>
-      <c r="S25" t="n">
-        <v>24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.25592417</v>
-      </c>
-      <c r="U25" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.27962086</v>
+        <v>0.2834008</v>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3490909</v>
+      </c>
+      <c r="I26" t="n">
         <v>7</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I26" t="n">
-        <v>13</v>
-      </c>
       <c r="J26" t="n">
-        <v>0.45971563</v>
+        <v>0.48582995</v>
       </c>
       <c r="K26" t="n">
         <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3333333</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1296296</v>
+        <v>1.2833333</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T26" t="n">
-        <v>0.21</v>
+        <v>0.24122807</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.27102804</v>
+        <v>0.2408377</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3510204</v>
+        <v>0.3116279</v>
       </c>
       <c r="I27" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.35078534</v>
+      </c>
+      <c r="K27" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" t="n">
+        <v>43</v>
+      </c>
+      <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.4150944</v>
+      </c>
+      <c r="O27" t="n">
+        <v>14</v>
+      </c>
+      <c r="P27" t="n">
         <v>5</v>
       </c>
-      <c r="J27" t="n">
-        <v>0.38317758</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20</v>
-      </c>
-      <c r="L27" t="n">
-        <v>45</v>
-      </c>
-      <c r="M27" t="n">
-        <v>11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.725</v>
-      </c>
-      <c r="O27" t="n">
-        <v>19</v>
-      </c>
-      <c r="P27" t="n">
-        <v>7</v>
-      </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36875</v>
+        <v>1.4150944</v>
       </c>
       <c r="S27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25373134</v>
+        <v>0.23737374</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.24870466</v>
+        <v>0.2513369</v>
       </c>
       <c r="C28" t="n">
         <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32579187</v>
+        <v>0.3106796</v>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4041451</v>
+        <v>0.4331551</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5961537</v>
+        <v>2.2075472</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.0384616</v>
+        <v>0.8490566000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.21465969</v>
+        <v>0.17391305</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.25490198</v>
+        <v>0.23469388</v>
       </c>
       <c r="C29" t="n">
+        <v>22</v>
+      </c>
+      <c r="D29" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.30555555</v>
+      </c>
+      <c r="I29" t="n">
+        <v>22</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3469388</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25</v>
+      </c>
+      <c r="L29" t="n">
+        <v>59</v>
+      </c>
+      <c r="M29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.5882354</v>
+      </c>
+      <c r="O29" t="n">
+        <v>18</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q29" t="n">
         <v>10</v>
       </c>
-      <c r="D29" t="n">
-        <v>30</v>
-      </c>
-      <c r="E29" t="n">
-        <v>12</v>
-      </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.34199134</v>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.4362745</v>
-      </c>
-      <c r="K29" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" t="n">
-        <v>63</v>
-      </c>
-      <c r="M29" t="n">
-        <v>26</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.9411764</v>
-      </c>
-      <c r="O29" t="n">
-        <v>22</v>
-      </c>
-      <c r="P29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.254902</v>
+        <v>1.2156863</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23979592</v>
+        <v>0.234375</v>
       </c>
       <c r="U29" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.275</v>
+        <v>0.255</v>
       </c>
       <c r="C30" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.34210527</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K30" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" t="n">
+        <v>47</v>
+      </c>
+      <c r="M30" t="n">
+        <v>14</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.4150944</v>
+      </c>
+      <c r="O30" t="n">
+        <v>14</v>
+      </c>
+      <c r="P30" t="n">
         <v>6</v>
       </c>
-      <c r="D30" t="n">
-        <v>21</v>
-      </c>
-      <c r="E30" t="n">
-        <v>25</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="Q30" t="n">
         <v>10</v>
       </c>
-      <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.33484164</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="R30" t="n">
+        <v>1.3773584</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.23671497</v>
+      </c>
+      <c r="U30" t="n">
         <v>11</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="K30" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" t="n">
-        <v>43</v>
-      </c>
-      <c r="M30" t="n">
-        <v>5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.180645</v>
-      </c>
-      <c r="O30" t="n">
-        <v>13</v>
-      </c>
-      <c r="P30" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>21</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.1612903</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.20304568</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.21105528</v>
+        <v>0.26060605</v>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
         <v>22</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H31" t="n">
-        <v>0.28181818</v>
+        <v>0.33152175</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J31" t="n">
-        <v>0.36180905</v>
+        <v>0.3939394</v>
       </c>
       <c r="K31" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L31" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O31" t="n">
         <v>21</v>
       </c>
-      <c r="N31" t="n">
-        <v>5.647059</v>
-      </c>
-      <c r="O31" t="n">
-        <v>27</v>
-      </c>
       <c r="P31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4705882</v>
+        <v>1.2222222</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25520834</v>
+        <v>0.2037037</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24328563</v>
+        <v>0.24357477</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3157158</v>
+        <v>0.31577116</v>
       </c>
       <c r="I2" t="n">
         <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3961968</v>
+        <v>0.39739096</v>
       </c>
       <c r="K2" t="n">
         <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.094535</v>
+        <v>4.0873075</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27548</v>
+        <v>1.2773294</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24824767</v>
+        <v>0.24845321</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24487405</v>
+        <v>0.24481086</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3176718</v>
+        <v>0.31718367</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4022652</v>
+        <v>0.40252182</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.395958</v>
+        <v>5.390625</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.498503</v>
+        <v>1.4962797</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27028582</v>
+        <v>0.27024966</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2475151</v>
+        <v>0.24738675</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -698,43 +698,43 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31104445</v>
+        <v>0.3106592</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4106412</v>
+        <v>0.41018197</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1229</v>
+        <v>1238</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6066666</v>
+        <v>3.638439</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q4" t="n">
         <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2474074</v>
+        <v>1.2511046</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23291741</v>
+        <v>0.23372024</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,46 +747,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23428571</v>
+        <v>0.23444226</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3152288</v>
+        <v>0.31511366</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3942857</v>
+        <v>0.3960861</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1428</v>
+        <v>1439</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1635513</v>
+        <v>4.1426826</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
         <v>166</v>
@@ -795,16 +795,16 @@
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3494835</v>
+        <v>1.3464451</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25408733</v>
+        <v>0.25377414</v>
       </c>
       <c r="U5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24772996</v>
+        <v>0.24690874</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32166725</v>
+        <v>0.32103515</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40307936</v>
+        <v>0.4019627</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.591067</v>
+        <v>3.6097682</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -862,13 +862,13 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2364764</v>
+        <v>1.2402565</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24199921</v>
+        <v>0.24284033</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -881,43 +881,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25091118</v>
+        <v>0.25157234</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33930066</v>
+        <v>0.33981714</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4289277</v>
+        <v>0.43148467</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.191599</v>
+        <v>4.1903367</v>
       </c>
       <c r="O7" t="n">
         <v>18</v>
@@ -929,13 +929,13 @@
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2711865</v>
+        <v>1.2693998</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24468708</v>
+        <v>0.24457784</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23482902</v>
+        <v>0.23478602</v>
       </c>
       <c r="C8" t="n">
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31914893</v>
+        <v>0.31895357</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40284643</v>
+        <v>0.40282685</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.119325</v>
+        <v>4.121578</v>
       </c>
       <c r="O8" t="n">
         <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3061275</v>
+        <v>1.3065351</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24135205</v>
+        <v>0.24091177</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2286397</v>
+        <v>0.22971903</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30636865</v>
+        <v>0.30736694</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39474207</v>
+        <v>0.3961219</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>1445</v>
+        <v>1450</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>4.870509</v>
+        <v>4.851301</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
@@ -1063,16 +1063,16 @@
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4446108</v>
+        <v>1.4460967</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2541845</v>
+        <v>0.25391608</v>
       </c>
       <c r="U9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -1082,61 +1082,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23688363</v>
+        <v>0.2364706</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G10" t="n">
         <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3141554</v>
+        <v>0.31410146</v>
       </c>
       <c r="I10" t="n">
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37475345</v>
+        <v>0.3745098</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8009386</v>
+        <v>3.795633</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2640158</v>
+        <v>1.263003</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23671784</v>
+        <v>0.2366621</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2545207</v>
+        <v>0.25376883</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32404667</v>
+        <v>0.3235854</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4188217</v>
+        <v>0.4178585</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.571213</v>
+        <v>5.5943513</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5301963</v>
+        <v>1.531867</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28812274</v>
+        <v>0.28850856</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,46 +1216,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23963858</v>
+        <v>0.23946136</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>171</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31698376</v>
+        <v>0.31685743</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>0.399725</v>
+        <v>0.39871195</v>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6430173</v>
+        <v>3.6414254</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>155</v>
@@ -1264,13 +1264,13 @@
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2218074</v>
+        <v>1.2234595</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2326139</v>
+        <v>0.23296921</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23939215</v>
+        <v>0.23941177</v>
       </c>
       <c r="C13" t="n">
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31356978</v>
+        <v>0.31334385</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40872312</v>
+        <v>0.40862745</v>
       </c>
       <c r="K13" t="n">
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5313745</v>
+        <v>4.527826</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3453686</v>
+        <v>1.3475143</v>
       </c>
       <c r="S13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23813322</v>
+        <v>0.23806694</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24505928</v>
+        <v>0.24494603</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E14" t="n">
         <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3148936</v>
+        <v>0.3152059</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3986166</v>
+        <v>0.39882237</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6308928</v>
+        <v>4.6132007</v>
       </c>
       <c r="O14" t="n">
         <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q14" t="n">
         <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3871615</v>
+        <v>1.385305</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25789267</v>
+        <v>0.2577926</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23365785</v>
+        <v>0.23401736</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
@@ -1432,28 +1432,28 @@
         <v>146</v>
       </c>
       <c r="G15" t="n">
+        <v>29</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.30890146</v>
+      </c>
+      <c r="I15" t="n">
         <v>28</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.3082399</v>
-      </c>
-      <c r="I15" t="n">
-        <v>29</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.37174648</v>
+        <v>0.37115234</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1433</v>
+        <v>1444</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.194896</v>
+        <v>4.207008</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
@@ -1465,13 +1465,13 @@
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3375031</v>
+        <v>1.3404572</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2357756</v>
+        <v>0.23597065</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2550296</v>
+        <v>0.2547521</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
@@ -1502,43 +1502,43 @@
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33663023</v>
+        <v>0.33683667</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42130178</v>
+        <v>0.420145</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6359103</v>
+        <v>3.6544373</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1596011</v>
+        <v>1.1638572</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21933535</v>
+        <v>0.22048819</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24901342</v>
+        <v>0.2492163</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32669115</v>
+        <v>0.32685298</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40114444</v>
+        <v>0.401058</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.103139</v>
+        <v>4.0957685</v>
       </c>
       <c r="O17" t="n">
         <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2825112</v>
+        <v>1.2828507</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23522411</v>
+        <v>0.23557219</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25920156</v>
+        <v>0.2592306</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1633,46 +1633,46 @@
         <v>146</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3416638</v>
+        <v>0.34149244</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40584224</v>
+        <v>0.40518075</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>1267</v>
+        <v>1279</v>
       </c>
       <c r="M18" t="n">
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5568464</v>
+        <v>3.559784</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1870984</v>
+        <v>1.1888044</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22297703</v>
+        <v>0.22376512</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24340291</v>
+        <v>0.24345447</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="E19" t="n">
         <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31739894</v>
+        <v>0.3174686</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40350533</v>
+        <v>0.40308714</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>1201</v>
+        <v>1212</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.70388</v>
+        <v>4.6717896</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
@@ -1733,13 +1733,13 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3794744</v>
+        <v>1.3765494</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25156128</v>
+        <v>0.25106382</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23798312</v>
+        <v>0.23777041</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
@@ -1770,46 +1770,46 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30857447</v>
+        <v>0.30808347</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3951344</v>
+        <v>0.39388034</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.16002</v>
+        <v>4.178888</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q20" t="n">
         <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2982413</v>
+        <v>1.2977363</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24080595</v>
+        <v>0.24091704</v>
       </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23557693</v>
+        <v>0.23521239</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
@@ -1834,46 +1834,46 @@
         <v>209</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31239966</v>
+        <v>0.31200284</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41105768</v>
+        <v>0.4092894</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1377</v>
+        <v>1394</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2066667</v>
+        <v>3.19163</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1614815</v>
+        <v>1.1622614</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22244368</v>
+        <v>0.22266166</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24190363</v>
+        <v>0.24146055</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
@@ -1904,25 +1904,25 @@
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31119376</v>
+        <v>0.31200564</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39968404</v>
+        <v>0.39870435</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="M22" t="n">
         <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0124254</v>
+        <v>3.9856825</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
@@ -1934,13 +1934,13 @@
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2837971</v>
+        <v>1.279684</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24732229</v>
+        <v>0.24666022</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,43 +1953,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25279385</v>
+        <v>0.25334865</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33002058</v>
+        <v>0.33015496</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40057802</v>
+        <v>0.40221968</v>
       </c>
       <c r="K23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>1405</v>
+        <v>1418</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1815934</v>
+        <v>4.1870236</v>
       </c>
       <c r="O23" t="n">
         <v>17</v>
@@ -2001,16 +2001,16 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3003464</v>
+        <v>1.3013024</v>
       </c>
       <c r="S23" t="n">
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23671784</v>
+        <v>0.23691407</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24043278</v>
+        <v>0.24120103</v>
       </c>
       <c r="C24" t="n">
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="E24" t="n">
         <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31639022</v>
+        <v>0.31699115</v>
       </c>
       <c r="I24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39290723</v>
+        <v>0.39431298</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L24" t="n">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9638584</v>
+        <v>3.957415</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2883848</v>
+        <v>1.2857143</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24164678</v>
+        <v>0.24095671</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24747671</v>
+        <v>0.24816956</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30887282</v>
+        <v>0.30969888</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40722048</v>
+        <v>0.40751445</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3624163</v>
+        <v>4.343449</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
@@ -2135,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.360179</v>
+        <v>1.3589933</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24808033</v>
+        <v>0.24736018</v>
       </c>
       <c r="U25" t="n">
         <v>19</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23203327</v>
+        <v>0.23225172</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
@@ -2169,28 +2169,28 @@
         <v>175</v>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31176367</v>
+        <v>0.31239092</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37992477</v>
+        <v>0.37974435</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4.223576</v>
+        <v>4.208745</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
@@ -2202,13 +2202,13 @@
         <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2549117</v>
+        <v>1.2576581</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25029355</v>
+        <v>0.2505345</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24283206</v>
+        <v>0.24215421</v>
       </c>
       <c r="C27" t="n">
         <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
@@ -2239,46 +2239,46 @@
         <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31624675</v>
+        <v>0.31591654</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38365516</v>
+        <v>0.3822162</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1194</v>
+        <v>1204</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2918305</v>
+        <v>4.280166</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3538387</v>
+        <v>1.3563752</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.253543</v>
+        <v>0.25419155</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2604208</v>
+        <v>0.26044953</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E28" t="n">
         <v>12</v>
@@ -2306,43 +2306,43 @@
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32846195</v>
+        <v>0.32807794</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40651053</v>
+        <v>0.40654573</v>
       </c>
       <c r="K28" t="n">
         <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7572815</v>
+        <v>3.7522256</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1389096</v>
+        <v>1.1372404</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22911265</v>
+        <v>0.22915429</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24312475</v>
+        <v>0.24396518</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
@@ -2370,46 +2370,46 @@
         <v>173</v>
       </c>
       <c r="G29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31741223</v>
+        <v>0.3180531</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39876446</v>
+        <v>0.39948556</v>
       </c>
       <c r="K29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L29" t="n">
-        <v>1290</v>
+        <v>1299</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3082933</v>
+        <v>4.299449</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3082933</v>
+        <v>1.3039559</v>
       </c>
       <c r="S29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24946068</v>
+        <v>0.24863495</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2483915</v>
+        <v>0.24864341</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -2440,25 +2440,25 @@
         <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3106556</v>
+        <v>0.31085354</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38506532</v>
+        <v>0.38468993</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9370837</v>
+        <v>3.9176471</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
@@ -2467,16 +2467,16 @@
         <v>158</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2982975</v>
+        <v>1.2977941</v>
       </c>
       <c r="S30" t="n">
         <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23614125</v>
+        <v>0.23598589</v>
       </c>
       <c r="U30" t="n">
         <v>9</v>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2481174</v>
+        <v>0.24745633</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
         <v>778</v>
@@ -2504,28 +2504,28 @@
         <v>200</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.323575</v>
+        <v>0.32282925</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42749566</v>
+        <v>0.42599347</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="M31" t="n">
         <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7238307</v>
+        <v>4.7123895</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
@@ -2537,13 +2537,13 @@
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3853006</v>
+        <v>1.3893806</v>
       </c>
       <c r="S31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25344193</v>
+        <v>0.25294003</v>
       </c>
       <c r="U31" t="n">
         <v>24</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.27230048</v>
+        <v>0.2744186</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.34583333</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4976744</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>52</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.857143</v>
+      </c>
+      <c r="O2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.46948355</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>49</v>
-      </c>
-      <c r="M2" t="n">
-        <v>18</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.090909</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S2" t="n">
         <v>11</v>
       </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5</v>
-      </c>
       <c r="T2" t="n">
-        <v>0.24880382</v>
+        <v>0.25462964</v>
       </c>
       <c r="U2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2195122</v>
+        <v>0.23529412</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2849162</v>
+        <v>0.28961748</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>0.36585367</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>6.5454545</v>
       </c>
       <c r="O3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6888889</v>
+        <v>1.7272727</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3114754</v>
+        <v>0.32258064</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2658228</v>
+        <v>0.27868852</v>
       </c>
       <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
         <v>9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.33333334</v>
+        <v>0.33948338</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>0.43459916</v>
+        <v>0.44262296</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N4" t="n">
-        <v>4.359375</v>
+        <v>4.571429</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28125</v>
+        <v>1.3333334</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25104603</v>
+        <v>0.25833333</v>
       </c>
       <c r="U4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -3001,61 +3001,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24651162</v>
+        <v>0.23963134</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2918455</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4423963</v>
+      </c>
+      <c r="K5" t="n">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.30341882</v>
-      </c>
-      <c r="I5" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.40465117</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
         <v>17</v>
       </c>
-      <c r="L5" t="n">
-        <v>77</v>
-      </c>
-      <c r="M5" t="n">
-        <v>29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.6666665</v>
-      </c>
-      <c r="O5" t="n">
-        <v>19</v>
-      </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
+        <v>21</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4814814</v>
+      </c>
+      <c r="S5" t="n">
         <v>27</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.537037</v>
-      </c>
-      <c r="S5" t="n">
-        <v>26</v>
-      </c>
       <c r="T5" t="n">
-        <v>0.27230048</v>
+        <v>0.26540285</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24242425</v>
+        <v>0.22012578</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.30555555</v>
+        <v>0.29545453</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.37575758</v>
+        <v>0.33962265</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0681818</v>
+        <v>3.139535</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.3023256</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24375</v>
+        <v>0.24390244</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24598931</v>
+        <v>0.27748692</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3632287</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>21</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.3438914</v>
-      </c>
-      <c r="I7" t="n">
-        <v>9</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.40106952</v>
+        <v>0.5026178</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9056604</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="n">
         <v>10</v>
       </c>
-      <c r="P7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>18</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.3396226</v>
+        <v>1.2777778</v>
       </c>
       <c r="S7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2364532</v>
+        <v>0.23152709</v>
       </c>
       <c r="U7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3202,46 +3202,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20535715</v>
+        <v>0.20353982</v>
       </c>
       <c r="C8" t="n">
         <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3345588</v>
+        <v>0.3272059</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>0.32142857</v>
+        <v>0.32300884</v>
       </c>
       <c r="K8" t="n">
         <v>27</v>
       </c>
       <c r="L8" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5604396</v>
+        <v>3.6201117</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P8" t="n">
         <v>7</v>
@@ -3250,16 +3250,16 @@
         <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2197802</v>
+        <v>1.2067039</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24782608</v>
+        <v>0.2300885</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.19072165</v>
+        <v>0.22564103</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.28301886</v>
+      </c>
+      <c r="I9" t="n">
         <v>28</v>
       </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
+        <v>0.35897437</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" t="n">
+        <v>54</v>
+      </c>
+      <c r="M9" t="n">
         <v>21</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.24038461</v>
-      </c>
-      <c r="I9" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3041237</v>
-      </c>
-      <c r="K9" t="n">
-        <v>30</v>
-      </c>
-      <c r="L9" t="n">
-        <v>62</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>7.7884617</v>
+      </c>
+      <c r="O9" t="n">
+        <v>29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
         <v>28</v>
       </c>
-      <c r="N9" t="n">
-        <v>10.058824</v>
-      </c>
-      <c r="O9" t="n">
-        <v>30</v>
-      </c>
-      <c r="P9" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>30</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.882353</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3222749</v>
+        <v>0.2961165</v>
       </c>
       <c r="U9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24271844</v>
+        <v>0.23</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3173913</v>
+        <v>0.3141593</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.44174758</v>
+        <v>0.425</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>3.5660377</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2692307</v>
+        <v>1.1886792</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23589744</v>
+        <v>0.22335026</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.28225806</v>
+        <v>0.2782258</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34558824</v>
+        <v>0.34671533</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.47580644</v>
+        <v>0.46370968</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>8.068966</v>
+        <v>8.389830999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
         <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8103448</v>
+        <v>1.8813559</v>
       </c>
       <c r="S11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.30801687</v>
+        <v>0.3237705</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.28643215</v>
+        <v>0.28078818</v>
       </c>
       <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
-        <v>48</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.38333333</v>
+      </c>
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>13</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.39834026</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
       <c r="J12" t="n">
-        <v>0.5125628</v>
+        <v>0.4827586</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8333333</v>
+        <v>3.0566037</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1481482</v>
+        <v>1.264151</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23</v>
+        <v>0.24875621</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.21649484</v>
+        <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2761905</v>
+        <v>0.26794258</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41752577</v>
+        <v>0.37894738</v>
       </c>
       <c r="K13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>5.0066223</v>
+        <v>4.0324674</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
         <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2119206</v>
+        <v>1.1688312</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23809524</v>
+        <v>0.21808511</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.19620253</v>
+        <v>0.19512194</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -3619,31 +3619,31 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2784091</v>
+        <v>0.29032257</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>0.31012657</v>
+        <v>0.3109756</v>
       </c>
       <c r="K14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
         <v>3.642857</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
         <v>6</v>
@@ -3652,16 +3652,16 @@
         <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2142857</v>
+        <v>1.1428572</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>0.24528302</v>
+        <v>0.2389937</v>
       </c>
       <c r="U14" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.21505377</v>
+        <v>0.2010582</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.30493274</v>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="K15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62</v>
+      </c>
+      <c r="M15" t="n">
         <v>27</v>
       </c>
-      <c r="E15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>13</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.30697674</v>
-      </c>
-      <c r="I15" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.4032258</v>
-      </c>
-      <c r="K15" t="n">
-        <v>18</v>
-      </c>
-      <c r="L15" t="n">
-        <v>56</v>
-      </c>
-      <c r="M15" t="n">
-        <v>24</v>
-      </c>
       <c r="N15" t="n">
-        <v>4.1273885</v>
+        <v>4.471338</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3184713</v>
+        <v>1.4331211</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="T15" t="n">
-        <v>0.25603864</v>
+        <v>0.26213592</v>
       </c>
       <c r="U15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23469388</v>
+        <v>0.20418848</v>
       </c>
       <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3347826</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.36649215</v>
+      </c>
+      <c r="K16" t="n">
         <v>22</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
-      </c>
-      <c r="E16" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.35193133</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.46938777</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8</v>
       </c>
       <c r="L16" t="n">
         <v>41</v>
       </c>
       <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.3529413</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="n">
         <v>7</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.4230769</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.0384616</v>
+        <v>1.2156863</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>0.20634921</v>
+        <v>0.24210526</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.28636363</v>
+        <v>0.25358853</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" t="n">
-        <v>7</v>
-      </c>
       <c r="G17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>0.35365853</v>
+        <v>0.32188842</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J17" t="n">
-        <v>0.45</v>
+        <v>0.39712918</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N17" t="n">
-        <v>6.018072</v>
+        <v>4.066265</v>
       </c>
       <c r="O17" t="n">
+        <v>19</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q17" t="n">
         <v>27</v>
       </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>22</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.5542169</v>
+        <v>1.3915663</v>
       </c>
       <c r="S17" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25925925</v>
+        <v>0.24285714</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -3878,58 +3878,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.39805827</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.3960396</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.5888889</v>
+        <v>0.5464481</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.2666667</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>0.23076923</v>
+        <v>0.26285714</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.19371727</v>
+        <v>0.20895523</v>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" t="n">
-        <v>0.26666668</v>
+        <v>0.2825112</v>
       </c>
       <c r="I19" t="n">
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>0.31937173</v>
+        <v>0.31840795</v>
       </c>
       <c r="K19" t="n">
         <v>28</v>
       </c>
       <c r="L19" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M19" t="n">
+        <v>22</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.8103447</v>
+      </c>
+      <c r="O19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="n">
         <v>21</v>
       </c>
-      <c r="N19" t="n">
-        <v>6.1132073</v>
-      </c>
-      <c r="O19" t="n">
-        <v>28</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>22</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.5283018</v>
+        <v>1.3793104</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T19" t="n">
-        <v>0.26666668</v>
+        <v>0.2555066</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2614679</v>
+        <v>0.23222749</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="n">
-        <v>11</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
       <c r="H20" t="n">
-        <v>0.33870968</v>
+        <v>0.29613733</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>0.44954127</v>
+        <v>0.3886256</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M20" t="n">
+        <v>13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.8333333</v>
+      </c>
+      <c r="O20" t="n">
         <v>14</v>
       </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>23</v>
-      </c>
       <c r="P20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>29</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.0925926</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.24257426</v>
+      </c>
+      <c r="U20" t="n">
         <v>12</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>28</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3333334</v>
-      </c>
-      <c r="S20" t="n">
-        <v>18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.28037384</v>
-      </c>
-      <c r="U20" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2735043</v>
+        <v>0.26506025</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32677165</v>
+        <v>0.31985295</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.437751</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.857143</v>
+        <v>2.8636363</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
         <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1269841</v>
+        <v>1.1818181</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>0.21276596</v>
+        <v>0.22540984</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -4140,61 +4140,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2415459</v>
+        <v>0.21393035</v>
       </c>
       <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23</v>
+      </c>
+      <c r="E22" t="n">
         <v>19</v>
       </c>
-      <c r="D22" t="n">
-        <v>31</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.30088496</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" t="n">
+        <v>39</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.689441</v>
+      </c>
+      <c r="O22" t="n">
         <v>13</v>
       </c>
-      <c r="F22" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="P22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" t="n">
         <v>19</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.29596412</v>
-      </c>
-      <c r="I22" t="n">
-        <v>25</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.38164252</v>
-      </c>
-      <c r="K22" t="n">
-        <v>21</v>
-      </c>
-      <c r="L22" t="n">
-        <v>44</v>
-      </c>
-      <c r="M22" t="n">
-        <v>11</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.863354</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
+        <v>1.416149</v>
+      </c>
+      <c r="S22" t="n">
         <v>22</v>
       </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>22</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5279503</v>
-      </c>
-      <c r="S22" t="n">
-        <v>24</v>
-      </c>
       <c r="T22" t="n">
-        <v>0.30660376</v>
+        <v>0.27804878</v>
       </c>
       <c r="U22" t="n">
         <v>27</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2413793</v>
+        <v>0.24878049</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
         <v>16</v>
@@ -4219,52 +4219,52 @@
         <v>27</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>0.30941704</v>
+        <v>0.3063063</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>0.33990148</v>
+        <v>0.38536584</v>
       </c>
       <c r="K23" t="n">
+        <v>18</v>
+      </c>
+      <c r="L23" t="n">
+        <v>48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.019231</v>
+      </c>
+      <c r="O23" t="n">
         <v>26</v>
       </c>
-      <c r="L23" t="n">
-        <v>40</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3076923</v>
+      </c>
+      <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="P23" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2692307</v>
-      </c>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23529412</v>
+        <v>0.23958333</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3288889</v>
+        <v>0.31555554</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
@@ -4283,22 +4283,22 @@
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.37551022</v>
+        <v>0.36437246</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5511111</v>
+        <v>0.53333336</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
@@ -4307,31 +4307,31 @@
         <v>43</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>5.6037736</v>
+        <v>5.773585</v>
       </c>
       <c r="O24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P24" t="n">
         <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4150944</v>
+        <v>1.4339622</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T24" t="n">
         <v>0.2688679</v>
       </c>
       <c r="U24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24757281</v>
+        <v>0.254717</v>
       </c>
       <c r="C25" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" t="n">
+        <v>32</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.33050847</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4198113</v>
+      </c>
+      <c r="K25" t="n">
         <v>14</v>
       </c>
-      <c r="D25" t="n">
-        <v>33</v>
-      </c>
-      <c r="E25" t="n">
-        <v>11</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>13</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.3171806</v>
-      </c>
-      <c r="I25" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.41262135</v>
-      </c>
-      <c r="K25" t="n">
-        <v>16</v>
-      </c>
       <c r="L25" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N25" t="n">
-        <v>4.754717</v>
+        <v>4.3333335</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4150944</v>
+        <v>1.4074074</v>
       </c>
       <c r="S25" t="n">
         <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2669903</v>
+        <v>0.24880382</v>
       </c>
       <c r="U25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2834008</v>
+        <v>0.29083666</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3490909</v>
+        <v>0.36491227</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.48582995</v>
+        <v>0.49003986</v>
       </c>
       <c r="K26" t="n">
         <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
         <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
+        <v>15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3666667</v>
+      </c>
+      <c r="S26" t="n">
         <v>18</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.2833333</v>
-      </c>
-      <c r="S26" t="n">
-        <v>16</v>
-      </c>
       <c r="T26" t="n">
-        <v>0.24122807</v>
+        <v>0.2521739</v>
       </c>
       <c r="U26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2408377</v>
+        <v>0.22164948</v>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>29</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3116279</v>
+        <v>0.29864255</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>0.35078534</v>
+        <v>0.31443298</v>
       </c>
       <c r="K27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M27" t="n">
+        <v>13</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O27" t="n">
         <v>9</v>
       </c>
-      <c r="N27" t="n">
-        <v>4.4150944</v>
-      </c>
-      <c r="O27" t="n">
-        <v>14</v>
-      </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4150944</v>
+        <v>1.4727273</v>
       </c>
       <c r="S27" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23737374</v>
+        <v>0.24509804</v>
       </c>
       <c r="U27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -4542,34 +4542,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2513369</v>
+        <v>0.24468085</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
         <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3106796</v>
+        <v>0.2920792</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4331551</v>
+        <v>0.43617022</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L28" t="n">
         <v>36</v>
@@ -4578,28 +4578,28 @@
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.2075472</v>
+        <v>2.3773584</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8490566000000001</v>
+        <v>0.8867925</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.17391305</v>
+        <v>0.19473684</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4609,34 +4609,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.23469388</v>
+        <v>0.26130652</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
+        <v>28</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.32876712</v>
+      </c>
+      <c r="I29" t="n">
+        <v>13</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.36683416</v>
+      </c>
+      <c r="K29" t="n">
         <v>21</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.30555555</v>
-      </c>
-      <c r="I29" t="n">
-        <v>22</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.3469388</v>
-      </c>
-      <c r="K29" t="n">
-        <v>25</v>
       </c>
       <c r="L29" t="n">
         <v>59</v>
@@ -4645,28 +4645,28 @@
         <v>25</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5882354</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2156863</v>
+        <v>1.1346154</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0.234375</v>
+        <v>0.21989529</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.255</v>
+        <v>0.27</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" t="n">
-        <v>0.34210527</v>
+        <v>0.35371178</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>0.42</v>
+        <v>0.435</v>
       </c>
       <c r="K30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L30" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4150944</v>
+        <v>4.1666665</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3773584</v>
+        <v>1.4444444</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23671497</v>
+        <v>0.24528302</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.26060605</v>
+        <v>0.2621951</v>
       </c>
       <c r="C31" t="n">
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>29</v>
       </c>
       <c r="H31" t="n">
-        <v>0.33152175</v>
+        <v>0.32967034</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3939394</v>
+        <v>0.38414633</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L31" t="n">
         <v>41</v>
       </c>
       <c r="M31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.5217392</v>
+      </c>
+      <c r="O31" t="n">
         <v>7</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>21</v>
-      </c>
       <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="n">
         <v>7</v>
       </c>
-      <c r="Q31" t="n">
-        <v>15</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.2222222</v>
+        <v>1.173913</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2037037</v>
+        <v>0.14285715</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -555,7 +555,7 @@
         <v>678</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
         <v>154</v>
@@ -573,7 +573,7 @@
         <v>0.39739096</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>1128</v>
@@ -603,7 +603,7 @@
         <v>0.24845321</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24481086</v>
+        <v>0.24426451</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31718367</v>
+        <v>0.31664646</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40252182</v>
+        <v>0.40158087</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.390625</v>
+        <v>5.411982</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4962797</v>
+        <v>1.4992603</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27024966</v>
+        <v>0.2699375</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -707,13 +707,13 @@
         <v>0.41018197</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>1238</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
         <v>3.638439</v>
@@ -750,31 +750,31 @@
         <v>0.23444226</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>688</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>188</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
         <v>0.31511366</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
         <v>0.3960861</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>1439</v>
@@ -798,7 +798,7 @@
         <v>1.3464451</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
         <v>0.25377414</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24690874</v>
+        <v>0.2463429</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32103515</v>
+        <v>0.32082683</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4019627</v>
+        <v>0.4012093</v>
       </c>
       <c r="K6" t="n">
         <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6097682</v>
+        <v>3.6057339</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2402565</v>
+        <v>1.2379318</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24284033</v>
+        <v>0.24234146</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -948,43 +948,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23478602</v>
+        <v>0.2343872</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31895357</v>
+        <v>0.31863588</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40282685</v>
+        <v>0.40241998</v>
       </c>
       <c r="K8" t="n">
         <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1402</v>
+        <v>1413</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.121578</v>
+        <v>4.1009307</v>
       </c>
       <c r="O8" t="n">
         <v>14</v>
@@ -996,13 +996,13 @@
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3065351</v>
+        <v>1.3074473</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24091177</v>
+        <v>0.24096856</v>
       </c>
       <c r="U8" t="n">
         <v>13</v>
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22971903</v>
+        <v>0.22960487</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30736694</v>
+        <v>0.3068162</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3961219</v>
+        <v>0.39610773</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.851301</v>
+        <v>4.8722305</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4460967</v>
+        <v>1.4497784</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25391608</v>
+        <v>0.25446513</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -1091,7 +1091,7 @@
         <v>631</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>147</v>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25376883</v>
+        <v>0.253889</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -1167,43 +1167,43 @@
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3235854</v>
+        <v>0.32364574</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4178585</v>
+        <v>0.41732284</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5943513</v>
+        <v>5.61718</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.531867</v>
+        <v>1.535005</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28850856</v>
+        <v>0.28915438</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23946136</v>
+        <v>0.23952676</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E12" t="n">
         <v>14</v>
@@ -1231,46 +1231,46 @@
         <v>171</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31685743</v>
+        <v>0.31719503</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39871195</v>
+        <v>0.39798293</v>
       </c>
       <c r="K12" t="n">
         <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6414254</v>
+        <v>3.6398523</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q12" t="n">
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2234595</v>
+        <v>1.2228782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23296921</v>
+        <v>0.2325765</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23941177</v>
+        <v>0.23996884</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31334385</v>
+        <v>0.31376305</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40862745</v>
+        <v>0.41137514</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.527826</v>
+        <v>4.5110564</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3475143</v>
+        <v>1.3422605</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23806694</v>
+        <v>0.23729815</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24494603</v>
+        <v>0.2441452</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E14" t="n">
         <v>24</v>
@@ -1368,43 +1368,43 @@
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3152059</v>
+        <v>0.31449074</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39882237</v>
+        <v>0.3973458</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6132007</v>
+        <v>4.6258974</v>
       </c>
       <c r="O14" t="n">
         <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.385305</v>
+        <v>1.3867294</v>
       </c>
       <c r="S14" t="n">
         <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2577926</v>
+        <v>0.25822785</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23401736</v>
+        <v>0.23393416</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>146</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30890146</v>
+        <v>0.30871776</v>
       </c>
       <c r="I15" t="n">
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37115234</v>
+        <v>0.37029782</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1444</v>
+        <v>1458</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.207008</v>
+        <v>4.195856</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3404572</v>
+        <v>1.3394178</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23597065</v>
+        <v>0.23617399</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2547521</v>
+        <v>0.25530258</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33683667</v>
+        <v>0.33766454</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.420145</v>
+        <v>0.4212882</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6544373</v>
+        <v>3.6434376</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q16" t="n">
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1638572</v>
+        <v>1.1612904</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22048819</v>
+        <v>0.22043331</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1560,13 +1560,13 @@
         <v>681</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>157</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
         <v>0.32685298</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2592306</v>
+        <v>0.25921658</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34149244</v>
+        <v>0.34160337</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40518075</v>
+        <v>0.40495393</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>1279</v>
+        <v>1288</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>3.559784</v>
+        <v>3.5784721</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1888044</v>
+        <v>1.1906273</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22376512</v>
+        <v>0.2237776</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24345447</v>
+        <v>0.24359968</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E19" t="n">
         <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.31729272</v>
+      </c>
+      <c r="I19" t="n">
         <v>13</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.3174686</v>
-      </c>
-      <c r="I19" t="n">
-        <v>12</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.40308714</v>
+        <v>0.40283164</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>1212</v>
+        <v>1227</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6717896</v>
+        <v>4.6661744</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
@@ -1733,13 +1733,13 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3765494</v>
+        <v>1.3751847</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25106382</v>
+        <v>0.2508644</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23777041</v>
+        <v>0.23725528</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
@@ -1770,25 +1770,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30808347</v>
+        <v>0.30788004</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39388034</v>
+        <v>0.39251792</v>
       </c>
       <c r="K20" t="n">
         <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.178888</v>
+        <v>4.1645074</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
@@ -1800,13 +1800,13 @@
         <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2977363</v>
+        <v>1.2987045</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24091704</v>
+        <v>0.24111283</v>
       </c>
       <c r="U20" t="n">
         <v>14</v>
@@ -1828,7 +1828,7 @@
         <v>697</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
         <v>209</v>
@@ -1846,7 +1846,7 @@
         <v>0.4092894</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
         <v>1394</v>
@@ -1864,13 +1864,13 @@
         <v>156</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
         <v>1.1622614</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>0.22266166</v>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24146055</v>
+        <v>0.24165528</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
         <v>177</v>
@@ -1904,25 +1904,25 @@
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31200564</v>
+        <v>0.31231442</v>
       </c>
       <c r="I22" t="n">
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39870435</v>
+        <v>0.39820418</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="M22" t="n">
         <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9856825</v>
+        <v>3.9592938</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
@@ -1934,13 +1934,13 @@
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.279684</v>
+        <v>1.2778323</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24666022</v>
+        <v>0.24610052</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25334865</v>
+        <v>0.25318623</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33015496</v>
+        <v>0.33040094</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40221968</v>
+        <v>0.4023207</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1870236</v>
+        <v>4.185791</v>
       </c>
       <c r="O23" t="n">
         <v>17</v>
       </c>
       <c r="P23" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3013024</v>
+        <v>1.3037109</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23691407</v>
+        <v>0.23705141</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24120103</v>
+        <v>0.24225685</v>
       </c>
       <c r="C24" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" t="n">
+        <v>668</v>
+      </c>
+      <c r="E24" t="n">
         <v>20</v>
       </c>
-      <c r="D24" t="n">
-        <v>659</v>
-      </c>
-      <c r="E24" t="n">
-        <v>21</v>
-      </c>
       <c r="F24" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G24" t="n">
         <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31699115</v>
+        <v>0.31782266</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39431298</v>
+        <v>0.39672518</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L24" t="n">
-        <v>1221</v>
+        <v>1230</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.957415</v>
+        <v>3.944417</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2068,13 +2068,13 @@
         <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2857143</v>
+        <v>1.2860304</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24095671</v>
+        <v>0.24116261</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2187,7 +2187,7 @@
         <v>1329</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
         <v>4.208745</v>
@@ -2199,7 +2199,7 @@
         <v>186</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1.2576581</v>
@@ -2224,13 +2224,13 @@
         <v>0.24215421</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" t="n">
         <v>693</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
         <v>158</v>
@@ -2278,7 +2278,7 @@
         <v>0.25419155</v>
       </c>
       <c r="U27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26044953</v>
+        <v>0.26018807</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
         <v>162</v>
@@ -2306,43 +2306,43 @@
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32807794</v>
+        <v>0.32864428</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40654573</v>
+        <v>0.4057602</v>
       </c>
       <c r="K28" t="n">
         <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7522256</v>
+        <v>3.733972</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1372404</v>
+        <v>1.1355932</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22915429</v>
+        <v>0.22869514</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24396518</v>
+        <v>0.243456</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G29" t="n">
         <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3180531</v>
+        <v>0.31772575</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39948556</v>
+        <v>0.3987404</v>
       </c>
       <c r="K29" t="n">
         <v>17</v>
       </c>
       <c r="L29" t="n">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.299449</v>
+        <v>4.2974386</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3039559</v>
+        <v>1.302661</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24863495</v>
+        <v>0.24806201</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2473,13 +2473,13 @@
         <v>1.2977941</v>
       </c>
       <c r="S30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
         <v>0.23598589</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -2522,7 +2522,7 @@
         <v>1281</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
         <v>4.7123895</v>
@@ -2809,7 +2809,7 @@
         <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>11</v>
@@ -2821,43 +2821,43 @@
         <v>0.34583333</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>0.4976744</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
         <v>3.857143</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
         <v>0.25462964</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2867,43 +2867,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.23529412</v>
+        <v>0.22277227</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.28961748</v>
+        <v>0.2798165</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>0.37623763</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>6.5454545</v>
+        <v>6.923077</v>
       </c>
       <c r="O3" t="n">
         <v>28</v>
@@ -2912,16 +2912,16 @@
         <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7272727</v>
+        <v>1.7692307</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.32258064</v>
+        <v>0.30733946</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.27868852</v>
+        <v>0.28372094</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
         <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.33948338</v>
+        <v>0.35123968</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.44262296</v>
+        <v>0.45581394</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.1666665</v>
+      </c>
+      <c r="O4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.4074074</v>
+      </c>
+      <c r="S4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>4.571429</v>
-      </c>
-      <c r="O4" t="n">
-        <v>24</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>19</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.3333334</v>
-      </c>
-      <c r="S4" t="n">
-        <v>17</v>
-      </c>
       <c r="T4" t="n">
-        <v>0.25833333</v>
+        <v>0.27272728</v>
       </c>
       <c r="U4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -3010,13 +3010,13 @@
         <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0.2918455</v>
@@ -3028,7 +3028,7 @@
         <v>0.4423963</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>78</v>
@@ -3040,25 +3040,25 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
         <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>1.4814814</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T5" t="n">
         <v>0.26540285</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.22012578</v>
+        <v>0.20942408</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29545453</v>
+        <v>0.29439253</v>
       </c>
       <c r="I6" t="n">
         <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.33962265</v>
+        <v>0.32984293</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>3.139535</v>
+        <v>3.1153846</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3023256</v>
+        <v>1.2307693</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24390244</v>
+        <v>0.2303665</v>
       </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -3138,19 +3138,19 @@
         <v>0.27748692</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>37</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
         <v>0.3632287</v>
@@ -3162,7 +3162,7 @@
         <v>0.5026178</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>28</v>
@@ -3174,19 +3174,19 @@
         <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
         <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
         <v>1.2777778</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
         <v>0.23152709</v>
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20353982</v>
+        <v>0.21585903</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3272059</v>
+        <v>0.34181818</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.32300884</v>
+        <v>0.3524229</v>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>75</v>
       </c>
       <c r="M8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6201117</v>
+        <v>3.4692738</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2067039</v>
+        <v>1.2905028</v>
       </c>
       <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.23451327</v>
+      </c>
+      <c r="U8" t="n">
         <v>9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.2300885</v>
-      </c>
-      <c r="U8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22564103</v>
+        <v>0.2236842</v>
       </c>
       <c r="C9" t="n">
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>0.28301886</v>
+        <v>0.2734694</v>
       </c>
       <c r="I9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.35897437</v>
+        <v>0.3640351</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>7.7884617</v>
+        <v>7.819672</v>
       </c>
       <c r="O9" t="n">
         <v>29</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R9" t="n">
-        <v>1.75</v>
+        <v>1.7868853</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2961165</v>
+        <v>0.30165288</v>
       </c>
       <c r="U9" t="n">
         <v>28</v>
@@ -3339,7 +3339,7 @@
         <v>0.23</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
         <v>33</v>
@@ -3351,13 +3351,13 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
         <v>0.3141593</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>0.425</v>
@@ -3375,7 +3375,7 @@
         <v>3.5660377</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
         <v>4</v>
@@ -3387,7 +3387,7 @@
         <v>1.1886792</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
         <v>0.22335026</v>
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2782258</v>
+        <v>0.2857143</v>
       </c>
       <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3494424</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.45714286</v>
+      </c>
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
-        <v>32</v>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.34671533</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.46370968</v>
-      </c>
-      <c r="K11" t="n">
-        <v>7</v>
-      </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>8.389830999999999</v>
+        <v>8.1</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8813559</v>
+        <v>1.8833333</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3237705</v>
+        <v>0.332</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.28078818</v>
+        <v>0.27659574</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -3485,49 +3485,49 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.38333333</v>
+        <v>0.38129497</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4827586</v>
+        <v>0.45531914</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0566037</v>
+        <v>3.0983605</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.264151</v>
+        <v>1.2459016</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>0.24875621</v>
+        <v>0.23809524</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -3537,61 +3537,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2</v>
+        <v>0.21465969</v>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>29</v>
       </c>
       <c r="F13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2809524</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.45549738</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>46</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.26794258</v>
-      </c>
-      <c r="I13" t="n">
-        <v>30</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.37894738</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="n">
-        <v>49</v>
-      </c>
-      <c r="M13" t="n">
-        <v>16</v>
-      </c>
       <c r="N13" t="n">
-        <v>4.0324674</v>
+        <v>4.2077923</v>
       </c>
       <c r="O13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
         <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1688312</v>
+        <v>1.1883117</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21808511</v>
+        <v>0.21693122</v>
       </c>
       <c r="U13" t="n">
         <v>3</v>
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.19512194</v>
+        <v>0.18134715</v>
       </c>
       <c r="C14" t="n">
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
         <v>30</v>
@@ -3619,49 +3619,49 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H14" t="n">
-        <v>0.29032257</v>
+        <v>0.27522936</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3109756</v>
+        <v>0.2849741</v>
       </c>
       <c r="K14" t="n">
         <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N14" t="n">
-        <v>3.642857</v>
+        <v>4.14</v>
       </c>
       <c r="O14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1428572</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2389937</v>
+        <v>0.253886</v>
       </c>
       <c r="U14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2010582</v>
+        <v>0.20444444</v>
       </c>
       <c r="C15" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" t="n">
         <v>28</v>
       </c>
-      <c r="D15" t="n">
-        <v>23</v>
-      </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30493274</v>
+        <v>0.30152673</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>0.33333334</v>
+        <v>0.32</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L15" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="M15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.471338</v>
+        <v>4.1871657</v>
       </c>
       <c r="O15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4331211</v>
+        <v>1.3957219</v>
       </c>
       <c r="S15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="T15" t="n">
-        <v>0.26213592</v>
+        <v>0.26229507</v>
       </c>
       <c r="U15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.20418848</v>
+        <v>0.2246696</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.35272726</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.40088105</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16</v>
+      </c>
+      <c r="L16" t="n">
+        <v>44</v>
+      </c>
+      <c r="M16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.3347826</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.36649215</v>
-      </c>
-      <c r="K16" t="n">
-        <v>22</v>
-      </c>
-      <c r="L16" t="n">
-        <v>41</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6</v>
-      </c>
       <c r="N16" t="n">
-        <v>3.3529413</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2156863</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.23766816</v>
+      </c>
+      <c r="U16" t="n">
         <v>10</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.24210526</v>
-      </c>
-      <c r="U16" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -3808,61 +3808,61 @@
         <v>0.25358853</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
         <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
         <v>0.32188842</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
         <v>0.39712918</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>62</v>
       </c>
       <c r="M17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
         <v>4.066265</v>
       </c>
       <c r="O17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P17" t="n">
         <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R17" t="n">
         <v>1.3915663</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T17" t="n">
         <v>0.24285714</v>
       </c>
       <c r="U17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.33333334</v>
+        <v>0.32110092</v>
       </c>
       <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
-        <v>46</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.39805827</v>
+        <v>0.39112905</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5464481</v>
+        <v>0.51834863</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>4.075472</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="n">
+        <v>19</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3018868</v>
+      </c>
+      <c r="S18" t="n">
         <v>15</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.2666667</v>
-      </c>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.26285714</v>
+        <v>0.25728154</v>
       </c>
       <c r="U18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.20895523</v>
+        <v>0.21757323</v>
       </c>
       <c r="C19" t="n">
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2840909</v>
+      </c>
+      <c r="I19" t="n">
         <v>26</v>
       </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
+        <v>0.32635984</v>
+      </c>
+      <c r="K19" t="n">
+        <v>27</v>
+      </c>
+      <c r="L19" t="n">
+        <v>70</v>
+      </c>
+      <c r="M19" t="n">
+        <v>27</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.678218</v>
+      </c>
+      <c r="O19" t="n">
         <v>24</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.2825112</v>
-      </c>
-      <c r="I19" t="n">
-        <v>29</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.31840795</v>
-      </c>
-      <c r="K19" t="n">
-        <v>28</v>
-      </c>
-      <c r="L19" t="n">
-        <v>55</v>
-      </c>
-      <c r="M19" t="n">
-        <v>22</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8103447</v>
-      </c>
-      <c r="O19" t="n">
-        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>9</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3793104</v>
+        <v>1.3514851</v>
       </c>
       <c r="S19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2555066</v>
+        <v>0.25095057</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -4006,46 +4006,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23222749</v>
+        <v>0.22175732</v>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D20" t="n">
         <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29613733</v>
+        <v>0.2932331</v>
       </c>
       <c r="I20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.35983264</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23</v>
+      </c>
+      <c r="L20" t="n">
+        <v>56</v>
+      </c>
+      <c r="M20" t="n">
         <v>22</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.3886256</v>
-      </c>
-      <c r="K20" t="n">
-        <v>17</v>
-      </c>
-      <c r="L20" t="n">
-        <v>48</v>
-      </c>
-      <c r="M20" t="n">
-        <v>13</v>
-      </c>
       <c r="N20" t="n">
-        <v>3.8333333</v>
+        <v>3.5714285</v>
       </c>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P20" t="n">
         <v>14</v>
@@ -4054,16 +4054,16 @@
         <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0925926</v>
+        <v>1.1428572</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24257426</v>
+        <v>0.24675325</v>
       </c>
       <c r="U20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.26506025</v>
+        <v>0.25581396</v>
       </c>
       <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="n">
+        <v>30</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="n">
         <v>10</v>
       </c>
-      <c r="D21" t="n">
-        <v>40</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>12</v>
-      </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31985295</v>
+        <v>0.30603448</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>0.437751</v>
+        <v>0.41860464</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8636363</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1818181</v>
+        <v>1.1403508</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22540984</v>
+        <v>0.22596154</v>
       </c>
       <c r="U21" t="n">
         <v>6</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.21393035</v>
+        <v>0.23762377</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
+        <v>26</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3304721</v>
+      </c>
+      <c r="I22" t="n">
+        <v>13</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.35643566</v>
+      </c>
+      <c r="K22" t="n">
         <v>24</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.30088496</v>
-      </c>
-      <c r="I22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="K22" t="n">
-        <v>25</v>
-      </c>
       <c r="L22" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.689441</v>
+        <v>3.3540373</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.416149</v>
+        <v>1.3788819</v>
       </c>
       <c r="S22" t="n">
+        <v>17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="U22" t="n">
         <v>22</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.27804878</v>
-      </c>
-      <c r="U22" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.24878049</v>
+        <v>0.25</v>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3063063</v>
+        <v>0.32599118</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>0.38536584</v>
+        <v>0.3970588</v>
       </c>
       <c r="K23" t="n">
         <v>18</v>
       </c>
       <c r="L23" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>5.019231</v>
+        <v>5.7115383</v>
       </c>
       <c r="O23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3076923</v>
+        <v>1.5192307</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23958333</v>
+        <v>0.26767677</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -4274,46 +4274,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.31555554</v>
+        <v>0.3245283</v>
       </c>
       <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>49</v>
+      </c>
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="n">
-        <v>40</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4</v>
-      </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>0.36437246</v>
+        <v>0.37328768</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.53333336</v>
+        <v>0.5584905999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N24" t="n">
-        <v>5.773585</v>
+        <v>5.225806</v>
       </c>
       <c r="O24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P24" t="n">
         <v>10</v>
@@ -4322,13 +4322,13 @@
         <v>25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4339622</v>
+        <v>1.4193548</v>
       </c>
       <c r="S24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2688679</v>
+        <v>0.26938775</v>
       </c>
       <c r="U24" t="n">
         <v>26</v>
@@ -4356,13 +4356,13 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
         <v>0.33050847</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
         <v>0.4198113</v>
@@ -4374,13 +4374,13 @@
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N25" t="n">
         <v>4.3333335</v>
       </c>
       <c r="O25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
         <v>4</v>
@@ -4392,13 +4392,13 @@
         <v>1.4074074</v>
       </c>
       <c r="S25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T25" t="n">
         <v>0.24880382</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.29083666</v>
+        <v>0.3080357</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>0.36491227</v>
+        <v>0.38039216</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.49003986</v>
+        <v>0.51785713</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.0588236</v>
+      </c>
+      <c r="O26" t="n">
+        <v>15</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>9</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4509804</v>
+      </c>
+      <c r="S26" t="n">
         <v>24</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>16</v>
-      </c>
-      <c r="P26" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>15</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.3666667</v>
-      </c>
-      <c r="S26" t="n">
-        <v>18</v>
-      </c>
       <c r="T26" t="n">
-        <v>0.2521739</v>
+        <v>0.26732674</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -4478,13 +4478,13 @@
         <v>0.22164948</v>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -4496,7 +4496,7 @@
         <v>0.29864255</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
         <v>0.31443298</v>
@@ -4508,31 +4508,31 @@
         <v>48</v>
       </c>
       <c r="M27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
         <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
         <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R27" t="n">
         <v>1.4727273</v>
       </c>
       <c r="S27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T27" t="n">
         <v>0.24509804</v>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.24468085</v>
+        <v>0.25396827</v>
       </c>
       <c r="C28" t="n">
+        <v>14</v>
+      </c>
+      <c r="D28" t="n">
+        <v>36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" t="n">
         <v>16</v>
       </c>
-      <c r="D28" t="n">
-        <v>27</v>
-      </c>
-      <c r="E28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" t="n">
-        <v>12</v>
-      </c>
       <c r="H28" t="n">
-        <v>0.2920792</v>
+        <v>0.32380953</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>0.43617022</v>
+        <v>0.43915343</v>
       </c>
       <c r="K28" t="n">
         <v>11</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M28" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
         <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.3773584</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8867925</v>
+        <v>0.8888889</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.19473684</v>
+        <v>0.18134715</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.26130652</v>
+        <v>0.26262626</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4627,25 +4627,25 @@
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32876712</v>
+        <v>0.32718894</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J29" t="n">
-        <v>0.36683416</v>
+        <v>0.36868685</v>
       </c>
       <c r="K29" t="n">
         <v>21</v>
       </c>
       <c r="L29" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>4.4150944</v>
       </c>
       <c r="O29" t="n">
         <v>23</v>
@@ -4657,13 +4657,13 @@
         <v>15</v>
       </c>
       <c r="R29" t="n">
-        <v>1.1346154</v>
+        <v>1.1886792</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>0.21989529</v>
+        <v>0.21938775</v>
       </c>
       <c r="U29" t="n">
         <v>4</v>
@@ -4685,13 +4685,13 @@
         <v>30</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H30" t="n">
         <v>0.35371178</v>
@@ -4709,31 +4709,31 @@
         <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
         <v>4.1666665</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P30" t="n">
         <v>5</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
         <v>1.4444444</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T30" t="n">
         <v>0.24528302</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -4764,7 +4764,7 @@
         <v>0.32967034</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J31" t="n">
         <v>0.38414633</v>
@@ -4776,25 +4776,25 @@
         <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
         <v>3.5217392</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P31" t="n">
         <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
         <v>1.173913</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
         <v>0.14285715</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24357477</v>
+        <v>0.24332689</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31577116</v>
+        <v>0.3152437</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39739096</v>
+        <v>0.3969052</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0873075</v>
+        <v>4.1129737</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2773294</v>
+        <v>1.2791545</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24845321</v>
+        <v>0.24831957</v>
       </c>
       <c r="U2" t="n">
         <v>21</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24426451</v>
+        <v>0.24357499</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E3" t="n">
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31664646</v>
+        <v>0.31627908</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40158087</v>
+        <v>0.40065208</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.411982</v>
+        <v>5.413235</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4992603</v>
+        <v>1.5014706</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2699375</v>
+        <v>0.27019393</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,43 +680,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24738675</v>
+        <v>0.2476465</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3106592</v>
+        <v>0.31070495</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41018197</v>
+        <v>0.41133526</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.638439</v>
+        <v>3.6276517</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -725,16 +725,16 @@
         <v>170</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2511046</v>
+        <v>1.2479883</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23372024</v>
+        <v>0.23323558</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23444226</v>
+        <v>0.23495145</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31511366</v>
+        <v>0.3153727</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3960861</v>
+        <v>0.39650485</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1439</v>
+        <v>1452</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1426826</v>
+        <v>4.1452827</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3464451</v>
+        <v>1.3482901</v>
       </c>
       <c r="S5" t="n">
         <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25377414</v>
+        <v>0.25379363</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2463429</v>
+        <v>0.2463684</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G6" t="n">
         <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32082683</v>
+        <v>0.32073843</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4012093</v>
+        <v>0.40131706</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>1242</v>
+        <v>1253</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6057339</v>
+        <v>3.59518</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -859,19 +859,19 @@
         <v>148</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2379318</v>
+        <v>1.2400194</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24234146</v>
+        <v>0.24180725</v>
       </c>
       <c r="U6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25157234</v>
+        <v>0.25160924</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33981714</v>
+        <v>0.3398844</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43148467</v>
+        <v>0.43089738</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1903367</v>
+        <v>4.2052402</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
         <v>227</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2693998</v>
+        <v>1.2714702</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24457784</v>
+        <v>0.24475256</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2343872</v>
+        <v>0.23415391</v>
       </c>
       <c r="C8" t="n">
         <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31863588</v>
+        <v>0.3185084</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40241998</v>
+        <v>0.40220973</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>1413</v>
+        <v>1423</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1009307</v>
+        <v>4.146264</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3074473</v>
+        <v>1.3141884</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24096856</v>
+        <v>0.24220112</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22960487</v>
+        <v>0.22986709</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
@@ -1033,43 +1033,43 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3068162</v>
+        <v>0.30721003</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39610773</v>
+        <v>0.39581704</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>1458</v>
+        <v>1465</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8722305</v>
+        <v>4.866471</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4497784</v>
+        <v>1.4497433</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25446513</v>
+        <v>0.254483</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2364706</v>
+        <v>0.23694466</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31410146</v>
+        <v>0.3148052</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3745098</v>
+        <v>0.37548715</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="M10" t="n">
         <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>3.795633</v>
+        <v>3.7903972</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q10" t="n">
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.263003</v>
+        <v>1.25981</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2366621</v>
+        <v>0.23600312</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.253889</v>
+        <v>0.25471517</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
         <v>169</v>
@@ -1167,43 +1167,43 @@
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32364574</v>
+        <v>0.32400137</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41732284</v>
+        <v>0.41779387</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="M11" t="n">
         <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.61718</v>
+        <v>5.6130705</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.535005</v>
+        <v>1.5329224</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28915438</v>
+        <v>0.28900018</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23952676</v>
+        <v>0.24076213</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G12" t="n">
         <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31719503</v>
+        <v>0.31846154</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39798293</v>
+        <v>0.40011546</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6398523</v>
+        <v>3.6290324</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q12" t="n">
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2228782</v>
+        <v>1.2228739</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2325765</v>
+        <v>0.23235294</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23996884</v>
+        <v>0.23945025</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E13" t="n">
         <v>16</v>
@@ -1301,43 +1301,43 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31376305</v>
+        <v>0.31312782</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41137514</v>
+        <v>0.40998837</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5110564</v>
+        <v>4.520869</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3422605</v>
+        <v>1.3429339</v>
       </c>
       <c r="S13" t="n">
         <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23729815</v>
+        <v>0.23763925</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2441452</v>
+        <v>0.24413419</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E14" t="n">
         <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31449074</v>
+        <v>0.31431553</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3973458</v>
+        <v>0.39790577</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>1198</v>
+        <v>1209</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6258974</v>
+        <v>4.6517353</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P14" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3867294</v>
+        <v>1.3918287</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25822785</v>
+        <v>0.25928074</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23393416</v>
+        <v>0.23330088</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
@@ -1426,7 +1426,7 @@
         <v>619</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
         <v>146</v>
@@ -1435,46 +1435,46 @@
         <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30871776</v>
+        <v>0.30810812</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37029782</v>
+        <v>0.3688413</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.195856</v>
+        <v>4.187944</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3394178</v>
+        <v>1.3371723</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23617399</v>
+        <v>0.23636363</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25530258</v>
+        <v>0.255751</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33766454</v>
+        <v>0.33814538</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4212882</v>
+        <v>0.42373863</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6434376</v>
+        <v>3.6325831</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q16" t="n">
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1612904</v>
+        <v>1.1587573</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22043331</v>
+        <v>0.22007112</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2492163</v>
+        <v>0.24941634</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32685298</v>
+        <v>0.32666436</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.401058</v>
+        <v>0.4011673</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0957685</v>
+        <v>4.1247234</v>
       </c>
       <c r="O17" t="n">
         <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q17" t="n">
         <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828507</v>
+        <v>1.2870848</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23557219</v>
+        <v>0.23630673</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25921658</v>
+        <v>0.25919574</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34160337</v>
+        <v>0.34170854</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40495393</v>
+        <v>0.40461215</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5784721</v>
+        <v>3.5851707</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1906273</v>
+        <v>1.1928762</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2237776</v>
+        <v>0.22437403</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24359968</v>
+        <v>0.24373795</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E19" t="n">
         <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.31704798</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.40250483</v>
+      </c>
+      <c r="K19" t="n">
         <v>12</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.31729272</v>
-      </c>
-      <c r="I19" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.40283164</v>
-      </c>
-      <c r="K19" t="n">
-        <v>11</v>
-      </c>
       <c r="L19" t="n">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6661744</v>
+        <v>4.635363</v>
       </c>
       <c r="O19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>178</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3751847</v>
+        <v>1.3712399</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2508644</v>
+        <v>0.2501432</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23725528</v>
+        <v>0.23811357</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30788004</v>
+        <v>0.30857143</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39251792</v>
+        <v>0.39326274</v>
       </c>
       <c r="K20" t="n">
         <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1645074</v>
+        <v>4.1568723</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2987045</v>
+        <v>1.295289</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24111283</v>
+        <v>0.24073718</v>
       </c>
       <c r="U20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23521239</v>
+        <v>0.23516656</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31200284</v>
+        <v>0.31221482</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4092894</v>
+        <v>0.40961954</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.19163</v>
+        <v>3.1838074</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q21" t="n">
         <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1622614</v>
+        <v>1.1604668</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22266166</v>
+        <v>0.2225496</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24165528</v>
+        <v>0.2412723</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31231442</v>
+        <v>0.31180555</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39820418</v>
+        <v>0.39837083</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L22" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9592938</v>
+        <v>3.9756217</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2778323</v>
+        <v>1.2813262</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24610052</v>
+        <v>0.24689233</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25318623</v>
+        <v>0.2542501</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33040094</v>
+        <v>0.33142954</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4023207</v>
+        <v>0.40385342</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L23" t="n">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.185791</v>
+        <v>4.191123</v>
       </c>
       <c r="O23" t="n">
+        <v>18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3024496</v>
+      </c>
+      <c r="S23" t="n">
         <v>17</v>
       </c>
-      <c r="P23" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3037109</v>
-      </c>
-      <c r="S23" t="n">
-        <v>18</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23705141</v>
+        <v>0.23708558</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24225685</v>
+        <v>0.24294671</v>
       </c>
       <c r="C24" t="n">
         <v>18</v>
       </c>
       <c r="D24" t="n">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31782266</v>
+        <v>0.31845134</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39672518</v>
+        <v>0.39772728</v>
       </c>
       <c r="K24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L24" t="n">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.944417</v>
+        <v>3.9315906</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2856095</v>
+      </c>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.24141966</v>
+      </c>
+      <c r="U24" t="n">
         <v>14</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2860304</v>
-      </c>
-      <c r="S24" t="n">
-        <v>14</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.24116261</v>
-      </c>
-      <c r="U24" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24816956</v>
+        <v>0.24765371</v>
       </c>
       <c r="C25" t="n">
         <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30969888</v>
+        <v>0.3091384</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40751445</v>
+        <v>0.4066271</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1233</v>
+        <v>1247</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.343449</v>
+        <v>4.370861</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3589933</v>
+        <v>1.3627667</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24736018</v>
+        <v>0.24786325</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23225172</v>
+        <v>0.23246728</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G26" t="n">
         <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31239092</v>
+        <v>0.3124133</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37974435</v>
+        <v>0.38093376</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1329</v>
+        <v>1338</v>
       </c>
       <c r="M26" t="n">
         <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>4.208745</v>
+        <v>4.207362</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
@@ -2202,16 +2202,16 @@
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2576581</v>
+        <v>1.2611042</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2505345</v>
+        <v>0.25139773</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24215421</v>
+        <v>0.24196343</v>
       </c>
       <c r="C27" t="n">
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
         <v>158</v>
       </c>
       <c r="G27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31591654</v>
+        <v>0.31556395</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3822162</v>
+        <v>0.3813282</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.280166</v>
+        <v>4.304538</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3563752</v>
+        <v>1.3569522</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25419155</v>
+        <v>0.2539257</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26018807</v>
+        <v>0.2595405</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
         <v>162</v>
@@ -2306,43 +2306,43 @@
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32864428</v>
+        <v>0.32873604</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4057602</v>
+        <v>0.40478972</v>
       </c>
       <c r="K28" t="n">
         <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>1057</v>
+        <v>1066</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.733972</v>
+        <v>3.7357247</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1355932</v>
+        <v>1.136164</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22869514</v>
+        <v>0.22884503</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.243456</v>
+        <v>0.24354461</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
@@ -2373,28 +2373,28 @@
         <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31772575</v>
+        <v>0.3184836</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3987404</v>
+        <v>0.3984742</v>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2974386</v>
+        <v>4.2754445</v>
       </c>
       <c r="O29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P29" t="n">
         <v>183</v>
@@ -2403,16 +2403,16 @@
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.302661</v>
+        <v>1.29916</v>
       </c>
       <c r="S29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24806201</v>
+        <v>0.24749614</v>
       </c>
       <c r="U29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24864341</v>
+        <v>0.24807397</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -2437,28 +2437,28 @@
         <v>148</v>
       </c>
       <c r="G30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31085354</v>
+        <v>0.31023043</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38468993</v>
+        <v>0.3834746</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9176471</v>
+        <v>3.9144738</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
@@ -2470,13 +2470,13 @@
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2977941</v>
+        <v>1.3033626</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23598589</v>
+        <v>0.23611923</v>
       </c>
       <c r="U30" t="n">
         <v>8</v>
@@ -2489,43 +2489,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24745633</v>
+        <v>0.24723388</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32282925</v>
+        <v>0.32284403</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42599347</v>
+        <v>0.42598245</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7123895</v>
+        <v>4.687912</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
@@ -2534,16 +2534,16 @@
         <v>204</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3893806</v>
+        <v>1.3860806</v>
       </c>
       <c r="S31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25294003</v>
+        <v>0.252682</v>
       </c>
       <c r="U31" t="n">
         <v>24</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2744186</v>
+        <v>0.25700936</v>
       </c>
       <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.31623933</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.44859812</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.982143</v>
+      </c>
+      <c r="O2" t="n">
+        <v>25</v>
+      </c>
+      <c r="P2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.34583333</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.4976744</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>52</v>
-      </c>
-      <c r="M2" t="n">
-        <v>17</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.857143</v>
-      </c>
-      <c r="O2" t="n">
-        <v>13</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.3392857</v>
       </c>
       <c r="S2" t="n">
         <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25462964</v>
+        <v>0.26244345</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.22277227</v>
+        <v>0.17989418</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2798165</v>
+        <v>0.25480768</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>0.37623763</v>
+        <v>0.31746033</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>6.923077</v>
+        <v>7.56</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7692307</v>
+        <v>1.88</v>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.30733946</v>
+        <v>0.31904763</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.28372094</v>
+        <v>0.28504673</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -2943,55 +2943,55 @@
         <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.34599155</v>
+      </c>
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.35123968</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.45581394</v>
+        <v>0.47196263</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1666665</v>
+        <v>5.1923075</v>
       </c>
       <c r="O4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" t="n">
         <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4074074</v>
+        <v>1.3846154</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
-        <v>0.27272728</v>
+        <v>0.27093595</v>
       </c>
       <c r="U4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23963134</v>
+        <v>0.24200913</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2918455</v>
+        <v>0.29707113</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4423963</v>
+        <v>0.43835616</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M5" t="n">
         <v>30</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.090909</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4814814</v>
+        <v>1.5090909</v>
       </c>
       <c r="S5" t="n">
         <v>26</v>
       </c>
       <c r="T5" t="n">
-        <v>0.26540285</v>
+        <v>0.26291078</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -3068,46 +3068,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.20942408</v>
+        <v>0.21354167</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" t="n">
-        <v>27</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>23</v>
-      </c>
       <c r="H6" t="n">
-        <v>0.29439253</v>
+        <v>0.30092594</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>0.32984293</v>
+        <v>0.33854166</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1153846</v>
+        <v>2.9423077</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -3116,16 +3116,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2307693</v>
+        <v>1.2115384</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2303665</v>
+        <v>0.20634921</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27748692</v>
+        <v>0.24210526</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3632287</v>
+        <v>0.3438914</v>
       </c>
       <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.43157893</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>35</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.245283</v>
+      </c>
+      <c r="O7" t="n">
+        <v>17</v>
+      </c>
+      <c r="P7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.5026178</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>28</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>8</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="Q7" t="n">
-        <v>9</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.2777778</v>
+        <v>1.3584906</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23152709</v>
+        <v>0.24120604</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.21585903</v>
+        <v>0.20614035</v>
       </c>
       <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.32600734</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3377193</v>
+      </c>
+      <c r="K8" t="n">
         <v>26</v>
       </c>
-      <c r="D8" t="n">
+      <c r="L8" t="n">
+        <v>78</v>
+      </c>
+      <c r="M8" t="n">
         <v>29</v>
       </c>
-      <c r="E8" t="n">
+      <c r="N8" t="n">
+        <v>4.0054946</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
         <v>15</v>
       </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>21</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.34181818</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.3524229</v>
-      </c>
-      <c r="K8" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>75</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.4692738</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.2905028</v>
+        <v>1.3681319</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23451327</v>
+        <v>0.24242425</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2236842</v>
+        <v>0.25110132</v>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2734694</v>
+        <v>0.30645162</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3640351</v>
+        <v>0.40088105</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>7.819672</v>
+        <v>5.516129</v>
       </c>
       <c r="O9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7868853</v>
+        <v>1.5645162</v>
       </c>
       <c r="S9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.30165288</v>
+        <v>0.25541127</v>
       </c>
       <c r="U9" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -3336,34 +3336,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23</v>
+        <v>0.24623115</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
         <v>33</v>
       </c>
       <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3288889</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.44723618</v>
+      </c>
+      <c r="K10" t="n">
         <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3141593</v>
-      </c>
-      <c r="I10" t="n">
-        <v>19</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="K10" t="n">
-        <v>13</v>
       </c>
       <c r="L10" t="n">
         <v>37</v>
@@ -3372,25 +3372,25 @@
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5660377</v>
+        <v>3.7358491</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1886792</v>
+        <v>1.1698114</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>0.22335026</v>
+        <v>0.21243523</v>
       </c>
       <c r="U10" t="n">
         <v>5</v>
@@ -3403,43 +3403,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2857143</v>
+        <v>0.2988048</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3494424</v>
+        <v>0.35766423</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.45714286</v>
+        <v>0.4860558</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1</v>
+        <v>7.819672</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -3448,16 +3448,16 @@
         <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8833333</v>
+        <v>1.8524591</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T11" t="n">
-        <v>0.332</v>
+        <v>0.3385214</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.27659574</v>
+        <v>0.30645162</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.38129497</v>
+        <v>0.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.45531914</v>
+        <v>0.48387095</v>
       </c>
       <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>56</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.2459016</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2295082</v>
+      </c>
+      <c r="S12" t="n">
         <v>9</v>
       </c>
-      <c r="L12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.0983605</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2459016</v>
-      </c>
-      <c r="S12" t="n">
-        <v>11</v>
-      </c>
       <c r="T12" t="n">
-        <v>0.23809524</v>
+        <v>0.22608696</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.21465969</v>
+        <v>0.19473684</v>
       </c>
       <c r="C13" t="n">
         <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2809524</v>
+        <v>0.26666668</v>
       </c>
       <c r="I13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>0.45549738</v>
+        <v>0.4368421</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2077923</v>
+        <v>4.673077</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1883117</v>
+        <v>1.3076923</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21693122</v>
+        <v>0.23880596</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3604,46 +3604,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.18134715</v>
+        <v>0.171875</v>
       </c>
       <c r="C14" t="n">
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
         <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>0.27522936</v>
+        <v>0.25700936</v>
       </c>
       <c r="I14" t="n">
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2849741</v>
+        <v>0.296875</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>24</v>
       </c>
       <c r="N14" t="n">
-        <v>4.14</v>
+        <v>5.3265305</v>
       </c>
       <c r="O14" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="P14" t="n">
         <v>11</v>
@@ -3652,16 +3652,16 @@
         <v>26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.4081633</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T14" t="n">
-        <v>0.253886</v>
+        <v>0.2871795</v>
       </c>
       <c r="U14" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.20444444</v>
+        <v>0.20264317</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30152673</v>
+        <v>0.29389313</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.32</v>
+        <v>0.29955947</v>
       </c>
       <c r="K15" t="n">
         <v>28</v>
       </c>
       <c r="L15" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1871657</v>
+        <v>3.9789474</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.3957219</v>
+        <v>1.3421053</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T15" t="n">
-        <v>0.26229507</v>
+        <v>0.2701613</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2246696</v>
+        <v>0.23684211</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35272726</v>
+        <v>0.36363637</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.40088105</v>
+        <v>0.46052632</v>
       </c>
       <c r="K16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
         <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
         <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>0.23766816</v>
+        <v>0.21917808</v>
       </c>
       <c r="U16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25358853</v>
+        <v>0.25238097</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32188842</v>
+        <v>0.31601733</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39712918</v>
+        <v>0.4047619</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>4.066265</v>
+        <v>4.4723926</v>
       </c>
       <c r="O17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3915663</v>
+        <v>1.4723927</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T17" t="n">
-        <v>0.24285714</v>
+        <v>0.25943395</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.32110092</v>
+        <v>0.27014217</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.36065573</v>
+      </c>
+      <c r="I18" t="n">
         <v>5</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.39112905</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.51834863</v>
+        <v>0.4170616</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
         <v>14</v>
       </c>
       <c r="N18" t="n">
-        <v>4.075472</v>
+        <v>4.8333335</v>
       </c>
       <c r="O18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q18" t="n">
         <v>19</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3018868</v>
+        <v>1.4814814</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="n">
-        <v>0.25728154</v>
+        <v>0.29166666</v>
       </c>
       <c r="U18" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.21757323</v>
+        <v>0.22727273</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2840909</v>
+        <v>0.28301886</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>0.32635984</v>
+        <v>0.3429752</v>
       </c>
       <c r="K19" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M19" t="n">
         <v>27</v>
       </c>
       <c r="N19" t="n">
-        <v>4.678218</v>
+        <v>4.009901</v>
       </c>
       <c r="O19" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3514851</v>
+        <v>1.2623762</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25095057</v>
+        <v>0.2413793</v>
       </c>
       <c r="U19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.22175732</v>
+        <v>0.24279836</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2932331</v>
+        <v>0.3071161</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>0.35983264</v>
+        <v>0.38683128</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5714285</v>
+        <v>3.09375</v>
       </c>
       <c r="O20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
         <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1428572</v>
+        <v>1.015625</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24675325</v>
+        <v>0.2173913</v>
       </c>
       <c r="U20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -4073,43 +4073,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.25581396</v>
+        <v>0.23148148</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>0.30603448</v>
+        <v>0.29831934</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41860464</v>
+        <v>0.4027778</v>
       </c>
       <c r="K21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L21" t="n">
         <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.8421052</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -4118,19 +4118,19 @@
         <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1403508</v>
+        <v>1.0701754</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22596154</v>
+        <v>0.22380953</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23762377</v>
+        <v>0.23857868</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
+        <v>23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>23</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.32444444</v>
+      </c>
+      <c r="I22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.39086294</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21</v>
+      </c>
+      <c r="L22" t="n">
+        <v>32</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.8823528</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11</v>
+      </c>
+      <c r="P22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4705882</v>
+      </c>
+      <c r="S22" t="n">
+        <v>23</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.28061223</v>
+      </c>
+      <c r="U22" t="n">
         <v>25</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>26</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3304721</v>
-      </c>
-      <c r="I22" t="n">
-        <v>13</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.35643566</v>
-      </c>
-      <c r="K22" t="n">
-        <v>24</v>
-      </c>
-      <c r="L22" t="n">
-        <v>36</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.3540373</v>
-      </c>
-      <c r="O22" t="n">
-        <v>6</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>15</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3788819</v>
-      </c>
-      <c r="S22" t="n">
-        <v>17</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="U22" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25</v>
+        <v>0.28365386</v>
       </c>
       <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>27</v>
+      </c>
+      <c r="E23" t="n">
         <v>16</v>
-      </c>
-      <c r="D23" t="n">
-        <v>21</v>
-      </c>
-      <c r="E23" t="n">
-        <v>25</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.32599118</v>
+        <v>0.36051503</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3970588</v>
+        <v>0.44230768</v>
       </c>
       <c r="K23" t="n">
+        <v>9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>56</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.4150944</v>
+      </c>
+      <c r="O23" t="n">
         <v>18</v>
       </c>
-      <c r="L23" t="n">
-        <v>53</v>
-      </c>
-      <c r="M23" t="n">
-        <v>19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5.7115383</v>
-      </c>
-      <c r="O23" t="n">
-        <v>27</v>
-      </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5192307</v>
+        <v>1.3396226</v>
       </c>
       <c r="S23" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>0.26767677</v>
+        <v>0.23076923</v>
       </c>
       <c r="U23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -4274,61 +4274,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3245283</v>
+        <v>0.32950193</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13</v>
+      </c>
+      <c r="G24" t="n">
         <v>2</v>
       </c>
-      <c r="F24" t="n">
-        <v>11</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
+        <v>0.3784722</v>
+      </c>
+      <c r="I24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.37328768</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
       <c r="J24" t="n">
-        <v>0.5584905999999999</v>
+        <v>0.55938697</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N24" t="n">
-        <v>5.225806</v>
+        <v>4.790323</v>
       </c>
       <c r="O24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P24" t="n">
         <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4193548</v>
+        <v>1.4032258</v>
       </c>
       <c r="S24" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0.26938775</v>
+        <v>0.28225806</v>
       </c>
       <c r="U24" t="n">
         <v>26</v>
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.254717</v>
+        <v>0.25238097</v>
       </c>
       <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>29</v>
+      </c>
+      <c r="E25" t="n">
         <v>13</v>
-      </c>
-      <c r="D25" t="n">
-        <v>32</v>
-      </c>
-      <c r="E25" t="n">
-        <v>9</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
       </c>
       <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3173913</v>
+      </c>
+      <c r="I25" t="n">
+        <v>17</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.40952381</v>
+      </c>
+      <c r="K25" t="n">
+        <v>16</v>
+      </c>
+      <c r="L25" t="n">
+        <v>59</v>
+      </c>
+      <c r="M25" t="n">
+        <v>23</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.5849056</v>
+      </c>
+      <c r="O25" t="n">
+        <v>21</v>
+      </c>
+      <c r="P25" t="n">
         <v>9</v>
       </c>
-      <c r="H25" t="n">
-        <v>0.33050847</v>
-      </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.4198113</v>
-      </c>
-      <c r="K25" t="n">
-        <v>14</v>
-      </c>
-      <c r="L25" t="n">
-        <v>56</v>
-      </c>
-      <c r="M25" t="n">
-        <v>22</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.3333335</v>
-      </c>
-      <c r="O25" t="n">
-        <v>22</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4</v>
-      </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4074074</v>
+        <v>1.4339622</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24880382</v>
+        <v>0.25</v>
       </c>
       <c r="U25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3080357</v>
+        <v>0.3119266</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>43</v>
@@ -4420,52 +4420,52 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>0.38039216</v>
+        <v>0.384</v>
       </c>
       <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5412844</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>47</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.8823528</v>
+      </c>
+      <c r="O26" t="n">
+        <v>11</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.51785713</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>42</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.0588236</v>
-      </c>
-      <c r="O26" t="n">
-        <v>15</v>
-      </c>
-      <c r="P26" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>9</v>
       </c>
       <c r="R26" t="n">
         <v>1.4509804</v>
       </c>
       <c r="S26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T26" t="n">
-        <v>0.26732674</v>
+        <v>0.26960784</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.22164948</v>
+        <v>0.19270833</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>0.29864255</v>
+        <v>0.2706422</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>0.31443298</v>
+        <v>0.265625</v>
       </c>
       <c r="K27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L27" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
         <v>11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>4.418182</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="P27" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" t="n">
         <v>6</v>
       </c>
-      <c r="Q27" t="n">
-        <v>9</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.4727273</v>
+        <v>1.4363636</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T27" t="n">
-        <v>0.24509804</v>
+        <v>0.2364532</v>
       </c>
       <c r="U27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25396827</v>
+        <v>0.2525773</v>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.33936653</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.41237113</v>
+      </c>
+      <c r="K28" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" t="n">
+        <v>44</v>
+      </c>
+      <c r="M28" t="n">
         <v>6</v>
       </c>
-      <c r="F28" t="n">
-        <v>7</v>
-      </c>
-      <c r="G28" t="n">
-        <v>16</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.32380953</v>
-      </c>
-      <c r="I28" t="n">
-        <v>17</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.43915343</v>
-      </c>
-      <c r="K28" t="n">
-        <v>11</v>
-      </c>
-      <c r="L28" t="n">
-        <v>40</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
-      </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8888889</v>
+        <v>0.9074074</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.18134715</v>
+        <v>0.17857143</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.26262626</v>
+        <v>0.2763819</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4627,46 +4627,46 @@
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32718894</v>
+        <v>0.3482143</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.36868685</v>
+        <v>0.3919598</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4150944</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.1886792</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>0.21938775</v>
+        <v>0.19170985</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.27</v>
+        <v>0.25128207</v>
       </c>
       <c r="C30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" t="n">
+        <v>27</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.33632287</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3846154</v>
+      </c>
+      <c r="K30" t="n">
+        <v>23</v>
+      </c>
+      <c r="L30" t="n">
+        <v>40</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.5660377</v>
+      </c>
+      <c r="O30" t="n">
         <v>9</v>
       </c>
-      <c r="D30" t="n">
-        <v>30</v>
-      </c>
-      <c r="E30" t="n">
-        <v>12</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="P30" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5660378</v>
+      </c>
+      <c r="S30" t="n">
+        <v>28</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.23902439</v>
+      </c>
+      <c r="U30" t="n">
         <v>13</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.35371178</v>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K30" t="n">
-        <v>12</v>
-      </c>
-      <c r="L30" t="n">
-        <v>42</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.1666665</v>
-      </c>
-      <c r="O30" t="n">
-        <v>19</v>
-      </c>
-      <c r="P30" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4444444</v>
-      </c>
-      <c r="S30" t="n">
-        <v>23</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.24528302</v>
-      </c>
-      <c r="U30" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -4743,61 +4743,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2621951</v>
+        <v>0.26347306</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32967034</v>
+        <v>0.33333334</v>
       </c>
       <c r="I31" t="n">
+        <v>13</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.41317365</v>
+      </c>
+      <c r="K31" t="n">
         <v>14</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.38414633</v>
-      </c>
-      <c r="K31" t="n">
-        <v>19</v>
-      </c>
       <c r="L31" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5217392</v>
+        <v>3.1304348</v>
       </c>
       <c r="O31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.173913</v>
+        <v>1.1956521</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>0.14285715</v>
+        <v>0.15822785</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24332689</v>
+        <v>0.24322246</v>
       </c>
       <c r="C2" t="n">
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3152437</v>
+        <v>0.3151838</v>
       </c>
       <c r="I2" t="n">
         <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3969052</v>
+        <v>0.39684677</v>
       </c>
       <c r="K2" t="n">
         <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>1139</v>
+        <v>1149</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1129737</v>
+        <v>4.1057205</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2791545</v>
+        <v>1.2773353</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24831957</v>
+        <v>0.24799542</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24357499</v>
+        <v>0.24409749</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E3" t="n">
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31627908</v>
+        <v>0.31662676</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40065208</v>
+        <v>0.4011805</v>
       </c>
       <c r="K3" t="n">
         <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.413235</v>
+        <v>5.4605265</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5014706</v>
+        <v>1.504386</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27019393</v>
+        <v>0.27097738</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2476465</v>
+        <v>0.24813896</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31070495</v>
+        <v>0.31125712</v>
       </c>
       <c r="I4" t="n">
         <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41133526</v>
+        <v>0.41210154</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6276517</v>
+        <v>3.6235466</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q4" t="n">
         <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2479883</v>
+        <v>1.2478198</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23323558</v>
+        <v>0.23359223</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23495145</v>
+        <v>0.23440818</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
@@ -765,28 +765,28 @@
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3153727</v>
+        <v>0.31496063</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39650485</v>
+        <v>0.39544314</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1452827</v>
+        <v>4.1248193</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
         <v>167</v>
@@ -795,16 +795,16 @@
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3482901</v>
+        <v>1.3424096</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25379363</v>
+        <v>0.25297114</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2463684</v>
+        <v>0.24639076</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>160</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32073843</v>
+        <v>0.3205832</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40131706</v>
+        <v>0.40153995</v>
       </c>
       <c r="K6" t="n">
         <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59518</v>
+        <v>3.5791001</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2400194</v>
+        <v>1.2380261</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24180725</v>
+        <v>0.24176459</v>
       </c>
       <c r="U6" t="n">
         <v>15</v>
@@ -881,46 +881,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25160924</v>
+        <v>0.25155222</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3398844</v>
+        <v>0.3397341</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43089738</v>
+        <v>0.43104422</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2052402</v>
+        <v>4.184382</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
         <v>227</v>
@@ -929,13 +929,13 @@
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2714702</v>
+        <v>1.2682574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24475256</v>
+        <v>0.24406585</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23415391</v>
+        <v>0.23370613</v>
       </c>
       <c r="C8" t="n">
         <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3185084</v>
+        <v>0.3180194</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40220973</v>
+        <v>0.4016583</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>1423</v>
+        <v>1435</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.146264</v>
+        <v>4.1257253</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
         <v>172</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3141884</v>
+        <v>1.313588</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24220112</v>
+        <v>0.24220254</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22986709</v>
+        <v>0.22925976</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
         <v>203</v>
@@ -1033,43 +1033,43 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30721003</v>
+        <v>0.30661356</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39581704</v>
+        <v>0.39421022</v>
       </c>
       <c r="K9" t="n">
         <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>1465</v>
+        <v>1474</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.866471</v>
+        <v>4.867347</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4497433</v>
+        <v>1.4482508</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.254483</v>
+        <v>0.25440758</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23694466</v>
+        <v>0.23801237</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G10" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3148052</v>
+        <v>0.315337</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37548715</v>
+        <v>0.3779969</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7903972</v>
+        <v>3.8048427</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q10" t="n">
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25981</v>
+        <v>1.2624698</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23600312</v>
+        <v>0.2365882</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25471517</v>
+        <v>0.2548277</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>169</v>
@@ -1167,43 +1167,43 @@
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32400137</v>
+        <v>0.32417303</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41779387</v>
+        <v>0.41688755</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="M11" t="n">
         <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6130705</v>
+        <v>5.5957866</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5329224</v>
+        <v>1.5301323</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28900018</v>
+        <v>0.2886636</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24076213</v>
+        <v>0.24077262</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
         <v>173</v>
@@ -1234,43 +1234,43 @@
         <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31846154</v>
+        <v>0.31856003</v>
       </c>
       <c r="I12" t="n">
         <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40011546</v>
+        <v>0.3991203</v>
       </c>
       <c r="K12" t="n">
         <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>1336</v>
+        <v>1345</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6290324</v>
+        <v>3.627551</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q12" t="n">
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2228739</v>
+        <v>1.2201166</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23235294</v>
+        <v>0.2319095</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23945025</v>
+        <v>0.23976159</v>
       </c>
       <c r="C13" t="n">
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31312782</v>
+        <v>0.3130809</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40998837</v>
+        <v>0.4103057</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.520869</v>
+        <v>4.530553</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3429339</v>
+        <v>1.3450534</v>
       </c>
       <c r="S13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23763925</v>
+        <v>0.23820618</v>
       </c>
       <c r="U13" t="n">
         <v>12</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24413419</v>
+        <v>0.24485081</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E14" t="n">
         <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31431553</v>
+        <v>0.3148532</v>
       </c>
       <c r="I14" t="n">
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39790577</v>
+        <v>0.39807507</v>
       </c>
       <c r="K14" t="n">
         <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6517353</v>
+        <v>4.664057</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3918287</v>
+        <v>1.3917298</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25928074</v>
+        <v>0.25941584</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23330088</v>
+        <v>0.23353294</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30810812</v>
+        <v>0.30884895</v>
       </c>
       <c r="I15" t="n">
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3688413</v>
+        <v>0.36951903</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1468</v>
+        <v>1480</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.187944</v>
+        <v>4.1871657</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3371723</v>
+        <v>1.335926</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23636363</v>
+        <v>0.23652579</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.255751</v>
+        <v>0.25676453</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33814538</v>
+        <v>0.33906594</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42373863</v>
+        <v>0.42506236</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6325831</v>
+        <v>3.634994</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q16" t="n">
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1587573</v>
+        <v>1.1584448</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22007112</v>
+        <v>0.22001962</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24941634</v>
+        <v>0.24937223</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32666436</v>
+        <v>0.32717317</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4011673</v>
+        <v>0.40139076</v>
       </c>
       <c r="K17" t="n">
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1276</v>
+        <v>1290</v>
       </c>
       <c r="M17" t="n">
+        <v>16</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.136086</v>
+      </c>
+      <c r="O17" t="n">
         <v>15</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.1247234</v>
-      </c>
-      <c r="O17" t="n">
-        <v>13</v>
-      </c>
       <c r="P17" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q17" t="n">
         <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2870848</v>
+        <v>1.2892743</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23630673</v>
+        <v>0.23669903</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25919574</v>
+        <v>0.25833964</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1633,28 +1633,28 @@
         <v>148</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34170854</v>
+        <v>0.34066668</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40461215</v>
+        <v>0.40333587</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L18" t="n">
-        <v>1298</v>
+        <v>1309</v>
       </c>
       <c r="M18" t="n">
         <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5851707</v>
+        <v>3.5618682</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1666,13 +1666,13 @@
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1928762</v>
+        <v>1.1901782</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22437403</v>
+        <v>0.2238864</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24373795</v>
+        <v>0.2438372</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31704798</v>
+        <v>0.31683168</v>
       </c>
       <c r="I19" t="n">
         <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40250483</v>
+        <v>0.402446</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>4.635363</v>
+        <v>4.6255765</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3712399</v>
+        <v>1.3722398</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2501432</v>
+        <v>0.25004736</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -1752,43 +1752,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23811357</v>
+        <v>0.23866896</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30857143</v>
+        <v>0.30960977</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39326274</v>
+        <v>0.39395678</v>
       </c>
       <c r="K20" t="n">
         <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>1296</v>
+        <v>1306</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1568723</v>
+        <v>4.1493363</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
@@ -1797,16 +1797,16 @@
         <v>179</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.295289</v>
+        <v>1.2962606</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24073718</v>
+        <v>0.24084668</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23516656</v>
+        <v>0.23471788</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31221482</v>
+        <v>0.31170416</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40961954</v>
+        <v>0.40928683</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1838074</v>
+        <v>3.184147</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q21" t="n">
         <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1604668</v>
+        <v>1.1614306</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2225496</v>
+        <v>0.2225693</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2412723</v>
+        <v>0.2413793</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
@@ -1904,46 +1904,46 @@
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31180555</v>
+        <v>0.31189656</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39837083</v>
+        <v>0.3978039</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9756217</v>
+        <v>4.0179353</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2813262</v>
+        <v>1.2869607</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24689233</v>
+        <v>0.24738742</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2542501</v>
+        <v>0.25441232</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33142954</v>
+        <v>0.33149633</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40385342</v>
+        <v>0.40518212</v>
       </c>
       <c r="K23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.191123</v>
+        <v>4.1963854</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P23" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3024496</v>
+        <v>1.3048192</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23708558</v>
+        <v>0.23784922</v>
       </c>
       <c r="U23" t="n">
         <v>11</v>
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24294671</v>
+        <v>0.24329054</v>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="E24" t="n">
         <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G24" t="n">
         <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31845134</v>
+        <v>0.3189133</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39772728</v>
+        <v>0.39848307</v>
       </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L24" t="n">
-        <v>1240</v>
+        <v>1251</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9315906</v>
+        <v>3.942275</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2856095</v>
+        <v>1.29008</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24141966</v>
+        <v>0.24162634</v>
       </c>
       <c r="U24" t="n">
         <v>14</v>
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24765371</v>
+        <v>0.24762087</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3091384</v>
+        <v>0.30923557</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4066271</v>
+        <v>0.40673772</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1247</v>
+        <v>1258</v>
       </c>
       <c r="M25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N25" t="n">
-        <v>4.370861</v>
+        <v>4.391368</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3627667</v>
+        <v>1.3694221</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24786325</v>
+        <v>0.24893945</v>
       </c>
       <c r="U25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23246728</v>
+        <v>0.23248594</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3124133</v>
+        <v>0.3121985</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38093376</v>
+        <v>0.38152534</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="M26" t="n">
         <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>4.207362</v>
+        <v>4.2090755</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
@@ -2202,13 +2202,13 @@
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2611042</v>
+        <v>1.2632349</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25139773</v>
+        <v>0.25153255</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24196343</v>
+        <v>0.24251097</v>
       </c>
       <c r="C27" t="n">
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
         <v>158</v>
       </c>
       <c r="G27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31556395</v>
+        <v>0.31582525</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3813282</v>
+        <v>0.38103417</v>
       </c>
       <c r="K27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" t="n">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.304538</v>
+        <v>4.3028407</v>
       </c>
       <c r="O27" t="n">
         <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3569522</v>
+        <v>1.3577275</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2539257</v>
+        <v>0.25403455</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,43 +2288,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2595405</v>
+        <v>0.25938106</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G28" t="n">
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32873604</v>
+        <v>0.32818466</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40478972</v>
+        <v>0.40425533</v>
       </c>
       <c r="K28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7357247</v>
+        <v>3.7178183</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
@@ -2336,13 +2336,13 @@
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.136164</v>
+        <v>1.136</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22884503</v>
+        <v>0.2289765</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24354461</v>
+        <v>0.24319066</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3184836</v>
+        <v>0.3185764</v>
       </c>
       <c r="I29" t="n">
         <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3984742</v>
+        <v>0.39824903</v>
       </c>
       <c r="K29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2754445</v>
+        <v>4.260368</v>
       </c>
       <c r="O29" t="n">
         <v>21</v>
       </c>
       <c r="P29" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29916</v>
+        <v>1.2957054</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24749614</v>
+        <v>0.24712864</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24807397</v>
+        <v>0.24770291</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G30" t="n">
         <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31023043</v>
+        <v>0.30978826</v>
       </c>
       <c r="I30" t="n">
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3834746</v>
+        <v>0.38284838</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9144738</v>
+        <v>3.9244187</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q30" t="n">
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3033626</v>
+        <v>1.3023256</v>
       </c>
       <c r="S30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23611923</v>
+        <v>0.23580702</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2489,46 +2489,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24723388</v>
+        <v>0.24739929</v>
       </c>
       <c r="C31" t="n">
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32284403</v>
+        <v>0.32282004</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42598245</v>
+        <v>0.425383</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.687912</v>
+        <v>4.6569767</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
         <v>204</v>
@@ -2537,16 +2537,16 @@
         <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3860806</v>
+        <v>1.3866279</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.252682</v>
+        <v>0.2531333</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25700936</v>
+        <v>0.26291078</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31623933</v>
+        <v>0.32478634</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>0.44859812</v>
+        <v>0.46948355</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>60</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N2" t="n">
-        <v>4.982143</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3392857</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>0.26244345</v>
+        <v>0.23831776</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.17989418</v>
+        <v>0.2113402</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25480768</v>
+        <v>0.28169015</v>
       </c>
       <c r="I3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.37628865</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>47</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.7959185</v>
+      </c>
+      <c r="O3" t="n">
         <v>30</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.31746033</v>
-      </c>
-      <c r="K3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L3" t="n">
-        <v>50</v>
-      </c>
-      <c r="M3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="O3" t="n">
-        <v>29</v>
-      </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>1.88</v>
+        <v>1.6530613</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.31904763</v>
+        <v>0.29064038</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -2934,61 +2934,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.28504673</v>
+        <v>0.2783019</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.33620688</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.45754716</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.3653846</v>
+      </c>
+      <c r="O4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.34599155</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.47196263</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>54</v>
-      </c>
-      <c r="M4" t="n">
-        <v>14</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.1923075</v>
-      </c>
-      <c r="O4" t="n">
-        <v>26</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7</v>
-      </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3846154</v>
+        <v>1.4615384</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T4" t="n">
-        <v>0.27093595</v>
+        <v>0.2815534</v>
       </c>
       <c r="U4" t="n">
         <v>24</v>
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24200913</v>
+        <v>0.23831776</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2948718</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.42523363</v>
+      </c>
+      <c r="K5" t="n">
         <v>11</v>
       </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.29707113</v>
-      </c>
-      <c r="I5" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.43835616</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>72</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.0535715</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2678572</v>
+      </c>
+      <c r="S5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
-        <v>79</v>
-      </c>
-      <c r="M5" t="n">
-        <v>30</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.090909</v>
-      </c>
-      <c r="O5" t="n">
-        <v>16</v>
-      </c>
-      <c r="P5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5090909</v>
-      </c>
-      <c r="S5" t="n">
-        <v>26</v>
-      </c>
       <c r="T5" t="n">
-        <v>0.26291078</v>
+        <v>0.22748815</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3068,46 +3068,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.21354167</v>
+        <v>0.203125</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>0.30092594</v>
+        <v>0.29166666</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
         <v>0.33854166</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9423077</v>
+        <v>2.9612904</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -3116,16 +3116,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2115384</v>
+        <v>1.2580645</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.20634921</v>
+        <v>0.21989529</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24210526</v>
+        <v>0.25</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.34070796</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.43367347</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.075472</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.2830188</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.23469388</v>
+      </c>
+      <c r="U7" t="n">
         <v>12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.3438914</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.43157893</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" t="n">
-        <v>35</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.245283</v>
-      </c>
-      <c r="O7" t="n">
-        <v>17</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3584906</v>
-      </c>
-      <c r="S7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.24120604</v>
-      </c>
-      <c r="U7" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20614035</v>
+        <v>0.20179372</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32600734</v>
+        <v>0.3053435</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3377193</v>
+        <v>0.34080717</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L8" t="n">
         <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N8" t="n">
-        <v>4.0054946</v>
+        <v>3.412088</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
+        <v>16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3186812</v>
+      </c>
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.3681319</v>
-      </c>
-      <c r="S8" t="n">
-        <v>16</v>
-      </c>
       <c r="T8" t="n">
-        <v>0.24242425</v>
+        <v>0.24347825</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.25110132</v>
+        <v>0.21461187</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3242009</v>
+      </c>
+      <c r="K9" t="n">
         <v>28</v>
       </c>
-      <c r="E9" t="n">
-        <v>15</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.30645162</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
+        <v>59</v>
+      </c>
+      <c r="M9" t="n">
         <v>21</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.40088105</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19</v>
-      </c>
-      <c r="L9" t="n">
-        <v>61</v>
-      </c>
-      <c r="M9" t="n">
-        <v>26</v>
-      </c>
       <c r="N9" t="n">
-        <v>5.516129</v>
+        <v>4.285714</v>
       </c>
       <c r="O9" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5645162</v>
+        <v>1.3968254</v>
       </c>
       <c r="S9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25541127</v>
+        <v>0.23451327</v>
       </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24623115</v>
+        <v>0.28502417</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.35497835</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5362319</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
         <v>33</v>
       </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3288889</v>
-      </c>
-      <c r="I10" t="n">
-        <v>14</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.44723618</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>37</v>
-      </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7358491</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P10" t="n">
         <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1698114</v>
+        <v>1.2592592</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.21243523</v>
+        <v>0.23</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2988048</v>
+        <v>0.29032257</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.34814814</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.44354838</v>
+      </c>
+      <c r="K11" t="n">
         <v>9</v>
       </c>
-      <c r="F11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.35766423</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4860558</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>7.819672</v>
+        <v>6.532258</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
         <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8524591</v>
+        <v>1.5806452</v>
       </c>
       <c r="S11" t="n">
         <v>29</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3385214</v>
+        <v>0.30677292</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.30645162</v>
+        <v>0.27385893</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.37010676</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4107884</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
         <v>7</v>
       </c>
-      <c r="G12" t="n">
-        <v>13</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.48387095</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="R12" t="n">
+        <v>1.1166667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.19909503</v>
+      </c>
+      <c r="U12" t="n">
         <v>4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>56</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.2459016</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>10</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2295082</v>
-      </c>
-      <c r="S12" t="n">
-        <v>9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.22608696</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.19473684</v>
+        <v>0.21761657</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.26666668</v>
+        <v>0.27962086</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4368421</v>
+        <v>0.46632123</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.673077</v>
+        <v>5.09434</v>
       </c>
       <c r="O13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3076923</v>
+        <v>1.3584906</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23880596</v>
+        <v>0.25</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -3604,52 +3604,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.171875</v>
+        <v>0.20707071</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25700936</v>
+        <v>0.2927928</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>0.296875</v>
+        <v>0.32323232</v>
       </c>
       <c r="K14" t="n">
         <v>29</v>
       </c>
       <c r="L14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3265305</v>
+        <v>5.5102043</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R14" t="n">
         <v>1.4081633</v>
@@ -3658,10 +3658,10 @@
         <v>19</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2871795</v>
+        <v>0.2820513</v>
       </c>
       <c r="U14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.20264317</v>
+        <v>0.22457626</v>
       </c>
       <c r="C15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" t="n">
         <v>26</v>
       </c>
-      <c r="D15" t="n">
-        <v>25</v>
-      </c>
       <c r="E15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
         <v>20</v>
       </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>27</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.29389313</v>
+        <v>0.31617647</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>0.29955947</v>
+        <v>0.32627118</v>
       </c>
       <c r="K15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L15" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9789474</v>
+        <v>3.876923</v>
       </c>
       <c r="O15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3421053</v>
+        <v>1.2769231</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2701613</v>
+        <v>0.26587301</v>
       </c>
       <c r="U15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -3738,61 +3738,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23684211</v>
+        <v>0.27659574</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.36363637</v>
+        <v>0.39361703</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.46052632</v>
+        <v>0.50212765</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
         <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.0983605</v>
       </c>
       <c r="O16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
         <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.05</v>
+        <v>1.0163934</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21917808</v>
+        <v>0.22072072</v>
       </c>
       <c r="U16" t="n">
         <v>7</v>
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25238097</v>
+        <v>0.2580645</v>
       </c>
       <c r="C17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>29</v>
+      </c>
+      <c r="E17" t="n">
         <v>12</v>
       </c>
-      <c r="D17" t="n">
-        <v>27</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16</v>
-      </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.31601733</v>
+        <v>0.325</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4047619</v>
+        <v>0.41935483</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4723926</v>
+        <v>4.9390244</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P17" t="n">
         <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4723927</v>
+        <v>1.5731707</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25943395</v>
+        <v>0.28310502</v>
       </c>
       <c r="U17" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.27014217</v>
+        <v>0.22772278</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.31304348</v>
+      </c>
+      <c r="I18" t="n">
+        <v>19</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.33663365</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24</v>
+      </c>
+      <c r="L18" t="n">
+        <v>58</v>
+      </c>
+      <c r="M18" t="n">
+        <v>19</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.3333333</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
         <v>7</v>
       </c>
-      <c r="G18" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.36065573</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.4170616</v>
-      </c>
-      <c r="K18" t="n">
-        <v>13</v>
-      </c>
-      <c r="L18" t="n">
-        <v>54</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
+        <v>16</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2962962</v>
+      </c>
+      <c r="S18" t="n">
         <v>14</v>
       </c>
-      <c r="N18" t="n">
-        <v>4.8333335</v>
-      </c>
-      <c r="O18" t="n">
-        <v>24</v>
-      </c>
-      <c r="P18" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
+        <v>0.25728154</v>
+      </c>
+      <c r="U18" t="n">
         <v>19</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4814814</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.29166666</v>
-      </c>
-      <c r="U18" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.22727273</v>
+        <v>0.23228346</v>
       </c>
       <c r="C19" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" t="n">
         <v>23</v>
       </c>
-      <c r="D19" t="n">
-        <v>22</v>
-      </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>0.28301886</v>
+        <v>0.27737227</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3429752</v>
+        <v>0.3503937</v>
       </c>
       <c r="K19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M19" t="n">
         <v>27</v>
       </c>
       <c r="N19" t="n">
-        <v>4.009901</v>
+        <v>4.0434785</v>
       </c>
       <c r="O19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2623762</v>
+        <v>1.3623189</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2413793</v>
+        <v>0.2509225</v>
       </c>
       <c r="U19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.24279836</v>
+        <v>0.23628692</v>
       </c>
       <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.31835207</v>
+      </c>
+      <c r="I20" t="n">
         <v>17</v>
       </c>
-      <c r="D20" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.3071161</v>
-      </c>
-      <c r="I20" t="n">
-        <v>20</v>
-      </c>
       <c r="J20" t="n">
-        <v>0.38683128</v>
+        <v>0.32489452</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M20" t="n">
         <v>19</v>
       </c>
       <c r="N20" t="n">
-        <v>3.09375</v>
+        <v>3.234375</v>
       </c>
       <c r="O20" t="n">
+        <v>9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.09375</v>
+      </c>
+      <c r="S20" t="n">
         <v>5</v>
       </c>
-      <c r="P20" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>30</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.015625</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
       <c r="T20" t="n">
-        <v>0.2173913</v>
+        <v>0.22413793</v>
       </c>
       <c r="U20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23148148</v>
+        <v>0.22429906</v>
       </c>
       <c r="C21" t="n">
+        <v>23</v>
+      </c>
+      <c r="D21" t="n">
+        <v>34</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.29707113</v>
+      </c>
+      <c r="I21" t="n">
         <v>22</v>
       </c>
-      <c r="D21" t="n">
-        <v>33</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.29831934</v>
-      </c>
-      <c r="I21" t="n">
-        <v>23</v>
-      </c>
       <c r="J21" t="n">
-        <v>0.4027778</v>
+        <v>0.40654206</v>
       </c>
       <c r="K21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
         <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8421052</v>
+        <v>1.4378698</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0701754</v>
+        <v>0.99408287</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22380953</v>
+        <v>0.19900498</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4140,52 +4140,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23857868</v>
+        <v>0.245</v>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H22" t="n">
-        <v>0.32444444</v>
+        <v>0.3390558</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39086294</v>
+        <v>0.375</v>
       </c>
       <c r="K22" t="n">
+        <v>19</v>
+      </c>
+      <c r="L22" t="n">
+        <v>41</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.5882354</v>
+      </c>
+      <c r="O22" t="n">
         <v>21</v>
-      </c>
-      <c r="L22" t="n">
-        <v>32</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.8823528</v>
-      </c>
-      <c r="O22" t="n">
-        <v>11</v>
       </c>
       <c r="P22" t="n">
         <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R22" t="n">
         <v>1.4705882</v>
@@ -4194,10 +4194,10 @@
         <v>23</v>
       </c>
       <c r="T22" t="n">
-        <v>0.28061223</v>
+        <v>0.27319586</v>
       </c>
       <c r="U22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28365386</v>
+        <v>0.30097088</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.37117904</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>55</v>
+      </c>
+      <c r="M23" t="n">
         <v>16</v>
       </c>
-      <c r="F23" t="n">
+      <c r="N23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>19</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
         <v>7</v>
       </c>
-      <c r="G23" t="n">
-        <v>13</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.36051503</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.44230768</v>
-      </c>
-      <c r="K23" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" t="n">
-        <v>56</v>
-      </c>
-      <c r="M23" t="n">
-        <v>20</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.4150944</v>
-      </c>
-      <c r="O23" t="n">
-        <v>18</v>
-      </c>
-      <c r="P23" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.3396226</v>
+        <v>1.4444444</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23076923</v>
+        <v>0.25728154</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.32950193</v>
+        <v>0.32307693</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -4289,49 +4289,49 @@
         <v>13</v>
       </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3728223</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.3784722</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3</v>
-      </c>
       <c r="J24" t="n">
-        <v>0.55938697</v>
+        <v>0.5538462</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="M24" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="N24" t="n">
-        <v>4.790323</v>
+        <v>4.714286</v>
       </c>
       <c r="O24" t="n">
         <v>23</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4032258</v>
+        <v>1.5555556</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="T24" t="n">
-        <v>0.28225806</v>
+        <v>0.2868526</v>
       </c>
       <c r="U24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25238097</v>
+        <v>0.25358853</v>
       </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3173913</v>
+        <v>0.3304721</v>
       </c>
       <c r="I25" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.38277513</v>
+      </c>
+      <c r="K25" t="n">
         <v>17</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.40952381</v>
-      </c>
-      <c r="K25" t="n">
-        <v>16</v>
-      </c>
       <c r="L25" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5849056</v>
+        <v>4.8461537</v>
       </c>
       <c r="O25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
         <v>19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4339622</v>
+        <v>1.4807693</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25</v>
+        <v>0.26108375</v>
       </c>
       <c r="U25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3119266</v>
+        <v>0.25853658</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>0.384</v>
+        <v>0.32900432</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5412844</v>
+        <v>0.44878048</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8823528</v>
+        <v>4.68</v>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4509804</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>0.26960784</v>
+        <v>0.28921568</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.19270833</v>
+        <v>0.21078432</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
         <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2706422</v>
+        <v>0.27433628</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>0.265625</v>
+        <v>0.2647059</v>
       </c>
       <c r="K27" t="n">
         <v>30</v>
@@ -4508,31 +4508,31 @@
         <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N27" t="n">
-        <v>4.418182</v>
+        <v>4.105263</v>
       </c>
       <c r="O27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P27" t="n">
         <v>5</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4363636</v>
+        <v>1.4385965</v>
       </c>
       <c r="S27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2364532</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2525773</v>
+        <v>0.24875621</v>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33936653</v>
+        <v>0.32286996</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>0.41237113</v>
+        <v>0.41293532</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>2.3333333</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="n">
         <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9074074</v>
+        <v>0.9444444</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.17857143</v>
+        <v>0.19387755</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -4609,55 +4609,55 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2763819</v>
+        <v>0.24867725</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
         <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3482143</v>
+        <v>0.3409091</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3919598</v>
+        <v>0.35978836</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0.9814815</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -4666,7 +4666,7 @@
         <v>0.19170985</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4676,46 +4676,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.25128207</v>
+        <v>0.2244898</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>0.33632287</v>
+        <v>0.29816514</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3846154</v>
+        <v>0.33163264</v>
       </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5660377</v>
+        <v>4.1538463</v>
       </c>
       <c r="O30" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P30" t="n">
         <v>3</v>
@@ -4724,16 +4724,16 @@
         <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5660378</v>
+        <v>1.5769231</v>
       </c>
       <c r="S30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23902439</v>
+        <v>0.24120604</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.26347306</v>
+        <v>0.2601156</v>
       </c>
       <c r="C31" t="n">
         <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H31" t="n">
-        <v>0.33333334</v>
+        <v>0.32642487</v>
       </c>
       <c r="I31" t="n">
         <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>0.41317365</v>
+        <v>0.40462428</v>
       </c>
       <c r="K31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M31" t="n">
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1304348</v>
+        <v>2.2978723</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.1956521</v>
+        <v>1.2765957</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T31" t="n">
-        <v>0.15822785</v>
+        <v>0.20467836</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24322246</v>
+        <v>0.2437906</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3151838</v>
+        <v>0.31575355</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39684677</v>
+        <v>0.39759266</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1057205</v>
+        <v>4.105036</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2773353</v>
+        <v>1.276259</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24799542</v>
+        <v>0.24791351</v>
       </c>
       <c r="U2" t="n">
         <v>20</v>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24409749</v>
+        <v>0.24380086</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>670</v>
@@ -631,25 +631,25 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31662676</v>
+        <v>0.31609392</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4011805</v>
+        <v>0.40015143</v>
       </c>
       <c r="K3" t="n">
         <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4605265</v>
+        <v>5.43532</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.504386</v>
+        <v>1.5014535</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27097738</v>
+        <v>0.2707675</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24813896</v>
+        <v>0.24772382</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31125712</v>
+        <v>0.31099656</v>
       </c>
       <c r="I4" t="n">
         <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41210154</v>
+        <v>0.41141883</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1252</v>
+        <v>1266</v>
       </c>
       <c r="M4" t="n">
         <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6235466</v>
+        <v>3.6129963</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2478198</v>
+        <v>1.2469314</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23359223</v>
+        <v>0.23355834</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23440818</v>
+        <v>0.23378119</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>693</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>189</v>
@@ -765,43 +765,43 @@
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31496063</v>
+        <v>0.31444615</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39544314</v>
+        <v>0.39385796</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1248193</v>
+        <v>4.1175485</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3424096</v>
+        <v>1.342351</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25297114</v>
+        <v>0.25272045</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24639076</v>
+        <v>0.24603023</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3205832</v>
+        <v>0.32008868</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40153995</v>
+        <v>0.40099484</v>
       </c>
       <c r="K6" t="n">
         <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5791001</v>
+        <v>3.590909</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2380261</v>
+        <v>1.2352092</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24176459</v>
+        <v>0.24123396</v>
       </c>
       <c r="U6" t="n">
         <v>15</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25155222</v>
+        <v>0.25210086</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3397341</v>
+        <v>0.34006843</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43104422</v>
+        <v>0.43230626</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.184382</v>
+        <v>4.163793</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2682574</v>
+        <v>1.2636495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24406585</v>
+        <v>0.24338725</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23370613</v>
+        <v>0.23414448</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3180194</v>
+        <v>0.3189189</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4016583</v>
+        <v>0.4019927</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1257253</v>
+        <v>4.105453</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
         <v>172</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.313588</v>
+        <v>1.3129954</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24220254</v>
+        <v>0.24191387</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22925976</v>
+        <v>0.22865972</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30661356</v>
+        <v>0.30578512</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39421022</v>
+        <v>0.393202</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.867347</v>
+        <v>4.8942795</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q9" t="n">
         <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4482508</v>
+        <v>1.4511224</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25440758</v>
+        <v>0.25493884</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23801237</v>
+        <v>0.23798539</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
@@ -1100,25 +1100,25 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.315337</v>
+        <v>0.31503335</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3779969</v>
+        <v>0.37735486</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8048427</v>
+        <v>3.78013</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1130,16 +1130,16 @@
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2624698</v>
+        <v>1.2593217</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2365882</v>
+        <v>0.23633225</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1149,43 +1149,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2548277</v>
+        <v>0.2542341</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32417303</v>
+        <v>0.32349467</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41688755</v>
+        <v>0.41625893</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="M11" t="n">
         <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5957866</v>
+        <v>5.572159</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -1197,13 +1197,13 @@
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5301323</v>
+        <v>1.5251887</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2886636</v>
+        <v>0.28786212</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24077262</v>
+        <v>0.2404943</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E12" t="n">
         <v>13</v>
@@ -1234,43 +1234,43 @@
         <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31856003</v>
+        <v>0.31854227</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3991203</v>
+        <v>0.39828897</v>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>1345</v>
+        <v>1354</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.627551</v>
+        <v>3.6586957</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q12" t="n">
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2201166</v>
+        <v>1.226087</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2319095</v>
+        <v>0.23236434</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,64 +1283,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23976159</v>
+        <v>0.23968679</v>
       </c>
       <c r="C13" t="n">
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3130809</v>
+        <v>0.31280997</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4103057</v>
+        <v>0.41023684</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1271</v>
+        <v>1282</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.530553</v>
+        <v>4.527102</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3450534</v>
+        <v>1.3435317</v>
       </c>
       <c r="S13" t="n">
         <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23820618</v>
+        <v>0.23784722</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24485081</v>
+        <v>0.24493308</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3148532</v>
+        <v>0.3146241</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39807507</v>
+        <v>0.39789674</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.664057</v>
+        <v>4.663099</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917298</v>
+        <v>1.3930917</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25941584</v>
+        <v>0.25930876</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23353294</v>
+        <v>0.2326609</v>
       </c>
       <c r="C15" t="n">
         <v>28</v>
@@ -1426,55 +1426,55 @@
         <v>625</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
         <v>148</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30884895</v>
+        <v>0.3081815</v>
       </c>
       <c r="I15" t="n">
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.36951903</v>
+        <v>0.36791545</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1480</v>
+        <v>1491</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1871657</v>
+        <v>4.205506</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.335926</v>
+        <v>1.3380826</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23652579</v>
+        <v>0.23725227</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1484,46 +1484,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25676453</v>
+        <v>0.25719732</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G16" t="n">
         <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33906594</v>
+        <v>0.33897737</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42506236</v>
+        <v>0.42554814</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.634994</v>
+        <v>3.6178174</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
         <v>171</v>
@@ -1532,13 +1532,13 @@
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1584448</v>
+        <v>1.1545148</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22001962</v>
+        <v>0.21912195</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24937223</v>
+        <v>0.24875145</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32717317</v>
+        <v>0.3265827</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40139076</v>
+        <v>0.40049943</v>
       </c>
       <c r="K17" t="n">
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="M17" t="n">
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>4.136086</v>
+        <v>4.1578817</v>
       </c>
       <c r="O17" t="n">
         <v>15</v>
       </c>
       <c r="P17" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="n">
+        <v>10</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2905028</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.23712136</v>
+      </c>
+      <c r="U17" t="n">
         <v>9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2892743</v>
-      </c>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.23669903</v>
-      </c>
-      <c r="U17" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25833964</v>
+        <v>0.25805843</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34066668</v>
+        <v>0.34067938</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40333587</v>
+        <v>0.40301603</v>
       </c>
       <c r="K18" t="n">
         <v>11</v>
       </c>
       <c r="L18" t="n">
-        <v>1309</v>
+        <v>1323</v>
       </c>
       <c r="M18" t="n">
         <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5618682</v>
+        <v>3.5388663</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1663,16 +1663,16 @@
         <v>165</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1901782</v>
+        <v>1.187515</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2238864</v>
+        <v>0.22331786</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2438372</v>
+        <v>0.24449924</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31683168</v>
+        <v>0.31728813</v>
       </c>
       <c r="I19" t="n">
         <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>0.402446</v>
+        <v>0.40269348</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6255765</v>
+        <v>4.5954676</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
@@ -1733,16 +1733,16 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3722398</v>
+        <v>1.3669238</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25004736</v>
+        <v>0.24910496</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1752,46 +1752,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23866896</v>
+        <v>0.238891</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30960977</v>
+        <v>0.30936113</v>
       </c>
       <c r="I20" t="n">
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39395678</v>
+        <v>0.39384732</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1493363</v>
+        <v>4.167785</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
         <v>179</v>
@@ -1800,13 +1800,13 @@
         <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2962606</v>
+        <v>1.2993768</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24084668</v>
+        <v>0.24071266</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23471788</v>
+        <v>0.23472168</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31170416</v>
+        <v>0.31149247</v>
       </c>
       <c r="I21" t="n">
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40928683</v>
+        <v>0.4098871</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.184147</v>
+        <v>3.2176838</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q21" t="n">
         <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1614306</v>
+        <v>1.1655453</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2225693</v>
+        <v>0.22327837</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2413793</v>
+        <v>0.24124067</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
         <v>179</v>
       </c>
       <c r="G22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31189656</v>
+        <v>0.312393</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3978039</v>
+        <v>0.39728126</v>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L22" t="n">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0179353</v>
+        <v>4.0048156</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2869607</v>
+        <v>1.2858174</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24738742</v>
+        <v>0.24754716</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25441232</v>
+        <v>0.2543385</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G23" t="n">
         <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33149633</v>
+        <v>0.33156323</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40518212</v>
+        <v>0.4056727</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>1443</v>
+        <v>1452</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1963854</v>
+        <v>4.188652</v>
       </c>
       <c r="O23" t="n">
         <v>19</v>
       </c>
       <c r="P23" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3048192</v>
+        <v>1.3035672</v>
       </c>
       <c r="S23" t="n">
         <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23784922</v>
+        <v>0.23797756</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24329054</v>
+        <v>0.24367149</v>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3189133</v>
+        <v>0.31905743</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39848307</v>
+        <v>0.4</v>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.942275</v>
+        <v>3.9361446</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q24" t="n">
         <v>16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29008</v>
+        <v>1.286747</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24162634</v>
+        <v>0.24104737</v>
       </c>
       <c r="U24" t="n">
         <v>14</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24762087</v>
+        <v>0.24659349</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
@@ -2102,49 +2102,49 @@
         <v>177</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30923557</v>
+        <v>0.3083405</v>
       </c>
       <c r="I25" t="n">
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40673772</v>
+        <v>0.40480697</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L25" t="n">
-        <v>1258</v>
+        <v>1272</v>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N25" t="n">
-        <v>4.391368</v>
+        <v>4.3854547</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3694221</v>
+        <v>1.3694545</v>
       </c>
       <c r="S25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24893945</v>
+        <v>0.24942529</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23248594</v>
+        <v>0.23195678</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
@@ -2169,46 +2169,46 @@
         <v>179</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3121985</v>
+        <v>0.311804</v>
       </c>
       <c r="I26" t="n">
+        <v>23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3803551</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1352</v>
+      </c>
+      <c r="M26" t="n">
         <v>22</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.38152534</v>
-      </c>
-      <c r="K26" t="n">
-        <v>27</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1346</v>
-      </c>
-      <c r="M26" t="n">
-        <v>23</v>
-      </c>
       <c r="N26" t="n">
-        <v>4.2090755</v>
+        <v>4.1880755</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26" t="n">
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2632349</v>
+        <v>1.2600582</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25153255</v>
+        <v>0.250952</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24251097</v>
+        <v>0.24222307</v>
       </c>
       <c r="C27" t="n">
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31582525</v>
+        <v>0.31541583</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38103417</v>
+        <v>0.38182852</v>
       </c>
       <c r="K27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3028407</v>
+        <v>4.2944274</v>
       </c>
       <c r="O27" t="n">
         <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3577275</v>
+        <v>1.3554174</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25403455</v>
+        <v>0.25386938</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25938106</v>
+        <v>0.25875336</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G28" t="n">
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32818466</v>
+        <v>0.3276368</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40425533</v>
+        <v>0.4036168</v>
       </c>
       <c r="K28" t="n">
         <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7178183</v>
+        <v>3.7001445</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.136</v>
+        <v>1.1343931</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2289765</v>
+        <v>0.22872032</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24319066</v>
+        <v>0.24313878</v>
       </c>
       <c r="C29" t="n">
         <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G29" t="n">
         <v>18</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3185764</v>
+        <v>0.31855813</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39824903</v>
+        <v>0.397758</v>
       </c>
       <c r="K29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.260368</v>
+        <v>4.278401</v>
       </c>
       <c r="O29" t="n">
         <v>21</v>
@@ -2400,19 +2400,19 @@
         <v>184</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2957054</v>
+        <v>1.2996099</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24712864</v>
+        <v>0.24757558</v>
       </c>
       <c r="U29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24770291</v>
+        <v>0.24814604</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>149</v>
@@ -2440,43 +2440,43 @@
         <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30978826</v>
+        <v>0.31059432</v>
       </c>
       <c r="I30" t="n">
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38284838</v>
+        <v>0.3831527</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9244187</v>
+        <v>3.9119134</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q30" t="n">
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3023256</v>
+        <v>1.3025271</v>
       </c>
       <c r="S30" t="n">
         <v>17</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23580702</v>
+        <v>0.23580366</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24739929</v>
+        <v>0.24727342</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32282004</v>
+        <v>0.32248867</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.425383</v>
+        <v>0.4249718</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6569767</v>
+        <v>4.6625724</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q31" t="n">
         <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3866279</v>
+        <v>1.3843931</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2531333</v>
+        <v>0.2527846</v>
       </c>
       <c r="U31" t="n">
         <v>25</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.26291078</v>
+        <v>0.26190478</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3275862</v>
+      </c>
+      <c r="I2" t="n">
         <v>11</v>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.32478634</v>
-      </c>
-      <c r="I2" t="n">
-        <v>15</v>
-      </c>
       <c r="J2" t="n">
-        <v>0.46948355</v>
+        <v>0.45714286</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
         <v>60</v>
       </c>
       <c r="M2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" t="n">
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.2321428</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.23831776</v>
+        <v>0.23222749</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2113402</v>
+        <v>0.19689119</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.28169015</v>
+        <v>0.24390244</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>0.37628865</v>
+        <v>0.30569947</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>6.7959185</v>
+        <v>5.8125</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6530613</v>
+        <v>1.4791666</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T3" t="n">
-        <v>0.29064038</v>
+        <v>0.2741117</v>
       </c>
       <c r="U3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2783019</v>
+        <v>0.25480768</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3171806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.44230768</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.1538463</v>
+      </c>
+      <c r="O4" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.33620688</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.45754716</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.3653846</v>
-      </c>
-      <c r="O4" t="n">
-        <v>27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6</v>
-      </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4615384</v>
+        <v>1.2884616</v>
       </c>
       <c r="S4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2815534</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -3001,13 +3001,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23831776</v>
+        <v>0.21904762</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
         <v>23</v>
@@ -3016,49 +3016,49 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2948718</v>
+        <v>0.27192983</v>
       </c>
       <c r="I5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J5" t="n">
-        <v>0.42523363</v>
+        <v>0.4047619</v>
       </c>
       <c r="K5" t="n">
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0535715</v>
+        <v>2.2105262</v>
       </c>
       <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.1929824</v>
+      </c>
+      <c r="S5" t="n">
         <v>7</v>
       </c>
-      <c r="P5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.2678572</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
       <c r="T5" t="n">
-        <v>0.22748815</v>
+        <v>0.21359223</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.203125</v>
+        <v>0.19170985</v>
       </c>
       <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
         <v>29</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29166666</v>
+        <v>0.27102804</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J6" t="n">
-        <v>0.33854166</v>
+        <v>0.32642487</v>
       </c>
       <c r="K6" t="n">
         <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9612904</v>
+        <v>3.7302632</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.2580645</v>
+        <v>1.2039473</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
-        <v>0.21989529</v>
+        <v>0.21925133</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25</v>
+        <v>0.27669904</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.35470086</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4854369</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>39</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.5660377</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="n">
         <v>8</v>
       </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.34070796</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.43367347</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>33</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.075472</v>
-      </c>
-      <c r="O7" t="n">
-        <v>15</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
+        <v>1.1132076</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
+        <v>0.21243523</v>
+      </c>
+      <c r="U7" t="n">
         <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.2830188</v>
-      </c>
-      <c r="S7" t="n">
-        <v>13</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.23469388</v>
-      </c>
-      <c r="U7" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20179372</v>
+        <v>0.2246696</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I8" t="n">
         <v>8</v>
       </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3053435</v>
-      </c>
-      <c r="I8" t="n">
-        <v>20</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.34080717</v>
+        <v>0.37004405</v>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M8" t="n">
         <v>30</v>
       </c>
       <c r="N8" t="n">
-        <v>3.412088</v>
+        <v>3.5027027</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
         <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3186812</v>
+        <v>1.4108108</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24347825</v>
+        <v>0.25</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.21461187</v>
+        <v>0.19907407</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>0.275</v>
+        <v>0.25641027</v>
       </c>
       <c r="I9" t="n">
         <v>29</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3242009</v>
+        <v>0.30092594</v>
       </c>
       <c r="K9" t="n">
         <v>28</v>
@@ -3305,28 +3305,28 @@
         <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>4.285714</v>
+        <v>5.142857</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3968254</v>
+        <v>1.5238096</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.23451327</v>
+        <v>0.25316456</v>
       </c>
       <c r="U9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.28502417</v>
+        <v>0.26262626</v>
       </c>
       <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.32718894</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.46464646</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.6666667</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>42</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2407408</v>
+      </c>
+      <c r="S10" t="n">
         <v>13</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.35497835</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5362319</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>33</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>13</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2592592</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.23</v>
+        <v>0.23232323</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.29032257</v>
+        <v>0.28915662</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -3412,52 +3412,52 @@
         <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34814814</v>
+        <v>0.34686348</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.44354838</v>
+        <v>0.44578314</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>6.532258</v>
+        <v>5.571429</v>
       </c>
       <c r="O11" t="n">
         <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5806452</v>
+        <v>1.4285715</v>
       </c>
       <c r="S11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="T11" t="n">
-        <v>0.30677292</v>
+        <v>0.2931727</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.27385893</v>
+        <v>0.26556018</v>
       </c>
       <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="D12" t="n">
-        <v>38</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H12" t="n">
-        <v>0.37010676</v>
+        <v>0.3607143</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4107884</v>
+        <v>0.373444</v>
       </c>
       <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.8135593</v>
+      </c>
+      <c r="O12" t="n">
         <v>14</v>
-      </c>
-      <c r="L12" t="n">
-        <v>57</v>
-      </c>
-      <c r="M12" t="n">
-        <v>17</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
       </c>
       <c r="P12" t="n">
         <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1166667</v>
+        <v>1.338983</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19909503</v>
+        <v>0.21973094</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.21761657</v>
+        <v>0.23350254</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0.27962086</v>
       </c>
       <c r="I13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J13" t="n">
-        <v>0.46632123</v>
+        <v>0.4568528</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
         <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.09434</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3584906</v>
+        <v>1.2037038</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>0.25</v>
+        <v>0.21393035</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.20707071</v>
+        <v>0.2238806</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
+        <v>22</v>
+      </c>
+      <c r="E14" t="n">
         <v>20</v>
       </c>
-      <c r="E14" t="n">
-        <v>28</v>
-      </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2927928</v>
+        <v>0.29090908</v>
       </c>
       <c r="I14" t="n">
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>0.32323232</v>
+        <v>0.35820895</v>
       </c>
       <c r="K14" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
         <v>5.5102043</v>
       </c>
       <c r="O14" t="n">
+        <v>27</v>
+      </c>
+      <c r="P14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>30</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4489796</v>
+      </c>
+      <c r="S14" t="n">
+        <v>24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.27918783</v>
+      </c>
+      <c r="U14" t="n">
         <v>28</v>
-      </c>
-      <c r="P14" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>29</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4081633</v>
-      </c>
-      <c r="S14" t="n">
-        <v>19</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2820513</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.22457626</v>
+        <v>0.21794872</v>
       </c>
       <c r="C15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" t="n">
         <v>21</v>
       </c>
-      <c r="D15" t="n">
-        <v>26</v>
-      </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31617647</v>
+        <v>0.3071161</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.32627118</v>
+        <v>0.2863248</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>3.876923</v>
+        <v>3.9545455</v>
       </c>
       <c r="O15" t="n">
+        <v>16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
         <v>12</v>
       </c>
-      <c r="P15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.2769231</v>
+        <v>1.2575758</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T15" t="n">
-        <v>0.26587301</v>
+        <v>0.2627451</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3738,31 +3738,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.27659574</v>
+        <v>0.2851064</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.39361703</v>
+        <v>0.38545454</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.50212765</v>
+        <v>0.5106383</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -3771,31 +3771,31 @@
         <v>43</v>
       </c>
       <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.3225806</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
         <v>6</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.0983605</v>
-      </c>
-      <c r="O16" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>7</v>
-      </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0163934</v>
+        <v>0.9032258</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22072072</v>
+        <v>0.19178082</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2580645</v>
+        <v>0.23943663</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>0.325</v>
+        <v>0.31223628</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="n">
-        <v>0.41935483</v>
+        <v>0.39906102</v>
       </c>
       <c r="K17" t="n">
         <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9390244</v>
+        <v>5.5341616</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5731707</v>
+        <v>1.5652174</v>
       </c>
       <c r="S17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>0.28310502</v>
+        <v>0.28899083</v>
       </c>
       <c r="U17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -3875,61 +3875,61 @@
         <v>0.22772278</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" t="n">
-        <v>0.31304348</v>
+        <v>0.32188842</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33663365</v>
+        <v>0.32673267</v>
       </c>
       <c r="K18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L18" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3333333</v>
+        <v>2.6666667</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
+        <v>12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2222222</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2413793</v>
+      </c>
+      <c r="U18" t="n">
         <v>16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.2962962</v>
-      </c>
-      <c r="S18" t="n">
-        <v>14</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.25728154</v>
-      </c>
-      <c r="U18" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.23228346</v>
+        <v>0.25384617</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.27737227</v>
+        <v>0.29893237</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3503937</v>
+        <v>0.3653846</v>
       </c>
       <c r="K19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L19" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M19" t="n">
         <v>27</v>
       </c>
       <c r="N19" t="n">
-        <v>4.0434785</v>
+        <v>2.8695652</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3623189</v>
+        <v>1.173913</v>
       </c>
       <c r="S19" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2509225</v>
+        <v>0.21538462</v>
       </c>
       <c r="U19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23628692</v>
+        <v>0.2581967</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H20" t="n">
-        <v>0.31835207</v>
+        <v>0.33088234</v>
       </c>
       <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.35655737</v>
+      </c>
+      <c r="K20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" t="n">
+        <v>56</v>
+      </c>
+      <c r="M20" t="n">
         <v>17</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.32489452</v>
-      </c>
-      <c r="K20" t="n">
-        <v>27</v>
-      </c>
-      <c r="L20" t="n">
-        <v>58</v>
-      </c>
-      <c r="M20" t="n">
-        <v>19</v>
-      </c>
       <c r="N20" t="n">
-        <v>3.234375</v>
+        <v>3.876923</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.2153846</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.23430963</v>
+      </c>
+      <c r="U20" t="n">
         <v>13</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>28</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.09375</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.22413793</v>
-      </c>
-      <c r="U20" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.22429906</v>
+        <v>0.23766816</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.30081302</v>
+      </c>
+      <c r="I21" t="n">
+        <v>19</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.42600897</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>53</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.7650602</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" t="n">
         <v>5</v>
       </c>
-      <c r="F21" t="n">
-        <v>11</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.29707113</v>
-      </c>
-      <c r="I21" t="n">
-        <v>22</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.40654206</v>
-      </c>
-      <c r="K21" t="n">
-        <v>15</v>
-      </c>
-      <c r="L21" t="n">
-        <v>54</v>
-      </c>
-      <c r="M21" t="n">
-        <v>15</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.4378698</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4</v>
-      </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>0.99408287</v>
+        <v>1.1927711</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>0.19900498</v>
+        <v>0.23529412</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -4140,46 +4140,46 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.245</v>
+        <v>0.20942408</v>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
+        <v>22</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.32900432</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.31937173</v>
+      </c>
+      <c r="K22" t="n">
         <v>24</v>
       </c>
-      <c r="E22" t="n">
+      <c r="L22" t="n">
+        <v>44</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.2352943</v>
+      </c>
+      <c r="O22" t="n">
         <v>19</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>26</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3390558</v>
-      </c>
-      <c r="I22" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K22" t="n">
-        <v>19</v>
-      </c>
-      <c r="L22" t="n">
-        <v>41</v>
-      </c>
-      <c r="M22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.5882354</v>
-      </c>
-      <c r="O22" t="n">
-        <v>21</v>
       </c>
       <c r="P22" t="n">
         <v>6</v>
@@ -4188,16 +4188,16 @@
         <v>12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4705882</v>
+        <v>1.3529412</v>
       </c>
       <c r="S22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="T22" t="n">
-        <v>0.27319586</v>
+        <v>0.26288658</v>
       </c>
       <c r="U22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.30097088</v>
+        <v>0.297561</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -4216,55 +4216,55 @@
         <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.37117904</v>
+        <v>0.36842105</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.52682924</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N23" t="n">
         <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4444444</v>
+        <v>1.425926</v>
       </c>
       <c r="S23" t="n">
         <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0.25728154</v>
+        <v>0.27014217</v>
       </c>
       <c r="U23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -4274,61 +4274,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.32307693</v>
+        <v>0.32945737</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3728223</v>
+        <v>0.3811189</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5538462</v>
+        <v>0.5813952999999999</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N24" t="n">
-        <v>4.714286</v>
+        <v>4.571429</v>
       </c>
       <c r="O24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P24" t="n">
         <v>8</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5555556</v>
+        <v>1.4603175</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2868526</v>
+        <v>0.27459016</v>
       </c>
       <c r="U24" t="n">
         <v>27</v>
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25358853</v>
+        <v>0.22660099</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3304721</v>
+        <v>0.30530974</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>0.38277513</v>
+        <v>0.3448276</v>
       </c>
       <c r="K25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L25" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8461537</v>
+        <v>4.4117646</v>
       </c>
       <c r="O25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
         <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4807693</v>
+        <v>1.5294118</v>
       </c>
       <c r="S25" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="T25" t="n">
-        <v>0.26108375</v>
+        <v>0.27227724</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.25853658</v>
+        <v>0.22727273</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>0.32900432</v>
+        <v>0.29864255</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>0.44878048</v>
+        <v>0.3888889</v>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L26" t="n">
         <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N26" t="n">
-        <v>4.68</v>
+        <v>3.3529413</v>
       </c>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.58</v>
+        <v>1.3921568</v>
       </c>
       <c r="S26" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28921568</v>
+        <v>0.26960784</v>
       </c>
       <c r="U26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.21078432</v>
+        <v>0.2184466</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27433628</v>
+        <v>0.28695652</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2647059</v>
+        <v>0.3106796</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.4210525</v>
+      </c>
+      <c r="O27" t="n">
+        <v>22</v>
+      </c>
+      <c r="P27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q27" t="n">
         <v>12</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.105263</v>
-      </c>
-      <c r="O27" t="n">
-        <v>16</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7</v>
       </c>
       <c r="R27" t="n">
         <v>1.4385965</v>
       </c>
       <c r="S27" t="n">
+        <v>23</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.2614679</v>
+      </c>
+      <c r="U27" t="n">
         <v>20</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U27" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.24875621</v>
+        <v>0.20634921</v>
       </c>
       <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.29245284</v>
+      </c>
+      <c r="I28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.31746033</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>54</v>
+      </c>
+      <c r="M28" t="n">
         <v>14</v>
       </c>
-      <c r="D28" t="n">
-        <v>34</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="N28" t="n">
+        <v>1.8333334</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
         <v>6</v>
       </c>
-      <c r="G28" t="n">
-        <v>14</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.32286996</v>
-      </c>
-      <c r="I28" t="n">
-        <v>16</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.41293532</v>
-      </c>
-      <c r="K28" t="n">
-        <v>13</v>
-      </c>
-      <c r="L28" t="n">
-        <v>52</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="Q28" t="n">
         <v>12</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.3333333</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
+        <v>0.9074074</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.20304568</v>
+      </c>
+      <c r="U28" t="n">
         <v>3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>19</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.9444444</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.19387755</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4609,61 +4609,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24867725</v>
+        <v>0.24193548</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3409091</v>
+        <v>0.34545454</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>0.35978836</v>
+        <v>0.34946236</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N29" t="n">
+        <v>3.1666667</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>6</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>12</v>
-      </c>
       <c r="R29" t="n">
-        <v>0.9814815</v>
+        <v>1.037037</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0.19170985</v>
+        <v>0.1875</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2244898</v>
+        <v>0.2284264</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3063063</v>
+      </c>
+      <c r="I30" t="n">
+        <v>17</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.29441625</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29</v>
+      </c>
+      <c r="L30" t="n">
+        <v>33</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.326923</v>
+      </c>
+      <c r="O30" t="n">
         <v>20</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.29816514</v>
-      </c>
-      <c r="I30" t="n">
-        <v>21</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.33163264</v>
-      </c>
-      <c r="K30" t="n">
-        <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>34</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" t="n">
-        <v>4.1538463</v>
-      </c>
-      <c r="O30" t="n">
-        <v>17</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.5769231</v>
+        <v>1.5192307</v>
       </c>
       <c r="S30" t="n">
         <v>27</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24120604</v>
+        <v>0.23737374</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2601156</v>
+        <v>0.23214285</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.29787233</v>
+      </c>
+      <c r="I31" t="n">
+        <v>22</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3809524</v>
+      </c>
+      <c r="K31" t="n">
+        <v>14</v>
+      </c>
+      <c r="L31" t="n">
+        <v>35</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.5434783</v>
+      </c>
+      <c r="O31" t="n">
         <v>4</v>
       </c>
-      <c r="G31" t="n">
-        <v>26</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.32642487</v>
-      </c>
-      <c r="I31" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.40462428</v>
-      </c>
-      <c r="K31" t="n">
-        <v>16</v>
-      </c>
-      <c r="L31" t="n">
-        <v>37</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="P31" t="n">
         <v>4</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.2978723</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.2765957</v>
+        <v>1.2608696</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T31" t="n">
-        <v>0.20467836</v>
+        <v>0.21511628</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -555,7 +555,7 @@
         <v>693</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
         <v>157</v>
@@ -640,7 +640,7 @@
         <v>0.40015143</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
         <v>1329</v>
@@ -747,43 +747,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23378119</v>
+        <v>0.23363237</v>
       </c>
       <c r="C5" t="n">
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31444615</v>
+        <v>0.3141503</v>
       </c>
       <c r="I5" t="n">
         <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39385796</v>
+        <v>0.3949227</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>1464</v>
+        <v>1474</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1175485</v>
+        <v>4.110371</v>
       </c>
       <c r="O5" t="n">
         <v>14</v>
@@ -795,13 +795,13 @@
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.342351</v>
+        <v>1.3401521</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25272045</v>
+        <v>0.25242537</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -969,7 +969,7 @@
         <v>0.3189189</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>0.4019927</v>
@@ -1060,7 +1060,7 @@
         <v>209</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
         <v>1.4511224</v>
@@ -1182,7 +1182,7 @@
         <v>1357</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" t="n">
         <v>5.572159</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2404943</v>
+        <v>0.24117091</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31854227</v>
+        <v>0.3191418</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39828897</v>
+        <v>0.40075544</v>
       </c>
       <c r="K12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>1354</v>
+        <v>1361</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6586957</v>
+        <v>3.6479483</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.226087</v>
+        <v>1.2231822</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23236434</v>
+        <v>0.23189522</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
         <v>1282</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>4.527102</v>
@@ -1359,7 +1359,7 @@
         <v>656</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>162</v>
@@ -1389,7 +1389,7 @@
         <v>4.663099</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P14" t="n">
         <v>196</v>
@@ -1578,7 +1578,7 @@
         <v>0.40049943</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
         <v>1296</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24449924</v>
+        <v>0.24382424</v>
       </c>
       <c r="C19" t="n">
         <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31728813</v>
+        <v>0.31641942</v>
       </c>
       <c r="I19" t="n">
         <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40269348</v>
+        <v>0.40222517</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5954676</v>
+        <v>4.6013904</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3669238</v>
+        <v>1.3662512</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24910496</v>
+        <v>0.2494382</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1828,7 +1828,7 @@
         <v>713</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
         <v>216</v>
@@ -1895,7 +1895,7 @@
         <v>697</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
         <v>179</v>
@@ -1919,7 +1919,7 @@
         <v>1282</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N22" t="n">
         <v>4.0048156</v>
@@ -1968,7 +1968,7 @@
         <v>181</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
         <v>0.33156323</v>
@@ -2041,19 +2041,19 @@
         <v>0.31905743</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
         <v>0.4</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24" t="n">
         <v>1257</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N24" t="n">
         <v>3.9361446</v>
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24659349</v>
+        <v>0.24694377</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G25" t="n">
         <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3083405</v>
+        <v>0.30831054</v>
       </c>
       <c r="I25" t="n">
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40480697</v>
+        <v>0.40511566</v>
       </c>
       <c r="K25" t="n">
         <v>9</v>
       </c>
       <c r="L25" t="n">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3854547</v>
+        <v>4.369942</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3694545</v>
+        <v>1.3641618</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24942529</v>
+        <v>0.24871454</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2230,7 +2230,7 @@
         <v>704</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
         <v>161</v>
@@ -2376,7 +2376,7 @@
         <v>0.31855813</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
         <v>0.397758</v>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24814604</v>
+        <v>0.24787295</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -2440,43 +2440,43 @@
         <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31059432</v>
+        <v>0.3103271</v>
       </c>
       <c r="I30" t="n">
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3831527</v>
+        <v>0.3821138</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9119134</v>
+        <v>3.9152908</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q30" t="n">
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3025271</v>
+        <v>1.3007897</v>
       </c>
       <c r="S30" t="n">
         <v>17</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23580366</v>
+        <v>0.23564318</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24727342</v>
+        <v>0.24672897</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32248867</v>
+        <v>0.3218276</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4249718</v>
+        <v>0.42411214</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1300</v>
+        <v>1311</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6625724</v>
+        <v>4.6939654</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3843931</v>
+        <v>1.387931</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2527846</v>
+        <v>0.25337586</v>
       </c>
       <c r="U31" t="n">
         <v>25</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.26190478</v>
+        <v>0.25142857</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="I2" t="n">
         <v>13</v>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
+        <v>0.42285714</v>
+      </c>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.0212765</v>
+      </c>
+      <c r="O2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.1702127</v>
+      </c>
+      <c r="S2" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.3275862</v>
-      </c>
-      <c r="I2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.45714286</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="T2" t="n">
+        <v>0.21387284</v>
+      </c>
+      <c r="U2" t="n">
         <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>60</v>
-      </c>
-      <c r="M2" t="n">
-        <v>23</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>23</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.2321428</v>
-      </c>
-      <c r="S2" t="n">
-        <v>12</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.23222749</v>
-      </c>
-      <c r="U2" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2894,13 +2894,13 @@
         <v>0.30569947</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
         <v>5.8125</v>
@@ -2912,19 +2912,19 @@
         <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
         <v>1.4791666</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T3" t="n">
         <v>0.2741117</v>
       </c>
       <c r="U3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25480768</v>
+        <v>0.2556818</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3171806</v>
+        <v>0.3105263</v>
       </c>
       <c r="I4" t="n">
         <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>0.44230768</v>
+        <v>0.46022728</v>
       </c>
       <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>46</v>
+      </c>
+      <c r="M4" t="n">
         <v>9</v>
       </c>
-      <c r="L4" t="n">
-        <v>55</v>
-      </c>
-      <c r="M4" t="n">
-        <v>16</v>
-      </c>
       <c r="N4" t="n">
-        <v>4.1538463</v>
+        <v>3.4772727</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2884616</v>
+        <v>1.1818181</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.23952095</v>
       </c>
       <c r="U4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21904762</v>
+        <v>0.21078432</v>
       </c>
       <c r="C5" t="n">
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.27192983</v>
+        <v>0.2690583</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4047619</v>
+        <v>0.43137255</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M5" t="n">
         <v>26</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2105262</v>
+        <v>2.5263157</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1929824</v>
+        <v>1.1578947</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21359223</v>
+        <v>0.21568628</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3077,19 +3077,19 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>0.27102804</v>
       </c>
       <c r="I6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
         <v>0.32642487</v>
@@ -3101,13 +3101,13 @@
         <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
         <v>3.7302632</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -3119,7 +3119,7 @@
         <v>1.2039473</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
         <v>0.21925133</v>
@@ -3135,61 +3135,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27669904</v>
+        <v>0.2716763</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.35470086</v>
+        <v>0.3469388</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4854369</v>
+        <v>0.48554912</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>35</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6818182</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
-        <v>39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.5660377</v>
-      </c>
-      <c r="O7" t="n">
-        <v>11</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="Q7" t="n">
-        <v>8</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.1132076</v>
+        <v>1.0454545</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21243523</v>
+        <v>0.20496894</v>
       </c>
       <c r="U7" t="n">
         <v>4</v>
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2246696</v>
+        <v>0.21875</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3215859</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.36979166</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.101266</v>
+      </c>
+      <c r="O8" t="n">
+        <v>19</v>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
+      <c r="Q8" t="n">
         <v>13</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.37004405</v>
-      </c>
-      <c r="K8" t="n">
-        <v>16</v>
-      </c>
-      <c r="L8" t="n">
-        <v>76</v>
-      </c>
-      <c r="M8" t="n">
-        <v>30</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.5027027</v>
-      </c>
-      <c r="O8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
+        <v>1.4810126</v>
+      </c>
+      <c r="S8" t="n">
+        <v>26</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2562814</v>
+      </c>
+      <c r="U8" t="n">
         <v>19</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4108108</v>
-      </c>
-      <c r="S8" t="n">
-        <v>20</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.19907407</v>
+        <v>0.20967741</v>
       </c>
       <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.27093595</v>
+      </c>
+      <c r="I9" t="n">
         <v>28</v>
       </c>
-      <c r="D9" t="n">
-        <v>18</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="J9" t="n">
+        <v>0.31182796</v>
+      </c>
+      <c r="K9" t="n">
+        <v>27</v>
+      </c>
+      <c r="L9" t="n">
+        <v>48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.3333335</v>
+      </c>
+      <c r="O9" t="n">
         <v>28</v>
       </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.25641027</v>
-      </c>
-      <c r="I9" t="n">
-        <v>29</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.30092594</v>
-      </c>
-      <c r="K9" t="n">
-        <v>28</v>
-      </c>
-      <c r="L9" t="n">
-        <v>59</v>
-      </c>
-      <c r="M9" t="n">
-        <v>21</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.142857</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.6111112</v>
+      </c>
+      <c r="S9" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.27403846</v>
+      </c>
+      <c r="U9" t="n">
         <v>26</v>
-      </c>
-      <c r="P9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>27</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5238096</v>
-      </c>
-      <c r="S9" t="n">
-        <v>28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.25316456</v>
-      </c>
-      <c r="U9" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.26262626</v>
+        <v>0.27272728</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32718894</v>
+        <v>0.34065935</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.46464646</v>
+        <v>0.4909091</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O10" t="n">
-        <v>12</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2407408</v>
+        <v>1.1777778</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23232323</v>
+        <v>0.22699386</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.28915662</v>
+        <v>0.27751195</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34686348</v>
+        <v>0.33480176</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.44578314</v>
+        <v>0.40669855</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>5.571429</v>
+        <v>5.1666665</v>
       </c>
       <c r="O11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4285715</v>
+        <v>1.3703704</v>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2931727</v>
+        <v>0.2843602</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.26556018</v>
+        <v>0.28033474</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
       <c r="G12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3607143</v>
+        <v>0.37857142</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.373444</v>
+        <v>0.44351465</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8135593</v>
+        <v>3.3559322</v>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
         <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.338983</v>
+        <v>1.220339</v>
       </c>
       <c r="S12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21973094</v>
+        <v>0.2081448</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3546,19 +3546,19 @@
         <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0.27962086</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
         <v>0.4568528</v>
@@ -3570,31 +3570,31 @@
         <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
         <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
         <v>1.2037038</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
         <v>0.21393035</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3607,43 +3607,43 @@
         <v>0.2238806</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
         <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
         <v>0.29090908</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
         <v>0.35820895</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>5.5102043</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P14" t="n">
         <v>15</v>
@@ -3671,16 +3671,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.21794872</v>
+        <v>0.20689656</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -3689,46 +3689,46 @@
         <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3071161</v>
+        <v>0.30472103</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2863248</v>
+        <v>0.27093595</v>
       </c>
       <c r="K15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L15" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9545455</v>
+        <v>3.9473684</v>
       </c>
       <c r="O15" t="n">
+        <v>15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2631578</v>
+      </c>
+      <c r="S15" t="n">
         <v>16</v>
       </c>
-      <c r="P15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.2575758</v>
-      </c>
-      <c r="S15" t="n">
-        <v>14</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.2627451</v>
+        <v>0.26696834</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -3738,61 +3738,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2851064</v>
+        <v>0.3106796</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.38545454</v>
+        <v>0.40416667</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5106383</v>
+        <v>0.5388349</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.3225806</v>
+        <v>2.54717</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9032258</v>
+        <v>0.9622642</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.19178082</v>
+        <v>0.2010582</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
@@ -3805,61 +3805,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.23943663</v>
+        <v>0.22285715</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
         <v>14</v>
       </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
+        <v>0.30612245</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.35428572</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48</v>
+      </c>
+      <c r="M17" t="n">
         <v>11</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.31223628</v>
-      </c>
-      <c r="I17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.39906102</v>
-      </c>
-      <c r="K17" t="n">
-        <v>12</v>
-      </c>
-      <c r="L17" t="n">
-        <v>61</v>
-      </c>
-      <c r="M17" t="n">
-        <v>24</v>
-      </c>
       <c r="N17" t="n">
-        <v>5.5341616</v>
+        <v>4.9632354</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
         <v>29</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5652174</v>
+        <v>1.5220588</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>0.28899083</v>
+        <v>0.284153</v>
       </c>
       <c r="U17" t="n">
         <v>29</v>
@@ -3875,13 +3875,13 @@
         <v>0.22772278</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -3893,7 +3893,7 @@
         <v>0.32188842</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
         <v>0.32673267</v>
@@ -3905,7 +3905,7 @@
         <v>64</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
         <v>2.6666667</v>
@@ -3917,13 +3917,13 @@
         <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R18" t="n">
         <v>1.2222222</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T18" t="n">
         <v>0.2413793</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25384617</v>
+        <v>0.24902724</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
         <v>10</v>
       </c>
-      <c r="F19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" t="n">
-        <v>13</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.29893237</v>
+        <v>0.28467155</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3653846</v>
+        <v>0.36575875</v>
       </c>
       <c r="K19" t="n">
         <v>17</v>
       </c>
       <c r="L19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8695652</v>
+        <v>2.6470587</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.173913</v>
+        <v>1.2058823</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>0.21538462</v>
+        <v>0.2248062</v>
       </c>
       <c r="U19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2581967</v>
+        <v>0.2688679</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>18</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.33617023</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.36792454</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.33088234</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.35655737</v>
-      </c>
-      <c r="K20" t="n">
-        <v>19</v>
-      </c>
       <c r="L20" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.876923</v>
+        <v>4.339286</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="P20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
         <v>25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2153846</v>
+        <v>1.2321428</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23430963</v>
+        <v>0.23039216</v>
       </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23766816</v>
+        <v>0.2393617</v>
       </c>
       <c r="C21" t="n">
         <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.30952382</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.40957448</v>
+      </c>
+      <c r="K21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L21" t="n">
+        <v>44</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.1079137</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7</v>
+      </c>
+      <c r="P21" t="n">
         <v>4</v>
       </c>
-      <c r="F21" t="n">
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2086332</v>
+      </c>
+      <c r="S21" t="n">
         <v>12</v>
       </c>
-      <c r="G21" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.30081302</v>
-      </c>
-      <c r="I21" t="n">
-        <v>19</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.42600897</v>
-      </c>
-      <c r="K21" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" t="n">
-        <v>53</v>
-      </c>
-      <c r="M21" t="n">
-        <v>11</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.7650602</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1927711</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6</v>
-      </c>
       <c r="T21" t="n">
-        <v>0.23529412</v>
+        <v>0.24705882</v>
       </c>
       <c r="U21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -4149,7 +4149,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -4179,25 +4179,25 @@
         <v>4.2352943</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
         <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
         <v>1.3529412</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T22" t="n">
         <v>0.26288658</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -4210,55 +4210,55 @@
         <v>0.297561</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
         <v>0.36842105</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>0.52682924</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>57</v>
       </c>
       <c r="M23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N23" t="n">
         <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
         <v>1.425926</v>
       </c>
       <c r="S23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T23" t="n">
         <v>0.27014217</v>
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.32945737</v>
+        <v>0.3272727</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3811189</v>
+        <v>0.38114753</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5813952999999999</v>
+        <v>0.5863636</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>4.571429</v>
+        <v>4.1666665</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4603175</v>
+        <v>1.3703704</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T24" t="n">
-        <v>0.27459016</v>
+        <v>0.25980392</v>
       </c>
       <c r="U24" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.22660099</v>
+        <v>0.24390244</v>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3080357</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3804878</v>
+      </c>
+      <c r="K25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L25" t="n">
+        <v>68</v>
+      </c>
+      <c r="M25" t="n">
+        <v>29</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.326923</v>
+      </c>
+      <c r="O25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3653846</v>
+      </c>
+      <c r="S25" t="n">
         <v>18</v>
       </c>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="T25" t="n">
+        <v>0.25123152</v>
+      </c>
+      <c r="U25" t="n">
         <v>18</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.30530974</v>
-      </c>
-      <c r="I25" t="n">
-        <v>18</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.3448276</v>
-      </c>
-      <c r="K25" t="n">
-        <v>21</v>
-      </c>
-      <c r="L25" t="n">
-        <v>67</v>
-      </c>
-      <c r="M25" t="n">
-        <v>28</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.4117646</v>
-      </c>
-      <c r="O25" t="n">
-        <v>21</v>
-      </c>
-      <c r="P25" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>22</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5294118</v>
-      </c>
-      <c r="S25" t="n">
-        <v>29</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.27227724</v>
-      </c>
-      <c r="U25" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -4408,46 +4408,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22727273</v>
+        <v>0.22560975</v>
       </c>
       <c r="C26" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" t="n">
+        <v>26</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.29891303</v>
+      </c>
+      <c r="I26" t="n">
         <v>19</v>
       </c>
-      <c r="D26" t="n">
-        <v>22</v>
-      </c>
-      <c r="E26" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="J26" t="n">
+        <v>0.37804878</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14</v>
+      </c>
+      <c r="L26" t="n">
+        <v>40</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.7209303</v>
+      </c>
+      <c r="O26" t="n">
         <v>6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>13</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.29864255</v>
-      </c>
-      <c r="I26" t="n">
-        <v>21</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.3888889</v>
-      </c>
-      <c r="K26" t="n">
-        <v>13</v>
-      </c>
-      <c r="L26" t="n">
-        <v>51</v>
-      </c>
-      <c r="M26" t="n">
-        <v>9</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.3529413</v>
-      </c>
-      <c r="O26" t="n">
-        <v>9</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -4456,16 +4456,16 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3921568</v>
+        <v>1.3953488</v>
       </c>
       <c r="S26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T26" t="n">
-        <v>0.26960784</v>
+        <v>0.26589596</v>
       </c>
       <c r="U26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2184466</v>
+        <v>0.21022727</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.28695652</v>
+        <v>0.2755102</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3106796</v>
+        <v>0.3125</v>
       </c>
       <c r="K27" t="n">
         <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>4.4210525</v>
+        <v>5.0625</v>
       </c>
       <c r="O27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P27" t="n">
         <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4385965</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2614679</v>
+        <v>0.27272728</v>
       </c>
       <c r="U27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -4545,13 +4545,13 @@
         <v>0.20634921</v>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
         <v>25</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -4563,7 +4563,7 @@
         <v>0.29245284</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
         <v>0.31746033</v>
@@ -4575,7 +4575,7 @@
         <v>54</v>
       </c>
       <c r="M28" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N28" t="n">
         <v>1.8333334</v>
@@ -4587,13 +4587,13 @@
         <v>6</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
         <v>0.9074074</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0.20304568</v>
@@ -4612,13 +4612,13 @@
         <v>0.24193548</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
         <v>29</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4630,19 +4630,19 @@
         <v>0.34545454</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
         <v>0.34946236</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L29" t="n">
         <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N29" t="n">
         <v>3.1666667</v>
@@ -4654,7 +4654,7 @@
         <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
         <v>1.037037</v>
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2284264</v>
+        <v>0.22279793</v>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3063063</v>
+        <v>0.29166666</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.29441625</v>
+        <v>0.26943004</v>
       </c>
       <c r="K30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.326923</v>
+        <v>4.0588236</v>
       </c>
       <c r="O30" t="n">
+        <v>18</v>
+      </c>
+      <c r="P30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q30" t="n">
         <v>20</v>
       </c>
-      <c r="P30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.5192307</v>
+        <v>1.4901961</v>
       </c>
       <c r="S30" t="n">
         <v>27</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23737374</v>
+        <v>0.23157895</v>
       </c>
       <c r="U30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23214285</v>
+        <v>0.22</v>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="n">
         <v>14</v>
       </c>
-      <c r="F31" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
+        <v>0.2837838</v>
+      </c>
+      <c r="I31" t="n">
+        <v>24</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="K31" t="n">
         <v>18</v>
       </c>
-      <c r="H31" t="n">
-        <v>0.29787233</v>
-      </c>
-      <c r="I31" t="n">
-        <v>22</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.3809524</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>46</v>
+      </c>
+      <c r="M31" t="n">
+        <v>9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.6666667</v>
+      </c>
+      <c r="O31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>20</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.3703704</v>
+      </c>
+      <c r="S31" t="n">
+        <v>19</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.23671497</v>
+      </c>
+      <c r="U31" t="n">
         <v>14</v>
-      </c>
-      <c r="L31" t="n">
-        <v>35</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.5434783</v>
-      </c>
-      <c r="O31" t="n">
-        <v>4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.2608696</v>
-      </c>
-      <c r="S31" t="n">
-        <v>15</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.21511628</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2437906</v>
+        <v>0.24454562</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31575355</v>
+        <v>0.3161017</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>0.39759266</v>
+        <v>0.3987858</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.105036</v>
+        <v>4.0850606</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q2" t="n">
         <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.276259</v>
+        <v>1.2709078</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24791351</v>
+        <v>0.24712318</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24380086</v>
+        <v>0.24478285</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="E3" t="n">
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31609392</v>
+        <v>0.316999</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40015143</v>
+        <v>0.40251926</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.43532</v>
+        <v>5.4454875</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5014535</v>
+        <v>1.5061371</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2707675</v>
+        <v>0.27158672</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24772382</v>
+        <v>0.24754901</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
@@ -695,46 +695,46 @@
         <v>198</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31099656</v>
+        <v>0.31072772</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41141883</v>
+        <v>0.41044495</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="M4" t="n">
         <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6129963</v>
+        <v>3.615495</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q4" t="n">
         <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2469314</v>
+        <v>1.2482066</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23355834</v>
+        <v>0.23386325</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -756,7 +756,7 @@
         <v>697</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
         <v>192</v>
@@ -786,7 +786,7 @@
         <v>4.110371</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
         <v>168</v>
@@ -798,7 +798,7 @@
         <v>1.3401521</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
         <v>0.25242537</v>
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24603023</v>
+        <v>0.2460076</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32008868</v>
+        <v>0.32011524</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.40099484</v>
+        <v>0.4013308</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>1271</v>
+        <v>1283</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.590909</v>
+        <v>3.5870967</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -862,13 +862,13 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2352092</v>
+        <v>1.2387097</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24123396</v>
+        <v>0.24177288</v>
       </c>
       <c r="U6" t="n">
         <v>15</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25210086</v>
+        <v>0.25134283</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -899,43 +899,43 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34006843</v>
+        <v>0.33942136</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43230626</v>
+        <v>0.43045008</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1294</v>
+        <v>1311</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.163793</v>
+        <v>4.173077</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2636495</v>
+        <v>1.2628205</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24338725</v>
+        <v>0.24339622</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23414448</v>
+        <v>0.23488018</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3189189</v>
+        <v>0.31981227</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4019927</v>
+        <v>0.40414608</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>1442</v>
+        <v>1454</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.105453</v>
+        <v>4.149881</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q8" t="n">
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3129954</v>
+        <v>1.3159904</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24191387</v>
+        <v>0.24263728</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22865972</v>
+        <v>0.22899885</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30578512</v>
+        <v>0.30596888</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.393202</v>
+        <v>0.394323</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>1482</v>
+        <v>1492</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8942795</v>
+        <v>4.86259</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
@@ -1063,13 +1063,13 @@
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4511224</v>
+        <v>1.4482014</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25493884</v>
+        <v>0.25472227</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23798539</v>
+        <v>0.23854962</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
@@ -1100,43 +1100,43 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31503335</v>
+        <v>0.3156823</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37735486</v>
+        <v>0.37729007</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1233</v>
+        <v>1242</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.78013</v>
+        <v>3.7686424</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q10" t="n">
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2593217</v>
+        <v>1.2597992</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23633225</v>
+        <v>0.23637056</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2542341</v>
+        <v>0.25341567</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32349467</v>
+        <v>0.3227105</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41625893</v>
+        <v>0.41530976</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1357</v>
+        <v>1368</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.572159</v>
+        <v>5.5814795</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5251887</v>
+        <v>1.5261122</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28786212</v>
+        <v>0.28828993</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24117091</v>
+        <v>0.24103624</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E12" t="n">
         <v>12</v>
@@ -1234,43 +1234,43 @@
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3191418</v>
+        <v>0.3194005</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40075544</v>
+        <v>0.40003756</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>1361</v>
+        <v>1372</v>
       </c>
       <c r="M12" t="n">
         <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6479483</v>
+        <v>3.643777</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2231822</v>
+        <v>1.2203147</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23189522</v>
+        <v>0.23177034</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23968679</v>
+        <v>0.24023512</v>
       </c>
       <c r="C13" t="n">
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31280997</v>
+        <v>0.3135291</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41023684</v>
+        <v>0.4114524</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.527102</v>
+        <v>4.4978456</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3435317</v>
+        <v>1.3413117</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23784722</v>
+        <v>0.23724587</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24493308</v>
+        <v>0.24563402</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3146241</v>
+        <v>0.31521553</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39789674</v>
+        <v>0.39939255</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.663099</v>
+        <v>4.7240214</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3930917</v>
+        <v>1.3977766</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25930876</v>
+        <v>0.25985596</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2326609</v>
+        <v>0.233791</v>
       </c>
       <c r="C15" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" t="n">
+        <v>632</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" t="n">
+        <v>149</v>
+      </c>
+      <c r="G15" t="n">
         <v>28</v>
       </c>
-      <c r="D15" t="n">
-        <v>625</v>
-      </c>
-      <c r="E15" t="n">
-        <v>30</v>
-      </c>
-      <c r="F15" t="n">
-        <v>148</v>
-      </c>
-      <c r="G15" t="n">
-        <v>30</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.3081815</v>
+        <v>0.3093979</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.36791545</v>
+        <v>0.36880243</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.205506</v>
+        <v>4.239616</v>
       </c>
       <c r="O15" t="n">
         <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3380826</v>
+        <v>1.342617</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23725227</v>
+        <v>0.23829544</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1484,46 +1484,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25719732</v>
+        <v>0.25734317</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33897737</v>
+        <v>0.33922026</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42554814</v>
+        <v>0.42637864</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6178174</v>
+        <v>3.594387</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
         <v>171</v>
@@ -1532,13 +1532,13 @@
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1545148</v>
+        <v>1.1520748</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21912195</v>
+        <v>0.21868941</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,46 +1551,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24875145</v>
+        <v>0.24871454</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3265827</v>
+        <v>0.32664078</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40049943</v>
+        <v>0.39992383</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>1296</v>
+        <v>1310</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1578817</v>
+        <v>4.1283407</v>
       </c>
       <c r="O17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P17" t="n">
         <v>167</v>
@@ -1599,13 +1599,13 @@
         <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2905028</v>
+        <v>1.2879846</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23712136</v>
+        <v>0.23646452</v>
       </c>
       <c r="U17" t="n">
         <v>9</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25805843</v>
+        <v>0.25763538</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1636,43 +1636,43 @@
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34067938</v>
+        <v>0.34003294</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40301603</v>
+        <v>0.4017238</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>1323</v>
+        <v>1338</v>
       </c>
       <c r="M18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5388663</v>
+        <v>3.550773</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q18" t="n">
         <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.187515</v>
+        <v>1.188585</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22331786</v>
+        <v>0.22348194</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24382424</v>
+        <v>0.24353206</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E19" t="n">
         <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31641942</v>
+        <v>0.31589538</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40222517</v>
+        <v>0.40194976</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="M19" t="n">
         <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6013904</v>
+        <v>4.584663</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
@@ -1733,13 +1733,13 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3662512</v>
+        <v>1.3660395</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2494382</v>
+        <v>0.24916202</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.238891</v>
+        <v>0.23910993</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
@@ -1770,43 +1770,43 @@
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30936113</v>
+        <v>0.30964896</v>
       </c>
       <c r="I20" t="n">
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39384732</v>
+        <v>0.39392796</v>
       </c>
       <c r="K20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N20" t="n">
-        <v>4.167785</v>
+        <v>4.1538463</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
         <v>179</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2993768</v>
+        <v>1.2945939</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24071266</v>
+        <v>0.2399623</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,43 +1819,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23472168</v>
+        <v>0.23359631</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31149247</v>
+        <v>0.31030345</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4098871</v>
+        <v>0.40773523</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1415</v>
+        <v>1439</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2176838</v>
+        <v>3.2148957</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1864,16 +1864,16 @@
         <v>159</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1655453</v>
+        <v>1.1620018</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22327837</v>
+        <v>0.22318007</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,43 +1886,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24124067</v>
+        <v>0.24129401</v>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="E22" t="n">
         <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G22" t="n">
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>0.312393</v>
+        <v>0.31240427</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39728126</v>
+        <v>0.39733586</v>
       </c>
       <c r="K22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="M22" t="n">
         <v>12</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0048156</v>
+        <v>4.0047846</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
@@ -1934,16 +1934,16 @@
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2858174</v>
+        <v>1.2832536</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24754716</v>
+        <v>0.2471868</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2543385</v>
+        <v>0.25389755</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
@@ -1971,28 +1971,28 @@
         <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33156323</v>
+        <v>0.33113238</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4056727</v>
+        <v>0.40515962</v>
       </c>
       <c r="K23" t="n">
         <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.188652</v>
+        <v>4.161751</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
         <v>150</v>
@@ -2001,16 +2001,16 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3035672</v>
+        <v>1.2973359</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23797756</v>
+        <v>0.23690678</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24367149</v>
+        <v>0.24308756</v>
       </c>
       <c r="C24" t="n">
         <v>17</v>
@@ -2029,52 +2029,52 @@
         <v>690</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
         <v>179</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31905743</v>
+        <v>0.318345</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4</v>
+        <v>0.3984255</v>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>1257</v>
+        <v>1267</v>
       </c>
       <c r="M24" t="n">
         <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9361446</v>
+        <v>3.9587924</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.286747</v>
+        <v>1.2886919</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24104737</v>
+        <v>0.24129353</v>
       </c>
       <c r="U24" t="n">
         <v>14</v>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24694377</v>
+        <v>0.24668038</v>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>178</v>
@@ -2105,43 +2105,43 @@
         <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30831054</v>
+        <v>0.30858114</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40511566</v>
+        <v>0.40396485</v>
       </c>
       <c r="K25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="M25" t="n">
         <v>14</v>
       </c>
       <c r="N25" t="n">
-        <v>4.369942</v>
+        <v>4.361091</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3641618</v>
+        <v>1.3603733</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24871454</v>
+        <v>0.24839076</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23195678</v>
+        <v>0.2313891</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
@@ -2169,46 +2169,46 @@
         <v>179</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" t="n">
-        <v>0.311804</v>
+        <v>0.31159544</v>
       </c>
       <c r="I26" t="n">
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3803551</v>
+        <v>0.37893322</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1880755</v>
+        <v>4.206357</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q26" t="n">
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2600582</v>
+        <v>1.2641463</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.250952</v>
+        <v>0.25141776</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24222307</v>
+        <v>0.24113208</v>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="n">
         <v>704</v>
@@ -2236,31 +2236,31 @@
         <v>161</v>
       </c>
       <c r="G27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31541583</v>
+        <v>0.31432897</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38182852</v>
+        <v>0.38018867</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1234</v>
+        <v>1248</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2944274</v>
+        <v>4.2827587</v>
       </c>
       <c r="O27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P27" t="n">
         <v>155</v>
@@ -2269,13 +2269,13 @@
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3554174</v>
+        <v>1.3533889</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25386938</v>
+        <v>0.25342596</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25875336</v>
+        <v>0.25821775</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
@@ -2306,43 +2306,43 @@
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3276368</v>
+        <v>0.32662117</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4036168</v>
+        <v>0.40167204</v>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L28" t="n">
-        <v>1085</v>
+        <v>1099</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7001445</v>
+        <v>3.674518</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1343931</v>
+        <v>1.1299073</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22872032</v>
+        <v>0.22767176</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24313878</v>
+        <v>0.24236017</v>
       </c>
       <c r="C29" t="n">
         <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
@@ -2373,28 +2373,28 @@
         <v>18</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31855813</v>
+        <v>0.31796366</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.397758</v>
+        <v>0.39630982</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.278401</v>
+        <v>4.283119</v>
       </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P29" t="n">
         <v>184</v>
@@ -2403,16 +2403,16 @@
         <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2996099</v>
+        <v>1.3020102</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24757558</v>
+        <v>0.24773414</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2443,7 +2443,7 @@
         <v>0.3103271</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
         <v>0.3821138</v>
@@ -2489,46 +2489,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24672897</v>
+        <v>0.24651681</v>
       </c>
       <c r="C31" t="n">
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3218276</v>
+        <v>0.3212272</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42411214</v>
+        <v>0.4239272</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6939654</v>
+        <v>4.6702356</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
         <v>210</v>
@@ -2537,13 +2537,13 @@
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.387931</v>
+        <v>1.3882941</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25337586</v>
+        <v>0.25316927</v>
       </c>
       <c r="U31" t="n">
         <v>25</v>
@@ -2800,43 +2800,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25142857</v>
+        <v>0.28235295</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3125</v>
+        <v>0.32795697</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.42285714</v>
+        <v>0.4764706</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="M2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0212765</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>17</v>
@@ -2845,19 +2845,19 @@
         <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1702127</v>
+        <v>1.1333333</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>0.21387284</v>
+        <v>0.21212122</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.19689119</v>
+        <v>0.24242425</v>
       </c>
       <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2990654</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4090909</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="n">
+        <v>44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.7959185</v>
+      </c>
+      <c r="O3" t="n">
         <v>29</v>
-      </c>
-      <c r="D3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.24390244</v>
-      </c>
-      <c r="I3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.30569947</v>
-      </c>
-      <c r="K3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L3" t="n">
-        <v>53</v>
-      </c>
-      <c r="M3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.8125</v>
-      </c>
-      <c r="O3" t="n">
-        <v>30</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4791666</v>
+        <v>1.7142857</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2741117</v>
+        <v>0.3043478</v>
       </c>
       <c r="U3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2556818</v>
+        <v>0.24855492</v>
       </c>
       <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.30107528</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.40462428</v>
+      </c>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="n">
+        <v>42</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.8863637</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
+      <c r="Q4" t="n">
         <v>26</v>
       </c>
-      <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3105263</v>
-      </c>
-      <c r="I4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.46022728</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>46</v>
-      </c>
-      <c r="M4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.4772727</v>
-      </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.1818181</v>
+        <v>1.2727273</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23952095</v>
+        <v>0.2616279</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21078432</v>
+        <v>0.21341464</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2802198</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.41463414</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>46</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.5434783</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.2690583</v>
-      </c>
-      <c r="I5" t="n">
-        <v>29</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.43137255</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>63</v>
-      </c>
-      <c r="M5" t="n">
-        <v>26</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.5263157</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.0652174</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.19875777</v>
+      </c>
+      <c r="U5" t="n">
         <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1578947</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.21568628</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3068,16 +3068,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.19170985</v>
+        <v>0.20103092</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
@@ -3086,46 +3086,46 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>0.27102804</v>
+        <v>0.27906978</v>
       </c>
       <c r="I6" t="n">
         <v>27</v>
       </c>
       <c r="J6" t="n">
-        <v>0.32642487</v>
+        <v>0.3556701</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7302632</v>
+        <v>3.483871</v>
       </c>
       <c r="O6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2039473</v>
+        <v>1.2967741</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="n">
-        <v>0.21925133</v>
+        <v>0.23589744</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2716763</v>
+        <v>0.26344085</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.34285715</v>
+      </c>
+      <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.3469388</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>0.47311828</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6382978</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.0212766</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.20467836</v>
+      </c>
+      <c r="U7" t="n">
         <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.48554912</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>35</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.6818182</v>
-      </c>
-      <c r="O7" t="n">
-        <v>13</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.0454545</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.20496894</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.21875</v>
+        <v>0.2361809</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
-        <v>18</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.3215859</v>
+        <v>0.33620688</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.36979166</v>
+        <v>0.43718594</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>62</v>
       </c>
       <c r="M8" t="n">
+        <v>24</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.924528</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5660378</v>
+      </c>
+      <c r="S8" t="n">
+        <v>28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.27450982</v>
+      </c>
+      <c r="U8" t="n">
         <v>25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.101266</v>
-      </c>
-      <c r="O8" t="n">
-        <v>19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>13</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4810126</v>
-      </c>
-      <c r="S8" t="n">
-        <v>26</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.2562814</v>
-      </c>
-      <c r="U8" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.20967741</v>
+        <v>0.23834197</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.27093595</v>
+        <v>0.2952381</v>
       </c>
       <c r="I9" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
-        <v>0.31182796</v>
+        <v>0.3834197</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3333335</v>
+        <v>4.6666665</v>
       </c>
       <c r="O9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6111112</v>
+        <v>1.537037</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T9" t="n">
-        <v>0.27403846</v>
+        <v>0.26794258</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.27272728</v>
+        <v>0.2882353</v>
       </c>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.36125654</v>
+      </c>
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>0.45294118</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
         <v>6</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.34065935</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.4909091</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>29</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>11</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.1777778</v>
+        <v>1.1333333</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>0.22699386</v>
+        <v>0.22560975</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.27751195</v>
+        <v>0.225</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.28767124</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K11" t="n">
         <v>24</v>
       </c>
-      <c r="E11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="L11" t="n">
+        <v>56</v>
+      </c>
+      <c r="M11" t="n">
         <v>21</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.33480176</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.40669855</v>
-      </c>
-      <c r="K11" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" t="n">
-        <v>48</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
       <c r="N11" t="n">
-        <v>5.1666665</v>
+        <v>5.8333335</v>
       </c>
       <c r="O11" t="n">
+        <v>28</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.425926</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.29245284</v>
+      </c>
+      <c r="U11" t="n">
         <v>27</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>25</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3703704</v>
-      </c>
-      <c r="S11" t="n">
-        <v>19</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.2843602</v>
-      </c>
-      <c r="U11" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.28033474</v>
+        <v>0.27118644</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>0.37857142</v>
+        <v>0.36956522</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.44351465</v>
+        <v>0.40677965</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M12" t="n">
         <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3559322</v>
+        <v>3.661017</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>1.220339</v>
+        <v>1.1864407</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2081448</v>
+        <v>0.21266969</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23350254</v>
+        <v>0.26086956</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
         <v>19</v>
-      </c>
-      <c r="E13" t="n">
-        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.27962086</v>
+        <v>0.3125</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4568528</v>
+        <v>0.47826087</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.6666667</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
         <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2037038</v>
+        <v>1.2407408</v>
       </c>
       <c r="S13" t="n">
+        <v>14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="U13" t="n">
         <v>9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.21393035</v>
-      </c>
-      <c r="U13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2238806</v>
+        <v>0.2596154</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
         <v>7</v>
       </c>
-      <c r="G14" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.29090908</v>
+        <v>0.3231441</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>0.35820895</v>
+        <v>0.41826922</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5102043</v>
+        <v>7.2</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
         <v>30</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4489796</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>0.27918783</v>
+        <v>0.30769232</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.20689656</v>
+        <v>0.23696682</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.33606556</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2985782</v>
+      </c>
+      <c r="K15" t="n">
+        <v>26</v>
+      </c>
+      <c r="L15" t="n">
+        <v>65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.303571</v>
+      </c>
+      <c r="O15" t="n">
+        <v>27</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4642857</v>
+      </c>
+      <c r="S15" t="n">
         <v>25</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.30472103</v>
-      </c>
-      <c r="I15" t="n">
-        <v>18</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.27093595</v>
-      </c>
-      <c r="K15" t="n">
-        <v>29</v>
-      </c>
-      <c r="L15" t="n">
-        <v>68</v>
-      </c>
-      <c r="M15" t="n">
-        <v>29</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.9473684</v>
-      </c>
-      <c r="O15" t="n">
-        <v>15</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.2631578</v>
-      </c>
-      <c r="S15" t="n">
-        <v>16</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.26696834</v>
+        <v>0.29464287</v>
       </c>
       <c r="U15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3106796</v>
+        <v>0.31400967</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.40416667</v>
+        <v>0.40167364</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5388349</v>
+        <v>0.5507246</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
         <v>2.54717</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
         <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9622642</v>
+        <v>0.9811321</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2010582</v>
+        <v>0.20725389</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3805,16 +3805,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.22285715</v>
+        <v>0.24590164</v>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -3823,46 +3823,46 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>0.30612245</v>
+        <v>0.33009708</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.35428572</v>
+        <v>0.3715847</v>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9632354</v>
+        <v>4.8561153</v>
       </c>
       <c r="O17" t="n">
         <v>25</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5220588</v>
+        <v>1.4460433</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="T17" t="n">
-        <v>0.284153</v>
+        <v>0.27027026</v>
       </c>
       <c r="U17" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.22772278</v>
+        <v>0.21782178</v>
       </c>
       <c r="C18" t="n">
+        <v>23</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23</v>
+      </c>
+      <c r="E18" t="n">
         <v>16</v>
-      </c>
-      <c r="D18" t="n">
-        <v>24</v>
-      </c>
-      <c r="E18" t="n">
-        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H18" t="n">
-        <v>0.32188842</v>
+        <v>0.2982456</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>0.32673267</v>
+        <v>0.2970297</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6666667</v>
+        <v>3.3962264</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
         <v>6</v>
       </c>
       <c r="Q18" t="n">
+        <v>15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.226415</v>
+      </c>
+      <c r="S18" t="n">
         <v>13</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.2222222</v>
-      </c>
-      <c r="S18" t="n">
-        <v>14</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.2413793</v>
+        <v>0.2361809</v>
       </c>
       <c r="U18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24902724</v>
+        <v>0.24609375</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
         <v>7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>10</v>
       </c>
       <c r="H19" t="n">
         <v>0.28467155</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>0.36575875</v>
+        <v>0.37109375</v>
       </c>
       <c r="K19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6470587</v>
+        <v>2.3823528</v>
       </c>
       <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.117647</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.20325203</v>
+      </c>
+      <c r="U19" t="n">
         <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.2058823</v>
-      </c>
-      <c r="S19" t="n">
-        <v>11</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.2248062</v>
-      </c>
-      <c r="U19" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2688679</v>
+        <v>0.2669903</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>0.33617023</v>
+        <v>0.33624455</v>
       </c>
       <c r="I20" t="n">
         <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.36792454</v>
+        <v>0.36407766</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
+        <v>9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.2037038</v>
+      </c>
+      <c r="S20" t="n">
         <v>11</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.339286</v>
-      </c>
-      <c r="O20" t="n">
-        <v>23</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
+        <v>0.21761657</v>
+      </c>
+      <c r="U20" t="n">
         <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.2321428</v>
-      </c>
-      <c r="S20" t="n">
-        <v>15</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.23039216</v>
-      </c>
-      <c r="U20" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2393617</v>
+        <v>0.1902439</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2631579</v>
+      </c>
+      <c r="I21" t="n">
         <v>28</v>
       </c>
-      <c r="E21" t="n">
+      <c r="J21" t="n">
+        <v>0.33170733</v>
+      </c>
+      <c r="K21" t="n">
+        <v>22</v>
+      </c>
+      <c r="L21" t="n">
+        <v>62</v>
+      </c>
+      <c r="M21" t="n">
+        <v>24</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.4156628</v>
+      </c>
+      <c r="O21" t="n">
         <v>9</v>
-      </c>
-      <c r="F21" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.30952382</v>
-      </c>
-      <c r="I21" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.40957448</v>
-      </c>
-      <c r="K21" t="n">
-        <v>11</v>
-      </c>
-      <c r="L21" t="n">
-        <v>44</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.1079137</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2086332</v>
+        <v>1.1746988</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24705882</v>
+        <v>0.2413793</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.20942408</v>
+        <v>0.22513089</v>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H22" t="n">
-        <v>0.32900432</v>
+        <v>0.34199134</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.31937173</v>
+        <v>0.33507854</v>
       </c>
       <c r="K22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.8076923</v>
+      </c>
+      <c r="O22" t="n">
+        <v>18</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
         <v>6</v>
       </c>
-      <c r="N22" t="n">
-        <v>4.2352943</v>
-      </c>
-      <c r="O22" t="n">
-        <v>21</v>
-      </c>
-      <c r="P22" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>13</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.3529412</v>
+        <v>1.2692307</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>0.26288658</v>
+        <v>0.24365482</v>
       </c>
       <c r="U22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.297561</v>
+        <v>0.28282827</v>
       </c>
       <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="n">
-        <v>30</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.36842105</v>
+        <v>0.36036035</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.52682924</v>
+        <v>0.5252525</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="M23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>3.6666667</v>
       </c>
       <c r="O23" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R23" t="n">
-        <v>1.425926</v>
+        <v>1.2222222</v>
       </c>
       <c r="S23" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>0.27014217</v>
+        <v>0.2415459</v>
       </c>
       <c r="U23" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -4274,46 +4274,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3272727</v>
+        <v>0.30414745</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>0.38114753</v>
+        <v>0.36363637</v>
       </c>
       <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5253456</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>0.5863636</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
       <c r="L24" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1666665</v>
+        <v>3.8333333</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P24" t="n">
         <v>7</v>
@@ -4322,16 +4322,16 @@
         <v>20</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3703704</v>
+        <v>1.2962962</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0.25980392</v>
+        <v>0.23232323</v>
       </c>
       <c r="U24" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24390244</v>
+        <v>0.22564103</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="n">
+        <v>22</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.30092594</v>
+      </c>
+      <c r="I25" t="n">
+        <v>18</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.31794873</v>
+      </c>
+      <c r="K25" t="n">
+        <v>25</v>
+      </c>
+      <c r="L25" t="n">
+        <v>67</v>
+      </c>
+      <c r="M25" t="n">
         <v>28</v>
-      </c>
-      <c r="E25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F25" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" t="n">
-        <v>14</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.3080357</v>
-      </c>
-      <c r="I25" t="n">
-        <v>16</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.3804878</v>
-      </c>
-      <c r="K25" t="n">
-        <v>13</v>
-      </c>
-      <c r="L25" t="n">
-        <v>68</v>
-      </c>
-      <c r="M25" t="n">
-        <v>29</v>
       </c>
       <c r="N25" t="n">
         <v>4.326923</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P25" t="n">
         <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
         <v>1.3653846</v>
       </c>
       <c r="S25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25123152</v>
+        <v>0.25615764</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22560975</v>
+        <v>0.21118012</v>
       </c>
       <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="n">
         <v>17</v>
-      </c>
-      <c r="D26" t="n">
-        <v>18</v>
       </c>
       <c r="E26" t="n">
         <v>26</v>
@@ -4423,19 +4423,19 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>0.29891303</v>
+        <v>0.30645162</v>
       </c>
       <c r="I26" t="n">
+        <v>16</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3478261</v>
+      </c>
+      <c r="K26" t="n">
         <v>19</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.37804878</v>
-      </c>
-      <c r="K26" t="n">
-        <v>14</v>
       </c>
       <c r="L26" t="n">
         <v>40</v>
@@ -4444,28 +4444,28 @@
         <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7209303</v>
+        <v>3.6818182</v>
       </c>
       <c r="O26" t="n">
+        <v>16</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
         <v>6</v>
       </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.3953488</v>
+        <v>1.5454545</v>
       </c>
       <c r="S26" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="T26" t="n">
-        <v>0.26589596</v>
+        <v>0.28333333</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.21022727</v>
+        <v>0.19075145</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2565445</v>
+      </c>
+      <c r="I27" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.27745664</v>
+      </c>
+      <c r="K27" t="n">
+        <v>30</v>
+      </c>
+      <c r="L27" t="n">
+        <v>54</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.0212765</v>
+      </c>
+      <c r="O27" t="n">
+        <v>22</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3404255</v>
+      </c>
+      <c r="S27" t="n">
         <v>19</v>
       </c>
-      <c r="E27" t="n">
-        <v>22</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>21</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.2755102</v>
-      </c>
-      <c r="I27" t="n">
-        <v>26</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="K27" t="n">
-        <v>26</v>
-      </c>
-      <c r="L27" t="n">
-        <v>45</v>
-      </c>
-      <c r="M27" t="n">
-        <v>8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.0625</v>
-      </c>
-      <c r="O27" t="n">
-        <v>26</v>
-      </c>
-      <c r="P27" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>13</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>28</v>
-      </c>
       <c r="T27" t="n">
-        <v>0.27272728</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.20634921</v>
+        <v>0.20888889</v>
       </c>
       <c r="C28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" t="n">
+        <v>29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.28514057</v>
+      </c>
+      <c r="I28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.29333332</v>
+      </c>
+      <c r="K28" t="n">
         <v>28</v>
       </c>
-      <c r="D28" t="n">
-        <v>25</v>
-      </c>
-      <c r="E28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" t="n">
-        <v>25</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.29245284</v>
-      </c>
-      <c r="I28" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.31746033</v>
-      </c>
-      <c r="K28" t="n">
-        <v>25</v>
-      </c>
       <c r="L28" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>1.8333334</v>
+        <v>1.8870968</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9074074</v>
+        <v>0.9354839</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.20304568</v>
+        <v>0.19555555</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24193548</v>
+        <v>0.22162162</v>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34545454</v>
+        <v>0.33183858</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>0.34946236</v>
+        <v>0.32972974</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1666667</v>
+        <v>3.6666667</v>
       </c>
       <c r="O29" t="n">
+        <v>13</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.1481482</v>
+      </c>
+      <c r="S29" t="n">
         <v>8</v>
       </c>
-      <c r="P29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.037037</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
+        <v>0.20304568</v>
+      </c>
+      <c r="U29" t="n">
         <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.22279793</v>
+        <v>0.23125</v>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -4694,46 +4694,46 @@
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.29166666</v>
+        <v>0.3</v>
       </c>
       <c r="I30" t="n">
+        <v>19</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29</v>
+      </c>
+      <c r="L30" t="n">
+        <v>25</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.2142856</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>11</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3809524</v>
+      </c>
+      <c r="S30" t="n">
         <v>21</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.26943004</v>
-      </c>
-      <c r="K30" t="n">
-        <v>30</v>
-      </c>
-      <c r="L30" t="n">
-        <v>31</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.0588236</v>
-      </c>
-      <c r="O30" t="n">
-        <v>18</v>
-      </c>
-      <c r="P30" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>20</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4901961</v>
-      </c>
-      <c r="S30" t="n">
-        <v>27</v>
-      </c>
       <c r="T30" t="n">
-        <v>0.23157895</v>
+        <v>0.21935484</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -4743,16 +4743,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.22</v>
+        <v>0.20588236</v>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>6</v>
@@ -4761,16 +4761,16 @@
         <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2837838</v>
+        <v>0.2600897</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>0.365</v>
+        <v>0.33333334</v>
       </c>
       <c r="K31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L31" t="n">
         <v>46</v>
@@ -4779,28 +4779,28 @@
         <v>9</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6666667</v>
+        <v>3.3333333</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3703704</v>
+        <v>1.462963</v>
       </c>
       <c r="S31" t="n">
+        <v>24</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.24637681</v>
+      </c>
+      <c r="U31" t="n">
         <v>19</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.23671497</v>
-      </c>
-      <c r="U31" t="n">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24454562</v>
+        <v>0.24448633</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3161017</v>
+        <v>0.3156387</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3987858</v>
+        <v>0.39868048</v>
       </c>
       <c r="K2" t="n">
         <v>19</v>
       </c>
       <c r="L2" t="n">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0850606</v>
+        <v>4.078125</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2709078</v>
+        <v>1.2691761</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24712318</v>
+        <v>0.24690664</v>
       </c>
       <c r="U2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24478285</v>
+        <v>0.2455649</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.316999</v>
+        <v>0.31772408</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40251926</v>
+        <v>0.4035481</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="M3" t="n">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4454875</v>
+        <v>5.429699</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5061371</v>
+        <v>1.5043042</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27158672</v>
+        <v>0.27146003</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24754901</v>
+        <v>0.24732997</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31072772</v>
+        <v>0.31064335</v>
       </c>
       <c r="I4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41044495</v>
+        <v>0.41053027</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="M4" t="n">
         <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3.615495</v>
+        <v>3.602564</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2482066</v>
+        <v>1.2435898</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23386325</v>
+        <v>0.23334602</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23363237</v>
+        <v>0.23286119</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3141503</v>
+        <v>0.31340033</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3949227</v>
+        <v>0.39395657</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>1474</v>
+        <v>1489</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.110371</v>
+        <v>4.083607</v>
       </c>
       <c r="O5" t="n">
         <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3401521</v>
+        <v>1.3372475</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25242537</v>
+        <v>0.25221077</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2460076</v>
+        <v>0.24660121</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>162</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32011524</v>
+        <v>0.32019538</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4013308</v>
+        <v>0.4008686</v>
       </c>
       <c r="K6" t="n">
         <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>1283</v>
+        <v>1293</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5870967</v>
+        <v>3.5641026</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -862,16 +862,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2387097</v>
+        <v>1.2364672</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24177288</v>
+        <v>0.2413467</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25134283</v>
+        <v>0.25128865</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -896,46 +896,46 @@
         <v>217</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33942136</v>
+        <v>0.33922544</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.43045008</v>
+        <v>0.429676</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.173077</v>
+        <v>4.165605</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2628205</v>
+        <v>1.2632697</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24339622</v>
+        <v>0.24371953</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23488018</v>
+        <v>0.23507181</v>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>203</v>
@@ -966,28 +966,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31981227</v>
+        <v>0.31984007</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40414608</v>
+        <v>0.40343916</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>1454</v>
+        <v>1461</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.149881</v>
+        <v>4.1518745</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
         <v>174</v>
@@ -996,13 +996,13 @@
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3159904</v>
+        <v>1.3184623</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24263728</v>
+        <v>0.24334529</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22899885</v>
+        <v>0.22851153</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30596888</v>
+        <v>0.3052864</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.394323</v>
+        <v>0.3939394</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>1492</v>
+        <v>1507</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.86259</v>
+        <v>4.8430204</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4482014</v>
+        <v>1.4449737</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25472227</v>
+        <v>0.25446096</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23854962</v>
+        <v>0.23814042</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -1100,25 +1100,25 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3156823</v>
+        <v>0.31527427</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37729007</v>
+        <v>0.3760911</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7686424</v>
+        <v>3.7535646</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1130,16 +1130,16 @@
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2597992</v>
+        <v>1.2611692</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23637056</v>
+        <v>0.23703143</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25341567</v>
+        <v>0.2531622</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3227105</v>
+        <v>0.3222741</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41530976</v>
+        <v>0.41480654</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5814795</v>
+        <v>5.5517654</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5261122</v>
+        <v>1.5219793</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28828993</v>
+        <v>0.2879638</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24103624</v>
+        <v>0.24104477</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E12" t="n">
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G12" t="n">
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3194005</v>
+        <v>0.31965587</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40003756</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
         <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>1372</v>
+        <v>1381</v>
       </c>
       <c r="M12" t="n">
         <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.643777</v>
+        <v>3.6460555</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2203147</v>
+        <v>1.2196162</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23177034</v>
+        <v>0.2315449</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24023512</v>
+        <v>0.24039909</v>
       </c>
       <c r="C13" t="n">
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3135291</v>
+        <v>0.31350076</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4114524</v>
+        <v>0.4118976</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4978456</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3413117</v>
+        <v>1.3437946</v>
       </c>
       <c r="S13" t="n">
         <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23724587</v>
+        <v>0.23737855</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24563402</v>
+        <v>0.24632214</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
@@ -1365,28 +1365,28 @@
         <v>164</v>
       </c>
       <c r="G14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31521553</v>
+        <v>0.31566468</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39939255</v>
+        <v>0.3994719</v>
       </c>
       <c r="K14" t="n">
         <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7240214</v>
+        <v>4.719328</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
@@ -1398,13 +1398,13 @@
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3977766</v>
+        <v>1.3959184</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25985596</v>
+        <v>0.259887</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.233791</v>
+        <v>0.23388931</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G15" t="n">
         <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3093979</v>
+        <v>0.309544</v>
       </c>
       <c r="I15" t="n">
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.36880243</v>
+        <v>0.3692191</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1498</v>
+        <v>1507</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.239616</v>
+        <v>4.260444</v>
       </c>
       <c r="O15" t="n">
         <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q15" t="n">
         <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.342617</v>
+        <v>1.3463833</v>
       </c>
       <c r="S15" t="n">
         <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23829544</v>
+        <v>0.23913456</v>
       </c>
       <c r="U15" t="n">
         <v>12</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25734317</v>
+        <v>0.2575786</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
@@ -1499,46 +1499,46 @@
         <v>199</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33922026</v>
+        <v>0.33945712</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42637864</v>
+        <v>0.4257202</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.594387</v>
+        <v>3.5905623</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q16" t="n">
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1520748</v>
+        <v>1.1518112</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21868941</v>
+        <v>0.21879815</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,43 +1551,43 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24871454</v>
+        <v>0.24900663</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32664078</v>
+        <v>0.3266812</v>
       </c>
       <c r="I17" t="n">
         <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39992383</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1283407</v>
+        <v>4.1145935</v>
       </c>
       <c r="O17" t="n">
         <v>14</v>
@@ -1599,16 +1599,16 @@
         <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2879846</v>
+        <v>1.2868421</v>
       </c>
       <c r="S17" t="n">
         <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23646452</v>
+        <v>0.2365019</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25763538</v>
+        <v>0.25721735</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34003294</v>
+        <v>0.3393413</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4017238</v>
+        <v>0.4017508</v>
       </c>
       <c r="K18" t="n">
         <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>1338</v>
+        <v>1349</v>
       </c>
       <c r="M18" t="n">
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>3.550773</v>
+        <v>3.5344992</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1666,13 +1666,13 @@
         <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.188585</v>
+        <v>1.1880908</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22348194</v>
+        <v>0.2232194</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24353206</v>
+        <v>0.24362078</v>
       </c>
       <c r="C19" t="n">
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31589538</v>
+        <v>0.3158421</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40194976</v>
+        <v>0.40193704</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="M19" t="n">
         <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>4.584663</v>
+        <v>4.5681496</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
@@ -1733,13 +1733,13 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3660395</v>
+        <v>1.3629911</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24916202</v>
+        <v>0.24861163</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -1752,46 +1752,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23910993</v>
+        <v>0.23899607</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30964896</v>
+        <v>0.30970025</v>
       </c>
       <c r="I20" t="n">
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39392796</v>
+        <v>0.39445588</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="M20" t="n">
         <v>17</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1538463</v>
+        <v>4.140085</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
         <v>179</v>
@@ -1800,13 +1800,13 @@
         <v>17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2945939</v>
+        <v>1.2898723</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2399623</v>
+        <v>0.23931783</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23359631</v>
+        <v>0.23428243</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31030345</v>
+        <v>0.3108614</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40773523</v>
+        <v>0.40970764</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1439</v>
+        <v>1450</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2148957</v>
+        <v>3.2071648</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q21" t="n">
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1620018</v>
+        <v>1.1609709</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22318007</v>
+        <v>0.22292024</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24129401</v>
+        <v>0.24092284</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
         <v>180</v>
@@ -1904,46 +1904,46 @@
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31240427</v>
+        <v>0.31225696</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39733586</v>
+        <v>0.39655825</v>
       </c>
       <c r="K22" t="n">
         <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="M22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0047846</v>
+        <v>4.004754</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2832536</v>
+        <v>1.2800095</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2471868</v>
+        <v>0.24683072</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25389755</v>
+        <v>0.25350553</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G23" t="n">
         <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33113238</v>
+        <v>0.3304876</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40515962</v>
+        <v>0.40479705</v>
       </c>
       <c r="K23" t="n">
         <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>1456</v>
+        <v>1465</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.161751</v>
+        <v>4.1671</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
         <v>150</v>
@@ -2001,13 +2001,13 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2973359</v>
+        <v>1.2989837</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23690678</v>
+        <v>0.23727222</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24308756</v>
+        <v>0.24303702</v>
       </c>
       <c r="C24" t="n">
         <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E24" t="n">
         <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.318345</v>
+        <v>0.31827447</v>
       </c>
       <c r="I24" t="n">
         <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3984255</v>
+        <v>0.39813048</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="M24" t="n">
         <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9587924</v>
+        <v>3.9397762</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2068,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2886919</v>
+        <v>1.2911211</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24129353</v>
+        <v>0.24163498</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24668038</v>
+        <v>0.2461424</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -2105,43 +2105,43 @@
         <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30858114</v>
+        <v>0.30810812</v>
       </c>
       <c r="I25" t="n">
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40396485</v>
+        <v>0.4026771</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L25" t="n">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="M25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N25" t="n">
-        <v>4.361091</v>
+        <v>4.358773</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3603733</v>
+        <v>1.3601997</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24839076</v>
+        <v>0.24844837</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2313891</v>
+        <v>0.23156089</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
@@ -2169,46 +2169,46 @@
         <v>179</v>
       </c>
       <c r="G26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31159544</v>
+        <v>0.31208792</v>
       </c>
       <c r="I26" t="n">
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37893322</v>
+        <v>0.37831143</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.206357</v>
+        <v>4.2020082</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q26" t="n">
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2641463</v>
+        <v>1.2644035</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25141776</v>
+        <v>0.2515015</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24113208</v>
+        <v>0.24146982</v>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
         <v>161</v>
@@ -2239,46 +2239,46 @@
         <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31432897</v>
+        <v>0.31478697</v>
       </c>
       <c r="I27" t="n">
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>0.38018867</v>
+        <v>0.37982753</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2827587</v>
+        <v>4.2618146</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3533889</v>
+        <v>1.3497165</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25342596</v>
+        <v>0.2530323</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25821775</v>
+        <v>0.2577417</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G28" t="n">
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32662117</v>
+        <v>0.32615334</v>
       </c>
       <c r="I28" t="n">
         <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40167204</v>
+        <v>0.4010574</v>
       </c>
       <c r="K28" t="n">
         <v>14</v>
       </c>
       <c r="L28" t="n">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.674518</v>
+        <v>3.7111425</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1299073</v>
+        <v>1.1348474</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22767176</v>
+        <v>0.22839272</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24236017</v>
+        <v>0.24168895</v>
       </c>
       <c r="C29" t="n">
         <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
@@ -2370,46 +2370,46 @@
         <v>176</v>
       </c>
       <c r="G29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31796366</v>
+        <v>0.31708148</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39630982</v>
+        <v>0.39472678</v>
       </c>
       <c r="K29" t="n">
         <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.283119</v>
+        <v>4.30077</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3020102</v>
+        <v>1.3029355</v>
       </c>
       <c r="S29" t="n">
         <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24773414</v>
+        <v>0.24756189</v>
       </c>
       <c r="U29" t="n">
         <v>20</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24787295</v>
+        <v>0.24775952</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3103271</v>
+        <v>0.30998307</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3821138</v>
+        <v>0.38162807</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9152908</v>
+        <v>3.9219306</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q30" t="n">
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3007897</v>
+        <v>1.2959546</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23564318</v>
+        <v>0.23484848</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2489,64 +2489,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24651681</v>
+        <v>0.24621353</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3212272</v>
+        <v>0.32102227</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4239272</v>
+        <v>0.42316216</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="M31" t="n">
         <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6702356</v>
+        <v>4.6531916</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3882941</v>
+        <v>1.3893617</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25316927</v>
+        <v>0.25310358</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2800,40 +2800,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.28235295</v>
+        <v>0.27218935</v>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
-        <v>25</v>
-      </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.32795697</v>
+        <v>0.3114754</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4764706</v>
+        <v>0.43786982</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
         <v>3.8</v>
@@ -2848,16 +2848,16 @@
         <v>26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1333333</v>
+        <v>1.0222223</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.21212122</v>
+        <v>0.19753087</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24242425</v>
+        <v>0.265</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2990654</v>
+        <v>0.3318182</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4090909</v>
+        <v>0.43</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>6.7959185</v>
+        <v>6.48</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7142857</v>
+        <v>1.72</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3043478</v>
+        <v>0.30243903</v>
       </c>
       <c r="U3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24855492</v>
+        <v>0.24561404</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.30107528</v>
+        <v>0.31016043</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40462428</v>
+        <v>0.42105263</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8863637</v>
+        <v>2.5434783</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2727273</v>
+        <v>1.0217391</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2616279</v>
+        <v>0.22222222</v>
       </c>
       <c r="U4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21341464</v>
+        <v>0.1891892</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2657005</v>
+      </c>
+      <c r="I5" t="n">
         <v>28</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
+        <v>0.33513513</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.6181817</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.1090909</v>
+      </c>
+      <c r="S5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2802198</v>
-      </c>
-      <c r="I5" t="n">
-        <v>26</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.41463414</v>
-      </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" t="n">
-        <v>46</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="T5" t="n">
+        <v>0.21025641</v>
+      </c>
+      <c r="U5" t="n">
         <v>9</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.5434783</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.0652174</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.19875777</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.20103092</v>
+        <v>0.23880596</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>0.27906978</v>
+        <v>0.29816514</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3556701</v>
+        <v>0.37313432</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>3.483871</v>
+        <v>2.392405</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2967741</v>
+        <v>1.1392405</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>0.23589744</v>
+        <v>0.2010582</v>
       </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.26344085</v>
+        <v>0.24324325</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34285715</v>
+        <v>0.3221154</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>0.47311828</v>
+        <v>0.3783784</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6382978</v>
+        <v>3.4468086</v>
       </c>
       <c r="O7" t="n">
         <v>11</v>
       </c>
       <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.0212766</v>
+        <v>1.0851064</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0.20467836</v>
+        <v>0.21764706</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -3202,37 +3202,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2361809</v>
+        <v>0.24242425</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.33620688</v>
+        <v>0.34199134</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.43718594</v>
+        <v>0.41919193</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M8" t="n">
         <v>24</v>
@@ -3241,25 +3241,25 @@
         <v>4.924528</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5660378</v>
+        <v>1.6226416</v>
       </c>
       <c r="S8" t="n">
         <v>28</v>
       </c>
       <c r="T8" t="n">
-        <v>0.27450982</v>
+        <v>0.3028846</v>
       </c>
       <c r="U8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -3269,58 +3269,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23834197</v>
+        <v>0.19689119</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2952381</v>
+        <v>0.24880382</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3834197</v>
+        <v>0.33678755</v>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6666665</v>
+        <v>4.6380367</v>
       </c>
       <c r="O9" t="n">
         <v>24</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.537037</v>
+        <v>1.4171779</v>
       </c>
       <c r="S9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T9" t="n">
         <v>0.26794258</v>
@@ -3339,61 +3339,61 @@
         <v>0.2882353</v>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.35106382</v>
+      </c>
+      <c r="I10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>27</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>0.42352942</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.4545455</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2045455</v>
+      </c>
+      <c r="S10" t="n">
         <v>14</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.36125654</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.45294118</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>36</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.1333333</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.22560975</v>
+        <v>0.24848485</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.225</v>
+        <v>0.23762377</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
         <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" t="n">
         <v>0.28767124</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>0.325</v>
+        <v>0.33663365</v>
       </c>
       <c r="K11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>17</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2777778</v>
+      </c>
+      <c r="S11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.27403846</v>
+      </c>
+      <c r="U11" t="n">
         <v>24</v>
-      </c>
-      <c r="L11" t="n">
-        <v>56</v>
-      </c>
-      <c r="M11" t="n">
-        <v>21</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.8333335</v>
-      </c>
-      <c r="O11" t="n">
-        <v>28</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>23</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.425926</v>
-      </c>
-      <c r="S11" t="n">
-        <v>22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.29245284</v>
-      </c>
-      <c r="U11" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.27118644</v>
+        <v>0.27542374</v>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>19</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.36956522</v>
+        <v>0.37769786</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40677965</v>
+        <v>0.4279661</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M12" t="n">
+        <v>28</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
         <v>24</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.661017</v>
-      </c>
-      <c r="O12" t="n">
-        <v>12</v>
-      </c>
-      <c r="P12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>20</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.1864407</v>
+        <v>1.1333333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21266969</v>
+        <v>0.19909503</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3537,16 +3537,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.26086956</v>
+        <v>0.26415095</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -3555,46 +3555,46 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3125</v>
+        <v>0.3173913</v>
       </c>
       <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.49056605</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>58</v>
+      </c>
+      <c r="M13" t="n">
+        <v>23</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.809816</v>
+      </c>
+      <c r="O13" t="n">
+        <v>18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
         <v>15</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.47826087</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>52</v>
-      </c>
-      <c r="M13" t="n">
-        <v>18</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
+        <v>1.2515337</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U13" t="n">
         <v>13</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>23</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.2407408</v>
-      </c>
-      <c r="S13" t="n">
-        <v>14</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="U13" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2596154</v>
+        <v>0.28019324</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>31</v>
@@ -3616,37 +3616,37 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3231441</v>
+        <v>0.32735425</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.41826922</v>
+        <v>0.41545895</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N14" t="n">
-        <v>7.2</v>
+        <v>7.56</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
         <v>30</v>
@@ -3658,7 +3658,7 @@
         <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>0.30769232</v>
+        <v>0.3110048</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23696682</v>
+        <v>0.23076923</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="n">
-        <v>22</v>
-      </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33606556</v>
+        <v>0.32489452</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2985782</v>
+        <v>0.3221154</v>
       </c>
       <c r="K15" t="n">
+        <v>24</v>
+      </c>
+      <c r="L15" t="n">
+        <v>63</v>
+      </c>
+      <c r="M15" t="n">
         <v>26</v>
       </c>
-      <c r="L15" t="n">
-        <v>65</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>5.5636363</v>
+      </c>
+      <c r="O15" t="n">
+        <v>28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4909091</v>
+      </c>
+      <c r="S15" t="n">
         <v>27</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.303571</v>
-      </c>
-      <c r="O15" t="n">
-        <v>27</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>15</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4642857</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.29464287</v>
+        <v>0.30973452</v>
       </c>
       <c r="U15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.31400967</v>
+        <v>0.32692307</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.40167364</v>
+        <v>0.40336135</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5507246</v>
+        <v>0.5625</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.54717</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
         <v>4</v>
       </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9811321</v>
+        <v>0.8703704</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.20725389</v>
+        <v>0.18041237</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24590164</v>
+        <v>0.24861878</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33009708</v>
+        <v>0.32673267</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3715847</v>
+        <v>0.3756906</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8561153</v>
+        <v>4.6618705</v>
       </c>
       <c r="O17" t="n">
         <v>25</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4460433</v>
+        <v>1.4028777</v>
       </c>
       <c r="S17" t="n">
         <v>23</v>
       </c>
       <c r="T17" t="n">
-        <v>0.27027026</v>
+        <v>0.26229507</v>
       </c>
       <c r="U17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.21782178</v>
+        <v>0.20408164</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2982456</v>
+        <v>0.28181818</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2970297</v>
+        <v>0.3112245</v>
       </c>
       <c r="K18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L18" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M18" t="n">
         <v>30</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3962264</v>
+        <v>2.8867924</v>
       </c>
       <c r="O18" t="n">
         <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.226415</v>
+        <v>1.1698114</v>
       </c>
       <c r="S18" t="n">
         <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2361809</v>
+        <v>0.20918368</v>
       </c>
       <c r="U18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24609375</v>
+        <v>0.24701196</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
@@ -3954,46 +3954,46 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.28467155</v>
+        <v>0.28089887</v>
       </c>
       <c r="I19" t="n">
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>0.37109375</v>
+        <v>0.37848607</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L19" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3823528</v>
+        <v>2.53125</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.117647</v>
+        <v>1.09375</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>0.20325203</v>
+        <v>0.19827586</v>
       </c>
       <c r="U19" t="n">
         <v>4</v>
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2669903</v>
+        <v>0.26923078</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.34893617</v>
+      </c>
+      <c r="I20" t="n">
         <v>4</v>
       </c>
-      <c r="G20" t="n">
-        <v>20</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.33624455</v>
-      </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
       <c r="J20" t="n">
-        <v>0.36407766</v>
+        <v>0.40865386</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
         <v>9</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.1666667</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.0925926</v>
+      </c>
+      <c r="S20" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" t="n">
-        <v>15</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.2037038</v>
-      </c>
-      <c r="S20" t="n">
-        <v>11</v>
-      </c>
       <c r="T20" t="n">
-        <v>0.21761657</v>
+        <v>0.1957672</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1902439</v>
+        <v>0.21538462</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2857143</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.42564103</v>
+      </c>
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="G21" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.2631579</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.33170733</v>
-      </c>
-      <c r="K21" t="n">
-        <v>22</v>
-      </c>
       <c r="L21" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4156628</v>
+        <v>3.611465</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1746988</v>
+        <v>1.1273886</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2413793</v>
+        <v>0.22959183</v>
       </c>
       <c r="U21" t="n">
         <v>16</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22513089</v>
+        <v>0.22680412</v>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" t="n">
-        <v>0.34199134</v>
+        <v>0.31858408</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>0.33507854</v>
+        <v>0.34020618</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L22" t="n">
         <v>43</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8076923</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2692307</v>
+        <v>1.2884616</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24365482</v>
+        <v>0.2512563</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -4207,61 +4207,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28282827</v>
+        <v>0.25773194</v>
       </c>
       <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.33944955</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4742268</v>
+      </c>
+      <c r="K23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
-        <v>31</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.36036035</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.5252525</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N23" t="n">
         <v>3.6666667</v>
       </c>
       <c r="O23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2222222</v>
+        <v>1.2407408</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2415459</v>
+        <v>0.24630542</v>
       </c>
       <c r="U23" t="n">
         <v>17</v>
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.30414745</v>
+        <v>0.28638497</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3487395</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.48826292</v>
+      </c>
+      <c r="K24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.36363637</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.5253456</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8333333</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2962962</v>
+        <v>1.425926</v>
       </c>
       <c r="S24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23232323</v>
+        <v>0.25870648</v>
       </c>
       <c r="U24" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.22564103</v>
+        <v>0.1904762</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
+        <v>27</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.26442307</v>
+      </c>
+      <c r="I25" t="n">
+        <v>29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.26984128</v>
+      </c>
+      <c r="K25" t="n">
+        <v>29</v>
+      </c>
+      <c r="L25" t="n">
+        <v>69</v>
+      </c>
+      <c r="M25" t="n">
+        <v>29</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.7647057</v>
+      </c>
+      <c r="O25" t="n">
+        <v>26</v>
+      </c>
+      <c r="P25" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>29</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3921568</v>
+      </c>
+      <c r="S25" t="n">
         <v>22</v>
       </c>
-      <c r="F25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25" t="n">
-        <v>20</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.30092594</v>
-      </c>
-      <c r="I25" t="n">
-        <v>18</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.31794873</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="T25" t="n">
+        <v>0.27586207</v>
+      </c>
+      <c r="U25" t="n">
         <v>25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>67</v>
-      </c>
-      <c r="M25" t="n">
-        <v>28</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.326923</v>
-      </c>
-      <c r="O25" t="n">
-        <v>23</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>28</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.3653846</v>
-      </c>
-      <c r="S25" t="n">
-        <v>20</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.25615764</v>
-      </c>
-      <c r="U25" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.21118012</v>
+        <v>0.20987654</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H26" t="n">
-        <v>0.30645162</v>
+        <v>0.3027027</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3478261</v>
+        <v>0.33333334</v>
       </c>
       <c r="K26" t="n">
+        <v>23</v>
+      </c>
+      <c r="L26" t="n">
+        <v>39</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
         <v>19</v>
       </c>
-      <c r="L26" t="n">
-        <v>40</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
         <v>5</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.6818182</v>
-      </c>
-      <c r="O26" t="n">
-        <v>16</v>
-      </c>
-      <c r="P26" t="n">
-        <v>4</v>
-      </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5454545</v>
+        <v>1.4666667</v>
       </c>
       <c r="S26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28333333</v>
+        <v>0.27868852</v>
       </c>
       <c r="U26" t="n">
         <v>26</v>
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.19075145</v>
+        <v>0.22093023</v>
       </c>
       <c r="C27" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
         <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2565445</v>
+        <v>0.2795699</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>0.27745664</v>
+        <v>0.30813953</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L27" t="n">
         <v>54</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N27" t="n">
-        <v>4.0212765</v>
+        <v>3.7173913</v>
       </c>
       <c r="O27" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P27" t="n">
         <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3404255</v>
+        <v>1.1521739</v>
       </c>
       <c r="S27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25</v>
+        <v>0.21764706</v>
       </c>
       <c r="U27" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.20888889</v>
+        <v>0.19642857</v>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H28" t="n">
-        <v>0.28514057</v>
+        <v>0.28286853</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>0.29333332</v>
+        <v>0.2767857</v>
       </c>
       <c r="K28" t="n">
         <v>28</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N28" t="n">
-        <v>1.8870968</v>
+        <v>2.8032787</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9354839</v>
+        <v>1.0819672</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.19555555</v>
+        <v>0.21145375</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.22162162</v>
+        <v>0.17777778</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" t="n">
-        <v>0.33183858</v>
+        <v>0.29166666</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>0.32972974</v>
+        <v>0.2611111</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L29" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6666667</v>
+        <v>4.3333335</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.1481482</v>
+        <v>1.2777778</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.20304568</v>
+        <v>0.22058824</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.23125</v>
+        <v>0.2244898</v>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3</v>
+        <v>0.28703704</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2875</v>
+        <v>0.3010204</v>
       </c>
       <c r="K30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2142856</v>
+        <v>4.0408163</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3809524</v>
+        <v>1.244898</v>
       </c>
       <c r="S30" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.21935484</v>
+        <v>0.20224719</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.20588236</v>
+        <v>0.21463415</v>
       </c>
       <c r="C31" t="n">
+        <v>23</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.27433628</v>
+      </c>
+      <c r="I31" t="n">
         <v>27</v>
       </c>
-      <c r="D31" t="n">
-        <v>25</v>
-      </c>
-      <c r="E31" t="n">
-        <v>11</v>
-      </c>
-      <c r="F31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G31" t="n">
-        <v>14</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.2600897</v>
-      </c>
-      <c r="I31" t="n">
-        <v>29</v>
-      </c>
       <c r="J31" t="n">
-        <v>0.33333334</v>
+        <v>0.3512195</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L31" t="n">
         <v>46</v>
       </c>
       <c r="M31" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.1666667</v>
+      </c>
+      <c r="O31" t="n">
         <v>9</v>
       </c>
-      <c r="N31" t="n">
-        <v>3.3333333</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>7</v>
       </c>
-      <c r="P31" t="n">
-        <v>6</v>
-      </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.462963</v>
+        <v>1.3888888</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="T31" t="n">
-        <v>0.24637681</v>
+        <v>0.25714287</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24448633</v>
+        <v>0.24584034</v>
       </c>
       <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>717</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>162</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.31689787</v>
+      </c>
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="D2" t="n">
-        <v>705</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="J2" t="n">
+        <v>0.40157038</v>
+      </c>
+      <c r="K2" t="n">
         <v>14</v>
       </c>
-      <c r="F2" t="n">
-        <v>159</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3156387</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.39868048</v>
-      </c>
-      <c r="K2" t="n">
-        <v>19</v>
-      </c>
       <c r="L2" t="n">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.078125</v>
+        <v>4.1030345</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2691761</v>
+        <v>1.2738179</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24690664</v>
+        <v>0.2480476</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2455649</v>
+        <v>0.2459655</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31772408</v>
+        <v>0.31799233</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4035481</v>
+        <v>0.40511966</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>1337</v>
+        <v>1351</v>
       </c>
       <c r="M3" t="n">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.429699</v>
+        <v>5.439772</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5043042</v>
+        <v>1.5032074</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27146003</v>
+        <v>0.271452</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24732997</v>
+        <v>0.2479062</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31064335</v>
+        <v>0.31114107</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41053027</v>
+        <v>0.4109436</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.602564</v>
+        <v>3.624204</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q4" t="n">
         <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2435898</v>
+        <v>1.2420382</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23334602</v>
+        <v>0.23321354</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -756,7 +756,7 @@
         <v>705</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
         <v>194</v>
@@ -786,7 +786,7 @@
         <v>4.083607</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
         <v>169</v>
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24660121</v>
+        <v>0.2456338</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
         <v>681</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
         <v>162</v>
@@ -832,43 +832,43 @@
         <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32019538</v>
+        <v>0.3194305</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4008686</v>
+        <v>0.39906102</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>1293</v>
+        <v>1305</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5641026</v>
+        <v>3.5477707</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2364672</v>
+        <v>1.2321302</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2413467</v>
+        <v>0.24064673</v>
       </c>
       <c r="U6" t="n">
         <v>14</v>
@@ -881,43 +881,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25128865</v>
+        <v>0.25105292</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33922544</v>
+        <v>0.33914018</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.429676</v>
+        <v>0.42940852</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.165605</v>
+        <v>4.14557</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
@@ -929,13 +929,13 @@
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2632697</v>
+        <v>1.2609001</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24371953</v>
+        <v>0.24324325</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23507181</v>
+        <v>0.23564728</v>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31984007</v>
+        <v>0.32066116</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40343916</v>
+        <v>0.40375236</v>
       </c>
       <c r="K8" t="n">
         <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>1461</v>
+        <v>1473</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1518745</v>
+        <v>4.1318088</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q8" t="n">
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3184623</v>
+        <v>1.3157275</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24334529</v>
+        <v>0.24315196</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22851153</v>
+        <v>0.2284091</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3052864</v>
+        <v>0.3051191</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3939394</v>
+        <v>0.39469698</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8430204</v>
+        <v>4.8504143</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4449737</v>
+        <v>1.4471005</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25446096</v>
+        <v>0.25498524</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23814042</v>
+        <v>0.23745756</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G10" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31527427</v>
+        <v>0.31436723</v>
       </c>
       <c r="I10" t="n">
         <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3760911</v>
+        <v>0.37514144</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7535646</v>
+        <v>3.729634</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1130,16 +1130,16 @@
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2611692</v>
+        <v>1.257379</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23703143</v>
+        <v>0.23611373</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2531622</v>
+        <v>0.25424355</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3222741</v>
+        <v>0.32285288</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41480654</v>
+        <v>0.41697416</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5517654</v>
+        <v>5.5933175</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5219793</v>
+        <v>1.5286397</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2879638</v>
+        <v>0.28892082</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1219,25 +1219,25 @@
         <v>0.24104477</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
         <v>709</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>177</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
         <v>0.31965587</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>0.4</v>
@@ -1249,7 +1249,7 @@
         <v>1381</v>
       </c>
       <c r="M12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
         <v>3.6460555</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24039909</v>
+        <v>0.24060573</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31350076</v>
+        <v>0.31346282</v>
       </c>
       <c r="I13" t="n">
         <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4118976</v>
+        <v>0.4137222</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.503189</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3437946</v>
+        <v>1.3451453</v>
       </c>
       <c r="S13" t="n">
         <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23737855</v>
+        <v>0.23784295</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24632214</v>
+        <v>0.24611059</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31566468</v>
+        <v>0.3152046</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3994719</v>
+        <v>0.39943767</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L14" t="n">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.719328</v>
+        <v>4.7340174</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3959184</v>
+        <v>1.3998091</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.259887</v>
+        <v>0.26028422</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23388931</v>
+        <v>0.23404256</v>
       </c>
       <c r="C15" t="n">
         <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>151</v>
       </c>
       <c r="G15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.309544</v>
+        <v>0.31004882</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3692191</v>
+        <v>0.3688571</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1507</v>
+        <v>1520</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.260444</v>
+        <v>4.258776</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q15" t="n">
         <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3463833</v>
+        <v>1.3462998</v>
       </c>
       <c r="S15" t="n">
         <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23913456</v>
+        <v>0.23901151</v>
       </c>
       <c r="U15" t="n">
         <v>12</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2575786</v>
+        <v>0.25720164</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
@@ -1502,25 +1502,25 @@
         <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33945712</v>
+        <v>0.33898026</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4257202</v>
+        <v>0.42461655</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1231</v>
+        <v>1243</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5905623</v>
+        <v>3.5931802</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
@@ -1532,13 +1532,13 @@
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1518112</v>
+        <v>1.1501303</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21879815</v>
+        <v>0.21860643</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24900663</v>
+        <v>0.2484951</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>163</v>
@@ -1569,46 +1569,46 @@
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3266812</v>
+        <v>0.32616308</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.39879608</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1145935</v>
+        <v>4.1039486</v>
       </c>
       <c r="O17" t="n">
         <v>14</v>
       </c>
       <c r="P17" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q17" t="n">
         <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2868421</v>
+        <v>1.2873453</v>
       </c>
       <c r="S17" t="n">
         <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2365019</v>
+        <v>0.23633957</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25721735</v>
+        <v>0.2575393</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3393413</v>
+        <v>0.33978844</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4017508</v>
+        <v>0.40203515</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>1349</v>
+        <v>1361</v>
       </c>
       <c r="M18" t="n">
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5344992</v>
+        <v>3.5184317</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1666,16 +1666,16 @@
         <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1880908</v>
+        <v>1.186194</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2232194</v>
+        <v>0.22262289</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1706,19 +1706,19 @@
         <v>0.3158421</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
         <v>0.40193704</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>1275</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>4.5681496</v>
@@ -1730,7 +1730,7 @@
         <v>181</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R19" t="n">
         <v>1.3629911</v>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23899607</v>
+        <v>0.23845008</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
@@ -1770,43 +1770,43 @@
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30970025</v>
+        <v>0.309097</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39445588</v>
+        <v>0.39344263</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="M20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.140085</v>
+        <v>4.1357646</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q20" t="n">
         <v>17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2898723</v>
+        <v>1.2896471</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23931783</v>
+        <v>0.2393736</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,43 +1819,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23428243</v>
+        <v>0.23423253</v>
       </c>
       <c r="C21" t="n">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3108614</v>
+        <v>0.31076506</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>0.40970764</v>
+        <v>0.4101444</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1450</v>
+        <v>1457</v>
       </c>
       <c r="M21" t="n">
         <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2071648</v>
+        <v>3.1995316</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1867,16 +1867,16 @@
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1609709</v>
+        <v>1.1648712</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22292024</v>
+        <v>0.22310455</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24092284</v>
+        <v>0.24022557</v>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
@@ -1904,46 +1904,46 @@
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31225696</v>
+        <v>0.31171232</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39655825</v>
+        <v>0.39511278</v>
       </c>
       <c r="K22" t="n">
         <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>4.004754</v>
+        <v>4.011101</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2800095</v>
+        <v>1.2838923</v>
       </c>
       <c r="S22" t="n">
         <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24683072</v>
+        <v>0.24722221</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25350553</v>
+        <v>0.25339448</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>182</v>
@@ -1971,43 +1971,43 @@
         <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3304876</v>
+        <v>0.33050433</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40479705</v>
+        <v>0.4040367</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1671</v>
+        <v>4.1470175</v>
       </c>
       <c r="O23" t="n">
         <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2989837</v>
+        <v>1.2956787</v>
       </c>
       <c r="S23" t="n">
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23727222</v>
+        <v>0.23683228</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24303702</v>
+        <v>0.24270004</v>
       </c>
       <c r="C24" t="n">
         <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E24" t="n">
         <v>19</v>
@@ -2038,25 +2038,25 @@
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31827447</v>
+        <v>0.31774437</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39813048</v>
+        <v>0.3970421</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="M24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9397762</v>
+        <v>3.927389</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2068,13 +2068,13 @@
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2911211</v>
+        <v>1.289262</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24163498</v>
+        <v>0.24135977</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2090,7 +2090,7 @@
         <v>0.2461424</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
         <v>665</v>
@@ -2120,7 +2120,7 @@
         <v>1302</v>
       </c>
       <c r="M25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N25" t="n">
         <v>4.358773</v>
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23156089</v>
+        <v>0.23148324</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31208792</v>
+        <v>0.31216398</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37831143</v>
+        <v>0.37810192</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2020082</v>
+        <v>4.2071257</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
@@ -2202,13 +2202,13 @@
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2644035</v>
+        <v>1.2669834</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2515015</v>
+        <v>0.2515383</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,46 +2221,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24146982</v>
+        <v>0.24100652</v>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31478697</v>
+        <v>0.31433794</v>
       </c>
       <c r="I27" t="n">
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>0.37982753</v>
+        <v>0.37931034</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2618146</v>
+        <v>4.244126</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
         <v>156</v>
@@ -2269,13 +2269,13 @@
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3497165</v>
+        <v>1.350564</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2530323</v>
+        <v>0.25292262</v>
       </c>
       <c r="U27" t="n">
         <v>25</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2577417</v>
+        <v>0.25768942</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
@@ -2306,43 +2306,43 @@
         <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32615334</v>
+        <v>0.32648593</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4010574</v>
+        <v>0.40022504</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7111425</v>
+        <v>3.7282991</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1348474</v>
+        <v>1.1354976</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22839272</v>
+        <v>0.22837761</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24168895</v>
+        <v>0.24154314</v>
       </c>
       <c r="C29" t="n">
         <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31708148</v>
+        <v>0.3169408</v>
       </c>
       <c r="I29" t="n">
         <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39472678</v>
+        <v>0.39509693</v>
       </c>
       <c r="K29" t="n">
         <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.30077</v>
+        <v>4.2794647</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
@@ -2400,19 +2400,19 @@
         <v>187</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3029355</v>
+        <v>1.2988286</v>
       </c>
       <c r="S29" t="n">
         <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24756189</v>
+        <v>0.24696885</v>
       </c>
       <c r="U29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -2425,13 +2425,13 @@
         <v>0.24775952</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
         <v>636</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
         <v>150</v>
@@ -2443,7 +2443,7 @@
         <v>0.30998307</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
         <v>0.38162807</v>
@@ -2458,7 +2458,7 @@
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9219306</v>
+        <v>3.9155428</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
@@ -2470,13 +2470,13 @@
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2959546</v>
+        <v>1.2952448</v>
       </c>
       <c r="S30" t="n">
         <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23484848</v>
+        <v>0.23465909</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2492,7 +2492,7 @@
         <v>0.24621353</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
         <v>807</v>
@@ -2522,7 +2522,7 @@
         <v>1327</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
         <v>4.6531916</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.27218935</v>
+        <v>0.3004695</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="n">
-        <v>18</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.3114754</v>
+        <v>0.3448276</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.43786982</v>
+        <v>0.5023474</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
+        <v>23</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>29</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.1851852</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.23786408</v>
+      </c>
+      <c r="U2" t="n">
         <v>17</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>26</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.0222223</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.19753087</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.265</v>
+        <v>0.28921568</v>
       </c>
       <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3318182</v>
+        <v>0.35267857</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.43</v>
+        <v>0.49509802</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>6.48</v>
+        <v>6.1764708</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.72</v>
+        <v>1.6078432</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.30243903</v>
+        <v>0.30952382</v>
       </c>
       <c r="U3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24561404</v>
+        <v>0.26086956</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31016043</v>
+        <v>0.3231441</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>0.42105263</v>
+        <v>0.4299517</v>
       </c>
       <c r="K4" t="n">
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5434783</v>
+        <v>3.2727273</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0217391</v>
+        <v>1.0181818</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22222222</v>
+        <v>0.22058824</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3010,13 +3010,13 @@
         <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
         <v>0.2657005</v>
@@ -3028,7 +3028,7 @@
         <v>0.33513513</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>50</v>
@@ -3052,7 +3052,7 @@
         <v>1.1090909</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
         <v>0.21025641</v>
@@ -3068,46 +3068,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23880596</v>
+        <v>0.22727273</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29816514</v>
+        <v>0.28169015</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.37313432</v>
+        <v>0.34343433</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N6" t="n">
-        <v>2.392405</v>
+        <v>2.050633</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -3116,16 +3116,16 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1392405</v>
+        <v>1.0822785</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2010582</v>
+        <v>0.19587629</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3135,46 +3135,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24324325</v>
+        <v>0.23831776</v>
       </c>
       <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" t="n">
         <v>14</v>
       </c>
-      <c r="D7" t="n">
-        <v>22</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17</v>
-      </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.32231405</v>
+      </c>
+      <c r="I7" t="n">
         <v>11</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.3221154</v>
-      </c>
-      <c r="I7" t="n">
-        <v>12</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.3783784</v>
+        <v>0.37850466</v>
       </c>
       <c r="K7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L7" t="n">
+        <v>54</v>
+      </c>
+      <c r="M7" t="n">
         <v>15</v>
       </c>
-      <c r="L7" t="n">
-        <v>49</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12</v>
-      </c>
       <c r="N7" t="n">
-        <v>3.4468086</v>
+        <v>3.0535715</v>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -3183,16 +3183,16 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0851064</v>
+        <v>1.0535715</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21764706</v>
+        <v>0.20895523</v>
       </c>
       <c r="U7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24242425</v>
+        <v>0.2669903</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3220,46 +3220,46 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.34199134</v>
+        <v>0.36885247</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41919193</v>
+        <v>0.4368932</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N8" t="n">
         <v>4.924528</v>
       </c>
       <c r="O8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6226416</v>
+        <v>1.5283018</v>
       </c>
       <c r="S8" t="n">
         <v>28</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3028846</v>
+        <v>0.2966507</v>
       </c>
       <c r="U8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -3272,61 +3272,61 @@
         <v>0.19689119</v>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.24880382</v>
+        <v>0.25943395</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33678755</v>
+        <v>0.35751295</v>
       </c>
       <c r="K9" t="n">
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3067484</v>
+      </c>
+      <c r="O9" t="n">
         <v>20</v>
       </c>
-      <c r="L9" t="n">
-        <v>57</v>
-      </c>
-      <c r="M9" t="n">
-        <v>21</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.6380367</v>
-      </c>
-      <c r="O9" t="n">
-        <v>24</v>
-      </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4171779</v>
+        <v>1.3803681</v>
       </c>
       <c r="S9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T9" t="n">
         <v>0.26794258</v>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -3336,46 +3336,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2882353</v>
+        <v>0.26237625</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>0.35106382</v>
+        <v>0.32126698</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>0.42352942</v>
+        <v>0.3910891</v>
       </c>
       <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>47</v>
+      </c>
+      <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="L10" t="n">
-        <v>39</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
       <c r="N10" t="n">
-        <v>2.4545455</v>
+        <v>2.037736</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -3384,16 +3384,16 @@
         <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2045455</v>
+        <v>1.1132076</v>
       </c>
       <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.22164948</v>
+      </c>
+      <c r="U10" t="n">
         <v>14</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.24848485</v>
-      </c>
-      <c r="U10" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.23762377</v>
+        <v>0.26291078</v>
       </c>
       <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3026316</v>
+      </c>
+      <c r="I11" t="n">
         <v>17</v>
       </c>
-      <c r="D11" t="n">
-        <v>17</v>
-      </c>
-      <c r="E11" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>24</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.28767124</v>
-      </c>
-      <c r="I11" t="n">
-        <v>20</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.33663365</v>
+        <v>0.4084507</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
+        <v>26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
         <v>22</v>
       </c>
-      <c r="P11" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>18</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.2777778</v>
+        <v>1.3703704</v>
       </c>
       <c r="S11" t="n">
         <v>18</v>
       </c>
       <c r="T11" t="n">
-        <v>0.27403846</v>
+        <v>0.28301886</v>
       </c>
       <c r="U11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.27542374</v>
+        <v>0.27941176</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.37769786</v>
+        <v>0.37916666</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4279661</v>
+        <v>0.4509804</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.8076923</v>
       </c>
       <c r="O12" t="n">
         <v>16</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1333333</v>
+        <v>1.1346154</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19909503</v>
+        <v>0.20418848</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.26415095</v>
+        <v>0.25581396</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3173913</v>
+        <v>0.30603448</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.49056605</v>
+        <v>0.46976745</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N13" t="n">
-        <v>3.809816</v>
+        <v>4.3067484</v>
       </c>
       <c r="O13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2515337</v>
+        <v>1.4171779</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22</v>
+        <v>0.25120774</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.28019324</v>
+        <v>0.29383886</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.32735425</v>
+        <v>0.33333334</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.41545895</v>
+        <v>0.45023698</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N14" t="n">
-        <v>7.56</v>
+        <v>7.5882354</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
+        <v>27</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.745098</v>
+      </c>
+      <c r="S14" t="n">
         <v>30</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S14" t="n">
-        <v>29</v>
-      </c>
       <c r="T14" t="n">
-        <v>0.3110048</v>
+        <v>0.30985916</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23076923</v>
+        <v>0.23671497</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
@@ -3686,28 +3686,28 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
-        <v>0.32489452</v>
+        <v>0.34166667</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3221154</v>
+        <v>0.33333334</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5636363</v>
+        <v>5.8333335</v>
       </c>
       <c r="O15" t="n">
         <v>28</v>
@@ -3716,19 +3716,19 @@
         <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4909091</v>
+        <v>1.5185186</v>
       </c>
       <c r="S15" t="n">
         <v>27</v>
       </c>
       <c r="T15" t="n">
-        <v>0.30973452</v>
+        <v>0.30454546</v>
       </c>
       <c r="U15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -3738,61 +3738,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.32692307</v>
+        <v>0.3043478</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.40336135</v>
+        <v>0.37229437</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5625</v>
+        <v>0.5072464</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.3333333</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.8703704</v>
+        <v>0.8888889</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.18041237</v>
+        <v>0.1761658</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24861878</v>
+        <v>0.23584905</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32673267</v>
+        <v>0.31355932</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3756906</v>
+        <v>0.3490566</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6618705</v>
+        <v>4.3067484</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4028777</v>
+        <v>1.3987731</v>
       </c>
       <c r="S17" t="n">
         <v>23</v>
       </c>
       <c r="T17" t="n">
-        <v>0.26229507</v>
+        <v>0.254717</v>
       </c>
       <c r="U17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.20408164</v>
+        <v>0.21319798</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.28181818</v>
+        <v>0.29090908</v>
       </c>
       <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3248731</v>
+      </c>
+      <c r="K18" t="n">
         <v>24</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.3112245</v>
-      </c>
-      <c r="K18" t="n">
-        <v>25</v>
-      </c>
       <c r="L18" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M18" t="n">
         <v>30</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8867924</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.074074</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1928934</v>
+      </c>
+      <c r="U18" t="n">
         <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.1698114</v>
-      </c>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.20918368</v>
-      </c>
-      <c r="U18" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -3939,43 +3939,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24701196</v>
+        <v>0.24413146</v>
       </c>
       <c r="C19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.27876106</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3802817</v>
+      </c>
+      <c r="K19" t="n">
+        <v>15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>48</v>
+      </c>
+      <c r="M19" t="n">
         <v>12</v>
       </c>
-      <c r="D19" t="n">
-        <v>29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.28089887</v>
-      </c>
-      <c r="I19" t="n">
-        <v>25</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.37848607</v>
-      </c>
-      <c r="K19" t="n">
-        <v>14</v>
-      </c>
-      <c r="L19" t="n">
-        <v>63</v>
-      </c>
-      <c r="M19" t="n">
-        <v>26</v>
-      </c>
       <c r="N19" t="n">
-        <v>2.53125</v>
+        <v>2.304878</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
@@ -3987,13 +3987,13 @@
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.09375</v>
+        <v>1.0792682</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>0.19827586</v>
+        <v>0.19387755</v>
       </c>
       <c r="U19" t="n">
         <v>4</v>
@@ -4006,13 +4006,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.26923078</v>
+        <v>0.26794258</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -4021,46 +4021,46 @@
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>0.34893617</v>
+        <v>0.3390558</v>
       </c>
       <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.41626793</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" t="n">
+        <v>44</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.3962264</v>
+      </c>
+      <c r="O20" t="n">
+        <v>13</v>
+      </c>
+      <c r="P20" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.40865386</v>
-      </c>
-      <c r="K20" t="n">
-        <v>13</v>
-      </c>
-      <c r="L20" t="n">
-        <v>45</v>
-      </c>
-      <c r="M20" t="n">
-        <v>9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.1666667</v>
-      </c>
-      <c r="O20" t="n">
-        <v>9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0925926</v>
+        <v>1.0566038</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1957672</v>
+        <v>0.19148937</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -4073,46 +4073,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.21538462</v>
+        <v>0.21681416</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2857143</v>
+        <v>0.2868526</v>
       </c>
       <c r="I21" t="n">
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42564103</v>
+        <v>0.43362832</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.611465</v>
+        <v>3.375</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
@@ -4121,13 +4121,13 @@
         <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1273886</v>
+        <v>1.2228261</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22959183</v>
+        <v>0.23275863</v>
       </c>
       <c r="U21" t="n">
         <v>16</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22680412</v>
+        <v>0.20304568</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
         <v>23</v>
-      </c>
-      <c r="E22" t="n">
-        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31858408</v>
+        <v>0.29646018</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>0.34020618</v>
+        <v>0.3147208</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L22" t="n">
         <v>43</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>5.3653846</v>
       </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2884616</v>
+        <v>1.4423077</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2512563</v>
+        <v>0.2753623</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -4207,46 +4207,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25773194</v>
+        <v>0.25906736</v>
       </c>
       <c r="C23" t="n">
+        <v>11</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
         <v>10</v>
       </c>
-      <c r="D23" t="n">
-        <v>28</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="H23" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I23" t="n">
         <v>8</v>
       </c>
-      <c r="F23" t="n">
+      <c r="J23" t="n">
+        <v>0.4507772</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>44</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.1666667</v>
+      </c>
+      <c r="O23" t="n">
         <v>8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.33944955</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.4742268</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>47</v>
-      </c>
-      <c r="M23" t="n">
-        <v>11</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O23" t="n">
-        <v>14</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
@@ -4255,16 +4255,16 @@
         <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2407408</v>
+        <v>1.0925926</v>
       </c>
       <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.23115578</v>
+      </c>
+      <c r="U23" t="n">
         <v>15</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.24630542</v>
-      </c>
-      <c r="U23" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -4274,46 +4274,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.28638497</v>
+        <v>0.25365853</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3487395</v>
+        <v>0.31578946</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J24" t="n">
-        <v>0.48826292</v>
+        <v>0.40487805</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M24" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N24" t="n">
         <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P24" t="n">
         <v>6</v>
@@ -4322,16 +4322,16 @@
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.425926</v>
+        <v>1.3703704</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0.25870648</v>
+        <v>0.24630542</v>
       </c>
       <c r="U24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -4350,13 +4350,13 @@
         <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H25" t="n">
         <v>0.26442307</v>
@@ -4368,7 +4368,7 @@
         <v>0.26984128</v>
       </c>
       <c r="K25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L25" t="n">
         <v>69</v>
@@ -4380,13 +4380,13 @@
         <v>4.7647057</v>
       </c>
       <c r="O25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P25" t="n">
         <v>11</v>
       </c>
       <c r="Q25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R25" t="n">
         <v>1.3921568</v>
@@ -4408,43 +4408,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.20987654</v>
+        <v>0.2113402</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3027027</v>
+        <v>0.3063063</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J26" t="n">
-        <v>0.33333334</v>
+        <v>0.33505154</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L26" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M26" t="n">
         <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1666665</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
@@ -4456,16 +4456,16 @@
         <v>12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4666667</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
         <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>0.27868852</v>
+        <v>0.27522936</v>
       </c>
       <c r="U26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -4475,46 +4475,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.22093023</v>
+        <v>0.21182266</v>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2795699</v>
+        <v>0.27272728</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>0.30813953</v>
+        <v>0.30541873</v>
       </c>
       <c r="K27" t="n">
         <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M27" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="N27" t="n">
-        <v>3.7173913</v>
+        <v>3.3333333</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P27" t="n">
         <v>4</v>
@@ -4523,13 +4523,13 @@
         <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1521739</v>
+        <v>1.2037038</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>0.21764706</v>
+        <v>0.22</v>
       </c>
       <c r="U27" t="n">
         <v>11</v>
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.19642857</v>
+        <v>0.20175439</v>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>0.28286853</v>
+        <v>0.2777778</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2767857</v>
+        <v>0.27631578</v>
       </c>
       <c r="K28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L28" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M28" t="n">
+        <v>22</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15</v>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="n">
         <v>25</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.8032787</v>
-      </c>
-      <c r="O28" t="n">
-        <v>7</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>26</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.0819672</v>
+        <v>1.1333333</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>0.21145375</v>
+        <v>0.22123894</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.17777778</v>
+        <v>0.1878453</v>
       </c>
       <c r="C29" t="n">
         <v>30</v>
@@ -4621,52 +4621,52 @@
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>24</v>
       </c>
       <c r="H29" t="n">
-        <v>0.29166666</v>
+        <v>0.2962963</v>
       </c>
       <c r="I29" t="n">
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2611111</v>
+        <v>0.29281768</v>
       </c>
       <c r="K29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3333335</v>
+        <v>3.8333333</v>
       </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2777778</v>
+        <v>1.2037038</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T29" t="n">
-        <v>0.22058824</v>
+        <v>0.21890548</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -4679,13 +4679,13 @@
         <v>0.2244898</v>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" t="n">
         <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
@@ -4712,28 +4712,28 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.0408163</v>
+        <v>3.857143</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P30" t="n">
         <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.244898</v>
+        <v>1.2244898</v>
       </c>
       <c r="S30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T30" t="n">
-        <v>0.20224719</v>
+        <v>0.19662921</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -4746,25 +4746,25 @@
         <v>0.21463415</v>
       </c>
       <c r="C31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D31" t="n">
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
         <v>0.27433628</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
         <v>0.3512195</v>
@@ -4776,19 +4776,19 @@
         <v>46</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N31" t="n">
         <v>3.1666667</v>
       </c>
       <c r="O31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R31" t="n">
         <v>1.3888888</v>
@@ -4800,7 +4800,7 @@
         <v>0.25714287</v>
       </c>
       <c r="U31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,46 +546,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24584034</v>
+        <v>0.24586508</v>
       </c>
       <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="n">
+        <v>728</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>165</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.31762365</v>
+      </c>
+      <c r="I2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" t="n">
-        <v>717</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>162</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.31689787</v>
-      </c>
-      <c r="I2" t="n">
-        <v>15</v>
-      </c>
       <c r="J2" t="n">
-        <v>0.40157038</v>
+        <v>0.4028991</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1030345</v>
+        <v>4.102384</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
         <v>183</v>
@@ -594,16 +594,16 @@
         <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2738179</v>
+        <v>1.2741935</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2480476</v>
+        <v>0.24833703</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2459655</v>
+        <v>0.24594395</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -628,46 +628,46 @@
         <v>194</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31799233</v>
+        <v>0.31803116</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40511966</v>
+        <v>0.40449852</v>
       </c>
       <c r="K3" t="n">
         <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="M3" t="n">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.439772</v>
+        <v>5.436969</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5032074</v>
+        <v>1.5014164</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.271452</v>
+        <v>0.2708824</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2479062</v>
+        <v>0.24680614</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>731</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>201</v>
@@ -698,43 +698,43 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31114107</v>
+        <v>0.3099631</v>
       </c>
       <c r="I4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4109436</v>
+        <v>0.40899834</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.624204</v>
+        <v>3.6228008</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2420382</v>
+        <v>1.244898</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23321354</v>
+        <v>0.23377845</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23286119</v>
+        <v>0.23394752</v>
       </c>
       <c r="C5" t="n">
         <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31340033</v>
+        <v>0.31440833</v>
       </c>
       <c r="I5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.39624047</v>
+      </c>
+      <c r="K5" t="n">
         <v>21</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.39395657</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24</v>
-      </c>
       <c r="L5" t="n">
-        <v>1489</v>
+        <v>1518</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.083607</v>
+        <v>4.079137</v>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
         <v>169</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3372475</v>
+        <v>1.3374332</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25221077</v>
+        <v>0.2522752</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2456338</v>
+        <v>0.24535662</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E6" t="n">
         <v>22</v>
@@ -829,28 +829,28 @@
         <v>162</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3194305</v>
+        <v>0.31947663</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>0.39906102</v>
+        <v>0.39821693</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>1305</v>
+        <v>1319</v>
       </c>
       <c r="M6" t="n">
         <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5477707</v>
+        <v>3.5220125</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -862,13 +862,13 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321302</v>
+        <v>1.2299092</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24064673</v>
+        <v>0.24034175</v>
       </c>
       <c r="U6" t="n">
         <v>14</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25105292</v>
+        <v>0.25063336</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -896,31 +896,31 @@
         <v>218</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33914018</v>
+        <v>0.33849558</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.42940852</v>
+        <v>0.42743394</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="M7" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.1307373</v>
+      </c>
+      <c r="O7" t="n">
         <v>16</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.14557</v>
-      </c>
-      <c r="O7" t="n">
-        <v>17</v>
       </c>
       <c r="P7" t="n">
         <v>230</v>
@@ -929,13 +929,13 @@
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2609001</v>
+        <v>1.2621697</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24324325</v>
+        <v>0.2429941</v>
       </c>
       <c r="U7" t="n">
         <v>17</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23564728</v>
+        <v>0.23614997</v>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32066116</v>
+        <v>0.32056552</v>
       </c>
       <c r="I8" t="n">
         <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40375236</v>
+        <v>0.40440217</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1318088</v>
+        <v>4.111996</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3157275</v>
+        <v>1.3116214</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24315196</v>
+        <v>0.24249208</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2284091</v>
+        <v>0.22903347</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3051191</v>
+        <v>0.30530378</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39469698</v>
+        <v>0.3948853</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>1514</v>
+        <v>1525</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8504143</v>
+        <v>4.8547893</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
@@ -1060,16 +1060,16 @@
         <v>212</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4471005</v>
+        <v>1.4495175</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25498524</v>
+        <v>0.2552762</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23745756</v>
+        <v>0.23758666</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G10" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31436723</v>
+        <v>0.3154653</v>
       </c>
       <c r="I10" t="n">
         <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37514144</v>
+        <v>0.37624133</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.729634</v>
+        <v>3.763022</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.257379</v>
+        <v>1.2620835</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23611373</v>
+        <v>0.2369553</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25424355</v>
+        <v>0.25353146</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32285288</v>
+        <v>0.3220869</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41697416</v>
+        <v>0.4162539</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1381</v>
+        <v>1392</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5933175</v>
+        <v>5.599905</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5286397</v>
+        <v>1.5270528</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28892082</v>
+        <v>0.28910714</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24104477</v>
+        <v>0.24128984</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="E12" t="n">
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31965587</v>
+        <v>0.32019058</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.40048185</v>
       </c>
       <c r="K12" t="n">
         <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="M12" t="n">
         <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6460555</v>
+        <v>3.667373</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2196162</v>
+        <v>1.2196327</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2315449</v>
+        <v>0.2314237</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24060573</v>
+        <v>0.24019334</v>
       </c>
       <c r="C13" t="n">
         <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31346282</v>
+        <v>0.31336328</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4137222</v>
+        <v>0.41364565</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.503189</v>
+        <v>4.509514</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3451453</v>
+        <v>1.3460183</v>
       </c>
       <c r="S13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23784295</v>
+        <v>0.23787138</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24611059</v>
+        <v>0.2468814</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G14" t="n">
         <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3152046</v>
+        <v>0.31600067</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39943767</v>
+        <v>0.40104264</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7340174</v>
+        <v>4.774117</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3998091</v>
+        <v>1.4064944</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26028422</v>
+        <v>0.2602638</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23404256</v>
+        <v>0.2342932</v>
       </c>
       <c r="C15" t="n">
         <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E15" t="n">
         <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31004882</v>
+        <v>0.3101488</v>
       </c>
       <c r="I15" t="n">
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3688571</v>
+        <v>0.37023187</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.258776</v>
+        <v>4.2634926</v>
       </c>
       <c r="O15" t="n">
         <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3462998</v>
+        <v>1.3455102</v>
       </c>
       <c r="S15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23901151</v>
+        <v>0.23880038</v>
       </c>
       <c r="U15" t="n">
         <v>12</v>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25720164</v>
+        <v>0.25697285</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33898026</v>
+        <v>0.338459</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42461655</v>
+        <v>0.42450726</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5931802</v>
+        <v>3.570353</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
@@ -1529,16 +1529,16 @@
         <v>172</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1501303</v>
+        <v>1.1449412</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21860643</v>
+        <v>0.21801218</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2484951</v>
+        <v>0.2489712</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32616308</v>
+        <v>0.32664567</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39879608</v>
+        <v>0.39992517</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1039486</v>
+        <v>4.0777593</v>
       </c>
       <c r="O17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
         <v>168</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2873453</v>
+        <v>1.2805483</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23633957</v>
+        <v>0.23528305</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2575393</v>
+        <v>0.25813568</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1633,46 +1633,46 @@
         <v>152</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33978844</v>
+        <v>0.34044617</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40203515</v>
+        <v>0.40227982</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="M18" t="n">
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5184317</v>
+        <v>3.5214653</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.186194</v>
+        <v>1.1836212</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22262289</v>
+        <v>0.22236891</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24362078</v>
+        <v>0.24407846</v>
       </c>
       <c r="C19" t="n">
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3158421</v>
+        <v>0.3161728</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40193704</v>
+        <v>0.40247965</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>1275</v>
+        <v>1284</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5681496</v>
+        <v>4.5518456</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
@@ -1730,19 +1730,19 @@
         <v>181</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3629911</v>
+        <v>1.3599812</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24861163</v>
+        <v>0.24829744</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23845008</v>
+        <v>0.2386595</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.309097</v>
+        <v>0.30925432</v>
       </c>
       <c r="I20" t="n">
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39344263</v>
+        <v>0.39418626</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>1332</v>
+        <v>1344</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1357646</v>
+        <v>4.1567616</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q20" t="n">
         <v>17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2896471</v>
+        <v>1.293636</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2393736</v>
+        <v>0.23999259</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23423253</v>
+        <v>0.23452158</v>
       </c>
       <c r="C21" t="n">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
@@ -1837,43 +1837,43 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31076506</v>
+        <v>0.3109328</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4101444</v>
+        <v>0.40919325</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1457</v>
+        <v>1480</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1995316</v>
+        <v>3.2407494</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1648712</v>
+        <v>1.173913</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22310455</v>
+        <v>0.2243339</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24022557</v>
+        <v>0.23962617</v>
       </c>
       <c r="C22" t="n">
         <v>22</v>
@@ -1895,55 +1895,55 @@
         <v>705</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
         <v>180</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31171232</v>
+        <v>0.3111631</v>
       </c>
       <c r="I22" t="n">
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39511278</v>
+        <v>0.39364487</v>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L22" t="n">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>4.011101</v>
+        <v>3.9983573</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q22" t="n">
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2838923</v>
+        <v>1.2813894</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24722221</v>
+        <v>0.24682496</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25339448</v>
+        <v>0.25314608</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G23" t="n">
         <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33050433</v>
+        <v>0.33041364</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4040367</v>
+        <v>0.40361115</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>1473</v>
+        <v>1487</v>
       </c>
       <c r="M23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1470175</v>
+        <v>4.167912</v>
       </c>
       <c r="O23" t="n">
         <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2956787</v>
+        <v>1.300327</v>
       </c>
       <c r="S23" t="n">
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23683228</v>
+        <v>0.23710576</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24270004</v>
+        <v>0.24302939</v>
       </c>
       <c r="C24" t="n">
         <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E24" t="n">
         <v>19</v>
@@ -2035,46 +2035,46 @@
         <v>180</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31774437</v>
+        <v>0.31783855</v>
       </c>
       <c r="I24" t="n">
         <v>13</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3970421</v>
+        <v>0.39657122</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>3.927389</v>
+        <v>3.9722679</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q24" t="n">
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.289262</v>
+        <v>1.2923619</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24135977</v>
+        <v>0.24141167</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2461424</v>
+        <v>0.2454226</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
         <v>665</v>
@@ -2105,46 +2105,46 @@
         <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30810812</v>
+        <v>0.30716208</v>
       </c>
       <c r="I25" t="n">
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4026771</v>
+        <v>0.40114665</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>1302</v>
+        <v>1316</v>
       </c>
       <c r="M25" t="n">
         <v>12</v>
       </c>
       <c r="N25" t="n">
-        <v>4.358773</v>
+        <v>4.343728</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3601997</v>
+        <v>1.3571935</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24844837</v>
+        <v>0.2482707</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23148324</v>
+        <v>0.23131941</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G26" t="n">
         <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31216398</v>
+        <v>0.31213486</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37810192</v>
+        <v>0.3779409</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1373</v>
+        <v>1385</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2071257</v>
+        <v>4.224923</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q26" t="n">
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2669834</v>
+        <v>1.2681142</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2515383</v>
+        <v>0.25166667</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,43 +2221,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24100652</v>
+        <v>0.24064468</v>
       </c>
       <c r="C27" t="n">
         <v>20</v>
       </c>
       <c r="D27" t="n">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31433794</v>
+        <v>0.31372872</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>0.37931034</v>
+        <v>0.37977028</v>
       </c>
       <c r="K27" t="n">
         <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>1271</v>
+        <v>1283</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>4.244126</v>
+        <v>4.2581778</v>
       </c>
       <c r="O27" t="n">
         <v>20</v>
@@ -2266,19 +2266,19 @@
         <v>156</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.350564</v>
+        <v>1.3549066</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25292262</v>
+        <v>0.2535497</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -2288,43 +2288,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25768942</v>
+        <v>0.25722274</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32648593</v>
+        <v>0.3259123</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40022504</v>
+        <v>0.39944082</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L28" t="n">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7282991</v>
+        <v>3.7047687</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
@@ -2336,13 +2336,13 @@
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1354976</v>
+        <v>1.1332399</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22837761</v>
+        <v>0.22784336</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24154314</v>
+        <v>0.24126205</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>178</v>
@@ -2373,46 +2373,46 @@
         <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3169408</v>
+        <v>0.31687173</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39509693</v>
+        <v>0.39410543</v>
       </c>
       <c r="K29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L29" t="n">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2794647</v>
+        <v>4.31923</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q29" t="n">
         <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2988286</v>
+        <v>1.3014023</v>
       </c>
       <c r="S29" t="n">
         <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24696885</v>
+        <v>0.24740548</v>
       </c>
       <c r="U29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24775952</v>
+        <v>0.24809797</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E30" t="n">
         <v>30</v>
@@ -2440,43 +2440,43 @@
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30998307</v>
+        <v>0.3107563</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38162807</v>
+        <v>0.3820746</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9155428</v>
+        <v>3.922426</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q30" t="n">
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2952448</v>
+        <v>1.2961918</v>
       </c>
       <c r="S30" t="n">
         <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23465909</v>
+        <v>0.2352388</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2489,64 +2489,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24621353</v>
+        <v>0.24678664</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32102227</v>
+        <v>0.32164508</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42316216</v>
+        <v>0.42343003</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6531916</v>
+        <v>4.6617336</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3893617</v>
+        <v>1.389711</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25310358</v>
+        <v>0.25322282</v>
       </c>
       <c r="U31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3004695</v>
+        <v>0.30805686</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.549763</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>40</v>
+      </c>
+      <c r="M2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3448276</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5023474</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>47</v>
-      </c>
-      <c r="M2" t="n">
-        <v>9</v>
-      </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.8333333</v>
       </c>
       <c r="O2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1851852</v>
+        <v>1.1481482</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.23786408</v>
+        <v>0.24878049</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2867,46 +2867,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.28921568</v>
+        <v>0.30476192</v>
       </c>
       <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="F3" t="n">
-        <v>8</v>
-      </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.35267857</v>
+        <v>0.3624454</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.49509802</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>6.1764708</v>
+        <v>6.0576925</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
         <v>13</v>
@@ -2915,16 +2915,16 @@
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6078432</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.30952382</v>
+        <v>0.28846154</v>
       </c>
       <c r="U3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.26086956</v>
+        <v>0.2244898</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3231441</v>
+        <v>0.29032257</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4299517</v>
+        <v>0.3469388</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2727273</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0181818</v>
+        <v>1.1666666</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22058824</v>
+        <v>0.24752475</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3001,61 +3001,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1891892</v>
+        <v>0.21076234</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.39013454</v>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>66</v>
+      </c>
+      <c r="M5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.612903</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.0967742</v>
+      </c>
+      <c r="S5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2657005</v>
-      </c>
-      <c r="I5" t="n">
-        <v>28</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.33513513</v>
-      </c>
-      <c r="K5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L5" t="n">
-        <v>50</v>
-      </c>
-      <c r="M5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.6181817</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1090909</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
       <c r="T5" t="n">
-        <v>0.21025641</v>
+        <v>0.21621622</v>
       </c>
       <c r="U5" t="n">
         <v>9</v>
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.22727273</v>
+        <v>0.22171946</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H6" t="n">
-        <v>0.28169015</v>
+        <v>0.2892562</v>
       </c>
       <c r="I6" t="n">
         <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.34343433</v>
+        <v>0.32579187</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>2.050633</v>
+        <v>1.8972973</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0822785</v>
+        <v>1.0054054</v>
       </c>
       <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.20704846</v>
+      </c>
+      <c r="U6" t="n">
         <v>7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.19587629</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.23831776</v>
+        <v>0.22950819</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32231405</v>
+        <v>0.30769232</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>0.37850466</v>
+        <v>0.352459</v>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0535715</v>
+        <v>2.53125</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0535715</v>
+        <v>1.0625</v>
       </c>
       <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2034632</v>
+      </c>
+      <c r="U7" t="n">
         <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.20895523</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2669903</v>
+        <v>0.28712872</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36885247</v>
+        <v>0.37130803</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4368932</v>
+        <v>0.46039605</v>
       </c>
       <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>56</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2264152</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="L8" t="n">
-        <v>60</v>
-      </c>
-      <c r="M8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.924528</v>
-      </c>
-      <c r="O8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.5283018</v>
+        <v>1.245283</v>
       </c>
       <c r="S8" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2966507</v>
+        <v>0.25</v>
       </c>
       <c r="U8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.19689119</v>
+        <v>0.20792079</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25943395</v>
+        <v>0.25462964</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9" t="n">
-        <v>0.35751295</v>
+        <v>0.37128714</v>
       </c>
       <c r="K9" t="n">
         <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.55625</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q9" t="n">
         <v>19</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.3067484</v>
-      </c>
-      <c r="O9" t="n">
-        <v>20</v>
-      </c>
-      <c r="P9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>22</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.3803681</v>
+        <v>1.44375</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26794258</v>
+        <v>0.2753623</v>
       </c>
       <c r="U9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.26237625</v>
+        <v>0.25365853</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32126698</v>
+        <v>0.33189654</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3910891</v>
+        <v>0.39512196</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.0566037</v>
+      </c>
+      <c r="O10" t="n">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.037736</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1132076</v>
+        <v>1.3207548</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>0.22164948</v>
+        <v>0.26108375</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -3403,43 +3403,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.26291078</v>
+        <v>0.22277227</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
         <v>23</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2706422</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.37623763</v>
+      </c>
+      <c r="K11" t="n">
         <v>15</v>
       </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="L11" t="n">
+        <v>53</v>
+      </c>
+      <c r="M11" t="n">
         <v>16</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.3026316</v>
-      </c>
-      <c r="I11" t="n">
-        <v>17</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4084507</v>
-      </c>
-      <c r="K11" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" t="n">
-        <v>51</v>
-      </c>
-      <c r="M11" t="n">
-        <v>14</v>
-      </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.264151</v>
       </c>
       <c r="O11" t="n">
         <v>26</v>
@@ -3448,19 +3448,19 @@
         <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3703704</v>
+        <v>1.3773584</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28301886</v>
+        <v>0.29186603</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.27941176</v>
+        <v>0.255</v>
       </c>
       <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H12" t="n">
-        <v>0.37916666</v>
+        <v>0.3628692</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4509804</v>
+        <v>0.41</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8076923</v>
+        <v>4.673077</v>
       </c>
       <c r="O12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P12" t="n">
         <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
         <v>1.1346154</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>0.20418848</v>
+        <v>0.20634921</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25581396</v>
+        <v>0.25821596</v>
       </c>
       <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.31914893</v>
+      </c>
+      <c r="I13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
+        <v>0.5023474</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0.30603448</v>
-      </c>
-      <c r="I13" t="n">
-        <v>16</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.46976745</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
       <c r="L13" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M13" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3067484</v>
+        <v>4.21875</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q13" t="n">
+        <v>13</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4250001</v>
+      </c>
+      <c r="S13" t="n">
         <v>22</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.4171779</v>
-      </c>
-      <c r="S13" t="n">
-        <v>24</v>
-      </c>
       <c r="T13" t="n">
-        <v>0.25120774</v>
+        <v>0.24378109</v>
       </c>
       <c r="U13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.29383886</v>
+        <v>0.31308413</v>
       </c>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>34</v>
+      </c>
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.33333334</v>
+        <v>0.3577586</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.45023698</v>
+        <v>0.47663552</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N14" t="n">
-        <v>7.5882354</v>
+        <v>7.9615383</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.745098</v>
+        <v>1.7884616</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.30985916</v>
+        <v>0.2843602</v>
       </c>
       <c r="U14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23671497</v>
+        <v>0.25821596</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>0.34166667</v>
+        <v>0.35772356</v>
       </c>
       <c r="I15" t="n">
         <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.33333334</v>
+        <v>0.40375587</v>
       </c>
       <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>61</v>
+      </c>
+      <c r="M15" t="n">
         <v>23</v>
       </c>
-      <c r="L15" t="n">
-        <v>62</v>
-      </c>
-      <c r="M15" t="n">
-        <v>25</v>
-      </c>
       <c r="N15" t="n">
-        <v>5.8333335</v>
+        <v>6.1666665</v>
       </c>
       <c r="O15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P15" t="n">
         <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5185186</v>
+        <v>1.5555556</v>
       </c>
       <c r="S15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T15" t="n">
-        <v>0.30454546</v>
+        <v>0.29545453</v>
       </c>
       <c r="U15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -3738,61 +3738,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3043478</v>
+        <v>0.28780487</v>
       </c>
       <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.34666666</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.44390243</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>46</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>31</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.37229437</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.5072464</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>45</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.3333333</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.8888889</v>
+        <v>0.8148148</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1761658</v>
+        <v>0.16842106</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.23584905</v>
+        <v>0.24271844</v>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3304721</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.37378642</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.9277108</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" t="n">
         <v>6</v>
       </c>
-      <c r="G17" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.31355932</v>
-      </c>
-      <c r="I17" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.3490566</v>
-      </c>
-      <c r="K17" t="n">
-        <v>19</v>
-      </c>
-      <c r="L17" t="n">
-        <v>54</v>
-      </c>
-      <c r="M17" t="n">
-        <v>15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.3067484</v>
-      </c>
-      <c r="O17" t="n">
-        <v>20</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
+        <v>13</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.1385542</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.20975609</v>
+      </c>
+      <c r="U17" t="n">
         <v>8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3987731</v>
-      </c>
-      <c r="S17" t="n">
-        <v>23</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.254717</v>
-      </c>
-      <c r="U17" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.21319798</v>
+        <v>0.22916667</v>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
         <v>23</v>
       </c>
-      <c r="E18" t="n">
-        <v>15</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>21</v>
-      </c>
       <c r="H18" t="n">
-        <v>0.29090908</v>
+        <v>0.30555555</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3248731</v>
+        <v>0.33854166</v>
       </c>
       <c r="K18" t="n">
         <v>24</v>
       </c>
       <c r="L18" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>1.8679246</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9433962</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
+        <v>0.16842106</v>
+      </c>
+      <c r="U18" t="n">
         <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.074074</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.1928934</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3939,61 +3939,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24413146</v>
+        <v>0.25233644</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.27876106</v>
+        <v>0.29385966</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3802817</v>
+        <v>0.40186915</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.304878</v>
+        <v>2.6341465</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0792682</v>
+        <v>1.097561</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>0.19387755</v>
+        <v>0.20408164</v>
       </c>
       <c r="U19" t="n">
         <v>4</v>
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.26794258</v>
+        <v>0.2524272</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="n">
         <v>7</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
+        <v>0.32618025</v>
+      </c>
+      <c r="I20" t="n">
         <v>10</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.3390558</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
+        <v>0.41747573</v>
+      </c>
+      <c r="K20" t="n">
         <v>7</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.41626793</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>48</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.1538463</v>
+      </c>
+      <c r="O20" t="n">
+        <v>17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>16</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.21925133</v>
+      </c>
+      <c r="U20" t="n">
         <v>11</v>
-      </c>
-      <c r="L20" t="n">
-        <v>44</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.3962264</v>
-      </c>
-      <c r="O20" t="n">
-        <v>13</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.0566038</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.19148937</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.21681416</v>
+        <v>0.22568093</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2868526</v>
+        <v>0.28873238</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.43362832</v>
+        <v>0.40466926</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>3.375</v>
+        <v>4.350711</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2228261</v>
+        <v>1.436019</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T21" t="n">
-        <v>0.23275863</v>
+        <v>0.25724638</v>
       </c>
       <c r="U21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.20304568</v>
+        <v>0.19587629</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H22" t="n">
-        <v>0.29646018</v>
+        <v>0.29464287</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3147208</v>
+        <v>0.26804122</v>
       </c>
       <c r="K22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>5.3653846</v>
+        <v>4.5849056</v>
       </c>
       <c r="O22" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
         <v>7</v>
       </c>
       <c r="Q22" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2830188</v>
+      </c>
+      <c r="S22" t="n">
+        <v>17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.24509804</v>
+      </c>
+      <c r="U22" t="n">
         <v>16</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4423077</v>
-      </c>
-      <c r="S22" t="n">
-        <v>25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.2753623</v>
-      </c>
-      <c r="U22" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25906736</v>
+        <v>0.22222222</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33333334</v>
+        <v>0.3018868</v>
       </c>
       <c r="I23" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3968254</v>
+      </c>
+      <c r="K23" t="n">
+        <v>12</v>
+      </c>
+      <c r="L23" t="n">
+        <v>51</v>
+      </c>
+      <c r="M23" t="n">
+        <v>14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.5660377</v>
+      </c>
+      <c r="O23" t="n">
+        <v>13</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
         <v>8</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.4507772</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>44</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.1666667</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
+        <v>1.245283</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.23762377</v>
+      </c>
+      <c r="U23" t="n">
         <v>12</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.0925926</v>
-      </c>
-      <c r="S23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.23115578</v>
-      </c>
-      <c r="U23" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.25365853</v>
+        <v>0.24509804</v>
       </c>
       <c r="C24" t="n">
         <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.30222222</v>
+      </c>
+      <c r="I24" t="n">
+        <v>16</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.36764705</v>
+      </c>
+      <c r="K24" t="n">
+        <v>18</v>
+      </c>
+      <c r="L24" t="n">
+        <v>55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" t="n">
         <v>5</v>
       </c>
-      <c r="F24" t="n">
+      <c r="O24" t="n">
+        <v>25</v>
+      </c>
+      <c r="P24" t="n">
         <v>8</v>
       </c>
-      <c r="G24" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.31578946</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="Q24" t="n">
+        <v>19</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.462963</v>
+      </c>
+      <c r="S24" t="n">
+        <v>26</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.24120604</v>
+      </c>
+      <c r="U24" t="n">
         <v>13</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.40487805</v>
-      </c>
-      <c r="K24" t="n">
-        <v>13</v>
-      </c>
-      <c r="L24" t="n">
-        <v>58</v>
-      </c>
-      <c r="M24" t="n">
-        <v>21</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>14</v>
-      </c>
-      <c r="P24" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>15</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3703704</v>
-      </c>
-      <c r="S24" t="n">
-        <v>18</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.24630542</v>
-      </c>
-      <c r="U24" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -4341,31 +4341,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1904762</v>
+        <v>0.1827957</v>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>27</v>
       </c>
       <c r="H25" t="n">
-        <v>0.26442307</v>
+        <v>0.25123152</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>0.26984128</v>
+        <v>0.24731183</v>
       </c>
       <c r="K25" t="n">
         <v>30</v>
@@ -4374,31 +4374,31 @@
         <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7647057</v>
+        <v>3.6346154</v>
       </c>
       <c r="O25" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3921568</v>
+        <v>1.2115384</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>0.27586207</v>
+        <v>0.25870648</v>
       </c>
       <c r="U25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2113402</v>
+        <v>0.20103092</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
         <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3063063</v>
+        <v>0.30493274</v>
       </c>
       <c r="I26" t="n">
         <v>15</v>
       </c>
       <c r="J26" t="n">
-        <v>0.33505154</v>
+        <v>0.29896906</v>
       </c>
       <c r="K26" t="n">
+        <v>26</v>
+      </c>
+      <c r="L26" t="n">
+        <v>47</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.6666665</v>
+      </c>
+      <c r="O26" t="n">
+        <v>23</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4444444</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.25821596</v>
+      </c>
+      <c r="U26" t="n">
         <v>22</v>
-      </c>
-      <c r="L26" t="n">
-        <v>44</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.1666665</v>
-      </c>
-      <c r="O26" t="n">
-        <v>19</v>
-      </c>
-      <c r="P26" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>12</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>26</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.27522936</v>
-      </c>
-      <c r="U26" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.21182266</v>
+        <v>0.20689656</v>
       </c>
       <c r="C27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="n">
         <v>23</v>
       </c>
-      <c r="D27" t="n">
-        <v>17</v>
-      </c>
-      <c r="E27" t="n">
-        <v>26</v>
-      </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27272728</v>
+        <v>0.2648402</v>
       </c>
       <c r="I27" t="n">
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>0.30541873</v>
+        <v>0.33990148</v>
       </c>
       <c r="K27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L27" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3333333</v>
+        <v>3.0566037</v>
       </c>
       <c r="O27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2037038</v>
+        <v>1.3018868</v>
       </c>
       <c r="S27" t="n">
+        <v>18</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.24378109</v>
+      </c>
+      <c r="U27" t="n">
         <v>14</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="U27" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.20175439</v>
+        <v>0.20524018</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -4551,55 +4551,55 @@
         <v>21</v>
       </c>
       <c r="E28" t="n">
+        <v>21</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
         <v>23</v>
       </c>
-      <c r="F28" t="n">
+      <c r="H28" t="n">
+        <v>0.2601626</v>
+      </c>
+      <c r="I28" t="n">
+        <v>28</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.279476</v>
+      </c>
+      <c r="K28" t="n">
+        <v>27</v>
+      </c>
+      <c r="L28" t="n">
+        <v>62</v>
+      </c>
+      <c r="M28" t="n">
+        <v>24</v>
+      </c>
+      <c r="N28" t="n">
         <v>3</v>
       </c>
-      <c r="G28" t="n">
-        <v>27</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.2777778</v>
-      </c>
-      <c r="I28" t="n">
-        <v>25</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.27631578</v>
-      </c>
-      <c r="K28" t="n">
-        <v>29</v>
-      </c>
-      <c r="L28" t="n">
-        <v>59</v>
-      </c>
-      <c r="M28" t="n">
-        <v>22</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1333333</v>
+        <v>1.0666667</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22123894</v>
+        <v>0.20454545</v>
       </c>
       <c r="U28" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1878453</v>
+        <v>0.18232045</v>
       </c>
       <c r="C29" t="n">
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2962963</v>
+        <v>0.27751195</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>0.29281768</v>
+        <v>0.2762431</v>
       </c>
       <c r="K29" t="n">
         <v>28</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
         <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8333333</v>
+        <v>5.4339623</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2037038</v>
+        <v>1.3584906</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T29" t="n">
-        <v>0.21890548</v>
+        <v>0.24509804</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2244898</v>
+        <v>0.24873096</v>
       </c>
       <c r="C30" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>0.28703704</v>
+        <v>0.3243243</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3010204</v>
+        <v>0.34517765</v>
       </c>
       <c r="K30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.857143</v>
+        <v>4.32</v>
       </c>
       <c r="O30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2244898</v>
+        <v>1.12</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>0.19662921</v>
+        <v>0.21621622</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.21463415</v>
+        <v>0.23529412</v>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27433628</v>
+        <v>0.29017857</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3512195</v>
+        <v>0.35784313</v>
       </c>
       <c r="K31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1666667</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3888888</v>
+        <v>1.4814814</v>
       </c>
       <c r="S31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25714287</v>
+        <v>0.26666668</v>
       </c>
       <c r="U31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24586508</v>
+        <v>0.24607717</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G2" t="n">
         <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31762365</v>
+        <v>0.31817433</v>
       </c>
       <c r="I2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4028991</v>
+        <v>0.40280598</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.102384</v>
+        <v>4.1422596</v>
       </c>
       <c r="O2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q2" t="n">
         <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2741935</v>
+        <v>1.2789401</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24833703</v>
+        <v>0.24903652</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24594395</v>
+        <v>0.24560118</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -631,43 +631,43 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31803116</v>
+        <v>0.31756756</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40449852</v>
+        <v>0.4032258</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="M3" t="n">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.436969</v>
+        <v>5.48487</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5014164</v>
+        <v>1.5059817</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2708824</v>
+        <v>0.27176258</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24680614</v>
+        <v>0.2469658</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3099631</v>
+        <v>0.31001166</v>
       </c>
       <c r="I4" t="n">
         <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40899834</v>
+        <v>0.40989333</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6228008</v>
+        <v>3.6188812</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
       </c>
       <c r="R4" t="n">
-        <v>1.244898</v>
+        <v>1.2433566</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23377845</v>
+        <v>0.23378807</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -756,13 +756,13 @@
         <v>718</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>199</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
         <v>0.31440833</v>
@@ -786,13 +786,13 @@
         <v>4.079137</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
         <v>169</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
         <v>1.3374332</v>
@@ -847,7 +847,7 @@
         <v>1319</v>
       </c>
       <c r="M6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
         <v>3.5220125</v>
@@ -914,13 +914,13 @@
         <v>1338</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
         <v>4.1307373</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P7" t="n">
         <v>230</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23614997</v>
+        <v>0.23605707</v>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32056552</v>
+        <v>0.32054213</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40440217</v>
+        <v>0.40503985</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.111996</v>
+        <v>4.136438</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3116214</v>
+        <v>1.3124564</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24249208</v>
+        <v>0.24286772</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22903347</v>
+        <v>0.22874229</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30530378</v>
+        <v>0.30531934</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3948853</v>
+        <v>0.39469257</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>1525</v>
+        <v>1537</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8547893</v>
+        <v>4.830449</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
@@ -1063,13 +1063,13 @@
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4495175</v>
+        <v>1.4459774</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2552762</v>
+        <v>0.25474453</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23758666</v>
+        <v>0.23851162</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G10" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3154653</v>
+        <v>0.3161461</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>0.37624133</v>
+        <v>0.38009304</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.763022</v>
+        <v>3.770809</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1130,13 +1130,13 @@
         <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2620835</v>
+        <v>1.2618326</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2369553</v>
+        <v>0.2372724</v>
       </c>
       <c r="U10" t="n">
         <v>9</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25353146</v>
+        <v>0.25382653</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3220869</v>
+        <v>0.32215863</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4162539</v>
+        <v>0.41745627</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="M11" t="n">
         <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.599905</v>
+        <v>5.596086</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5270528</v>
+        <v>1.5265268</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28910714</v>
+        <v>0.28867993</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24128984</v>
+        <v>0.24157614</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E12" t="n">
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32019058</v>
+        <v>0.3205484</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40048185</v>
+        <v>0.400847</v>
       </c>
       <c r="K12" t="n">
         <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>1386</v>
+        <v>1398</v>
       </c>
       <c r="M12" t="n">
         <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.667373</v>
+        <v>3.663158</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2196327</v>
+        <v>1.2189474</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2314237</v>
+        <v>0.2316363</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24019334</v>
+        <v>0.24132842</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31336328</v>
+        <v>0.31428573</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41364565</v>
+        <v>0.41678968</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>4.509514</v>
+        <v>4.4810925</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1328,16 +1328,16 @@
         <v>204</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3460183</v>
+        <v>1.3431373</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23787138</v>
+        <v>0.23757009</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2468814</v>
+        <v>0.24713281</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
         <v>168</v>
@@ -1368,43 +1368,43 @@
         <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31600067</v>
+        <v>0.31605184</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40104264</v>
+        <v>0.40140584</v>
       </c>
       <c r="K14" t="n">
         <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.774117</v>
+        <v>4.7882714</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4064944</v>
+        <v>1.4102684</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2602638</v>
+        <v>0.26102194</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2342932</v>
+        <v>0.23407023</v>
       </c>
       <c r="C15" t="n">
         <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E15" t="n">
         <v>29</v>
@@ -1435,46 +1435,46 @@
         <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3101488</v>
+        <v>0.3100814</v>
       </c>
       <c r="I15" t="n">
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37023187</v>
+        <v>0.369125</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2634926</v>
+        <v>4.2901335</v>
       </c>
       <c r="O15" t="n">
         <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3455102</v>
+        <v>1.3505976</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23880038</v>
+        <v>0.239434</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25697285</v>
+        <v>0.25692648</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G16" t="n">
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.338459</v>
+        <v>0.338264</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42450726</v>
+        <v>0.42463982</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1250</v>
+        <v>1261</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.570353</v>
+        <v>3.5667524</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
@@ -1532,13 +1532,13 @@
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1449412</v>
+        <v>1.1447276</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21801218</v>
+        <v>0.21835384</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2489712</v>
+        <v>0.24888475</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32664567</v>
+        <v>0.3264667</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39992517</v>
+        <v>0.39981413</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0777593</v>
+        <v>4.096289</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2805483</v>
+        <v>1.2815876</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23528305</v>
+        <v>0.23552485</v>
       </c>
       <c r="U17" t="n">
         <v>8</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25813568</v>
+        <v>0.2581825</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34044617</v>
+        <v>0.3406205</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40227982</v>
+        <v>0.402633</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>1366</v>
+        <v>1377</v>
       </c>
       <c r="M18" t="n">
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5214653</v>
+        <v>3.5119407</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1836212</v>
+        <v>1.1789938</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22236891</v>
+        <v>0.22168042</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24407846</v>
+        <v>0.24406841</v>
       </c>
       <c r="C19" t="n">
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>185</v>
@@ -1703,43 +1703,43 @@
         <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3161728</v>
+        <v>0.31599736</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40247965</v>
+        <v>0.40261173</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5518456</v>
+        <v>4.5609813</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3599812</v>
+        <v>1.361916</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24829744</v>
+        <v>0.248949</v>
       </c>
       <c r="U19" t="n">
         <v>21</v>
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2386595</v>
+        <v>0.2387346</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30925432</v>
+        <v>0.30947265</v>
       </c>
       <c r="I20" t="n">
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39418626</v>
+        <v>0.39507082</v>
       </c>
       <c r="K20" t="n">
         <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1567616</v>
+        <v>4.136945</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
         <v>182</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.293636</v>
+        <v>1.288305</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23999259</v>
+        <v>0.23921858</v>
       </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -1834,7 +1834,7 @@
         <v>223</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0.3109328</v>
@@ -1846,13 +1846,13 @@
         <v>0.40919325</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
         <v>1480</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>3.2407494</v>
@@ -1864,7 +1864,7 @@
         <v>165</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
         <v>1.173913</v>
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23962617</v>
+        <v>0.23941308</v>
       </c>
       <c r="C22" t="n">
         <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" t="n">
         <v>180</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3111631</v>
+        <v>0.31114063</v>
       </c>
       <c r="I22" t="n">
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39364487</v>
+        <v>0.39301634</v>
       </c>
       <c r="K22" t="n">
         <v>25</v>
       </c>
       <c r="L22" t="n">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9983573</v>
+        <v>4.048741</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2813894</v>
+        <v>1.2887126</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24682496</v>
+        <v>0.24794595</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25314608</v>
+        <v>0.25321734</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33041364</v>
+        <v>0.3301613</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40361115</v>
+        <v>0.40438643</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
-        <v>1487</v>
+        <v>1495</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.167912</v>
+        <v>4.167827</v>
       </c>
       <c r="O23" t="n">
         <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.300327</v>
+        <v>1.301532</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23710576</v>
+        <v>0.23741935</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24302939</v>
+        <v>0.24377923</v>
       </c>
       <c r="C24" t="n">
         <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31783855</v>
+        <v>0.31861356</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>0.39657122</v>
+        <v>0.3981291</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9722679</v>
+        <v>3.9850538</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q24" t="n">
         <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2923619</v>
+        <v>1.2954227</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24141167</v>
+        <v>0.2416558</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2454226</v>
+        <v>0.24558823</v>
       </c>
       <c r="C25" t="n">
         <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>178</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30716208</v>
+        <v>0.3069853</v>
       </c>
       <c r="I25" t="n">
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.40114665</v>
+        <v>0.4014706</v>
       </c>
       <c r="K25" t="n">
         <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N25" t="n">
-        <v>4.343728</v>
+        <v>4.3415494</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q25" t="n">
         <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3571935</v>
+        <v>1.3570423</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2482707</v>
+        <v>0.24828227</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23131941</v>
+        <v>0.23200598</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G26" t="n">
         <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31213486</v>
+        <v>0.3128936</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3779409</v>
+        <v>0.3787624</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L26" t="n">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.224923</v>
+        <v>4.210835</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
@@ -2202,13 +2202,13 @@
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2681142</v>
+        <v>1.2685272</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25166667</v>
+        <v>0.25133395</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24064468</v>
+        <v>0.23986736</v>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G27" t="n">
         <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31372872</v>
+        <v>0.31290057</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>0.37977028</v>
+        <v>0.3787767</v>
       </c>
       <c r="K27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" t="n">
-        <v>1283</v>
+        <v>1298</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2581778</v>
+        <v>4.253253</v>
       </c>
       <c r="O27" t="n">
         <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q27" t="n">
         <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3549066</v>
+        <v>1.3564126</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2535497</v>
+        <v>0.25362185</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,43 +2288,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25722274</v>
+        <v>0.25827324</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G28" t="n">
         <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3259123</v>
+        <v>0.3269135</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39944082</v>
+        <v>0.40081346</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L28" t="n">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7047687</v>
+        <v>3.681533</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
@@ -2336,13 +2336,13 @@
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1332399</v>
+        <v>1.1344948</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22784336</v>
+        <v>0.22770433</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24126205</v>
+        <v>0.24198087</v>
       </c>
       <c r="C29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31687173</v>
+        <v>0.317261</v>
       </c>
       <c r="I29" t="n">
         <v>15</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39410543</v>
+        <v>0.39561057</v>
       </c>
       <c r="K29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.31923</v>
+        <v>4.30444</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
@@ -2403,16 +2403,16 @@
         <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3014023</v>
+        <v>1.3001889</v>
       </c>
       <c r="S29" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2473752</v>
+      </c>
+      <c r="U29" t="n">
         <v>18</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.24740548</v>
-      </c>
-      <c r="U29" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24809797</v>
+        <v>0.24760148</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E30" t="n">
         <v>30</v>
@@ -2440,43 +2440,43 @@
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3107563</v>
+        <v>0.31032753</v>
       </c>
       <c r="I30" t="n">
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3820746</v>
+        <v>0.38118082</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.922426</v>
+        <v>3.9103014</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q30" t="n">
         <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2961918</v>
+        <v>1.296426</v>
       </c>
       <c r="S30" t="n">
         <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2352388</v>
+        <v>0.23490936</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24678664</v>
+        <v>0.24598247</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -2504,46 +2504,46 @@
         <v>208</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32164508</v>
+        <v>0.32073012</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42343003</v>
+        <v>0.42165816</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1331</v>
+        <v>1345</v>
       </c>
       <c r="M31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6617336</v>
+        <v>4.670168</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q31" t="n">
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.389711</v>
+        <v>1.390056</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25322282</v>
+        <v>0.2532016</v>
       </c>
       <c r="U31" t="n">
         <v>25</v>
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.30805686</v>
+        <v>0.3148148</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -2818,46 +2818,46 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.375</v>
+        <v>0.38866398</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.549763</v>
+        <v>0.5462963</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8333333</v>
+        <v>5.09434</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1481482</v>
+        <v>1.3207548</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24878049</v>
+        <v>0.2748815</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.30476192</v>
+        <v>0.28431374</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3624454</v>
+        <v>0.34234235</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.45588234</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>6.0576925</v>
+        <v>6.1132073</v>
       </c>
       <c r="O3" t="n">
         <v>28</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.5471698</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.28846154</v>
+        <v>0.29186603</v>
       </c>
       <c r="U3" t="n">
         <v>28</v>
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244898</v>
+        <v>0.2160804</v>
       </c>
       <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E4" t="n">
         <v>19</v>
-      </c>
-      <c r="D4" t="n">
-        <v>19</v>
-      </c>
-      <c r="E4" t="n">
-        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>0.29032257</v>
+        <v>0.27727273</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3469388</v>
+        <v>0.3517588</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
         <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1666666</v>
+        <v>1.1296296</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>0.24752475</v>
+        <v>0.23880596</v>
       </c>
       <c r="U4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21076234</v>
+        <v>0.22164948</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -3019,46 +3019,46 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.292</v>
+        <v>0.29953918</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39013454</v>
+        <v>0.41752577</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N5" t="n">
-        <v>2.612903</v>
+        <v>2.8867924</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0967742</v>
+        <v>1.2075472</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21621622</v>
+        <v>0.23316061</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.22171946</v>
+        <v>0.21693122</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
@@ -3086,46 +3086,46 @@
         <v>27</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2892562</v>
+        <v>0.28846154</v>
       </c>
       <c r="I6" t="n">
         <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.32579187</v>
+        <v>0.3068783</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8972973</v>
+        <v>2.037736</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0054054</v>
+        <v>1.018868</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0.20704846</v>
+        <v>0.20207255</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3135,43 +3135,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22950819</v>
+        <v>0.22748815</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>0.30769232</v>
+        <v>0.30638298</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>0.352459</v>
+        <v>0.3364929</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>2.53125</v>
+        <v>2.7818182</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
@@ -3180,19 +3180,19 @@
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0625</v>
+        <v>1.1090909</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2034632</v>
+        <v>0.215</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.28712872</v>
+        <v>0.29383886</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.37130803</v>
+        <v>0.3805668</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.46039605</v>
+        <v>0.48815167</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2264152</v>
+        <v>4.4150944</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.245283</v>
+        <v>1.2830188</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>0.25</v>
+        <v>0.25980392</v>
       </c>
       <c r="U8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.20792079</v>
+        <v>0.21568628</v>
       </c>
       <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="n">
         <v>24</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.27149323</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.40686274</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L9" t="n">
+        <v>63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.88125</v>
+      </c>
+      <c r="O9" t="n">
+        <v>17</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3875</v>
+      </c>
+      <c r="S9" t="n">
         <v>21</v>
       </c>
-      <c r="E9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.25462964</v>
-      </c>
-      <c r="I9" t="n">
-        <v>29</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.37128714</v>
-      </c>
-      <c r="K9" t="n">
-        <v>17</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-      <c r="M9" t="n">
-        <v>22</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.55625</v>
-      </c>
-      <c r="O9" t="n">
-        <v>21</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>19</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44375</v>
-      </c>
-      <c r="S9" t="n">
-        <v>24</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.2753623</v>
+        <v>0.26341462</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25365853</v>
+        <v>0.25123152</v>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.33189654</v>
+        <v>0.33617023</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.39512196</v>
+        <v>0.43349755</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0566037</v>
+        <v>2.8867924</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3207548</v>
+        <v>1.245283</v>
       </c>
       <c r="S10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
-        <v>0.26108375</v>
+        <v>0.255</v>
       </c>
       <c r="U10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.22277227</v>
+        <v>0.22815534</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2706422</v>
+        <v>0.26818183</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" t="n">
-        <v>0.37623763</v>
+        <v>0.43203884</v>
       </c>
       <c r="K11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>5.264151</v>
+        <v>5.6037736</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
         <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3773584</v>
+        <v>1.4339622</v>
       </c>
       <c r="S11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T11" t="n">
-        <v>0.29186603</v>
+        <v>0.2890995</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.255</v>
+        <v>0.26237625</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3628692</v>
+        <v>0.3697479</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.41</v>
+        <v>0.44554454</v>
       </c>
       <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.5849056</v>
+      </c>
+      <c r="O12" t="n">
+        <v>21</v>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
-      <c r="L12" t="n">
-        <v>50</v>
-      </c>
-      <c r="M12" t="n">
-        <v>13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.673077</v>
-      </c>
-      <c r="O12" t="n">
-        <v>24</v>
-      </c>
-      <c r="P12" t="n">
-        <v>7</v>
-      </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1346154</v>
+        <v>1.1886792</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.20634921</v>
+        <v>0.2244898</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25821596</v>
+        <v>0.27853882</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31914893</v>
+        <v>0.34285715</v>
       </c>
       <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5707763</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>63</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.20625</v>
+      </c>
+      <c r="O13" t="n">
         <v>12</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.5023474</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>57</v>
-      </c>
-      <c r="M13" t="n">
-        <v>19</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.21875</v>
-      </c>
-      <c r="O13" t="n">
-        <v>18</v>
-      </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4250001</v>
+        <v>1.29375</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24378109</v>
+        <v>0.22110553</v>
       </c>
       <c r="U13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.31308413</v>
+        <v>0.30331755</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3577586</v>
+        <v>0.34649122</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0.47663552</v>
+        <v>0.48341233</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>7.9615383</v>
+        <v>7.981132</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7884616</v>
+        <v>1.8867924</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2843602</v>
+        <v>0.29953918</v>
       </c>
       <c r="U14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -3671,43 +3671,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.25821596</v>
+        <v>0.24757281</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.34042552</v>
+      </c>
+      <c r="I15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.35772356</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.40375587</v>
+        <v>0.3592233</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
-        <v>6.1666665</v>
+        <v>7.0588236</v>
       </c>
       <c r="O15" t="n">
         <v>29</v>
@@ -3716,16 +3716,16 @@
         <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5555556</v>
+        <v>1.745098</v>
       </c>
       <c r="S15" t="n">
         <v>29</v>
       </c>
       <c r="T15" t="n">
-        <v>0.29545453</v>
+        <v>0.30985916</v>
       </c>
       <c r="U15" t="n">
         <v>30</v>
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.28780487</v>
+        <v>0.26108375</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34666666</v>
+        <v>0.3167421</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>0.44390243</v>
+        <v>0.41379312</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>1.8333334</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8148148</v>
+        <v>0.7962963</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.16842106</v>
+        <v>0.17368421</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -3805,46 +3805,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24271844</v>
+        <v>0.2364532</v>
       </c>
       <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>21</v>
+      </c>
+      <c r="E17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3080357</v>
+      </c>
+      <c r="I17" t="n">
         <v>14</v>
       </c>
-      <c r="D17" t="n">
-        <v>24</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.3304721</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
       <c r="J17" t="n">
-        <v>0.37378642</v>
+        <v>0.3596059</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9277108</v>
+        <v>3.1090908</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P17" t="n">
         <v>6</v>
@@ -3853,16 +3853,16 @@
         <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1385542</v>
+        <v>1.0909091</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>0.20975609</v>
+        <v>0.20588236</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -3872,34 +3872,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.22916667</v>
+        <v>0.253886</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.30555555</v>
+        <v>0.33936653</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33854166</v>
+        <v>0.3834197</v>
       </c>
       <c r="K18" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
         <v>68</v>
@@ -3908,25 +3908,25 @@
         <v>27</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8679246</v>
+        <v>2.2075472</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9433962</v>
+        <v>0.8867925</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.16842106</v>
+        <v>0.16230367</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25233644</v>
+        <v>0.25</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
         <v>6</v>
       </c>
-      <c r="F19" t="n">
-        <v>7</v>
-      </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.29385966</v>
+        <v>0.29357797</v>
       </c>
       <c r="I19" t="n">
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40186915</v>
+        <v>0.40686274</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6341465</v>
+        <v>2.8867924</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.097561</v>
+        <v>1.0943396</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>0.20408164</v>
+        <v>0.21875</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2524272</v>
+        <v>0.24038461</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
         <v>8</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
+        <v>0.30603448</v>
+      </c>
+      <c r="I20" t="n">
+        <v>16</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.42307693</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46</v>
+      </c>
+      <c r="M20" t="n">
         <v>7</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.32618025</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.41747573</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>48</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10</v>
-      </c>
       <c r="N20" t="n">
-        <v>4.1538463</v>
+        <v>3.8076923</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
       </c>
       <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.0769231</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1923077</v>
+      </c>
+      <c r="U20" t="n">
         <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.21925133</v>
-      </c>
-      <c r="U20" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.22568093</v>
+        <v>0.2300885</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2931727</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.40707964</v>
+      </c>
+      <c r="K21" t="n">
         <v>12</v>
       </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.28873238</v>
-      </c>
-      <c r="I21" t="n">
-        <v>24</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.40466926</v>
-      </c>
-      <c r="K21" t="n">
-        <v>9</v>
-      </c>
       <c r="L21" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M21" t="n">
         <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>4.350711</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.436019</v>
+        <v>1.451613</v>
       </c>
       <c r="S21" t="n">
+        <v>26</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.26122448</v>
+      </c>
+      <c r="U21" t="n">
         <v>23</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.25724638</v>
-      </c>
-      <c r="U21" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.19587629</v>
+        <v>0.1865285</v>
       </c>
       <c r="C22" t="n">
+        <v>29</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
         <v>28</v>
-      </c>
-      <c r="D22" t="n">
-        <v>18</v>
-      </c>
-      <c r="E22" t="n">
-        <v>27</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H22" t="n">
-        <v>0.29464287</v>
+        <v>0.29147983</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>0.26804122</v>
+        <v>0.2642487</v>
       </c>
       <c r="K22" t="n">
         <v>29</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5849056</v>
+        <v>4.8333335</v>
       </c>
       <c r="O22" t="n">
         <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2830188</v>
+        <v>1.3333334</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24509804</v>
+        <v>0.26168224</v>
       </c>
       <c r="U22" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -4207,43 +4207,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.22222222</v>
+        <v>0.21989529</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3018868</v>
+        <v>0.29245284</v>
       </c>
       <c r="I23" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.38219896</v>
+      </c>
+      <c r="K23" t="n">
         <v>17</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.3968254</v>
-      </c>
-      <c r="K23" t="n">
-        <v>12</v>
-      </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M23" t="n">
         <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5660377</v>
+        <v>3.4177215</v>
       </c>
       <c r="O23" t="n">
         <v>13</v>
@@ -4255,13 +4255,13 @@
         <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.245283</v>
+        <v>1.2151898</v>
       </c>
       <c r="S23" t="n">
         <v>14</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23762377</v>
+        <v>0.22613065</v>
       </c>
       <c r="U23" t="n">
         <v>12</v>
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24509804</v>
+        <v>0.25615764</v>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
+        <v>13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3108108</v>
+      </c>
+      <c r="I24" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.38916257</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.09434</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>16</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4339622</v>
+      </c>
+      <c r="S24" t="n">
+        <v>24</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.24242425</v>
+      </c>
+      <c r="U24" t="n">
         <v>17</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.30222222</v>
-      </c>
-      <c r="I24" t="n">
-        <v>16</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.36764705</v>
-      </c>
-      <c r="K24" t="n">
-        <v>18</v>
-      </c>
-      <c r="L24" t="n">
-        <v>55</v>
-      </c>
-      <c r="M24" t="n">
-        <v>17</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>25</v>
-      </c>
-      <c r="P24" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>19</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.462963</v>
-      </c>
-      <c r="S24" t="n">
-        <v>26</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.24120604</v>
-      </c>
-      <c r="U24" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1827957</v>
+        <v>0.18817204</v>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H25" t="n">
-        <v>0.25123152</v>
+        <v>0.24257426</v>
       </c>
       <c r="I25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.24731183</v>
+        <v>0.25268817</v>
       </c>
       <c r="K25" t="n">
         <v>30</v>
       </c>
       <c r="L25" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6346154</v>
+        <v>3.0566037</v>
       </c>
       <c r="O25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2115384</v>
+        <v>1.0377358</v>
       </c>
       <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.23115578</v>
+      </c>
+      <c r="U25" t="n">
         <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.25870648</v>
-      </c>
-      <c r="U25" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.20103092</v>
+        <v>0.21938775</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H26" t="n">
-        <v>0.30493274</v>
+        <v>0.33043477</v>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>0.29896906</v>
+        <v>0.30612245</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6666665</v>
+        <v>4.2545457</v>
       </c>
       <c r="O26" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
         <v>7</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4444444</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25821596</v>
+        <v>0.24651162</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.20689656</v>
+        <v>0.1657754</v>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2648402</v>
+        <v>0.22772278</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>0.33990148</v>
+        <v>0.315508</v>
       </c>
       <c r="K27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M27" t="n">
         <v>29</v>
       </c>
       <c r="N27" t="n">
-        <v>3.0566037</v>
+        <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3018868</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
         <v>18</v>
       </c>
       <c r="T27" t="n">
-        <v>0.24378109</v>
+        <v>0.24193548</v>
       </c>
       <c r="U27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.20524018</v>
+        <v>0.23430963</v>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
       </c>
       <c r="G28" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.29885057</v>
+      </c>
+      <c r="I28" t="n">
+        <v>18</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.32635984</v>
+      </c>
+      <c r="K28" t="n">
+        <v>24</v>
+      </c>
+      <c r="L28" t="n">
+        <v>59</v>
+      </c>
+      <c r="M28" t="n">
         <v>23</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.2601626</v>
-      </c>
-      <c r="I28" t="n">
-        <v>28</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.279476</v>
-      </c>
-      <c r="K28" t="n">
-        <v>27</v>
-      </c>
-      <c r="L28" t="n">
-        <v>62</v>
-      </c>
-      <c r="M28" t="n">
-        <v>24</v>
-      </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
         <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
-        <v>1.0666667</v>
+        <v>1.1</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>0.20454545</v>
+        <v>0.1981982</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -4609,37 +4609,37 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.18232045</v>
+        <v>0.21465969</v>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D29" t="n">
         <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.28638497</v>
+      </c>
+      <c r="I29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.32984293</v>
+      </c>
+      <c r="K29" t="n">
         <v>23</v>
       </c>
-      <c r="H29" t="n">
-        <v>0.27751195</v>
-      </c>
-      <c r="I29" t="n">
-        <v>25</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.2762431</v>
-      </c>
-      <c r="K29" t="n">
-        <v>28</v>
-      </c>
       <c r="L29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M29" t="n">
         <v>20</v>
@@ -4648,25 +4648,25 @@
         <v>5.4339623</v>
       </c>
       <c r="O29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3584906</v>
+        <v>1.4150944</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24509804</v>
+        <v>0.25365853</v>
       </c>
       <c r="U29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -4676,22 +4676,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24873096</v>
+        <v>0.24489796</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H30" t="n">
         <v>0.3243243</v>
@@ -4700,40 +4700,40 @@
         <v>11</v>
       </c>
       <c r="J30" t="n">
-        <v>0.34517765</v>
+        <v>0.33673468</v>
       </c>
       <c r="K30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.32</v>
+        <v>3.7058823</v>
       </c>
       <c r="O30" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
         <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
-        <v>1.12</v>
+        <v>1.1568627</v>
       </c>
       <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.21578947</v>
+      </c>
+      <c r="U30" t="n">
         <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.21621622</v>
-      </c>
-      <c r="U30" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23529412</v>
+        <v>0.20634921</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.26086956</v>
+      </c>
+      <c r="I31" t="n">
+        <v>28</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.31746033</v>
+      </c>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" t="n">
+        <v>50</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.019231</v>
+      </c>
+      <c r="O31" t="n">
+        <v>23</v>
+      </c>
+      <c r="P31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q31" t="n">
         <v>27</v>
       </c>
-      <c r="E31" t="n">
-        <v>11</v>
-      </c>
-      <c r="F31" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" t="n">
-        <v>9</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.29017857</v>
-      </c>
-      <c r="I31" t="n">
-        <v>22</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.35784313</v>
-      </c>
-      <c r="K31" t="n">
-        <v>19</v>
-      </c>
-      <c r="L31" t="n">
-        <v>44</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>16</v>
-      </c>
-      <c r="P31" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>25</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.4814814</v>
+        <v>1.4807693</v>
       </c>
       <c r="S31" t="n">
         <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.26666668</v>
+        <v>0.255</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24607717</v>
+        <v>0.2460099</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
         <v>166</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31817433</v>
+        <v>0.31782436</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.40280598</v>
+        <v>0.40212804</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1422596</v>
+        <v>4.175451</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2789401</v>
+        <v>1.2836338</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24903652</v>
+        <v>0.24949846</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24560118</v>
+        <v>0.24508017</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -631,43 +631,43 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31756756</v>
+        <v>0.3170572</v>
       </c>
       <c r="I3" t="n">
         <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4032258</v>
+        <v>0.4017857</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="M3" t="n">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.48487</v>
+        <v>5.506993</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5059817</v>
+        <v>1.5104895</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27176258</v>
+        <v>0.27211004</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2469658</v>
+        <v>0.24639006</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31001166</v>
+        <v>0.30948833</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40989333</v>
+        <v>0.4088832</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6188812</v>
+        <v>3.6300418</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2433566</v>
+        <v>1.2433937</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23378807</v>
+        <v>0.2339279</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -750,13 +750,13 @@
         <v>0.23394752</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>718</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
         <v>199</v>
@@ -768,7 +768,7 @@
         <v>0.31440833</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>0.39624047</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24535662</v>
+        <v>0.24492058</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G6" t="n">
         <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31947663</v>
+        <v>0.31916997</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>0.39821693</v>
+        <v>0.397488</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5220125</v>
+        <v>3.5375</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2299092</v>
+        <v>1.2333333</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24034175</v>
+        <v>0.24105497</v>
       </c>
       <c r="U6" t="n">
         <v>14</v>
@@ -881,64 +881,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25063336</v>
+        <v>0.25125808</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33849558</v>
+        <v>0.3388793</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.42743394</v>
+        <v>0.42846873</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1307373</v>
+        <v>4.1174846</v>
       </c>
       <c r="O7" t="n">
         <v>14</v>
       </c>
       <c r="P7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2621697</v>
+        <v>1.259848</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2429941</v>
+        <v>0.24257426</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23605707</v>
+        <v>0.23609577</v>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32054213</v>
+        <v>0.32023385</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40503985</v>
+        <v>0.40570903</v>
       </c>
       <c r="K8" t="n">
         <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.136438</v>
+        <v>4.123091</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q8" t="n">
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3124564</v>
+        <v>1.3105044</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24286772</v>
+        <v>0.24267551</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22874229</v>
+        <v>0.22868289</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
@@ -1033,43 +1033,43 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30531934</v>
+        <v>0.30497512</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39469257</v>
+        <v>0.3940182</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="M9" t="n">
         <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.830449</v>
+        <v>4.8348837</v>
       </c>
       <c r="O9" t="n">
         <v>28</v>
       </c>
       <c r="P9" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4459774</v>
+        <v>1.4434884</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25474453</v>
+        <v>0.25440347</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23851162</v>
+        <v>0.23863216</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G10" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3161461</v>
+        <v>0.31591916</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.38009304</v>
+        <v>0.38040665</v>
       </c>
       <c r="K10" t="n">
         <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.770809</v>
+        <v>3.7686064</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q10" t="n">
         <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2618326</v>
+        <v>1.263158</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2372724</v>
+        <v>0.23753232</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25382653</v>
+        <v>0.25357985</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32215863</v>
+        <v>0.32200357</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41745627</v>
+        <v>0.41689324</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1400</v>
+        <v>1409</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.596086</v>
+        <v>5.589918</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q11" t="n">
         <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5265268</v>
+        <v>1.523564</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28867993</v>
+        <v>0.28841066</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24157614</v>
+        <v>0.24079838</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E12" t="n">
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G12" t="n">
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3205484</v>
+        <v>0.31969476</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>0.400847</v>
+        <v>0.400293</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>1398</v>
+        <v>1411</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N12" t="n">
-        <v>3.663158</v>
+        <v>3.665272</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2189474</v>
+        <v>1.2182705</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2316363</v>
+        <v>0.23155929</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24132842</v>
+        <v>0.24189115</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31428573</v>
+        <v>0.31530645</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41678968</v>
+        <v>0.41744548</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="M13" t="n">
         <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4810925</v>
+        <v>4.4530272</v>
       </c>
       <c r="O13" t="n">
         <v>24</v>
@@ -1331,16 +1331,16 @@
         <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3431373</v>
+        <v>1.3402923</v>
       </c>
       <c r="S13" t="n">
         <v>21</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23757009</v>
+        <v>0.23708658</v>
       </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24713281</v>
+        <v>0.24733357</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E14" t="n">
         <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G14" t="n">
         <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31605184</v>
+        <v>0.31620684</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.40140584</v>
+        <v>0.40198603</v>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7882714</v>
+        <v>4.770653</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q14" t="n">
         <v>25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4102684</v>
+        <v>1.4083781</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26102194</v>
+        <v>0.26099706</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,43 +1417,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23407023</v>
+        <v>0.2338382</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E15" t="n">
         <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G15" t="n">
         <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3100814</v>
+        <v>0.30988938</v>
       </c>
       <c r="I15" t="n">
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>0.369125</v>
+        <v>0.3686738</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>1538</v>
+        <v>1550</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2901335</v>
+        <v>4.2913074</v>
       </c>
       <c r="O15" t="n">
         <v>21</v>
@@ -1465,13 +1465,13 @@
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3505976</v>
+        <v>1.3542297</v>
       </c>
       <c r="S15" t="n">
         <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>0.239434</v>
+        <v>0.24005918</v>
       </c>
       <c r="U15" t="n">
         <v>13</v>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25692648</v>
+        <v>0.25665015</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G16" t="n">
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.338264</v>
+        <v>0.33812135</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42463982</v>
+        <v>0.42432582</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5667524</v>
+        <v>3.5481775</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
@@ -1532,13 +1532,13 @@
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1447276</v>
+        <v>1.1416299</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21835384</v>
+        <v>0.21793908</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24888475</v>
+        <v>0.24893735</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="E17" t="n">
         <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3264667</v>
+        <v>0.32633993</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39981413</v>
+        <v>0.4004805</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N17" t="n">
-        <v>4.096289</v>
+        <v>4.0893817</v>
       </c>
       <c r="O17" t="n">
         <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q17" t="n">
         <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2815876</v>
+        <v>1.2791132</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>0.23552485</v>
+        <v>0.2350102</v>
       </c>
       <c r="U17" t="n">
         <v>8</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2581825</v>
+        <v>0.25845146</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3406205</v>
+        <v>0.34052756</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.402633</v>
+        <v>0.4025809</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L18" t="n">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="M18" t="n">
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5119407</v>
+        <v>3.514977</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1789938</v>
+        <v>1.1778802</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22168042</v>
+        <v>0.22118613</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24406841</v>
+        <v>0.24451353</v>
       </c>
       <c r="C19" t="n">
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31599736</v>
+        <v>0.3166503</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40261173</v>
+        <v>0.40343818</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5609813</v>
+        <v>4.5574646</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361916</v>
+        <v>1.3575575</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.248949</v>
+        <v>0.24863686</v>
       </c>
       <c r="U19" t="n">
         <v>21</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2387346</v>
+        <v>0.23880869</v>
       </c>
       <c r="C20" t="n">
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30947265</v>
+        <v>0.30957463</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39507082</v>
+        <v>0.39539558</v>
       </c>
       <c r="K20" t="n">
         <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>4.136945</v>
+        <v>4.151445</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q20" t="n">
         <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.288305</v>
+        <v>1.2894799</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23921858</v>
+        <v>0.23942114</v>
       </c>
       <c r="U20" t="n">
         <v>12</v>
@@ -1828,7 +1828,7 @@
         <v>739</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>223</v>
@@ -1846,7 +1846,7 @@
         <v>0.40919325</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>1480</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23941308</v>
+        <v>0.24016984</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="E22" t="n">
         <v>19</v>
       </c>
       <c r="F22" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G22" t="n">
         <v>16</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31114063</v>
+        <v>0.31182975</v>
       </c>
       <c r="I22" t="n">
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39301634</v>
+        <v>0.39486802</v>
       </c>
       <c r="K22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L22" t="n">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>4.048741</v>
+        <v>4.0421786</v>
       </c>
       <c r="O22" t="n">
         <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q22" t="n">
         <v>21</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2887126</v>
+        <v>1.2862109</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24794595</v>
+        <v>0.24782293</v>
       </c>
       <c r="U22" t="n">
         <v>19</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25321734</v>
+        <v>0.25301856</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3301613</v>
+        <v>0.3299118</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40438643</v>
+        <v>0.40403676</v>
       </c>
       <c r="K23" t="n">
         <v>9</v>
       </c>
       <c r="L23" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.167827</v>
+        <v>4.1543255</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.301532</v>
+        <v>1.2961937</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23741935</v>
+        <v>0.23666361</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24377923</v>
+        <v>0.24428332</v>
       </c>
       <c r="C24" t="n">
         <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31861356</v>
+        <v>0.31943065</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3981291</v>
+        <v>0.3984012</v>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L24" t="n">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9850538</v>
+        <v>3.9851475</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2065,16 +2065,16 @@
         <v>180</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2954227</v>
+        <v>1.2935716</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2416558</v>
+        <v>0.24161571</v>
       </c>
       <c r="U24" t="n">
         <v>15</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24558823</v>
+        <v>0.24502102</v>
       </c>
       <c r="C25" t="n">
         <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E25" t="n">
         <v>26</v>
@@ -2105,43 +2105,43 @@
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3069853</v>
+        <v>0.3063632</v>
       </c>
       <c r="I25" t="n">
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4014706</v>
+        <v>0.39996347</v>
       </c>
       <c r="K25" t="n">
+        <v>18</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1342</v>
+      </c>
+      <c r="M25" t="n">
         <v>14</v>
       </c>
-      <c r="L25" t="n">
-        <v>1326</v>
-      </c>
-      <c r="M25" t="n">
-        <v>13</v>
-      </c>
       <c r="N25" t="n">
-        <v>4.3415494</v>
+        <v>4.33007</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q25" t="n">
         <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3570423</v>
+        <v>1.3573426</v>
       </c>
       <c r="S25" t="n">
         <v>24</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24828227</v>
+        <v>0.24806345</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23200598</v>
+        <v>0.23268338</v>
       </c>
       <c r="C26" t="n">
         <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
@@ -2169,46 +2169,46 @@
         <v>182</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3128936</v>
+        <v>0.31358024</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3787624</v>
+        <v>0.37901577</v>
       </c>
       <c r="K26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.210835</v>
+        <v>4.203216</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q26" t="n">
         <v>22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2685272</v>
+        <v>1.2675366</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25133395</v>
+        <v>0.25100622</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.23986736</v>
+        <v>0.23928179</v>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31290057</v>
+        <v>0.3125817</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3787767</v>
+        <v>0.3783437</v>
       </c>
       <c r="K27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L27" t="n">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="M27" t="n">
         <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>4.253253</v>
+        <v>4.267098</v>
       </c>
       <c r="O27" t="n">
         <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q27" t="n">
         <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3564126</v>
+        <v>1.3565158</v>
       </c>
       <c r="S27" t="n">
         <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25362185</v>
+        <v>0.25391906</v>
       </c>
       <c r="U27" t="n">
         <v>26</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25827324</v>
+        <v>0.2580823</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G28" t="n">
         <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3269135</v>
+        <v>0.32634532</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40081346</v>
+        <v>0.401543</v>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.681533</v>
+        <v>3.7047818</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1344948</v>
+        <v>1.1392932</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.22770433</v>
+        <v>0.22853442</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24198087</v>
+        <v>0.24170086</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.31662226</v>
+      </c>
+      <c r="I29" t="n">
         <v>16</v>
       </c>
-      <c r="H29" t="n">
-        <v>0.317261</v>
-      </c>
-      <c r="I29" t="n">
-        <v>15</v>
-      </c>
       <c r="J29" t="n">
-        <v>0.39561057</v>
+        <v>0.39612085</v>
       </c>
       <c r="K29" t="n">
         <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.30444</v>
+        <v>4.3182244</v>
       </c>
       <c r="O29" t="n">
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q29" t="n">
         <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3001889</v>
+        <v>1.3034288</v>
       </c>
       <c r="S29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2473752</v>
+        <v>0.2478022</v>
       </c>
       <c r="U29" t="n">
         <v>18</v>
@@ -2422,43 +2422,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24760148</v>
+        <v>0.24729209</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E30" t="n">
         <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G30" t="n">
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31032753</v>
+        <v>0.3101729</v>
       </c>
       <c r="I30" t="n">
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38118082</v>
+        <v>0.3814944</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>1140</v>
+        <v>1149</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9103014</v>
+        <v>3.8920612</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
@@ -2467,16 +2467,16 @@
         <v>167</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.296426</v>
+        <v>1.2938719</v>
       </c>
       <c r="S30" t="n">
         <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23490936</v>
+        <v>0.2348133</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24598247</v>
+        <v>0.24614267</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32073012</v>
+        <v>0.32080364</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42165816</v>
+        <v>0.42276275</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.670168</v>
+        <v>4.665971</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q31" t="n">
         <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.390056</v>
+        <v>1.3903967</v>
       </c>
       <c r="S31" t="n">
         <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2532016</v>
+        <v>0.25318065</v>
       </c>
       <c r="U31" t="n">
         <v>25</v>
@@ -2800,61 +2800,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3148148</v>
+        <v>0.29953918</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.38866398</v>
+        <v>0.36734694</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5462963</v>
+        <v>0.51152074</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>5.09434</v>
+        <v>6.0576925</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.4807693</v>
+      </c>
+      <c r="S2" t="n">
         <v>25</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.3207548</v>
-      </c>
-      <c r="S2" t="n">
-        <v>19</v>
-      </c>
       <c r="T2" t="n">
-        <v>0.2748815</v>
+        <v>0.2890995</v>
       </c>
       <c r="U2" t="n">
         <v>26</v>
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.28431374</v>
+        <v>0.27804878</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.34234235</v>
+        <v>0.3422222</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.45588234</v>
+        <v>0.44390243</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>6.1132073</v>
+        <v>7.3333335</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5471698</v>
+        <v>1.7407408</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.29186603</v>
+        <v>0.30555555</v>
       </c>
       <c r="U3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2934,46 +2934,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2160804</v>
+        <v>0.21105528</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>0.27727273</v>
+        <v>0.26940638</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3517588</v>
+        <v>0.34170854</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>4.075472</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P4" t="n">
         <v>12</v>
@@ -2982,16 +2982,16 @@
         <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1296296</v>
+        <v>1.1509434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23880596</v>
+        <v>0.24365482</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.22164948</v>
+        <v>0.2392638</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -3019,43 +3019,43 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29953918</v>
+        <v>0.31318682</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.41752577</v>
+        <v>0.47239265</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8867924</v>
+        <v>2.8636363</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2075472</v>
+        <v>1.1818181</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23316061</v>
+        <v>0.23780487</v>
       </c>
       <c r="U5" t="n">
         <v>14</v>
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.21693122</v>
+        <v>0.21390374</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
@@ -3083,49 +3083,49 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.28846154</v>
+        <v>0.29326922</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3068783</v>
+        <v>0.29946524</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>2.037736</v>
+        <v>2.1666667</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.018868</v>
+        <v>1.1851852</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>0.20207255</v>
+        <v>0.2364532</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22748815</v>
+        <v>0.22966507</v>
       </c>
       <c r="C7" t="n">
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
         <v>25</v>
       </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>24</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.30638298</v>
+        <v>0.30769232</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3364929</v>
+        <v>0.33014354</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7818182</v>
+        <v>2.9454546</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1090909</v>
+        <v>1.1636363</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.215</v>
+        <v>0.22110553</v>
       </c>
       <c r="U7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.29383886</v>
+        <v>0.2843602</v>
       </c>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>47</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3805668</v>
+        <v>0.3529412</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.48815167</v>
+        <v>0.49763033</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.5849056</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>21</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.245283</v>
+      </c>
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.4150944</v>
-      </c>
-      <c r="O8" t="n">
-        <v>19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>16</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2830188</v>
-      </c>
-      <c r="S8" t="n">
-        <v>16</v>
-      </c>
       <c r="T8" t="n">
-        <v>0.25980392</v>
+        <v>0.26237625</v>
       </c>
       <c r="U8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.21568628</v>
+        <v>0.2292683</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2837838</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.41463414</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>62</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.267516</v>
+      </c>
+      <c r="O9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.27149323</v>
-      </c>
-      <c r="I9" t="n">
-        <v>26</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.40686274</v>
-      </c>
-      <c r="K9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L9" t="n">
-        <v>63</v>
-      </c>
-      <c r="M9" t="n">
-        <v>25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.88125</v>
-      </c>
-      <c r="O9" t="n">
-        <v>17</v>
-      </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3875</v>
+        <v>1.2420382</v>
       </c>
       <c r="S9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26341462</v>
+        <v>0.23958333</v>
       </c>
       <c r="U9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25123152</v>
+        <v>0.25480768</v>
       </c>
       <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E10" t="n">
-        <v>11</v>
-      </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.33617023</v>
+        <v>0.3375</v>
       </c>
       <c r="I10" t="n">
         <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.43349755</v>
+        <v>0.45673078</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8867924</v>
+        <v>3.4615386</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>1.245283</v>
+        <v>1.3653846</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>0.255</v>
+        <v>0.26865673</v>
       </c>
       <c r="U10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -3403,16 +3403,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.22815534</v>
+        <v>0.2364532</v>
       </c>
       <c r="C11" t="n">
         <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -3421,46 +3421,46 @@
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0.26818183</v>
+        <v>0.28181818</v>
       </c>
       <c r="I11" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.43349755</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.0576925</v>
+      </c>
+      <c r="O11" t="n">
+        <v>26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="n">
         <v>27</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.43203884</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>53</v>
-      </c>
-      <c r="M11" t="n">
-        <v>15</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.6037736</v>
-      </c>
-      <c r="O11" t="n">
-        <v>27</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>1.4807693</v>
+      </c>
+      <c r="S11" t="n">
         <v>25</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.4339622</v>
-      </c>
-      <c r="S11" t="n">
-        <v>24</v>
-      </c>
       <c r="T11" t="n">
-        <v>0.2890995</v>
+        <v>0.30232558</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,46 +3470,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.26237625</v>
+        <v>0.24875621</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3697479</v>
+        <v>0.34913793</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.44554454</v>
+        <v>0.45273632</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5849056</v>
+        <v>3.8333333</v>
       </c>
       <c r="O12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P12" t="n">
         <v>8</v>
@@ -3518,16 +3518,16 @@
         <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1886792</v>
+        <v>1.0185186</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2244898</v>
+        <v>0.21025641</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.27853882</v>
+        <v>0.29411766</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.34285715</v>
+        <v>0.37254903</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5707763</v>
+        <v>0.5882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>3.20625</v>
+        <v>2.53125</v>
       </c>
       <c r="O13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29375</v>
+        <v>1.25625</v>
       </c>
       <c r="S13" t="n">
         <v>17</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22110553</v>
+        <v>0.21717171</v>
       </c>
       <c r="U13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.30331755</v>
+        <v>0.30769232</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>34</v>
@@ -3616,31 +3616,31 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>0.34649122</v>
+        <v>0.35682818</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0.48341233</v>
+        <v>0.5048077</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
         <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>7.981132</v>
+        <v>7.5</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
@@ -3652,16 +3652,16 @@
         <v>29</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8867924</v>
+        <v>1.7962962</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>0.29953918</v>
+        <v>0.30136988</v>
       </c>
       <c r="U14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -3671,61 +3671,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.24757281</v>
+        <v>0.2631579</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>0.34042552</v>
+        <v>0.35146442</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3592233</v>
+        <v>0.3875598</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
-        <v>7.0588236</v>
+        <v>6.66</v>
       </c>
       <c r="O15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.745098</v>
+        <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T15" t="n">
-        <v>0.30985916</v>
+        <v>0.30952382</v>
       </c>
       <c r="U15" t="n">
         <v>30</v>
@@ -3738,16 +3738,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26108375</v>
+        <v>0.24271844</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
@@ -3756,25 +3756,25 @@
         <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3167421</v>
+        <v>0.31601733</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>0.41379312</v>
+        <v>0.39320388</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8333334</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -3786,16 +3786,16 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7962963</v>
+        <v>0.8181818</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.17368421</v>
+        <v>0.1865285</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2364532</v>
+        <v>0.25365853</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
         <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K17" t="n">
         <v>13</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.3080357</v>
-      </c>
-      <c r="I17" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.3596059</v>
-      </c>
-      <c r="K17" t="n">
-        <v>18</v>
-      </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.4107144</v>
+      </c>
+      <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.1090908</v>
-      </c>
-      <c r="O17" t="n">
-        <v>11</v>
-      </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0909091</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0.20588236</v>
+        <v>0.18137255</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.253886</v>
+        <v>0.26903552</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -3890,43 +3890,43 @@
         <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33936653</v>
+        <v>0.33636364</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3834197</v>
+        <v>0.39086294</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2075472</v>
+        <v>2.8867924</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8867925</v>
+        <v>0.9245283</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.16230367</v>
+        <v>0.1631579</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25</v>
+        <v>0.24489796</v>
       </c>
       <c r="C19" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
         <v>11</v>
       </c>
-      <c r="D19" t="n">
-        <v>29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
+        <v>0.2990654</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4234694</v>
+      </c>
+      <c r="K19" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" t="n">
+        <v>43</v>
+      </c>
+      <c r="M19" t="n">
         <v>6</v>
       </c>
-      <c r="G19" t="n">
-        <v>13</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.29357797</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.40686274</v>
-      </c>
-      <c r="K19" t="n">
-        <v>13</v>
-      </c>
-      <c r="L19" t="n">
-        <v>46</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7</v>
-      </c>
       <c r="N19" t="n">
-        <v>2.8867924</v>
+        <v>3.5660377</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0943396</v>
+        <v>1.1132076</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>0.21875</v>
+        <v>0.23589744</v>
       </c>
       <c r="U19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.24038461</v>
+        <v>0.23671497</v>
       </c>
       <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3148936</v>
+      </c>
+      <c r="I20" t="n">
         <v>14</v>
       </c>
-      <c r="D20" t="n">
-        <v>29</v>
-      </c>
-      <c r="E20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.30603448</v>
-      </c>
-      <c r="I20" t="n">
-        <v>16</v>
-      </c>
       <c r="J20" t="n">
-        <v>0.42307693</v>
+        <v>0.4347826</v>
       </c>
       <c r="K20" t="n">
         <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8076923</v>
+        <v>3.7058823</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0769231</v>
+        <v>1.0196079</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1923077</v>
+        <v>0.2021858</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2300885</v>
+        <v>0.22916667</v>
       </c>
       <c r="C21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.29577464</v>
+      </c>
+      <c r="I21" t="n">
+        <v>21</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16</v>
+      </c>
+      <c r="L21" t="n">
+        <v>65</v>
+      </c>
+      <c r="M21" t="n">
+        <v>28</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.8333333</v>
+      </c>
+      <c r="O21" t="n">
         <v>17</v>
       </c>
-      <c r="D21" t="n">
-        <v>30</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="P21" t="n">
         <v>6</v>
       </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.2931727</v>
-      </c>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.40707964</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12</v>
-      </c>
-      <c r="L21" t="n">
-        <v>73</v>
-      </c>
-      <c r="M21" t="n">
-        <v>30</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>20</v>
-      </c>
-      <c r="P21" t="n">
-        <v>7</v>
-      </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>1.451613</v>
+        <v>1.3888888</v>
       </c>
       <c r="S21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="T21" t="n">
-        <v>0.26122448</v>
+        <v>0.25</v>
       </c>
       <c r="U21" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1865285</v>
+        <v>0.2113402</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
         <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.29680365</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3298969</v>
+      </c>
+      <c r="K22" t="n">
+        <v>27</v>
+      </c>
+      <c r="L22" t="n">
+        <v>36</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>28</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.29147983</v>
-      </c>
-      <c r="I22" t="n">
-        <v>22</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.2642487</v>
-      </c>
-      <c r="K22" t="n">
-        <v>29</v>
-      </c>
-      <c r="L22" t="n">
-        <v>39</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
       <c r="N22" t="n">
-        <v>4.8333335</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3333334</v>
+        <v>1.2962962</v>
       </c>
       <c r="S22" t="n">
+        <v>18</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.254717</v>
+      </c>
+      <c r="U22" t="n">
         <v>20</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.26168224</v>
-      </c>
-      <c r="U22" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.21989529</v>
+        <v>0.21578947</v>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
         <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H23" t="n">
-        <v>0.29245284</v>
+        <v>0.28229666</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>0.38219896</v>
+        <v>0.35789475</v>
       </c>
       <c r="K23" t="n">
+        <v>19</v>
+      </c>
+      <c r="L23" t="n">
+        <v>53</v>
+      </c>
+      <c r="M23" t="n">
         <v>17</v>
       </c>
-      <c r="L23" t="n">
-        <v>52</v>
-      </c>
-      <c r="M23" t="n">
-        <v>14</v>
-      </c>
       <c r="N23" t="n">
-        <v>3.4177215</v>
+        <v>3.2468355</v>
       </c>
       <c r="O23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
         <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2151898</v>
+        <v>1.1012658</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>0.22613065</v>
+        <v>0.20103092</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.25615764</v>
+        <v>0.25980392</v>
       </c>
       <c r="C24" t="n">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3108108</v>
+        <v>0.32894737</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38916257</v>
+        <v>0.35784313</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N24" t="n">
-        <v>5.09434</v>
+        <v>5.264151</v>
       </c>
       <c r="O24" t="n">
         <v>24</v>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4339622</v>
+        <v>1.4716982</v>
       </c>
       <c r="S24" t="n">
         <v>24</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24242425</v>
+        <v>0.25615764</v>
       </c>
       <c r="U24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.18817204</v>
+        <v>0.2010582</v>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
         <v>13</v>
@@ -4356,31 +4356,31 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H25" t="n">
-        <v>0.24257426</v>
+        <v>0.25</v>
       </c>
       <c r="I25" t="n">
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.25268817</v>
+        <v>0.26455027</v>
       </c>
       <c r="K25" t="n">
         <v>30</v>
       </c>
       <c r="L25" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N25" t="n">
-        <v>3.0566037</v>
+        <v>2.9454546</v>
       </c>
       <c r="O25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P25" t="n">
         <v>9</v>
@@ -4389,16 +4389,16 @@
         <v>24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0377358</v>
+        <v>1.0545454</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T25" t="n">
-        <v>0.23115578</v>
+        <v>0.21287128</v>
       </c>
       <c r="U25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.21938775</v>
+        <v>0.25123152</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>0.33043477</v>
+        <v>0.35714287</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.30612245</v>
+        <v>0.3448276</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2545457</v>
+        <v>4.581818</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
         <v>7</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.4545455</v>
       </c>
       <c r="S26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24651162</v>
+        <v>0.25233644</v>
       </c>
       <c r="U26" t="n">
         <v>18</v>
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1657754</v>
+        <v>0.15591398</v>
       </c>
       <c r="C27" t="n">
         <v>30</v>
       </c>
       <c r="D27" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="n">
         <v>17</v>
       </c>
-      <c r="E27" t="n">
-        <v>27</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8</v>
-      </c>
-      <c r="G27" t="n">
-        <v>9</v>
-      </c>
       <c r="H27" t="n">
-        <v>0.22772278</v>
+        <v>0.23039216</v>
       </c>
       <c r="I27" t="n">
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>0.315508</v>
+        <v>0.2795699</v>
       </c>
       <c r="K27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L27" t="n">
         <v>72</v>
       </c>
       <c r="M27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>3.489796</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.3877552</v>
       </c>
       <c r="S27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.24193548</v>
+        <v>0.25531915</v>
       </c>
       <c r="U27" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.23430963</v>
+        <v>0.24390244</v>
       </c>
       <c r="C28" t="n">
+        <v>14</v>
+      </c>
+      <c r="D28" t="n">
+        <v>29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>21</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2981132</v>
+      </c>
+      <c r="I28" t="n">
+        <v>19</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.35772356</v>
+      </c>
+      <c r="K28" t="n">
+        <v>21</v>
+      </c>
+      <c r="L28" t="n">
+        <v>60</v>
+      </c>
+      <c r="M28" t="n">
+        <v>24</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.8135593</v>
+      </c>
+      <c r="O28" t="n">
         <v>16</v>
       </c>
-      <c r="D28" t="n">
-        <v>31</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" t="n">
         <v>24</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.29885057</v>
-      </c>
-      <c r="I28" t="n">
-        <v>18</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.32635984</v>
-      </c>
-      <c r="K28" t="n">
-        <v>24</v>
-      </c>
-      <c r="L28" t="n">
-        <v>59</v>
-      </c>
-      <c r="M28" t="n">
-        <v>23</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O28" t="n">
-        <v>5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>21</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.1</v>
+        <v>1.2542373</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1981982</v>
+        <v>0.22421524</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -4609,61 +4609,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.21465969</v>
+        <v>0.20744681</v>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>0.28638497</v>
+        <v>0.2669903</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>0.32984293</v>
+        <v>0.35638297</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M29" t="n">
         <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4339623</v>
+        <v>5.3653846</v>
       </c>
       <c r="O29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4150944</v>
+        <v>1.4038461</v>
       </c>
       <c r="S29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T29" t="n">
-        <v>0.25365853</v>
+        <v>0.25373134</v>
       </c>
       <c r="U29" t="n">
         <v>19</v>
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24489796</v>
+        <v>0.22340426</v>
       </c>
       <c r="C30" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" t="n">
+        <v>19</v>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>25</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2985782</v>
+      </c>
+      <c r="I30" t="n">
+        <v>18</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.33510637</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>38</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.5294118</v>
+      </c>
+      <c r="O30" t="n">
         <v>13</v>
       </c>
-      <c r="D30" t="n">
-        <v>21</v>
-      </c>
-      <c r="E30" t="n">
-        <v>19</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>28</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.3243243</v>
-      </c>
-      <c r="I30" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.33673468</v>
-      </c>
-      <c r="K30" t="n">
-        <v>21</v>
-      </c>
-      <c r="L30" t="n">
-        <v>34</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.7058823</v>
-      </c>
-      <c r="O30" t="n">
-        <v>15</v>
-      </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1568627</v>
+        <v>1.0784314</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>0.21578947</v>
+        <v>0.21276596</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.20634921</v>
+        <v>0.21465969</v>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>0.26086956</v>
+        <v>0.27272728</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>0.31746033</v>
+        <v>0.36125654</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L31" t="n">
         <v>50</v>
       </c>
       <c r="M31" t="n">
+        <v>12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.754717</v>
+      </c>
+      <c r="O31" t="n">
+        <v>22</v>
+      </c>
+      <c r="P31" t="n">
         <v>11</v>
       </c>
-      <c r="N31" t="n">
-        <v>5.019231</v>
-      </c>
-      <c r="O31" t="n">
-        <v>23</v>
-      </c>
-      <c r="P31" t="n">
-        <v>12</v>
-      </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4807693</v>
+        <v>1.5471698</v>
       </c>
       <c r="S31" t="n">
         <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.255</v>
+        <v>0.26341462</v>
       </c>
       <c r="U31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -2815,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>0.36734694</v>
@@ -2